--- a/cache/manual_references.xlsx
+++ b/cache/manual_references.xlsx
@@ -1,56 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamid\Documents\GitHub\FReD-data\cache\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149158CF-DD23-452F-B0AA-111AAF4847DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="7428" yWindow="-13068" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="396">
-  <si>
-    <t xml:space="preserve">key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference_apa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference_bibtex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177/2f10986111211035002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lum, C., Koper, C. S., &amp; Wu, X. (2021). Can we really defund the police? A nine-agency study of police response to calls for service. Police Quarterly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{Lum_2021,
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="411">
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>reference_apa</t>
+  </si>
+  <si>
+    <t>reference_bibtex</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>journal</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>issue</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>10.1177/2f10986111211035002</t>
+  </si>
+  <si>
+    <t>Lum, C., Koper, C. S., &amp; Wu, X. (2021). Can we really defund the police? A nine-agency study of police response to calls for service. Police Quarterly.</t>
+  </si>
+  <si>
+    <t>@article{Lum_2021,
   title={Can We Really Defund the Police? A Nine-Agency Study of Police Response to Calls for Service},
   author={Lum, Cynthia and Koper, Christopher S. and Wu, Xiaoyun},
   journal={Police Quarterly},
@@ -65,13 +73,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katla, J. (2024). Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA). https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{katla2024replication,
+    <t>https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>Katla, J. (2024). Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA). https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>@mastersthesis{katla2024replication,
   title={Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Katla, J.},
   year={2024},
@@ -80,13 +88,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://drive.google.com/file/d/1DDCuEgQah24QordxkRGO0EIt6Q681jyL/view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee, F. (2013). Replication of “With a clean conscience: Cleanliness reduces the severity of moral judgments” by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@unpublished{lee2013replication,
+    <t>https://drive.google.com/file/d/1DDCuEgQah24QordxkRGO0EIt6Q681jyL/view</t>
+  </si>
+  <si>
+    <t>Lee, F. (2013). Replication of “With a clean conscience: Cleanliness reduces the severity of moral judgments” by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
+  </si>
+  <si>
+    <t>@unpublished{lee2013replication,
   title={Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science)},
   author={Lee, F.},
   year={2013},
@@ -95,13 +103,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.jasnh.com/a14.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{murtagh_todd_2004,
+    <t>https://www.jasnh.com/a14.htm</t>
+  </si>
+  <si>
+    <t>Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51.</t>
+  </si>
+  <si>
+    <t>@article{murtagh_todd_2004,
   title={Self-regulation: A challenge to the strength model},
   author={Murtagh, Andrew M. and Todd, Sandra A.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -113,13 +121,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://drive.google.com/file/d/1i2aa1erQ9i9knP8Z5bgGiSt6DXX7U7Fa/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking . (2011, September 15). Retrieved from https://web.archive.org/web/20191117063540/http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pashler_harris_coburn_2011,
+    <t>https://drive.google.com/file/d/1i2aa1erQ9i9knP8Z5bgGiSt6DXX7U7Fa/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking . (2011, September 15). Retrieved from https://web.archive.org/web/20191117063540/http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>@misc{pashler_harris_coburn_2011,
   title={Elderly-Related Words Prime Slow Walking},
   author={Pashler, H. and Harris, C. and Coburn, N.},
   year={2011},
@@ -130,13 +138,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.jasnh.com/pdf/Vol6-No2.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6(2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{fayard_bassi_bernstein_roberts_2009,
+    <t>https://www.jasnh.com/pdf/Vol6-No2.pdf</t>
+  </si>
+  <si>
+    <t>Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6(2).</t>
+  </si>
+  <si>
+    <t>@article{fayard_bassi_bernstein_roberts_2009,
   title={Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006)},
   author={Fayard, Jennifer V. and Bassi, Alana K. and Bernstein, Daniel M. and Roberts, Brent W.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -147,13 +155,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Besman, M., Dubensky, C., Dunsmore, L., &amp; Daubman, K. (2013). Cleanliness primes less severe moral judgments. Retrieved from: https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{besman_dubensky_dunsmore_daubman_2013,
+    <t>https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
+  </si>
+  <si>
+    <t>Besman, M., Dubensky, C., Dunsmore, L., &amp; Daubman, K. (2013). Cleanliness primes less severe moral judgments. Retrieved from: https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
+  </si>
+  <si>
+    <t>@misc{besman_dubensky_dunsmore_daubman_2013,
   title={Cleanliness primes less severe moral judgments},
   author={Besman, M. and Dubensky, C. and Dunsmore, L. and Daubman, K.},
   year={2013},
@@ -162,13 +170,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2021, May 4). [97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2021_datacolada_97,
+    <t>https://datacolada.org/97</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2021, May 4). [97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2021_datacolada_97,
   title={[97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure?},
   author={Simmons, J. and Nelson, L. D.},
   year={2021},
@@ -179,13 +187,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_83,
+    <t>https://datacolada.org/83</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_83,
   title={[83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -194,13 +202,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_84,
+    <t>https://datacolada.org/84</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_84,
   title={[84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -209,13 +217,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_90,
+    <t>https://datacolada.org/90</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_90,
   title={[90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -224,13 +232,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/aczvt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown, B. T., Kleinberg, B., Hicks, G., Bentley, H., Attridge, P. R., Eboigbe, S., … Brown, K. (2023, September 28). Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1). Retrieved from osf.io/aczvt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{brown_kleinberg_hicks_bentley_attridge_eboigbe_devitt_vazquez_beyan_brown_2023,
+    <t>https://osf.io/aczvt</t>
+  </si>
+  <si>
+    <t>Brown, B. T., Kleinberg, B., Hicks, G., Bentley, H., Attridge, P. R., Eboigbe, S., … Brown, K. (2023, September 28). Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1). Retrieved from osf.io/aczvt</t>
+  </si>
+  <si>
+    <t>@misc{brown_kleinberg_hicks_bentley_attridge_eboigbe_devitt_vazquez_beyan_brown_2023,
  title={Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1)},
  url={osf.io/aczvt},
  publisher={OSF},
@@ -240,13 +248,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8nzfm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papenmeier, F., &amp; Rebholz, T. R. (2023, September). Bimodal Flanker: Audio vs. Visual. Retrieved from https://osf.io/8nzfm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{papenmeier_rebholz_2023,
+    <t>https://osf.io/8nzfm/</t>
+  </si>
+  <si>
+    <t>Papenmeier, F., &amp; Rebholz, T. R. (2023, September). Bimodal Flanker: Audio vs. Visual. Retrieved from https://osf.io/8nzfm/</t>
+  </si>
+  <si>
+    <t>@misc{papenmeier_rebholz_2023,
  title={Bimodal Flanker: Audio vs. Visual},
  url={osf.io/8nzfm},
  publisher={OSF},
@@ -256,13 +264,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_92,
+    <t>https://datacolada.org/92</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_92,
   title={[92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -271,13 +279,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [94] Data Replicada #9: Are Progression Ads More Credible? Data Colada. https://datacolada.org/94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_94,
+    <t>https://datacolada.org/94</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [94] Data Replicada #9: Are Progression Ads More Credible? Data Colada. https://datacolada.org/94</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_94,
   title={[94] Data Replicada #9: Are Progression Ads More Credible?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -286,22 +294,22 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chan, C. H. &amp; Feldman, G. Weinstein (1984): Replication and extension. [Unpublished manuscript]. Retrieved from https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{Chan2020Weinstein, author = {Chan, Chun Him and Feldman, Gilad}, title = {Weinstein (1984): Replication and extension}, year = {2020}, howpublished = {Unpublished manuscript}, url = {https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://datacolada.org/82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2019). [82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2019_datacolada_82,
+    <t>https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
+  </si>
+  <si>
+    <t>Chan, C. H. &amp; Feldman, G. Weinstein (1984): Replication and extension. [Unpublished manuscript]. Retrieved from https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
+  </si>
+  <si>
+    <t>@misc{Chan2020Weinstein, author = {Chan, Chun Him and Feldman, Gilad}, title = {Weinstein (1984): Replication and extension}, year = {2020}, howpublished = {Unpublished manuscript}, url = {https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk} }</t>
+  </si>
+  <si>
+    <t>https://datacolada.org/82</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2019). [82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2019_datacolada_82,
   title={[82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking?},
   author={Simmons, J. and Nelson, L. D.},
   year={2019},
@@ -310,13 +318,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://replications.clearerthinking.org/replication-2022psci33-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transparent Replications by Clearer Thinking. (2024). Report #11: Replication of a study from “Changes in the prevalence of thin bodies bias young women’s judgments about body size” (Psychological Science | Devine et al., 2022) https://replications.clearerthinking.org/replication-2022psci33-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{clearer_thinking_2024_report11,
+    <t>https://replications.clearerthinking.org/replication-2022psci33-8</t>
+  </si>
+  <si>
+    <t>Transparent Replications by Clearer Thinking. (2024). Report #11: Replication of a study from “Changes in the prevalence of thin bodies bias young women’s judgments about body size” (Psychological Science | Devine et al., 2022) https://replications.clearerthinking.org/replication-2022psci33-8</t>
+  </si>
+  <si>
+    <t>@misc{clearer_thinking_2024_report11,
   title={Report #11: Replication of a study from "Changes in the prevalence of thin bodies bias young women's judgments about body size" (Psychological Science | Devine et al., 2022)},
   author={{Transparent Replications by Clearer Thinking}},
   year={2024},
@@ -325,13 +333,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/74892/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavlović, Z. (2023, April 8). First impression replication study (Asch, 1945, Experiment 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pavlović_kaiser_2024,
+    <t>https://osf.io/74892/</t>
+  </si>
+  <si>
+    <t>Pavlović, Z. (2023, April 8). First impression replication study (Asch, 1945, Experiment 1).</t>
+  </si>
+  <si>
+    <t>@misc{pavlović_kaiser_2024,
  title={First impression replication study (Asch, 1945, Experiment 1)},
  url={osf.io/74892},
  publisher={OSF},
@@ -341,13 +349,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ns26x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lau &amp; Feldman, Van Boven and Ashworth (2007): Replication and extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{chin_feldman_2025,
+    <t>https://osf.io/ns26x</t>
+  </si>
+  <si>
+    <t>Lau &amp; Feldman, Van Boven and Ashworth (2007): Replication and extension</t>
+  </si>
+  <si>
+    <t>@misc{chin_feldman_2025,
  title={Revisiting the past-future emotional asymmetry:  Replication and extensions of Van Boven and Ashworth (2007)},
  url={osf.io/gcf3v},
  publisher={OSF},
@@ -357,13 +365,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_87,
+    <t>https://datacolada.org/87</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_87,
   title={[87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -372,13 +380,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.tijdschriftdepsycholoog.nl/wp-content/uploads/2015/10/Dijkstra-K.-Verkoeijen-P.-Van-Kuijk-I.-Soke-Yee-Chow-Bakker-A.-Zwaan-R.-2015.-Leidt-het-lezen-van-literaire-fictie-tot-meer-emphatie.-De-Psycholoog-10-10-21..pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijkstra, K., Verkoeijen, P., van Kuijk, I., Yee Chow, S., Bakker, A., &amp; Zwaan, R. (2015). Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013). De Psycholoog, 50(10), 10–21. Retrieved from http://hdl.handle.net/1765/98670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{dijkstra_verkoeijen_vankuijk_yeechow_bakker_zwaan_2015,
+    <t>https://www.tijdschriftdepsycholoog.nl/wp-content/uploads/2015/10/Dijkstra-K.-Verkoeijen-P.-Van-Kuijk-I.-Soke-Yee-Chow-Bakker-A.-Zwaan-R.-2015.-Leidt-het-lezen-van-literaire-fictie-tot-meer-emphatie.-De-Psycholoog-10-10-21..pdf</t>
+  </si>
+  <si>
+    <t>Dijkstra, K., Verkoeijen, P., van Kuijk, I., Yee Chow, S., Bakker, A., &amp; Zwaan, R. (2015). Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013). De Psycholoog, 50(10), 10–21. Retrieved from http://hdl.handle.net/1765/98670</t>
+  </si>
+  <si>
+    <t>@article{dijkstra_verkoeijen_vankuijk_yeechow_bakker_zwaan_2015,
   title={Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013)},
   author={Dijkstra, K. and Verkoeijen, P. and van Kuijk, I. and Yee Chow, S. and Bakker, A. and Zwaan, R.},
   journal={De Psycholoog},
@@ -390,13 +398,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [89] Data Replicada #6: The Problem of (Weird) Differential Attrition. Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_89,
+    <t>https://datacolada.org/89</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [89] Data Replicada #6: The Problem of (Weird) Differential Attrition. Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_89,
   title={[89] Data Replicada #6: The Problem of (Weird) Differential Attrition},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -405,13 +413,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://docs.google.com/document/d/1hW5moEcdB-U0Ud-MNOB5iYSkeQL60SqVekufodODxDQ/edit?tab=t.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hongye, L., &amp; Feldman, G. (2020). Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{hongye_feldman_2020_revisiting,
+    <t>https://docs.google.com/document/d/1hW5moEcdB-U0Ud-MNOB5iYSkeQL60SqVekufodODxDQ/edit?tab=t.0</t>
+  </si>
+  <si>
+    <t>Hongye, L., &amp; Feldman, G. (2020). Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986).</t>
+  </si>
+  <si>
+    <t>@misc{hongye_feldman_2020_revisiting,
   title={Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986)},
   author={Hongye, L. and Feldman, G.},
   year={2020},
@@ -419,19 +427,19 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ht4d5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCORE replication of Nyhan, B., &amp; Reifler, J. (2015). Displacing Misinformation about Events: An Experimental Test of Causal Corrections. Journal of Experimental Political Science, 2(1), 81–93. https://doi.org/10.1017/xps.2014.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/9hjxc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baskin, E., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Hahn, K. (2025, November 18). Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12. Retrieved from osf.io/cwmb5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{baskin_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_2025,
+    <t>https://osf.io/ht4d5</t>
+  </si>
+  <si>
+    <t>SCORE replication of Nyhan, B., &amp; Reifler, J. (2015). Displacing Misinformation about Events: An Experimental Test of Causal Corrections. Journal of Experimental Political Science, 2(1), 81–93. https://doi.org/10.1017/xps.2014.22</t>
+  </si>
+  <si>
+    <t>https://osf.io/9hjxc</t>
+  </si>
+  <si>
+    <t>Baskin, E., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Hahn, K. (2025, November 18). Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12. Retrieved from osf.io/cwmb5</t>
+  </si>
+  <si>
+    <t>@misc{baskin_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_2025,
  title={Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12},
  url={osf.io/cwmb5},
  publisher={OSF},
@@ -441,13 +449,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/36w4c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442. Retrieved from osf.io/23ghe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/36w4c</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442. Retrieved from osf.io/23ghe</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442},
  url={osf.io/23ghe},
  publisher={OSF},
@@ -457,13 +465,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/r58ch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56. Retrieved from osf.io/n35c2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/r58ch</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56. Retrieved from osf.io/n35c2</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56},
  url={osf.io/n35c2},
  publisher={OSF},
@@ -473,13 +481,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ahgfx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2. Retrieved from osf.io/ujg2c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/ahgfx</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2. Retrieved from osf.io/ujg2c</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2},
  url={osf.io/ujg2c},
  publisher={OSF},
@@ -489,13 +497,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/gyse6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2. Retrieved from osf.io/vhu2x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/gyse6</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2. Retrieved from osf.io/vhu2x</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2},
  url={osf.io/vhu2x},
  publisher={OSF},
@@ -505,13 +513,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/kpn34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6. Retrieved from osf.io/5k6jg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/kpn34</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6. Retrieved from osf.io/5k6jg</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6},
  url={osf.io/5k6jg},
  publisher={OSF},
@@ -521,13 +529,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/28mjt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2. Retrieved from osf.io/wjh3c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/28mjt</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2. Retrieved from osf.io/wjh3c</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2},
  url={osf.io/wjh3c},
  publisher={OSF},
@@ -537,13 +545,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/x9j47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoon, S., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k. Retrieved from osf.io/e9y6b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{yoon_tyner_loomas_miske_luis_2025,
+    <t>https://osf.io/x9j47</t>
+  </si>
+  <si>
+    <t>Yoon, S., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k. Retrieved from osf.io/e9y6b</t>
+  </si>
+  <si>
+    <t>@misc{yoon_tyner_loomas_miske_luis_2025,
  title={LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k},
  url={osf.io/e9y6b},
  publisher={OSF},
@@ -553,13 +561,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dnqrv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">de Leeuw, J. R., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Ostrowski, R. P. (2025, November 18). Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6. Retrieved from osf.io/ty5be</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{de leeuw_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_bader_et al._2025,
+    <t>https://osf.io/dnqrv</t>
+  </si>
+  <si>
+    <t>de Leeuw, J. R., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Ostrowski, R. P. (2025, November 18). Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6. Retrieved from osf.io/ty5be</t>
+  </si>
+  <si>
+    <t>@misc{de leeuw_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_bader_et al._2025,
  title={Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6},
  url={osf.io/ty5be},
  publisher={OSF},
@@ -569,13 +577,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/3u8x9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16. Retrieved from osf.io/er54t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/3u8x9</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16. Retrieved from osf.io/er54t</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16},
  url={osf.io/er54t},
  publisher={OSF},
@@ -585,13 +593,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/4usmq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6. Retrieved from osf.io/9mx5w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/4usmq</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6. Retrieved from osf.io/9mx5w</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6},
  url={osf.io/9mx5w},
  publisher={OSF},
@@ -601,13 +609,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/3d97y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2. Retrieved from osf.io/rywgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_hong_duan_reed_2025,
+    <t>https://osf.io/3d97y</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2. Retrieved from osf.io/rywgh</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_hong_duan_reed_2025,
  title={Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2},
  url={osf.io/rywgh},
  publisher={OSF},
@@ -617,13 +625,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/x46bu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6. Retrieved from osf.io/bawh3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/x46bu</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6. Retrieved from osf.io/bawh3</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6},
  url={osf.io/bawh3},
  publisher={OSF},
@@ -633,13 +641,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/n6jca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Bonfiglio, D. B. V. (2025, December 1). Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2. Retrieved from osf.io/vg6zy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_mallik_bonfiglio_2025,
+    <t>https://osf.io/n6jca</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Bonfiglio, D. B. V. (2025, December 1). Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2. Retrieved from osf.io/vg6zy</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_mallik_bonfiglio_2025,
  title={Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2},
  url={osf.io/vg6zy},
  publisher={OSF},
@@ -649,13 +657,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/7qjzp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OYEBANJO, A., Adeyemi, A. F., Loomas, Z., Miske, O., Luis, B., Tyner, A. H., … Parsons, E. S. (2025, November 18). Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81. Retrieved from osf.io/en9md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{oyebanjo_adeyemi_loomas_miske_luis_tyner_kline struhl_parsons_2025,
+    <t>https://osf.io/7qjzp</t>
+  </si>
+  <si>
+    <t>OYEBANJO, A., Adeyemi, A. F., Loomas, Z., Miske, O., Luis, B., Tyner, A. H., … Parsons, E. S. (2025, November 18). Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81. Retrieved from osf.io/en9md</t>
+  </si>
+  <si>
+    <t>@misc{oyebanjo_adeyemi_loomas_miske_luis_tyner_kline struhl_parsons_2025,
  title={Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81},
  url={osf.io/en9md},
  publisher={OSF},
@@ -665,13 +673,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/cdrmk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Mallinson, D. J. (2025, November 18). Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182. Retrieved from osf.io/h7av9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_mallinson_2025,
+    <t>https://osf.io/cdrmk</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Mallinson, D. J. (2025, November 18). Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182. Retrieved from osf.io/h7av9</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_mallinson_2025,
  title={Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182},
  url={osf.io/h7av9},
  publisher={OSF},
@@ -681,13 +689,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/39upt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w. Retrieved from osf.io/bmzuf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/39upt</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w. Retrieved from osf.io/bmzuf</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w},
  url={osf.io/bmzuf},
  publisher={OSF},
@@ -697,13 +705,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/nbc6v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Berry, Z. (2025, December 14). Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2. Retrieved from osf.io/tmn3q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_berry_2025,
+    <t>https://osf.io/nbc6v</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Berry, Z. (2025, December 14). Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2. Retrieved from osf.io/tmn3q</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_berry_2025,
  title={Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2},
  url={osf.io/tmn3q},
  publisher={OSF},
@@ -713,13 +721,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/gn3vj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6. Retrieved from osf.io/uwnya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/gn3vj</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6. Retrieved from osf.io/uwnya</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6},
  url={osf.io/uwnya},
  publisher={OSF},
@@ -729,13 +737,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qev3x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Tomašević, A. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6. Retrieved from osf.io/e48gd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_kołczyńska_silverstein_et al._2025,
+    <t>https://osf.io/qev3x</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Tomašević, A. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6. Retrieved from osf.io/e48gd</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_kołczyńska_silverstein_et al._2025,
  title={McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6},
  url={osf.io/e48gd},
  publisher={OSF},
@@ -745,13 +753,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/e9j6y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96. Retrieved from osf.io/qgm2c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/e9j6y</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96. Retrieved from osf.io/qgm2c</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96},
  url={osf.io/qgm2c},
  publisher={OSF},
@@ -761,13 +769,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/srk8q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg. Retrieved from osf.io/xwthk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/srk8q</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg. Retrieved from osf.io/xwthk</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg},
  url={osf.io/xwthk},
  publisher={OSF},
@@ -777,13 +785,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qfh2r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m. Retrieved from osf.io/n7m39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/qfh2r</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m. Retrieved from osf.io/n7m39</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m},
  url={osf.io/n7m39},
  publisher={OSF},
@@ -793,13 +801,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8mqzu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Zhang, Y. (2025, November 18). Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky. Retrieved from osf.io/bcqem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_zhang_2025,
+    <t>https://osf.io/8mqzu</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Zhang, Y. (2025, November 18). Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky. Retrieved from osf.io/bcqem</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_zhang_2025,
  title={Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky},
  url={osf.io/bcqem},
  publisher={OSF},
@@ -809,13 +817,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/syq4e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok. Retrieved from osf.io/gk92w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/syq4e</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok. Retrieved from osf.io/gk92w</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok},
  url={osf.io/gk92w},
  publisher={OSF},
@@ -825,13 +833,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/6rpxu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y. Retrieved from osf.io/tz9ef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/6rpxu</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y. Retrieved from osf.io/tz9ef</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y},
  url={osf.io/tz9ef},
  publisher={OSF},
@@ -841,13 +849,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/u58za</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9. Retrieved from osf.io/qxk38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/u58za</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9. Retrieved from osf.io/qxk38</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9},
  url={osf.io/qxk38},
  publisher={OSF},
@@ -857,13 +865,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/b2xma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6. Retrieved from osf.io/shvdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/b2xma</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6. Retrieved from osf.io/shvdk</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6},
  url={osf.io/shvdk},
  publisher={OSF},
@@ -873,13 +881,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/gvayj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12. Retrieved from osf.io/ub4c6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/gvayj</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12. Retrieved from osf.io/ub4c6</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12},
  url={osf.io/ub4c6},
  publisher={OSF},
@@ -889,13 +897,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ck8aq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2. Retrieved from osf.io/df36m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/ck8aq</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2. Retrieved from osf.io/df36m</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2},
  url={osf.io/df36m},
  publisher={OSF},
@@ -905,13 +913,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/c6a8e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16. Retrieved from osf.io/as7te</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/c6a8e</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16. Retrieved from osf.io/as7te</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16},
  url={osf.io/as7te},
  publisher={OSF},
@@ -921,13 +929,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/skwev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7. Retrieved from osf.io/yv2am</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
+    <t>https://osf.io/skwev</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7. Retrieved from osf.io/yv2am</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
  title={Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7},
  url={osf.io/yv2am},
  publisher={OSF},
@@ -937,13 +945,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/yd9bg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Vermeulen, J. (2025, November 18). van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487. Retrieved from osf.io/697dv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_vargo_vermeulen_2025,
+    <t>https://osf.io/yd9bg</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Vermeulen, J. (2025, November 18). van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487. Retrieved from osf.io/697dv</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_vargo_vermeulen_2025,
  title={van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487},
  url={osf.io/697dv},
  publisher={OSF},
@@ -953,13 +961,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/2f35a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chartier, C. R., Lewis, S. C., Kline Struhl, M., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189. Retrieved from osf.io/agv64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{chartier_lewis_kline struhl_miske_luis_loomas_2025,
+    <t>https://osf.io/2f35a</t>
+  </si>
+  <si>
+    <t>Chartier, C. R., Lewis, S. C., Kline Struhl, M., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189. Retrieved from osf.io/agv64</t>
+  </si>
+  <si>
+    <t>@misc{chartier_lewis_kline struhl_miske_luis_loomas_2025,
  title={Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189},
  url={osf.io/agv64},
  publisher={OSF},
@@ -969,13 +977,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/cnbt5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Ramljak, M. (2025, November 18). Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2. Retrieved from osf.io/em34f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_ramljak_2025,
+    <t>https://osf.io/cnbt5</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Ramljak, M. (2025, November 18). Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2. Retrieved from osf.io/em34f</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_ramljak_2025,
  title={Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2},
  url={osf.io/em34f},
  publisher={OSF},
@@ -985,13 +993,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/a6nsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field, S., Loomas, Z., Miske, O., Luis, B., &amp; Jarke-Neuert, J. (2025, November 18). Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182. Retrieved from osf.io/p9k76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{field_loomas_miske_luis_jarke-neuert_2025,
+    <t>https://osf.io/a6nsp</t>
+  </si>
+  <si>
+    <t>Field, S., Loomas, Z., Miske, O., Luis, B., &amp; Jarke-Neuert, J. (2025, November 18). Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182. Retrieved from osf.io/p9k76</t>
+  </si>
+  <si>
+    <t>@misc{field_loomas_miske_luis_jarke-neuert_2025,
  title={Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182},
  url={osf.io/p9k76},
  publisher={OSF},
@@ -1001,13 +1009,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/5869t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Baník, G. (2025, November 18). BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k. Retrieved from osf.io/8ndcx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_adamkovic_ropovik_baník_2025,
+    <t>https://osf.io/5869t</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Baník, G. (2025, November 18). BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k. Retrieved from osf.io/8ndcx</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_adamkovic_ropovik_baník_2025,
  title={BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k},
  url={osf.io/8ndcx},
  publisher={OSF},
@@ -1017,13 +1025,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xkwj9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molden, D. C. (2025, November 18). Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g. Retrieved from osf.io/w8xun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{molden_2025,
+    <t>https://osf.io/xkwj9</t>
+  </si>
+  <si>
+    <t>Molden, D. C. (2025, November 18). Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g. Retrieved from osf.io/w8xun</t>
+  </si>
+  <si>
+    <t>@misc{molden_2025,
  title={Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g},
  url={osf.io/w8xun},
  publisher={OSF},
@@ -1033,13 +1041,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xyrv6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Gooty, J. (2025, November 18). Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12. Retrieved from osf.io/7k8sy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_sargent_gooty_2025,
+    <t>https://osf.io/xyrv6</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Gooty, J. (2025, November 18). Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12. Retrieved from osf.io/7k8sy</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_sargent_gooty_2025,
  title={Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12},
  url={osf.io/7k8sy},
  publisher={OSF},
@@ -1049,13 +1057,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/phz9x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96. Retrieved from osf.io/q7hpx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
+    <t>https://osf.io/phz9x</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96. Retrieved from osf.io/q7hpx</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
  title={Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96},
  url={osf.io/q7hpx},
  publisher={OSF},
@@ -1065,13 +1073,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/zybuc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1. Retrieved from osf.io/u5d2y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t>https://osf.io/zybuc</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1. Retrieved from osf.io/u5d2y</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1},
  url={osf.io/u5d2y},
  publisher={OSF},
@@ -1081,13 +1089,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dkcu6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7. Retrieved from osf.io/h8ecm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
+    <t>https://osf.io/dkcu6</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7. Retrieved from osf.io/h8ecm</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
  title={Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7},
  url={osf.io/h8ecm},
  publisher={OSF},
@@ -1097,13 +1105,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qmbxr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6. Retrieved from osf.io/p2st5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
+    <t>https://osf.io/qmbxr</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6. Retrieved from osf.io/p2st5</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
  title={Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6},
  url={osf.io/p2st5},
  publisher={OSF},
@@ -1113,13 +1121,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/udbnf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syed, M., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26. Retrieved from osf.io/f5b6c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{syed_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/udbnf</t>
+  </si>
+  <si>
+    <t>Syed, M., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26. Retrieved from osf.io/f5b6c</t>
+  </si>
+  <si>
+    <t>@misc{syed_fox_loomas_miske_luis_2025,
  title={Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26},
  url={osf.io/f5b6c},
  publisher={OSF},
@@ -1129,13 +1137,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qu793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17. Retrieved from osf.io/8qkrx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
+    <t>https://osf.io/qu793</t>
+  </si>
+  <si>
+    <t>Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17. Retrieved from osf.io/8qkrx</t>
+  </si>
+  <si>
+    <t>@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
  title={Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17},
  url={osf.io/8qkrx},
  publisher={OSF},
@@ -1145,13 +1153,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/5r28d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Kačmár, P. (2025, November 18). Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3. Retrieved from osf.io/h37zx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_kačmár_2025,
+    <t>https://osf.io/5r28d</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Kačmár, P. (2025, November 18). Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3. Retrieved from osf.io/h37zx</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_kačmár_2025,
  title={Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3},
  url={osf.io/h37zx},
  publisher={OSF},
@@ -1161,13 +1169,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dyn6j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edlund, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk. Retrieved from osf.io/9qjhf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{edlund_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/dyn6j</t>
+  </si>
+  <si>
+    <t>Edlund, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk. Retrieved from osf.io/9qjhf</t>
+  </si>
+  <si>
+    <t>@misc{edlund_fox_loomas_miske_luis_2025,
  title={Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk},
  url={osf.io/9qjhf},
  publisher={OSF},
@@ -1177,13 +1185,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8hnxg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liu, A., Fox, N. W., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142. Retrieved from osf.io/nse8t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{liu_fox_tyner_loomas_miske_luis_2025,
+    <t>https://osf.io/8hnxg</t>
+  </si>
+  <si>
+    <t>Liu, A., Fox, N. W., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142. Retrieved from osf.io/nse8t</t>
+  </si>
+  <si>
+    <t>@misc{liu_fox_tyner_loomas_miske_luis_2025,
  title={Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142},
  url={osf.io/nse8t},
  publisher={OSF},
@@ -1193,13 +1201,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/9t4nh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Méndez-Chacón, E., Tutor, M., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496. Retrieved from osf.io/q4fpr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{méndez-chacón_tutor_tyner_abatayo_loomas_miske_luis_2025,
+    <t>https://osf.io/9t4nh</t>
+  </si>
+  <si>
+    <t>Méndez-Chacón, E., Tutor, M., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496. Retrieved from osf.io/q4fpr</t>
+  </si>
+  <si>
+    <t>@misc{méndez-chacón_tutor_tyner_abatayo_loomas_miske_luis_2025,
  title={Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496},
  url={osf.io/q4fpr},
  publisher={OSF},
@@ -1209,13 +1217,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/jx64p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gooty, J., McBride, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Arendt, B. (2025, November 18). Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y. Retrieved from osf.io/sv4e8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{gooty_mcbride_tyner_loomas_miske_luis_arendt_2025,
+    <t>https://osf.io/jx64p</t>
+  </si>
+  <si>
+    <t>Gooty, J., McBride, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Arendt, B. (2025, November 18). Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y. Retrieved from osf.io/sv4e8</t>
+  </si>
+  <si>
+    <t>@misc{gooty_mcbride_tyner_loomas_miske_luis_arendt_2025,
  title={Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y},
  url={osf.io/sv4e8},
  publisher={OSF},
@@ -1225,13 +1233,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/h7jfv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axxe, E., Ramljak, M., Tyner, A. H., Loomas, Z., Luis, B., Miske, O., … Parsons, E. S. (2025, November 18). O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7. Retrieved from osf.io/7qnrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{axxe_ramljak_tyner_loomas_luis_miske_abatayo_parsons_2025,
+    <t>https://osf.io/h7jfv</t>
+  </si>
+  <si>
+    <t>Axxe, E., Ramljak, M., Tyner, A. H., Loomas, Z., Luis, B., Miske, O., … Parsons, E. S. (2025, November 18). O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7. Retrieved from osf.io/7qnrs</t>
+  </si>
+  <si>
+    <t>@misc{axxe_ramljak_tyner_loomas_luis_miske_abatayo_parsons_2025,
  title={O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7},
  url={osf.io/7qnrs},
  publisher={OSF},
@@ -1241,13 +1249,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ab762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554. Retrieved from osf.io/afznv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
+    <t>https://osf.io/ab762</t>
+  </si>
+  <si>
+    <t>Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554. Retrieved from osf.io/afznv</t>
+  </si>
+  <si>
+    <t>@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
  title={Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554},
  url={osf.io/afznv},
  publisher={OSF},
@@ -1257,13 +1265,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/b9rcg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baskin, E., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m. Retrieved from osf.io/sw67c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{baskin_tyner_miske_loomas_2025,
+    <t>https://osf.io/b9rcg</t>
+  </si>
+  <si>
+    <t>Baskin, E., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m. Retrieved from osf.io/sw67c</t>
+  </si>
+  <si>
+    <t>@misc{baskin_tyner_miske_loomas_2025,
  title={Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m},
  url={osf.io/sw67c},
  publisher={OSF},
@@ -1273,13 +1281,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/k79vj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Méndez-Chacón, E., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Abatayo, A. (2025, November 18). Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945. Retrieved from osf.io/tacvb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{méndez-chacón_tyner_loomas_miske_luis_abatayo_2025,
+    <t>https://osf.io/k79vj</t>
+  </si>
+  <si>
+    <t>Méndez-Chacón, E., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Abatayo, A. (2025, November 18). Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945. Retrieved from osf.io/tacvb</t>
+  </si>
+  <si>
+    <t>@misc{méndez-chacón_tyner_loomas_miske_luis_abatayo_2025,
  title={Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945},
  url={osf.io/tacvb},
  publisher={OSF},
@@ -1289,13 +1297,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/vekdm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leahy, K. E., Purol, M., Oh, J., Chopik, W. J., Kline Struhl, M., Miske, O., &amp; Loomas, Z. (2025, November 18). Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67. Retrieved from osf.io/8hp5j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{leahy_purol_oh_chopik_kline struhl_miske_loomas_2025,
+    <t>https://osf.io/vekdm</t>
+  </si>
+  <si>
+    <t>Leahy, K. E., Purol, M., Oh, J., Chopik, W. J., Kline Struhl, M., Miske, O., &amp; Loomas, Z. (2025, November 18). Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67. Retrieved from osf.io/8hp5j</t>
+  </si>
+  <si>
+    <t>@misc{leahy_purol_oh_chopik_kline struhl_miske_loomas_2025,
  title={Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67},
  url={osf.io/8hp5j},
  publisher={OSF},
@@ -1305,13 +1313,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fzut6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baskin, E., Kline Struhl, M., Miske, O., Luis, B., Loomas, Z., &amp; Parsons, E. S. (2025, November 18). Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1. Retrieved from osf.io/e52qx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{baskin_kline struhl_miske_luis_loomas_parsons_2025,
+    <t>https://osf.io/fzut6</t>
+  </si>
+  <si>
+    <t>Baskin, E., Kline Struhl, M., Miske, O., Luis, B., Loomas, Z., &amp; Parsons, E. S. (2025, November 18). Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1. Retrieved from osf.io/e52qx</t>
+  </si>
+  <si>
+    <t>@misc{baskin_kline struhl_miske_luis_loomas_parsons_2025,
  title={Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1},
  url={osf.io/e52qx},
  publisher={OSF},
@@ -1321,13 +1329,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/q4e35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aczel, B., Szaszi, B., Bognar, M., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91. Retrieved from osf.io/2cjuw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{aczel_szaszi_bognar_kline struhl_miske_loomas_luis_2025,
+    <t>https://osf.io/q4e35</t>
+  </si>
+  <si>
+    <t>Aczel, B., Szaszi, B., Bognar, M., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91. Retrieved from osf.io/2cjuw</t>
+  </si>
+  <si>
+    <t>@misc{aczel_szaszi_bognar_kline struhl_miske_loomas_luis_2025,
  title={Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91},
  url={osf.io/2cjuw},
  publisher={OSF},
@@ -1337,13 +1345,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xe3d2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilbiks, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z. Retrieved from osf.io/qtv6j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{wilbiks_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/xe3d2</t>
+  </si>
+  <si>
+    <t>Wilbiks, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z. Retrieved from osf.io/qtv6j</t>
+  </si>
+  <si>
+    <t>@misc{wilbiks_fox_loomas_miske_luis_2025,
  title={Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z},
  url={osf.io/qtv6j},
  publisher={OSF},
@@ -1353,13 +1361,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/2vmgw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m. Retrieved from osf.io/mjfwp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t>https://osf.io/2vmgw</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m. Retrieved from osf.io/mjfwp</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m},
  url={osf.io/mjfwp},
  publisher={OSF},
@@ -1369,13 +1377,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/3cp2d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Forestier, J. M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., Loomas, Z., &amp; Ray, N. (2025, November 18). Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3. Retrieved from osf.io/tvhma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{le forestier_tyner_miske_luis_parsons_loomas_ray_2025,
+    <t>https://osf.io/3cp2d</t>
+  </si>
+  <si>
+    <t>Le Forestier, J. M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., Loomas, Z., &amp; Ray, N. (2025, November 18). Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3. Retrieved from osf.io/tvhma</t>
+  </si>
+  <si>
+    <t>@misc{le forestier_tyner_miske_luis_parsons_loomas_ray_2025,
  title={Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3},
  url={osf.io/tvhma},
  publisher={OSF},
@@ -1385,13 +1393,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8npm5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allen, P., Dujmović, M., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8. Retrieved from osf.io/834de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{allen_dujmović_kline struhl_loomas_miske_luis_2025,
+    <t>https://osf.io/8npm5</t>
+  </si>
+  <si>
+    <t>Allen, P., Dujmović, M., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8. Retrieved from osf.io/834de</t>
+  </si>
+  <si>
+    <t>@misc{allen_dujmović_kline struhl_loomas_miske_luis_2025,
  title={Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8},
  url={osf.io/834de},
  publisher={OSF},
@@ -1401,13 +1409,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/hmune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szabelska, A., Ghasemi, O., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796. Retrieved from osf.io/su48v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{szabelska_ghasemi_tyner_abatayo_loomas_miske_luis_2025,
+    <t>https://osf.io/hmune</t>
+  </si>
+  <si>
+    <t>Szabelska, A., Ghasemi, O., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796. Retrieved from osf.io/su48v</t>
+  </si>
+  <si>
+    <t>@misc{szabelska_ghasemi_tyner_abatayo_loomas_miske_luis_2025,
  title={Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796},
  url={osf.io/su48v},
  publisher={OSF},
@@ -1417,13 +1425,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/9s4e6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steffens, N. K., Munt, K. A., Peters, K. O., Fox, N. W., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g. Retrieved from osf.io/ty9du</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{steffens_munt_peters_fox_miske_loomas_luis_2025,
+    <t>https://osf.io/9s4e6</t>
+  </si>
+  <si>
+    <t>Steffens, N. K., Munt, K. A., Peters, K. O., Fox, N. W., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g. Retrieved from osf.io/ty9du</t>
+  </si>
+  <si>
+    <t>@misc{steffens_munt_peters_fox_miske_loomas_luis_2025,
  title={Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g},
  url={osf.io/ty9du},
  publisher={OSF},
@@ -1433,13 +1441,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fqdh4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weller, N., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Landgrave, M. G. (2025, November 18). Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m. Retrieved from osf.io/2ug8x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{weller_tyner_loomas_miske_luis_landgrave_2025,
+    <t>https://osf.io/fqdh4</t>
+  </si>
+  <si>
+    <t>Weller, N., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Landgrave, M. G. (2025, November 18). Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m. Retrieved from osf.io/2ug8x</t>
+  </si>
+  <si>
+    <t>@misc{weller_tyner_loomas_miske_luis_landgrave_2025,
  title={Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m},
  url={osf.io/2ug8x},
  publisher={OSF},
@@ -1449,13 +1457,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/tywer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mallik, P. R., Metzger, M., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Final Report. Retrieved from osf.io/4hau3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{mallik_metzger_kline struhl_loomas_miske_2025,
+    <t>https://osf.io/tywer</t>
+  </si>
+  <si>
+    <t>Mallik, P. R., Metzger, M., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Final Report. Retrieved from osf.io/4hau3</t>
+  </si>
+  <si>
+    <t>@misc{mallik_metzger_kline struhl_loomas_miske_2025,
  title={Final Report},
  url={osf.io/4hau3},
  publisher={OSF},
@@ -1465,13 +1473,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/9bkuf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0. Retrieved from osf.io/ndbrp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t>https://osf.io/9bkuf</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0. Retrieved from osf.io/ndbrp</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0},
  url={osf.io/ndbrp},
  publisher={OSF},
@@ -1481,13 +1489,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/rzny2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Abatayo, A., Fiala, N., … Fong, C. Y. M. (2025, November 18). Analysis. Retrieved from osf.io/9v6er</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_abatayo_fiala_volkman_fong_2025,
+    <t>https://osf.io/rzny2</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Abatayo, A., Fiala, N., … Fong, C. Y. M. (2025, November 18). Analysis. Retrieved from osf.io/9v6er</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_abatayo_fiala_volkman_fong_2025,
  title={Analysis},
  url={osf.io/9v6er},
  publisher={OSF},
@@ -1497,13 +1505,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/7efsw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OYEBANJO, A., Ramljak, M., Tyner, A. H., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51. Retrieved from osf.io/zt5y2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{oyebanjo_ramljak_tyner_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/7efsw</t>
+  </si>
+  <si>
+    <t>OYEBANJO, A., Ramljak, M., Tyner, A. H., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51. Retrieved from osf.io/zt5y2</t>
+  </si>
+  <si>
+    <t>@misc{oyebanjo_ramljak_tyner_fox_loomas_miske_luis_2025,
  title={Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51},
  url={osf.io/zt5y2},
  publisher={OSF},
@@ -1513,13 +1521,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fr6g8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vargo, E., Tyner, A. H., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2. Retrieved from osf.io/kvsa6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{vargo_tyner_miske_luis_loomas_2025,
+    <t>https://osf.io/fr6g8</t>
+  </si>
+  <si>
+    <t>Vargo, E., Tyner, A. H., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2. Retrieved from osf.io/kvsa6</t>
+  </si>
+  <si>
+    <t>@misc{vargo_tyner_miske_luis_loomas_2025,
  title={Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2},
  url={osf.io/kvsa6},
  publisher={OSF},
@@ -1529,13 +1537,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/yva89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Luis, B., Harper, S., Nandi, A., &amp; Loomas, Z. (2025, November 18). Analysis. Retrieved from osf.io/b6kfm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_luis_harper_nandi_loomas_2025,
+    <t>https://osf.io/yva89</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Luis, B., Harper, S., Nandi, A., &amp; Loomas, Z. (2025, November 18). Analysis. Retrieved from osf.io/b6kfm</t>
+  </si>
+  <si>
+    <t>@misc{tyner_luis_harper_nandi_loomas_2025,
  title={Analysis},
  url={osf.io/b6kfm},
  publisher={OSF},
@@ -1545,13 +1553,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ftv7q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Held, M. J., Schütz, A., Loomas, Z., Fox, N. W., Luis, B., &amp; Miske, O. (2025, November 18). Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308. Retrieved from osf.io/hd3vf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{held_schütz_loomas_fox_luis_miske_2025,
+    <t>https://osf.io/ftv7q</t>
+  </si>
+  <si>
+    <t>Held, M. J., Schütz, A., Loomas, Z., Fox, N. W., Luis, B., &amp; Miske, O. (2025, November 18). Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308. Retrieved from osf.io/hd3vf</t>
+  </si>
+  <si>
+    <t>@misc{held_schütz_loomas_fox_luis_miske_2025,
  title={Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308},
  url={osf.io/hd3vf},
  publisher={OSF},
@@ -1561,13 +1569,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ceaq3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szabelska, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Parsons, E. S. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7. Retrieved from osf.io/ta5vh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{szabelska_tyner_loomas_miske_luis_parsons_2025,
+    <t>https://osf.io/ceaq3</t>
+  </si>
+  <si>
+    <t>Szabelska, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Parsons, E. S. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7. Retrieved from osf.io/ta5vh</t>
+  </si>
+  <si>
+    <t>@misc{szabelska_tyner_loomas_miske_luis_parsons_2025,
  title={BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7},
  url={osf.io/ta5vh},
  publisher={OSF},
@@ -1577,13 +1585,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fgdxs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonseca, M., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964. Retrieved from osf.io/t9h6p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{fonseca_tyner_loomas_miske_luis_2025,
+    <t>https://osf.io/fgdxs</t>
+  </si>
+  <si>
+    <t>Fonseca, M., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964. Retrieved from osf.io/t9h6p</t>
+  </si>
+  <si>
+    <t>@misc{fonseca_tyner_loomas_miske_luis_2025,
  title={Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964},
  url={osf.io/t9h6p},
  publisher={OSF},
@@ -1593,13 +1601,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xr32n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cummins, J. (2025, November 18). Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130. Retrieved from osf.io/h24z8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{cummins_2025,
+    <t>https://osf.io/xr32n</t>
+  </si>
+  <si>
+    <t>Cummins, J. (2025, November 18). Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130. Retrieved from osf.io/h24z8</t>
+  </si>
+  <si>
+    <t>@misc{cummins_2025,
  title={Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130},
  url={osf.io/h24z8},
  publisher={OSF},
@@ -1609,13 +1617,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/kw5tv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kołczyńska, M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., &amp; Loomas, Z. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634. Retrieved from osf.io/rpumq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{kołczyńska_tyner_miske_luis_parsons_loomas_2025,
+    <t>https://osf.io/kw5tv</t>
+  </si>
+  <si>
+    <t>Kołczyńska, M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., &amp; Loomas, Z. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634. Retrieved from osf.io/rpumq</t>
+  </si>
+  <si>
+    <t>@misc{kołczyńska_tyner_miske_luis_parsons_loomas_2025,
  title={McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634},
  url={osf.io/rpumq},
  publisher={OSF},
@@ -1625,13 +1633,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/c2hry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hostler, T., Persson, S., &amp; Fox, N. W. (2025, November 18). Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z. Retrieved from osf.io/a8eg9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{hostler_persson_fox_2025,
+    <t>https://osf.io/c2hry</t>
+  </si>
+  <si>
+    <t>Hostler, T., Persson, S., &amp; Fox, N. W. (2025, November 18). Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z. Retrieved from osf.io/a8eg9</t>
+  </si>
+  <si>
+    <t>@misc{hostler_persson_fox_2025,
  title={Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z},
  url={osf.io/a8eg9},
  publisher={OSF},
@@ -1641,13 +1649,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ybzev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azevedo, F., Micheli, L., Wagner, D., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16. Retrieved from osf.io/8feku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{azevedo_micheli_wagner_tyner_miske_loomas_2025,
+    <t>https://osf.io/ybzev</t>
+  </si>
+  <si>
+    <t>Azevedo, F., Micheli, L., Wagner, D., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16. Retrieved from osf.io/8feku</t>
+  </si>
+  <si>
+    <t>@misc{azevedo_micheli_wagner_tyner_miske_loomas_2025,
  title={Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16},
  url={osf.io/8feku},
  publisher={OSF},
@@ -1657,13 +1665,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8rwkn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capitán, T., Nast, C., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Mallinson, D. J. (2025, November 18). Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762. Retrieved from osf.io/j8en2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{capitán_nast_tyner_loomas_miske_luis_abatayo_wintermantel_mallinson_2025,
+    <t>https://osf.io/8rwkn</t>
+  </si>
+  <si>
+    <t>Capitán, T., Nast, C., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Mallinson, D. J. (2025, November 18). Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762. Retrieved from osf.io/j8en2</t>
+  </si>
+  <si>
+    <t>@misc{capitán_nast_tyner_loomas_miske_luis_abatayo_wintermantel_mallinson_2025,
  title={Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762},
  url={osf.io/j8en2},
  publisher={OSF},
@@ -1673,13 +1681,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/esw45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930. Retrieved from osf.io/g6fkp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_miske_luis_kline struhl_2025,
+    <t>https://osf.io/esw45</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930. Retrieved from osf.io/g6fkp</t>
+  </si>
+  <si>
+    <t>@misc{tyner_miske_luis_kline struhl_2025,
  title={Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930},
  url={osf.io/g6fkp},
  publisher={OSF},
@@ -1689,13 +1697,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/2wfgv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bokhove, C., Nast, C., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., … Bokhove, C. (2025, November 18). Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6. Retrieved from osf.io/u52y3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{bokhove_nast_tyner_abatayo_loomas_miske_luis_bokhove_2025,
+    <t>https://osf.io/2wfgv</t>
+  </si>
+  <si>
+    <t>Bokhove, C., Nast, C., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., … Bokhove, C. (2025, November 18). Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6. Retrieved from osf.io/u52y3</t>
+  </si>
+  <si>
+    <t>@misc{bokhove_nast_tyner_abatayo_loomas_miske_luis_bokhove_2025,
  title={Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6},
  url={osf.io/u52y3},
  publisher={OSF},
@@ -1705,13 +1713,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/hzg3j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Röer, J. P., Fox, N. W., Loomas, Z., Miske, O., Luis, B., Ostermann, T., … Parsons, E. S. (2025, November 18). Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38. Retrieved from osf.io/apv5t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{röer_fox_loomas_miske_luis_ostermann_michalak_parsons_2025,
+    <t>https://osf.io/hzg3j</t>
+  </si>
+  <si>
+    <t>Röer, J. P., Fox, N. W., Loomas, Z., Miske, O., Luis, B., Ostermann, T., … Parsons, E. S. (2025, November 18). Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38. Retrieved from osf.io/apv5t</t>
+  </si>
+  <si>
+    <t>@misc{röer_fox_loomas_miske_luis_ostermann_michalak_parsons_2025,
  title={Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38},
  url={osf.io/apv5t},
  publisher={OSF},
@@ -1721,13 +1729,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/r6ynf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colvin, V., Smith, C., Fox, N. W., Miske, O., &amp; Loomas, Z. (2025, November 18). Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9. Retrieved from osf.io/etfqz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{colvin_smith_fox_miske_loomas_2025,
+    <t>https://osf.io/r6ynf</t>
+  </si>
+  <si>
+    <t>Colvin, V., Smith, C., Fox, N. W., Miske, O., &amp; Loomas, Z. (2025, November 18). Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9. Retrieved from osf.io/etfqz</t>
+  </si>
+  <si>
+    <t>@misc{colvin_smith_fox_miske_loomas_2025,
  title={Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9},
  url={osf.io/etfqz},
  publisher={OSF},
@@ -1737,13 +1745,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dscfg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slevc, L. R., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02. Retrieved from osf.io/78fvn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{slevc_kline struhl_loomas_miske_2025,
+    <t>https://osf.io/dscfg</t>
+  </si>
+  <si>
+    <t>Slevc, L. R., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02. Retrieved from osf.io/78fvn</t>
+  </si>
+  <si>
+    <t>@misc{slevc_kline struhl_loomas_miske_2025,
  title={Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02},
  url={osf.io/78fvn},
  publisher={OSF},
@@ -1753,13 +1761,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/nuzh2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Coupe, T., Tyner, A. H., Loomas, Z., … Kline Struhl, M. (2025, November 18). Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7. Retrieved from osf.io/62xh4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{reed_duan_hong_coupe_tyner_loomas_miske_luis_vo_kline struhl_2025,
+    <t>https://osf.io/nuzh2</t>
+  </si>
+  <si>
+    <t>Reed, W. R., Duan, J., Hong, S., Coupe, T., Tyner, A. H., Loomas, Z., … Kline Struhl, M. (2025, November 18). Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7. Retrieved from osf.io/62xh4</t>
+  </si>
+  <si>
+    <t>@misc{reed_duan_hong_coupe_tyner_loomas_miske_luis_vo_kline struhl_2025,
  title={Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7},
  url={osf.io/62xh4},
  publisher={OSF},
@@ -1769,13 +1777,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/pex6u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Tyner, A. H., Loomas, Z., Miske, O., … Vo, D. T. H. (2025, November 18). Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz. Retrieved from osf.io/925nz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{reed_duan_hong_tyner_loomas_miske_luis_coupe_vo_2025,
+    <t>https://osf.io/pex6u</t>
+  </si>
+  <si>
+    <t>Reed, W. R., Duan, J., Hong, S., Tyner, A. H., Loomas, Z., Miske, O., … Vo, D. T. H. (2025, November 18). Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz. Retrieved from osf.io/925nz</t>
+  </si>
+  <si>
+    <t>@misc{reed_duan_hong_tyner_loomas_miske_luis_coupe_vo_2025,
  title={Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz},
  url={osf.io/925nz},
  publisher={OSF},
@@ -1785,13 +1793,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xg6q5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Loomas, Z., Miske, O., Luis, B., … Vo, D. T. H. (2025, November 18). Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz. Retrieved from osf.io/devn8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{reed_duan_hong_loomas_miske_luis_tyner_abatayo_coupe_vo_2025,
+    <t>https://osf.io/xg6q5</t>
+  </si>
+  <si>
+    <t>Reed, W. R., Duan, J., Hong, S., Loomas, Z., Miske, O., Luis, B., … Vo, D. T. H. (2025, November 18). Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz. Retrieved from osf.io/devn8</t>
+  </si>
+  <si>
+    <t>@misc{reed_duan_hong_loomas_miske_luis_tyner_abatayo_coupe_vo_2025,
  title={Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz},
  url={osf.io/devn8},
  publisher={OSF},
@@ -1801,13 +1809,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qk34m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smalarz, L., Parsons, E. S., &amp; Hahn, K. (2025, November 18). Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707. Retrieved from osf.io/dhg3q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{smalarz_parsons_hahn_2025,
+    <t>https://osf.io/qk34m</t>
+  </si>
+  <si>
+    <t>Smalarz, L., Parsons, E. S., &amp; Hahn, K. (2025, November 18). Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707. Retrieved from osf.io/dhg3q</t>
+  </si>
+  <si>
+    <t>@misc{smalarz_parsons_hahn_2025,
  title={Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707},
  url={osf.io/dhg3q},
  publisher={OSF},
@@ -1817,49 +1825,49 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">osf.io/y2emk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavlov, Y. G. (2023, June 20). Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4. Retrieved from osf.io/y2emk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pavlov_2023,\n title={Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4},\n url={osf.io/y2emk},\n publisher={OSF},\n author={Pavlov, Yuri G},\n year={2023},\n month={Jun}\n}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">latham_2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latham, O. (2013). Bias at the Beeb? A quantitative study of slant in BBC online reporting. Centre for Policy Studies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@techreport{latham2013bias, author = {Latham, Oliver}, title = {Bias at the Beeb? {A} quantitative study of slant in {BBC} online reporting}, institution = {Centre for Policy Studies}, year = {2013}, type = {Pointmaker}, url = {https://cps.org.uk/research/bias-at-the-beeb-a-quantitative-study-of-slant-in-bbc-online-reporting/} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">djaerv_2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Djärv, K., Zehr, J., &amp; Schwarz, F. (2018). Cognitive vs. emotive factives: An experimental differentiation. Proceedings of Sinn und Bedeutung, 21(1), 367–386.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@inproceedings{djarv2018cognitive, author = {Dj{\"a}rv, Kajsa and Zehr, Jeremy and Schwarz, Florian}, title = {Cognitive vs. emotive factives: {A}n experimental differentiation}, booktitle = {Proceedings of Sinn und Bedeutung}, volume = {21}, number = {1}, pages = {367--386}, year = {2018} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">escholarship.orgucitem39d347bk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chopra, S., Tessler, M. H., &amp; Goodman, N. D. (2019, July). The first crank of the cultural ratchet: Learning and transmitting concepts through language. In Proceedings of the 41st Annual Conference of the Cognitive Science Society (pp. 226–232). Cognitive Science Society.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@inproceedings{chopra2019first, author = {Chopra, Sahil and Tessler, Michael Henry and Goodman, Noah D}, booktitle = {Proceedings of the 41st Annual Meeting of the Cognitive Science Society}, date-added = {2020-09-05 00:50:14 +0000}, date-modified = {2020-09-05 01:32:38 +0000}, pages = {226--232}, title = {The first crank of the cultural ratchet: Learning and transmitting concepts through language}, website = {https://cogsci.mindmodeling.org/2019/papers/0060/0060.pdf}, year = {2019} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">art00005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuter, K. (2011). Distinguishing the appearance from the reality of pain. Journal of Consciousness Studies, 18(9-10), 94-109.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{reuter2011distinguishing,
+    <t>osf.io/y2emk</t>
+  </si>
+  <si>
+    <t>Pavlov, Y. G. (2023, June 20). Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4. Retrieved from osf.io/y2emk</t>
+  </si>
+  <si>
+    <t>@misc{pavlov_2023,\n title={Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4},\n url={osf.io/y2emk},\n publisher={OSF},\n author={Pavlov, Yuri G},\n year={2023},\n month={Jun}\n}</t>
+  </si>
+  <si>
+    <t>latham_2012</t>
+  </si>
+  <si>
+    <t>Latham, O. (2013). Bias at the Beeb? A quantitative study of slant in BBC online reporting. Centre for Policy Studies.</t>
+  </si>
+  <si>
+    <t>@techreport{latham2013bias, author = {Latham, Oliver}, title = {Bias at the Beeb? {A} quantitative study of slant in {BBC} online reporting}, institution = {Centre for Policy Studies}, year = {2013}, type = {Pointmaker}, url = {https://cps.org.uk/research/bias-at-the-beeb-a-quantitative-study-of-slant-in-bbc-online-reporting/} }</t>
+  </si>
+  <si>
+    <t>djaerv_2018</t>
+  </si>
+  <si>
+    <t>Djärv, K., Zehr, J., &amp; Schwarz, F. (2018). Cognitive vs. emotive factives: An experimental differentiation. Proceedings of Sinn und Bedeutung, 21(1), 367–386.</t>
+  </si>
+  <si>
+    <t>@inproceedings{djarv2018cognitive, author = {Dj{\"a}rv, Kajsa and Zehr, Jeremy and Schwarz, Florian}, title = {Cognitive vs. emotive factives: {A}n experimental differentiation}, booktitle = {Proceedings of Sinn und Bedeutung}, volume = {21}, number = {1}, pages = {367--386}, year = {2018} }</t>
+  </si>
+  <si>
+    <t>escholarship.orgucitem39d347bk</t>
+  </si>
+  <si>
+    <t>Chopra, S., Tessler, M. H., &amp; Goodman, N. D. (2019, July). The first crank of the cultural ratchet: Learning and transmitting concepts through language. In Proceedings of the 41st Annual Conference of the Cognitive Science Society (pp. 226–232). Cognitive Science Society.</t>
+  </si>
+  <si>
+    <t>@inproceedings{chopra2019first, author = {Chopra, Sahil and Tessler, Michael Henry and Goodman, Noah D}, booktitle = {Proceedings of the 41st Annual Meeting of the Cognitive Science Society}, date-added = {2020-09-05 00:50:14 +0000}, date-modified = {2020-09-05 01:32:38 +0000}, pages = {226--232}, title = {The first crank of the cultural ratchet: Learning and transmitting concepts through language}, website = {https://cogsci.mindmodeling.org/2019/papers/0060/0060.pdf}, year = {2019} }</t>
+  </si>
+  <si>
+    <t>art00005</t>
+  </si>
+  <si>
+    <t>Reuter, K. (2011). Distinguishing the appearance from the reality of pain. Journal of Consciousness Studies, 18(9-10), 94-109.</t>
+  </si>
+  <si>
+    <t>@article{reuter2011distinguishing,
   title={Distinguishing the appearance from the reality of pain},
   author={Reuter, K.},
   journal={Journal of Consciousness Studies},
@@ -1870,13 +1878,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">scholars.indianastate.eduetds--2136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilfong, R. (2021). The mattering model: The foundational elements of mattering for K-12 educators (Order No. 28319407) [Doctoral dissertation, Indiana State University]. ProQuest Dissertations &amp; Theses Global. https://www.proquest.com/dissertations-theses/mattering-model-foundational-elements-k-12/docview/2537966312/se-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@phdthesis{wilfong2021mattering,
+    <t>scholars.indianastate.eduetds--2136</t>
+  </si>
+  <si>
+    <t>Wilfong, R. (2021). The mattering model: The foundational elements of mattering for K-12 educators (Order No. 28319407) [Doctoral dissertation, Indiana State University]. ProQuest Dissertations &amp; Theses Global. https://www.proquest.com/dissertations-theses/mattering-model-foundational-elements-k-12/docview/2537966312/se-2</t>
+  </si>
+  <si>
+    <t>@phdthesis{wilfong2021mattering,
   title={The mattering model: The foundational elements of mattering for K-12 educators},
   author={Wilfong, R.},
   year={2021},
@@ -1886,13 +1894,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">thekeep.eiu.edu/theses/4783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burback, S. (2020). Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/4783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{burback2020construct,
+    <t>thekeep.eiu.edu/theses/4783</t>
+  </si>
+  <si>
+    <t>Burback, S. (2020). Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/4783</t>
+  </si>
+  <si>
+    <t>@mastersthesis{burback2020construct,
   title={Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Burback, Shannon},
   year={2020},
@@ -1902,13 +1910,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wiebe_2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiebe, R. P. (2004). Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape. Individual Differences Research, 2, 38-62.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{wiebe2004delinquent,
+    <t>wiebe_2004</t>
+  </si>
+  <si>
+    <t>Wiebe, R. P. (2004). Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape. Individual Differences Research, 2, 38-62.</t>
+  </si>
+  <si>
+    <t>@article{wiebe2004delinquent,
   title={Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape},
   author={Wiebe, R. P.},
   journal={Individual Differences Research},
@@ -1918,13 +1926,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">pashler_2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N. (2011, September 15). Elderly-related words prime slow walking. PsychFileDrawer. Retrieved September 23, 2017, from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pashler_harris_coburn_2011_psychfiledrawer,
+    <t>pashler_2011</t>
+  </si>
+  <si>
+    <t>Pashler, H., Harris, C., &amp; Coburn, N. (2011, September 15). Elderly-related words prime slow walking. PsychFileDrawer. Retrieved September 23, 2017, from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>@misc{pashler_harris_coburn_2011_psychfiledrawer,
   title={Elderly-related words prime slow walking},
   author={Pashler, H. and Harris, C. and Coburn, N.},
   year={2011},
@@ -1935,13 +1943,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">murtagh_2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51. (Study 2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{murtagh_todd_2004_strength,
+    <t>murtagh_2004</t>
+  </si>
+  <si>
+    <t>Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51. (Study 2).</t>
+  </si>
+  <si>
+    <t>@article{murtagh_todd_2004_strength,
   title={Self-regulation: A challenge to the strength model},
   author={Murtagh, Andrew M. and Todd, Sandra A.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -1953,13 +1961,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">korbmacher_2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korbmacher, M., Kwan, C. I., &amp; Feldman, G. (2022). Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects. https://hdl.handle.net/11250/2990125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{korbmacher_kwan_feldman_2022_abovebelow,
+    <t>korbmacher_2022</t>
+  </si>
+  <si>
+    <t>Korbmacher, M., Kwan, C. I., &amp; Feldman, G. (2022). Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects. https://hdl.handle.net/11250/2990125</t>
+  </si>
+  <si>
+    <t>@misc{korbmacher_kwan_feldman_2022_abovebelow,
   title={Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects},
   author={Korbmacher, M. and Kwan, C. I. and Feldman, G.},
   year={2022},
@@ -1967,13 +1975,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">ferrell_2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferrell, J. D., Gosling, S. D., &amp; Donnellan, M. B. (2014). Showering and loneliness: Participants from the University of Texas, Austin. PsychFileDrawer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{ferrell_gosling_donnellan_2014_showering,
+    <t>ferrell_2013</t>
+  </si>
+  <si>
+    <t>Ferrell, J. D., Gosling, S. D., &amp; Donnellan, M. B. (2014). Showering and loneliness: Participants from the University of Texas, Austin. PsychFileDrawer.</t>
+  </si>
+  <si>
+    <t>@misc{ferrell_gosling_donnellan_2014_showering,
   title={Showering and loneliness: Participants from the University of Texas, Austin},
   author={Ferrell, J. D. and Gosling, S. D. and Donnellan, M. B.},
   year={2014},
@@ -1982,13 +1990,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">lee_2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee, F. (2013). Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@unpublished{lee2013clean,
+    <t>lee_2013</t>
+  </si>
+  <si>
+    <t>Lee, F. (2013). Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
+  </si>
+  <si>
+    <t>@unpublished{lee2013clean,
   title={Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science)},
   author={Lee, F.},
   year={2013},
@@ -1996,13 +2004,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">fayard_2009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6. (Study 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{fayard_bassi_bernstein_roberts_2009_cleanliness,
+    <t>fayard_2009</t>
+  </si>
+  <si>
+    <t>Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6. (Study 1).</t>
+  </si>
+  <si>
+    <t>@article{fayard_bassi_bernstein_roberts_2009_cleanliness,
   title={Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006)},
   author={Fayard, Jennifer V. and Bassi, Alana K. and Bernstein, Daniel M. and Roberts, Brent W.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -2012,13 +2020,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">vonpruski_2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruski, S. M. (2024). The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study (Bachelor's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@thesis{pruski2024impact,
+    <t>vonpruski_2024</t>
+  </si>
+  <si>
+    <t>Pruski, S. M. (2024). The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study (Bachelor's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100459</t>
+  </si>
+  <si>
+    <t>@thesis{pruski2024impact,
   title={The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study},
   author={Pruski, S. M.},
   year={2024},
@@ -2028,13 +2036,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">digitalcommons.memphis.edu--etd--3538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thornton, K. B. (2024). Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T) [Doctoral dissertation, University of Memphis]. Digital Commons @ University of Memphis. https://digitalcommons.memphis.edu/etd/3538/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@phdthesis{thornton2024perceptions,
+    <t>digitalcommons.memphis.edu--etd--3538</t>
+  </si>
+  <si>
+    <t>Thornton, K. B. (2024). Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T) [Doctoral dissertation, University of Memphis]. Digital Commons @ University of Memphis. https://digitalcommons.memphis.edu/etd/3538/</t>
+  </si>
+  <si>
+    <t>@phdthesis{thornton2024perceptions,
   title={Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T)},
   author={Thornton, K. B.},
   year={2024},
@@ -2043,13 +2051,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katla, J. (2024). Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{katla2024replication_basc,
+    <t>thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>Katla, J. (2024). Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>@mastersthesis{katla2024replication_basc,
   title={Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Katla, J.},
   year={2024},
@@ -2057,19 +2065,69 @@
   url={https://thekeep.eiu.edu/theses/5025}
 }</t>
   </si>
+  <si>
+    <t>@article{lacko2025comment, title={A comment on Combs et al. (2023) "Reducing political polarization in the United States with a mobile chat platform"}, author={Lacko, Daniel and Prošek, Tomáš}, journal={I4R Report}, year={2025}}</t>
+  </si>
+  <si>
+    <t>Lacko, D., &amp; Prošek, T. (2025). A comment on Combs et al. (2023) “Reducing political polarization in the United States with a mobile chat platform”. I4R Report.</t>
+  </si>
+  <si>
+    <t>https://osf.io/7jy4e/files/u93pc</t>
+  </si>
+  <si>
+    <t>Créchet, J., Cui, J., Sabada, B., &amp; Sawyer, A. (2024). Why don’t firms hire young workers during recessions? A replication of Forsythe (The Economic Journal, 2022). (I4R Discussion Paper Series No. 163)</t>
+  </si>
+  <si>
+    <t>https://osf.io/7qv89</t>
+  </si>
+  <si>
+    <t>@techreport{crechet2024youngworkers, title={Why Don't Firms Hire Young Workers During Recessions? A Replication of Forsythe (The Economic Journal, 2022)}, author={Créchet, Jonathan and Cui, Jing and Sabada, Barbara and Sawyer, Antoine}, institution={The Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={163}, keywords={Worker flows; business cycles; life cycle}, url={https://ideas.repec.org/p/zbw/i4rdps/163.html}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/txqjw/</t>
+  </si>
+  <si>
+    <t>@techreport{hallman2024robustness, title={Robustness Reproducibility of "Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention"}, author={Hallman, Alice and Johannesson, Magnus and Kujansuu, Essi}, institution={Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={118}, url={https://hdl.handle.net/10419/295247}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/8rb5k</t>
+  </si>
+  <si>
+    <t>Hallman, A., Johannesson, M., &amp; Kujansuu, E. (2024). Robustness Reproducibility of" Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention". (No. 118), I4R Discussion Paper Series.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodeur, A. (2024). Reproduction of  "Who Chooses Commitment? Evidence and Welfare Implications". </t>
+  </si>
+  <si>
+    <t>@misc{brodeur2024reproduction, author={Brodeur, Abel}, title={Reproduction of "Who Chooses Commitment? Evidence and Welfare Implications"}, year={2024}, month={July}, day={22}, howpublished={OSF}, url={https://osf.io/752q9}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/9erj6</t>
+  </si>
+  <si>
+    <t>Kjelsrud, A., Kotsadam, A., Rogeberg, O., &amp; Brodeur, A. (2025, February 22). A comment on “Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India” by Siddique et al. (2024)</t>
+  </si>
+  <si>
+    <t>@book{kjelsrud2025comment, title={A Comment on "Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India" by Siddique et al. (2024)}, author={Kjelsrud, Anders and Kotsadam, Andreas and Rogeberg, Ole and Brodeur, Abel}, year={2025}, publisher={JSTOR}}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2092,13 +2150,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2380,11 +2448,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J172"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.90625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2416,7 +2487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2426,15 +2497,8 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2444,15 +2508,8 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2462,15 +2519,8 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2480,15 +2530,8 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2498,15 +2541,8 @@
       <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2516,15 +2552,8 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2534,15 +2563,8 @@
       <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2552,15 +2574,8 @@
       <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -2570,15 +2585,8 @@
       <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2588,15 +2596,8 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-    </row>
-    <row r="12">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -2606,15 +2607,8 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-    </row>
-    <row r="13">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -2624,15 +2618,8 @@
       <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -2642,15 +2629,8 @@
       <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2660,15 +2640,8 @@
       <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -2678,15 +2651,8 @@
       <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2696,15 +2662,8 @@
       <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -2714,15 +2673,8 @@
       <c r="C18" t="s">
         <v>60</v>
       </c>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
-    </row>
-    <row r="19">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -2732,15 +2684,8 @@
       <c r="C19" t="s">
         <v>63</v>
       </c>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -2750,15 +2695,8 @@
       <c r="C20" t="s">
         <v>66</v>
       </c>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-    </row>
-    <row r="21">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -2768,15 +2706,8 @@
       <c r="C21" t="s">
         <v>69</v>
       </c>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-    </row>
-    <row r="22">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -2786,15 +2717,8 @@
       <c r="C22" t="s">
         <v>72</v>
       </c>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-    </row>
-    <row r="23">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -2804,15 +2728,8 @@
       <c r="C23" t="s">
         <v>75</v>
       </c>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-    </row>
-    <row r="24">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -2822,15 +2739,8 @@
       <c r="C24" t="s">
         <v>78</v>
       </c>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-    </row>
-    <row r="25">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -2840,31 +2750,16 @@
       <c r="C25" t="s">
         <v>81</v>
       </c>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-    </row>
-    <row r="26">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>82</v>
       </c>
       <c r="B26" t="s">
         <v>83</v>
       </c>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-    </row>
-    <row r="27">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -2874,15 +2769,8 @@
       <c r="C27" t="s">
         <v>86</v>
       </c>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
-    </row>
-    <row r="28">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -2892,15 +2780,8 @@
       <c r="C28" t="s">
         <v>89</v>
       </c>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
-    </row>
-    <row r="29">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -2910,15 +2791,8 @@
       <c r="C29" t="s">
         <v>92</v>
       </c>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
-    </row>
-    <row r="30">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -2928,15 +2802,8 @@
       <c r="C30" t="s">
         <v>95</v>
       </c>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-    </row>
-    <row r="31">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -2946,15 +2813,8 @@
       <c r="C31" t="s">
         <v>98</v>
       </c>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
-    </row>
-    <row r="32">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -2964,15 +2824,8 @@
       <c r="C32" t="s">
         <v>101</v>
       </c>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-    </row>
-    <row r="33">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -2982,15 +2835,8 @@
       <c r="C33" t="s">
         <v>104</v>
       </c>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-    </row>
-    <row r="34">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -3000,15 +2846,8 @@
       <c r="C34" t="s">
         <v>107</v>
       </c>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-    </row>
-    <row r="35">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -3018,15 +2857,8 @@
       <c r="C35" t="s">
         <v>110</v>
       </c>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>111</v>
       </c>
@@ -3036,15 +2868,8 @@
       <c r="C36" t="s">
         <v>113</v>
       </c>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-    </row>
-    <row r="37">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -3054,15 +2879,8 @@
       <c r="C37" t="s">
         <v>116</v>
       </c>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
-    </row>
-    <row r="38">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -3072,15 +2890,8 @@
       <c r="C38" t="s">
         <v>119</v>
       </c>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
-    </row>
-    <row r="39">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -3090,15 +2901,8 @@
       <c r="C39" t="s">
         <v>122</v>
       </c>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -3108,15 +2912,8 @@
       <c r="C40" t="s">
         <v>125</v>
       </c>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
-    </row>
-    <row r="41">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -3126,15 +2923,8 @@
       <c r="C41" t="s">
         <v>128</v>
       </c>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
-    </row>
-    <row r="42">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -3144,15 +2934,8 @@
       <c r="C42" t="s">
         <v>131</v>
       </c>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-    </row>
-    <row r="43">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -3162,15 +2945,8 @@
       <c r="C43" t="s">
         <v>131</v>
       </c>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-    </row>
-    <row r="44">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -3180,15 +2956,8 @@
       <c r="C44" t="s">
         <v>131</v>
       </c>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
-      <c r="J44"/>
-    </row>
-    <row r="45">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>129</v>
       </c>
@@ -3198,15 +2967,8 @@
       <c r="C45" t="s">
         <v>131</v>
       </c>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-    </row>
-    <row r="46">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -3216,15 +2978,8 @@
       <c r="C46" t="s">
         <v>134</v>
       </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-    </row>
-    <row r="47">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>135</v>
       </c>
@@ -3234,15 +2989,8 @@
       <c r="C47" t="s">
         <v>137</v>
       </c>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
-      <c r="I47"/>
-      <c r="J47"/>
-    </row>
-    <row r="48">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -3252,15 +3000,8 @@
       <c r="C48" t="s">
         <v>137</v>
       </c>
-      <c r="D48"/>
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
-      <c r="I48"/>
-      <c r="J48"/>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>135</v>
       </c>
@@ -3270,15 +3011,8 @@
       <c r="C49" t="s">
         <v>137</v>
       </c>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
-      <c r="I49"/>
-      <c r="J49"/>
-    </row>
-    <row r="50">
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -3288,15 +3022,8 @@
       <c r="C50" t="s">
         <v>140</v>
       </c>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -3306,15 +3033,8 @@
       <c r="C51" t="s">
         <v>140</v>
       </c>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-    </row>
-    <row r="52">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>138</v>
       </c>
@@ -3324,15 +3044,8 @@
       <c r="C52" t="s">
         <v>140</v>
       </c>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-    </row>
-    <row r="53">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>141</v>
       </c>
@@ -3342,15 +3055,8 @@
       <c r="C53" t="s">
         <v>143</v>
       </c>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-    </row>
-    <row r="54">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>144</v>
       </c>
@@ -3360,15 +3066,8 @@
       <c r="C54" t="s">
         <v>146</v>
       </c>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-    </row>
-    <row r="55">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>144</v>
       </c>
@@ -3378,15 +3077,8 @@
       <c r="C55" t="s">
         <v>146</v>
       </c>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -3396,15 +3088,8 @@
       <c r="C56" t="s">
         <v>146</v>
       </c>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56"/>
-    </row>
-    <row r="57">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>147</v>
       </c>
@@ -3414,15 +3099,8 @@
       <c r="C57" t="s">
         <v>149</v>
       </c>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-    </row>
-    <row r="58">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -3432,15 +3110,8 @@
       <c r="C58" t="s">
         <v>149</v>
       </c>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58"/>
-    </row>
-    <row r="59">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>147</v>
       </c>
@@ -3450,15 +3121,8 @@
       <c r="C59" t="s">
         <v>149</v>
       </c>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-    </row>
-    <row r="60">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -3468,15 +3132,8 @@
       <c r="C60" t="s">
         <v>149</v>
       </c>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60"/>
-    </row>
-    <row r="61">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -3486,15 +3143,8 @@
       <c r="C61" t="s">
         <v>152</v>
       </c>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
-    </row>
-    <row r="62">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>153</v>
       </c>
@@ -3504,15 +3154,8 @@
       <c r="C62" t="s">
         <v>155</v>
       </c>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-    </row>
-    <row r="63">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -3522,15 +3165,8 @@
       <c r="C63" t="s">
         <v>155</v>
       </c>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63"/>
-    </row>
-    <row r="64">
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -3540,15 +3176,8 @@
       <c r="C64" t="s">
         <v>158</v>
       </c>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-    </row>
-    <row r="65">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>156</v>
       </c>
@@ -3558,15 +3187,8 @@
       <c r="C65" t="s">
         <v>158</v>
       </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-    </row>
-    <row r="66">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>156</v>
       </c>
@@ -3576,15 +3198,8 @@
       <c r="C66" t="s">
         <v>158</v>
       </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-    </row>
-    <row r="67">
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>159</v>
       </c>
@@ -3594,15 +3209,8 @@
       <c r="C67" t="s">
         <v>161</v>
       </c>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-    </row>
-    <row r="68">
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>159</v>
       </c>
@@ -3612,15 +3220,8 @@
       <c r="C68" t="s">
         <v>161</v>
       </c>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-    </row>
-    <row r="69">
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>159</v>
       </c>
@@ -3630,15 +3231,8 @@
       <c r="C69" t="s">
         <v>161</v>
       </c>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-    </row>
-    <row r="70">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -3648,15 +3242,8 @@
       <c r="C70" t="s">
         <v>164</v>
       </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>162</v>
       </c>
@@ -3666,15 +3253,8 @@
       <c r="C71" t="s">
         <v>164</v>
       </c>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-    </row>
-    <row r="72">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>162</v>
       </c>
@@ -3684,15 +3264,8 @@
       <c r="C72" t="s">
         <v>164</v>
       </c>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-    </row>
-    <row r="73">
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -3702,15 +3275,8 @@
       <c r="C73" t="s">
         <v>167</v>
       </c>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
-      <c r="G73"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-    </row>
-    <row r="74">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -3720,15 +3286,8 @@
       <c r="C74" t="s">
         <v>170</v>
       </c>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
-      <c r="G74"/>
-      <c r="H74"/>
-      <c r="I74"/>
-      <c r="J74"/>
-    </row>
-    <row r="75">
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>168</v>
       </c>
@@ -3738,15 +3297,8 @@
       <c r="C75" t="s">
         <v>170</v>
       </c>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
-      <c r="G75"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75"/>
-    </row>
-    <row r="76">
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>171</v>
       </c>
@@ -3756,15 +3308,8 @@
       <c r="C76" t="s">
         <v>173</v>
       </c>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76"/>
-      <c r="H76"/>
-      <c r="I76"/>
-      <c r="J76"/>
-    </row>
-    <row r="77">
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>171</v>
       </c>
@@ -3774,15 +3319,8 @@
       <c r="C77" t="s">
         <v>173</v>
       </c>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
-      <c r="J77"/>
-    </row>
-    <row r="78">
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -3792,15 +3330,8 @@
       <c r="C78" t="s">
         <v>176</v>
       </c>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78"/>
-    </row>
-    <row r="79">
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>174</v>
       </c>
@@ -3810,15 +3341,8 @@
       <c r="C79" t="s">
         <v>176</v>
       </c>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
-      <c r="G79"/>
-      <c r="H79"/>
-      <c r="I79"/>
-      <c r="J79"/>
-    </row>
-    <row r="80">
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -3828,15 +3352,8 @@
       <c r="C80" t="s">
         <v>176</v>
       </c>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
-      <c r="G80"/>
-      <c r="H80"/>
-      <c r="I80"/>
-      <c r="J80"/>
-    </row>
-    <row r="81">
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>177</v>
       </c>
@@ -3846,15 +3363,8 @@
       <c r="C81" t="s">
         <v>179</v>
       </c>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
-      <c r="G81"/>
-      <c r="H81"/>
-      <c r="I81"/>
-      <c r="J81"/>
-    </row>
-    <row r="82">
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>177</v>
       </c>
@@ -3864,15 +3374,8 @@
       <c r="C82" t="s">
         <v>179</v>
       </c>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
-      <c r="I82"/>
-      <c r="J82"/>
-    </row>
-    <row r="83">
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>177</v>
       </c>
@@ -3882,15 +3385,8 @@
       <c r="C83" t="s">
         <v>179</v>
       </c>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
-      <c r="I83"/>
-      <c r="J83"/>
-    </row>
-    <row r="84">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>180</v>
       </c>
@@ -3900,15 +3396,8 @@
       <c r="C84" t="s">
         <v>182</v>
       </c>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-      <c r="I84"/>
-      <c r="J84"/>
-    </row>
-    <row r="85">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>183</v>
       </c>
@@ -3918,15 +3407,8 @@
       <c r="C85" t="s">
         <v>185</v>
       </c>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
-      <c r="I85"/>
-      <c r="J85"/>
-    </row>
-    <row r="86">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>186</v>
       </c>
@@ -3936,15 +3418,8 @@
       <c r="C86" t="s">
         <v>188</v>
       </c>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-      <c r="J86"/>
-    </row>
-    <row r="87">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>186</v>
       </c>
@@ -3954,15 +3429,8 @@
       <c r="C87" t="s">
         <v>188</v>
       </c>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
-    </row>
-    <row r="88">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>189</v>
       </c>
@@ -3972,15 +3440,8 @@
       <c r="C88" t="s">
         <v>191</v>
       </c>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88"/>
-      <c r="J88"/>
-    </row>
-    <row r="89">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -3990,15 +3451,8 @@
       <c r="C89" t="s">
         <v>194</v>
       </c>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89"/>
-      <c r="I89"/>
-      <c r="J89"/>
-    </row>
-    <row r="90">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>195</v>
       </c>
@@ -4008,15 +3462,8 @@
       <c r="C90" t="s">
         <v>197</v>
       </c>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
-      <c r="I90"/>
-      <c r="J90"/>
-    </row>
-    <row r="91">
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -4026,15 +3473,8 @@
       <c r="C91" t="s">
         <v>200</v>
       </c>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91"/>
-      <c r="I91"/>
-      <c r="J91"/>
-    </row>
-    <row r="92">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>201</v>
       </c>
@@ -4044,15 +3484,8 @@
       <c r="C92" t="s">
         <v>203</v>
       </c>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
-      <c r="I92"/>
-      <c r="J92"/>
-    </row>
-    <row r="93">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>201</v>
       </c>
@@ -4062,15 +3495,8 @@
       <c r="C93" t="s">
         <v>203</v>
       </c>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
-      <c r="G93"/>
-      <c r="H93"/>
-      <c r="I93"/>
-      <c r="J93"/>
-    </row>
-    <row r="94">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -4080,15 +3506,8 @@
       <c r="C94" t="s">
         <v>203</v>
       </c>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
-      <c r="I94"/>
-      <c r="J94"/>
-    </row>
-    <row r="95">
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>201</v>
       </c>
@@ -4098,15 +3517,8 @@
       <c r="C95" t="s">
         <v>203</v>
       </c>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
-      <c r="G95"/>
-      <c r="H95"/>
-      <c r="I95"/>
-      <c r="J95"/>
-    </row>
-    <row r="96">
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -4116,15 +3528,8 @@
       <c r="C96" t="s">
         <v>203</v>
       </c>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
-      <c r="I96"/>
-      <c r="J96"/>
-    </row>
-    <row r="97">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>201</v>
       </c>
@@ -4134,15 +3539,8 @@
       <c r="C97" t="s">
         <v>203</v>
       </c>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-      <c r="H97"/>
-      <c r="I97"/>
-      <c r="J97"/>
-    </row>
-    <row r="98">
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -4152,15 +3550,8 @@
       <c r="C98" t="s">
         <v>203</v>
       </c>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98"/>
-      <c r="H98"/>
-      <c r="I98"/>
-      <c r="J98"/>
-    </row>
-    <row r="99">
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>201</v>
       </c>
@@ -4170,15 +3561,8 @@
       <c r="C99" t="s">
         <v>203</v>
       </c>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
-      <c r="I99"/>
-      <c r="J99"/>
-    </row>
-    <row r="100">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -4188,15 +3572,8 @@
       <c r="C100" t="s">
         <v>206</v>
       </c>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100"/>
-      <c r="H100"/>
-      <c r="I100"/>
-      <c r="J100"/>
-    </row>
-    <row r="101">
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -4206,15 +3583,8 @@
       <c r="C101" t="s">
         <v>209</v>
       </c>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-      <c r="I101"/>
-      <c r="J101"/>
-    </row>
-    <row r="102">
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>207</v>
       </c>
@@ -4224,15 +3594,8 @@
       <c r="C102" t="s">
         <v>209</v>
       </c>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-    </row>
-    <row r="103">
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -4242,15 +3605,8 @@
       <c r="C103" t="s">
         <v>212</v>
       </c>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
-      <c r="I103"/>
-      <c r="J103"/>
-    </row>
-    <row r="104">
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -4260,15 +3616,8 @@
       <c r="C104" t="s">
         <v>215</v>
       </c>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
-      <c r="I104"/>
-      <c r="J104"/>
-    </row>
-    <row r="105">
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -4278,15 +3627,8 @@
       <c r="C105" t="s">
         <v>218</v>
       </c>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
-      <c r="I105"/>
-      <c r="J105"/>
-    </row>
-    <row r="106">
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>219</v>
       </c>
@@ -4296,15 +3638,8 @@
       <c r="C106" t="s">
         <v>221</v>
       </c>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-      <c r="I106"/>
-      <c r="J106"/>
-    </row>
-    <row r="107">
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -4314,15 +3649,8 @@
       <c r="C107" t="s">
         <v>221</v>
       </c>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
-      <c r="I107"/>
-      <c r="J107"/>
-    </row>
-    <row r="108">
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>219</v>
       </c>
@@ -4332,15 +3660,8 @@
       <c r="C108" t="s">
         <v>221</v>
       </c>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-      <c r="I108"/>
-      <c r="J108"/>
-    </row>
-    <row r="109">
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>219</v>
       </c>
@@ -4350,15 +3671,8 @@
       <c r="C109" t="s">
         <v>221</v>
       </c>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
-      <c r="I109"/>
-      <c r="J109"/>
-    </row>
-    <row r="110">
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>222</v>
       </c>
@@ -4368,15 +3682,8 @@
       <c r="C110" t="s">
         <v>224</v>
       </c>
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110"/>
-      <c r="G110"/>
-      <c r="H110"/>
-      <c r="I110"/>
-      <c r="J110"/>
-    </row>
-    <row r="111">
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>225</v>
       </c>
@@ -4386,15 +3693,8 @@
       <c r="C111" t="s">
         <v>227</v>
       </c>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-      <c r="J111"/>
-    </row>
-    <row r="112">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>228</v>
       </c>
@@ -4404,15 +3704,8 @@
       <c r="C112" t="s">
         <v>230</v>
       </c>
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
-      <c r="G112"/>
-      <c r="H112"/>
-      <c r="I112"/>
-      <c r="J112"/>
-    </row>
-    <row r="113">
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -4422,15 +3715,8 @@
       <c r="C113" t="s">
         <v>233</v>
       </c>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
-      <c r="I113"/>
-      <c r="J113"/>
-    </row>
-    <row r="114">
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>234</v>
       </c>
@@ -4440,15 +3726,8 @@
       <c r="C114" t="s">
         <v>236</v>
       </c>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
-      <c r="I114"/>
-      <c r="J114"/>
-    </row>
-    <row r="115">
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>237</v>
       </c>
@@ -4458,15 +3737,8 @@
       <c r="C115" t="s">
         <v>239</v>
       </c>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
-      <c r="G115"/>
-      <c r="H115"/>
-      <c r="I115"/>
-      <c r="J115"/>
-    </row>
-    <row r="116">
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>240</v>
       </c>
@@ -4476,15 +3748,8 @@
       <c r="C116" t="s">
         <v>242</v>
       </c>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
-      <c r="G116"/>
-      <c r="H116"/>
-      <c r="I116"/>
-      <c r="J116"/>
-    </row>
-    <row r="117">
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>243</v>
       </c>
@@ -4494,15 +3759,8 @@
       <c r="C117" t="s">
         <v>245</v>
       </c>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
-      <c r="G117"/>
-      <c r="H117"/>
-      <c r="I117"/>
-      <c r="J117"/>
-    </row>
-    <row r="118">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>246</v>
       </c>
@@ -4512,15 +3770,8 @@
       <c r="C118" t="s">
         <v>248</v>
       </c>
-      <c r="D118"/>
-      <c r="E118"/>
-      <c r="F118"/>
-      <c r="G118"/>
-      <c r="H118"/>
-      <c r="I118"/>
-      <c r="J118"/>
-    </row>
-    <row r="119">
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>249</v>
       </c>
@@ -4530,15 +3781,8 @@
       <c r="C119" t="s">
         <v>251</v>
       </c>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
-      <c r="G119"/>
-      <c r="H119"/>
-      <c r="I119"/>
-      <c r="J119"/>
-    </row>
-    <row r="120">
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>252</v>
       </c>
@@ -4548,15 +3792,8 @@
       <c r="C120" t="s">
         <v>254</v>
       </c>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120"/>
-      <c r="H120"/>
-      <c r="I120"/>
-      <c r="J120"/>
-    </row>
-    <row r="121">
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>255</v>
       </c>
@@ -4566,15 +3803,8 @@
       <c r="C121" t="s">
         <v>257</v>
       </c>
-      <c r="D121"/>
-      <c r="E121"/>
-      <c r="F121"/>
-      <c r="G121"/>
-      <c r="H121"/>
-      <c r="I121"/>
-      <c r="J121"/>
-    </row>
-    <row r="122">
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>258</v>
       </c>
@@ -4584,15 +3814,8 @@
       <c r="C122" t="s">
         <v>260</v>
       </c>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
-      <c r="G122"/>
-      <c r="H122"/>
-      <c r="I122"/>
-      <c r="J122"/>
-    </row>
-    <row r="123">
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>261</v>
       </c>
@@ -4602,15 +3825,8 @@
       <c r="C123" t="s">
         <v>263</v>
       </c>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-      <c r="I123"/>
-      <c r="J123"/>
-    </row>
-    <row r="124">
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>264</v>
       </c>
@@ -4620,15 +3836,8 @@
       <c r="C124" t="s">
         <v>266</v>
       </c>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
-      <c r="G124"/>
-      <c r="H124"/>
-      <c r="I124"/>
-      <c r="J124"/>
-    </row>
-    <row r="125">
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -4638,15 +3847,8 @@
       <c r="C125" t="s">
         <v>269</v>
       </c>
-      <c r="D125"/>
-      <c r="E125"/>
-      <c r="F125"/>
-      <c r="G125"/>
-      <c r="H125"/>
-      <c r="I125"/>
-      <c r="J125"/>
-    </row>
-    <row r="126">
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>270</v>
       </c>
@@ -4656,15 +3858,8 @@
       <c r="C126" t="s">
         <v>272</v>
       </c>
-      <c r="D126"/>
-      <c r="E126"/>
-      <c r="F126"/>
-      <c r="G126"/>
-      <c r="H126"/>
-      <c r="I126"/>
-      <c r="J126"/>
-    </row>
-    <row r="127">
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -4674,15 +3869,8 @@
       <c r="C127" t="s">
         <v>275</v>
       </c>
-      <c r="D127"/>
-      <c r="E127"/>
-      <c r="F127"/>
-      <c r="G127"/>
-      <c r="H127"/>
-      <c r="I127"/>
-      <c r="J127"/>
-    </row>
-    <row r="128">
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>276</v>
       </c>
@@ -4692,15 +3880,8 @@
       <c r="C128" t="s">
         <v>278</v>
       </c>
-      <c r="D128"/>
-      <c r="E128"/>
-      <c r="F128"/>
-      <c r="G128"/>
-      <c r="H128"/>
-      <c r="I128"/>
-      <c r="J128"/>
-    </row>
-    <row r="129">
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>279</v>
       </c>
@@ -4710,15 +3891,8 @@
       <c r="C129" t="s">
         <v>281</v>
       </c>
-      <c r="D129"/>
-      <c r="E129"/>
-      <c r="F129"/>
-      <c r="G129"/>
-      <c r="H129"/>
-      <c r="I129"/>
-      <c r="J129"/>
-    </row>
-    <row r="130">
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>282</v>
       </c>
@@ -4728,15 +3902,8 @@
       <c r="C130" t="s">
         <v>284</v>
       </c>
-      <c r="D130"/>
-      <c r="E130"/>
-      <c r="F130"/>
-      <c r="G130"/>
-      <c r="H130"/>
-      <c r="I130"/>
-      <c r="J130"/>
-    </row>
-    <row r="131">
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>285</v>
       </c>
@@ -4746,15 +3913,8 @@
       <c r="C131" t="s">
         <v>287</v>
       </c>
-      <c r="D131"/>
-      <c r="E131"/>
-      <c r="F131"/>
-      <c r="G131"/>
-      <c r="H131"/>
-      <c r="I131"/>
-      <c r="J131"/>
-    </row>
-    <row r="132">
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>288</v>
       </c>
@@ -4764,15 +3924,8 @@
       <c r="C132" t="s">
         <v>290</v>
       </c>
-      <c r="D132"/>
-      <c r="E132"/>
-      <c r="F132"/>
-      <c r="G132"/>
-      <c r="H132"/>
-      <c r="I132"/>
-      <c r="J132"/>
-    </row>
-    <row r="133">
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>291</v>
       </c>
@@ -4782,15 +3935,8 @@
       <c r="C133" t="s">
         <v>293</v>
       </c>
-      <c r="D133"/>
-      <c r="E133"/>
-      <c r="F133"/>
-      <c r="G133"/>
-      <c r="H133"/>
-      <c r="I133"/>
-      <c r="J133"/>
-    </row>
-    <row r="134">
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>294</v>
       </c>
@@ -4800,15 +3946,8 @@
       <c r="C134" t="s">
         <v>296</v>
       </c>
-      <c r="D134"/>
-      <c r="E134"/>
-      <c r="F134"/>
-      <c r="G134"/>
-      <c r="H134"/>
-      <c r="I134"/>
-      <c r="J134"/>
-    </row>
-    <row r="135">
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>297</v>
       </c>
@@ -4818,15 +3957,8 @@
       <c r="C135" t="s">
         <v>299</v>
       </c>
-      <c r="D135"/>
-      <c r="E135"/>
-      <c r="F135"/>
-      <c r="G135"/>
-      <c r="H135"/>
-      <c r="I135"/>
-      <c r="J135"/>
-    </row>
-    <row r="136">
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>300</v>
       </c>
@@ -4836,15 +3968,8 @@
       <c r="C136" t="s">
         <v>302</v>
       </c>
-      <c r="D136"/>
-      <c r="E136"/>
-      <c r="F136"/>
-      <c r="G136"/>
-      <c r="H136"/>
-      <c r="I136"/>
-      <c r="J136"/>
-    </row>
-    <row r="137">
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>303</v>
       </c>
@@ -4854,15 +3979,8 @@
       <c r="C137" t="s">
         <v>305</v>
       </c>
-      <c r="D137"/>
-      <c r="E137"/>
-      <c r="F137"/>
-      <c r="G137"/>
-      <c r="H137"/>
-      <c r="I137"/>
-      <c r="J137"/>
-    </row>
-    <row r="138">
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>306</v>
       </c>
@@ -4872,15 +3990,8 @@
       <c r="C138" t="s">
         <v>308</v>
       </c>
-      <c r="D138"/>
-      <c r="E138"/>
-      <c r="F138"/>
-      <c r="G138"/>
-      <c r="H138"/>
-      <c r="I138"/>
-      <c r="J138"/>
-    </row>
-    <row r="139">
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>309</v>
       </c>
@@ -4890,15 +4001,8 @@
       <c r="C139" t="s">
         <v>311</v>
       </c>
-      <c r="D139"/>
-      <c r="E139"/>
-      <c r="F139"/>
-      <c r="G139"/>
-      <c r="H139"/>
-      <c r="I139"/>
-      <c r="J139"/>
-    </row>
-    <row r="140">
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>312</v>
       </c>
@@ -4908,15 +4012,8 @@
       <c r="C140" t="s">
         <v>314</v>
       </c>
-      <c r="D140"/>
-      <c r="E140"/>
-      <c r="F140"/>
-      <c r="G140"/>
-      <c r="H140"/>
-      <c r="I140"/>
-      <c r="J140"/>
-    </row>
-    <row r="141">
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>315</v>
       </c>
@@ -4926,15 +4023,8 @@
       <c r="C141" t="s">
         <v>317</v>
       </c>
-      <c r="D141"/>
-      <c r="E141"/>
-      <c r="F141"/>
-      <c r="G141"/>
-      <c r="H141"/>
-      <c r="I141"/>
-      <c r="J141"/>
-    </row>
-    <row r="142">
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>318</v>
       </c>
@@ -4944,15 +4034,8 @@
       <c r="C142" t="s">
         <v>320</v>
       </c>
-      <c r="D142"/>
-      <c r="E142"/>
-      <c r="F142"/>
-      <c r="G142"/>
-      <c r="H142"/>
-      <c r="I142"/>
-      <c r="J142"/>
-    </row>
-    <row r="143">
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>321</v>
       </c>
@@ -4962,15 +4045,8 @@
       <c r="C143" t="s">
         <v>323</v>
       </c>
-      <c r="D143"/>
-      <c r="E143"/>
-      <c r="F143"/>
-      <c r="G143"/>
-      <c r="H143"/>
-      <c r="I143"/>
-      <c r="J143"/>
-    </row>
-    <row r="144">
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>324</v>
       </c>
@@ -4980,15 +4056,8 @@
       <c r="C144" t="s">
         <v>326</v>
       </c>
-      <c r="D144"/>
-      <c r="E144"/>
-      <c r="F144"/>
-      <c r="G144"/>
-      <c r="H144"/>
-      <c r="I144"/>
-      <c r="J144"/>
-    </row>
-    <row r="145">
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>327</v>
       </c>
@@ -4998,15 +4067,8 @@
       <c r="C145" t="s">
         <v>329</v>
       </c>
-      <c r="D145"/>
-      <c r="E145"/>
-      <c r="F145"/>
-      <c r="G145"/>
-      <c r="H145"/>
-      <c r="I145"/>
-      <c r="J145"/>
-    </row>
-    <row r="146">
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -5016,15 +4078,8 @@
       <c r="C146" t="s">
         <v>332</v>
       </c>
-      <c r="D146"/>
-      <c r="E146"/>
-      <c r="F146"/>
-      <c r="G146"/>
-      <c r="H146"/>
-      <c r="I146"/>
-      <c r="J146"/>
-    </row>
-    <row r="147">
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>333</v>
       </c>
@@ -5034,15 +4089,8 @@
       <c r="C147" t="s">
         <v>335</v>
       </c>
-      <c r="D147"/>
-      <c r="E147"/>
-      <c r="F147"/>
-      <c r="G147"/>
-      <c r="H147"/>
-      <c r="I147"/>
-      <c r="J147"/>
-    </row>
-    <row r="148">
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>336</v>
       </c>
@@ -5052,15 +4100,8 @@
       <c r="C148" t="s">
         <v>338</v>
       </c>
-      <c r="D148"/>
-      <c r="E148"/>
-      <c r="F148"/>
-      <c r="G148"/>
-      <c r="H148"/>
-      <c r="I148"/>
-      <c r="J148"/>
-    </row>
-    <row r="149">
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>339</v>
       </c>
@@ -5070,15 +4111,8 @@
       <c r="C149" t="s">
         <v>341</v>
       </c>
-      <c r="D149"/>
-      <c r="E149"/>
-      <c r="F149"/>
-      <c r="G149"/>
-      <c r="H149"/>
-      <c r="I149"/>
-      <c r="J149"/>
-    </row>
-    <row r="150">
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>342</v>
       </c>
@@ -5088,15 +4122,8 @@
       <c r="C150" t="s">
         <v>344</v>
       </c>
-      <c r="D150"/>
-      <c r="E150"/>
-      <c r="F150"/>
-      <c r="G150"/>
-      <c r="H150"/>
-      <c r="I150"/>
-      <c r="J150"/>
-    </row>
-    <row r="151">
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>345</v>
       </c>
@@ -5106,15 +4133,8 @@
       <c r="C151" t="s">
         <v>347</v>
       </c>
-      <c r="D151"/>
-      <c r="E151"/>
-      <c r="F151"/>
-      <c r="G151"/>
-      <c r="H151"/>
-      <c r="I151"/>
-      <c r="J151"/>
-    </row>
-    <row r="152">
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>348</v>
       </c>
@@ -5124,15 +4144,8 @@
       <c r="C152" t="s">
         <v>350</v>
       </c>
-      <c r="D152"/>
-      <c r="E152"/>
-      <c r="F152"/>
-      <c r="G152"/>
-      <c r="H152"/>
-      <c r="I152"/>
-      <c r="J152"/>
-    </row>
-    <row r="153">
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>351</v>
       </c>
@@ -5142,15 +4155,8 @@
       <c r="C153" t="s">
         <v>353</v>
       </c>
-      <c r="D153"/>
-      <c r="E153"/>
-      <c r="F153"/>
-      <c r="G153"/>
-      <c r="H153"/>
-      <c r="I153"/>
-      <c r="J153"/>
-    </row>
-    <row r="154">
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>354</v>
       </c>
@@ -5160,15 +4166,8 @@
       <c r="C154" t="s">
         <v>356</v>
       </c>
-      <c r="D154"/>
-      <c r="E154"/>
-      <c r="F154"/>
-      <c r="G154"/>
-      <c r="H154"/>
-      <c r="I154"/>
-      <c r="J154"/>
-    </row>
-    <row r="155">
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>357</v>
       </c>
@@ -5178,15 +4177,8 @@
       <c r="C155" t="s">
         <v>359</v>
       </c>
-      <c r="D155"/>
-      <c r="E155"/>
-      <c r="F155"/>
-      <c r="G155"/>
-      <c r="H155"/>
-      <c r="I155"/>
-      <c r="J155"/>
-    </row>
-    <row r="156">
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>360</v>
       </c>
@@ -5196,15 +4188,8 @@
       <c r="C156" t="s">
         <v>362</v>
       </c>
-      <c r="D156"/>
-      <c r="E156"/>
-      <c r="F156"/>
-      <c r="G156"/>
-      <c r="H156"/>
-      <c r="I156"/>
-      <c r="J156"/>
-    </row>
-    <row r="157">
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>363</v>
       </c>
@@ -5214,15 +4199,8 @@
       <c r="C157" t="s">
         <v>365</v>
       </c>
-      <c r="D157"/>
-      <c r="E157"/>
-      <c r="F157"/>
-      <c r="G157"/>
-      <c r="H157"/>
-      <c r="I157"/>
-      <c r="J157"/>
-    </row>
-    <row r="158">
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>366</v>
       </c>
@@ -5232,15 +4210,8 @@
       <c r="C158" t="s">
         <v>368</v>
       </c>
-      <c r="D158"/>
-      <c r="E158"/>
-      <c r="F158"/>
-      <c r="G158"/>
-      <c r="H158"/>
-      <c r="I158"/>
-      <c r="J158"/>
-    </row>
-    <row r="159">
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>369</v>
       </c>
@@ -5250,15 +4221,8 @@
       <c r="C159" t="s">
         <v>371</v>
       </c>
-      <c r="D159"/>
-      <c r="E159"/>
-      <c r="F159"/>
-      <c r="G159"/>
-      <c r="H159"/>
-      <c r="I159"/>
-      <c r="J159"/>
-    </row>
-    <row r="160">
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>372</v>
       </c>
@@ -5268,15 +4232,8 @@
       <c r="C160" t="s">
         <v>374</v>
       </c>
-      <c r="D160"/>
-      <c r="E160"/>
-      <c r="F160"/>
-      <c r="G160"/>
-      <c r="H160"/>
-      <c r="I160"/>
-      <c r="J160"/>
-    </row>
-    <row r="161">
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>375</v>
       </c>
@@ -5286,15 +4243,8 @@
       <c r="C161" t="s">
         <v>377</v>
       </c>
-      <c r="D161"/>
-      <c r="E161"/>
-      <c r="F161"/>
-      <c r="G161"/>
-      <c r="H161"/>
-      <c r="I161"/>
-      <c r="J161"/>
-    </row>
-    <row r="162">
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>378</v>
       </c>
@@ -5304,15 +4254,8 @@
       <c r="C162" t="s">
         <v>380</v>
       </c>
-      <c r="D162"/>
-      <c r="E162"/>
-      <c r="F162"/>
-      <c r="G162"/>
-      <c r="H162"/>
-      <c r="I162"/>
-      <c r="J162"/>
-    </row>
-    <row r="163">
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>381</v>
       </c>
@@ -5322,15 +4265,8 @@
       <c r="C163" t="s">
         <v>383</v>
       </c>
-      <c r="D163"/>
-      <c r="E163"/>
-      <c r="F163"/>
-      <c r="G163"/>
-      <c r="H163"/>
-      <c r="I163"/>
-      <c r="J163"/>
-    </row>
-    <row r="164">
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>384</v>
       </c>
@@ -5340,15 +4276,8 @@
       <c r="C164" t="s">
         <v>386</v>
       </c>
-      <c r="D164"/>
-      <c r="E164"/>
-      <c r="F164"/>
-      <c r="G164"/>
-      <c r="H164"/>
-      <c r="I164"/>
-      <c r="J164"/>
-    </row>
-    <row r="165">
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>387</v>
       </c>
@@ -5358,15 +4287,8 @@
       <c r="C165" t="s">
         <v>389</v>
       </c>
-      <c r="D165"/>
-      <c r="E165"/>
-      <c r="F165"/>
-      <c r="G165"/>
-      <c r="H165"/>
-      <c r="I165"/>
-      <c r="J165"/>
-    </row>
-    <row r="166">
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>390</v>
       </c>
@@ -5376,15 +4298,8 @@
       <c r="C166" t="s">
         <v>392</v>
       </c>
-      <c r="D166"/>
-      <c r="E166"/>
-      <c r="F166"/>
-      <c r="G166"/>
-      <c r="H166"/>
-      <c r="I166"/>
-      <c r="J166"/>
-    </row>
-    <row r="167">
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -5394,16 +4309,64 @@
       <c r="C167" t="s">
         <v>395</v>
       </c>
-      <c r="D167"/>
-      <c r="E167"/>
-      <c r="F167"/>
-      <c r="G167"/>
-      <c r="H167"/>
-      <c r="I167"/>
-      <c r="J167"/>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>398</v>
+      </c>
+      <c r="B168" t="s">
+        <v>397</v>
+      </c>
+      <c r="C168" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>400</v>
+      </c>
+      <c r="B169" t="s">
+        <v>399</v>
+      </c>
+      <c r="C169" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>402</v>
+      </c>
+      <c r="B170" t="s">
+        <v>405</v>
+      </c>
+      <c r="C170" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>404</v>
+      </c>
+      <c r="B171" t="s">
+        <v>406</v>
+      </c>
+      <c r="C171" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>408</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C172" t="s">
+        <v>410</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/cache/manual_references.xlsx
+++ b/cache/manual_references.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaswallrich/Documents/Coding/fred_data/cache/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6E7DCD-5A4C-2842-A269-70C2D32B63A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E369A472-9054-DD42-8CD9-9B199C2E7B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-34440" yWindow="720" windowWidth="27880" windowHeight="15160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="459">
   <si>
     <t>key</t>
   </si>
@@ -2275,6 +2275,15 @@
   address = {Helsinki, Finland},
   url     = {http://hdl.handle.net/10138/576172}
 }</t>
+  </si>
+  <si>
+    <t>http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking. (2011, September 15). Retrieved September 23, 2017 from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>@misc{pashler2011elderly, author = {Pashler, H. and Harris, C. and Coburn, N.}, title = {Elderly-Related Words Prime Slow Walking}, year = {2011}, month = {September 15}, howpublished = {\url{http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D}}, note = {Retrieved September 23, 2017} }</t>
   </si>
 </sst>
 </file>
@@ -2330,7 +2339,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2635,7 +2644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -4754,6 +4763,17 @@
         <v>455</v>
       </c>
     </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>456</v>
+      </c>
+      <c r="B183" t="s">
+        <v>457</v>
+      </c>
+      <c r="C183" t="s">
+        <v>458</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/cache/manual_references.xlsx
+++ b/cache/manual_references.xlsx
@@ -1,56 +1,64 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaswallrich/Documents/Coding/fred_data/cache/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6E3F6D-7EC2-7049-BA71-B917D2255443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0" calcCompleted="0" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="469">
-  <si>
-    <t xml:space="preserve">key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference_apa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reference_bibtex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">issue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1177/2f10986111211035002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lum, C., Koper, C. S., &amp; Wu, X. (2021). Can we really defund the police? A nine-agency study of police response to calls for service. Police Quarterly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{Lum_2021,
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="474">
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>reference_apa</t>
+  </si>
+  <si>
+    <t>reference_bibtex</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>journal</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>issue</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>10.1177/2f10986111211035002</t>
+  </si>
+  <si>
+    <t>Lum, C., Koper, C. S., &amp; Wu, X. (2021). Can we really defund the police? A nine-agency study of police response to calls for service. Police Quarterly.</t>
+  </si>
+  <si>
+    <t>@article{Lum_2021,
   title={Can We Really Defund the Police? A Nine-Agency Study of Police Response to Calls for Service},
   author={Lum, Cynthia and Koper, Christopher S. and Wu, Xiaoyun},
   journal={Police Quarterly},
@@ -65,13 +73,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katla, J. (2024). Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA). https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{katla2024replication,
+    <t>https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>Katla, J. (2024). Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA). https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>@mastersthesis{katla2024replication,
   title={Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Katla, J.},
   year={2024},
@@ -80,13 +88,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://drive.google.com/file/d/1DDCuEgQah24QordxkRGO0EIt6Q681jyL/view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee, F. (2013). Replication of “With a clean conscience: Cleanliness reduces the severity of moral judgments” by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@unpublished{lee2013replication,
+    <t>https://drive.google.com/file/d/1DDCuEgQah24QordxkRGO0EIt6Q681jyL/view</t>
+  </si>
+  <si>
+    <t>Lee, F. (2013). Replication of “With a clean conscience: Cleanliness reduces the severity of moral judgments” by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
+  </si>
+  <si>
+    <t>@unpublished{lee2013replication,
   title={Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science)},
   author={Lee, F.},
   year={2013},
@@ -95,13 +103,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.jasnh.com/a14.htm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{murtagh_todd_2004,
+    <t>https://www.jasnh.com/a14.htm</t>
+  </si>
+  <si>
+    <t>Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51.</t>
+  </si>
+  <si>
+    <t>@article{murtagh_todd_2004,
   title={Self-regulation: A challenge to the strength model},
   author={Murtagh, Andrew M. and Todd, Sandra A.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -113,13 +121,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://drive.google.com/file/d/1i2aa1erQ9i9knP8Z5bgGiSt6DXX7U7Fa/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking . (2011, September 15). Retrieved from https://web.archive.org/web/20191117063540/http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pashler_harris_coburn_2011,
+    <t>https://drive.google.com/file/d/1i2aa1erQ9i9knP8Z5bgGiSt6DXX7U7Fa/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking . (2011, September 15). Retrieved from https://web.archive.org/web/20191117063540/http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>@misc{pashler_harris_coburn_2011,
   title={Elderly-Related Words Prime Slow Walking},
   author={Pashler, H. and Harris, C. and Coburn, N.},
   year={2011},
@@ -130,13 +138,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.jasnh.com/pdf/Vol6-No2.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6(2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{fayard_bassi_bernstein_roberts_2009,
+    <t>https://www.jasnh.com/pdf/Vol6-No2.pdf</t>
+  </si>
+  <si>
+    <t>Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6(2).</t>
+  </si>
+  <si>
+    <t>@article{fayard_bassi_bernstein_roberts_2009,
   title={Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006)},
   author={Fayard, Jennifer V. and Bassi, Alana K. and Bernstein, Daniel M. and Roberts, Brent W.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -147,13 +155,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Besman, M., Dubensky, C., Dunsmore, L., &amp; Daubman, K. (2013). Cleanliness primes less severe moral judgments. Retrieved from: https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{besman_dubensky_dunsmore_daubman_2013,
+    <t>https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
+  </si>
+  <si>
+    <t>Besman, M., Dubensky, C., Dunsmore, L., &amp; Daubman, K. (2013). Cleanliness primes less severe moral judgments. Retrieved from: https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
+  </si>
+  <si>
+    <t>@misc{besman_dubensky_dunsmore_daubman_2013,
   title={Cleanliness primes less severe moral judgments},
   author={Besman, M. and Dubensky, C. and Dunsmore, L. and Daubman, K.},
   year={2013},
@@ -162,13 +170,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2021, May 4). [97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2021_datacolada_97,
+    <t>https://datacolada.org/97</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2021, May 4). [97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2021_datacolada_97,
   title={[97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure?},
   author={Simmons, J. and Nelson, L. D.},
   year={2021},
@@ -179,13 +187,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_83,
+    <t>https://datacolada.org/83</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_83,
   title={[83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -194,13 +202,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_84,
+    <t>https://datacolada.org/84</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_84,
   title={[84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -209,13 +217,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_90,
+    <t>https://datacolada.org/90</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_90,
   title={[90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -224,13 +232,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/aczvt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brown, B. T., Kleinberg, B., Hicks, G., Bentley, H., Attridge, P. R., Eboigbe, S., … Brown, K. (2023, September 28). Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1). Retrieved from osf.io/aczvt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{brown_kleinberg_hicks_bentley_attridge_eboigbe_devitt_vazquez_beyan_brown_2023,
+    <t>https://osf.io/aczvt</t>
+  </si>
+  <si>
+    <t>Brown, B. T., Kleinberg, B., Hicks, G., Bentley, H., Attridge, P. R., Eboigbe, S., … Brown, K. (2023, September 28). Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1). Retrieved from osf.io/aczvt</t>
+  </si>
+  <si>
+    <t>@misc{brown_kleinberg_hicks_bentley_attridge_eboigbe_devitt_vazquez_beyan_brown_2023,
  title={Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1)},
  url={osf.io/aczvt},
  publisher={OSF},
@@ -240,13 +248,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8nzfm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papenmeier, F., &amp; Rebholz, T. R. (2023, September). Bimodal Flanker: Audio vs. Visual. Retrieved from https://osf.io/8nzfm/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{papenmeier_rebholz_2023,
+    <t>https://osf.io/8nzfm/</t>
+  </si>
+  <si>
+    <t>Papenmeier, F., &amp; Rebholz, T. R. (2023, September). Bimodal Flanker: Audio vs. Visual. Retrieved from https://osf.io/8nzfm/</t>
+  </si>
+  <si>
+    <t>@misc{papenmeier_rebholz_2023,
  title={Bimodal Flanker: Audio vs. Visual},
  url={osf.io/8nzfm},
  publisher={OSF},
@@ -256,13 +264,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_92,
+    <t>https://datacolada.org/92</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_92,
   title={[92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -271,13 +279,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [94] Data Replicada #9: Are Progression Ads More Credible? Data Colada. https://datacolada.org/94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_94,
+    <t>https://datacolada.org/94</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [94] Data Replicada #9: Are Progression Ads More Credible? Data Colada. https://datacolada.org/94</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_94,
   title={[94] Data Replicada #9: Are Progression Ads More Credible?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -286,22 +294,22 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chan, C. H. &amp; Feldman, G. Weinstein (1984): Replication and extension. [Unpublished manuscript]. Retrieved from https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{Chan2020Weinstein, author = {Chan, Chun Him and Feldman, Gilad}, title = {Weinstein (1984): Replication and extension}, year = {2020}, howpublished = {Unpublished manuscript}, url = {https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://datacolada.org/82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2019). [82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2019_datacolada_82,
+    <t>https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
+  </si>
+  <si>
+    <t>Chan, C. H. &amp; Feldman, G. Weinstein (1984): Replication and extension. [Unpublished manuscript]. Retrieved from https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
+  </si>
+  <si>
+    <t>@misc{Chan2020Weinstein, author = {Chan, Chun Him and Feldman, Gilad}, title = {Weinstein (1984): Replication and extension}, year = {2020}, howpublished = {Unpublished manuscript}, url = {https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk} }</t>
+  </si>
+  <si>
+    <t>https://datacolada.org/82</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2019). [82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2019_datacolada_82,
   title={[82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking?},
   author={Simmons, J. and Nelson, L. D.},
   year={2019},
@@ -310,13 +318,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://replications.clearerthinking.org/replication-2022psci33-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transparent Replications by Clearer Thinking. (2024). Report #11: Replication of a study from “Changes in the prevalence of thin bodies bias young women’s judgments about body size” (Psychological Science | Devine et al., 2022) https://replications.clearerthinking.org/replication-2022psci33-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{clearer_thinking_2024_report11,
+    <t>https://replications.clearerthinking.org/replication-2022psci33-8</t>
+  </si>
+  <si>
+    <t>Transparent Replications by Clearer Thinking. (2024). Report #11: Replication of a study from “Changes in the prevalence of thin bodies bias young women’s judgments about body size” (Psychological Science | Devine et al., 2022) https://replications.clearerthinking.org/replication-2022psci33-8</t>
+  </si>
+  <si>
+    <t>@misc{clearer_thinking_2024_report11,
   title={Report #11: Replication of a study from "Changes in the prevalence of thin bodies bias young women's judgments about body size" (Psychological Science | Devine et al., 2022)},
   author={{Transparent Replications by Clearer Thinking}},
   year={2024},
@@ -325,13 +333,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/74892/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavlović, Z. (2023, April 8). First impression replication study (Asch, 1945, Experiment 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pavlović_kaiser_2024,
+    <t>https://osf.io/74892/</t>
+  </si>
+  <si>
+    <t>Pavlović, Z. (2023, April 8). First impression replication study (Asch, 1945, Experiment 1).</t>
+  </si>
+  <si>
+    <t>@misc{pavlović_kaiser_2024,
  title={First impression replication study (Asch, 1945, Experiment 1)},
  url={osf.io/74892},
  publisher={OSF},
@@ -341,13 +349,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ns26x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lau &amp; Feldman, Van Boven and Ashworth (2007): Replication and extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{chin_feldman_2025,
+    <t>https://osf.io/ns26x</t>
+  </si>
+  <si>
+    <t>Lau &amp; Feldman, Van Boven and Ashworth (2007): Replication and extension</t>
+  </si>
+  <si>
+    <t>@misc{chin_feldman_2025,
  title={Revisiting the past-future emotional asymmetry:  Replication and extensions of Van Boven and Ashworth (2007)},
  url={osf.io/gcf3v},
  publisher={OSF},
@@ -357,13 +365,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments? Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_87,
+    <t>https://datacolada.org/87</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments? Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_87,
   title={[87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -372,13 +380,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.tijdschriftdepsycholoog.nl/wp-content/uploads/2015/10/Dijkstra-K.-Verkoeijen-P.-Van-Kuijk-I.-Soke-Yee-Chow-Bakker-A.-Zwaan-R.-2015.-Leidt-het-lezen-van-literaire-fictie-tot-meer-emphatie.-De-Psycholoog-10-10-21..pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijkstra, K., Verkoeijen, P., van Kuijk, I., Yee Chow, S., Bakker, A., &amp; Zwaan, R. (2015). Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013). De Psycholoog, 50(10), 10–21. Retrieved from http://hdl.handle.net/1765/98670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{dijkstra_verkoeijen_vankuijk_yeechow_bakker_zwaan_2015,
+    <t>https://www.tijdschriftdepsycholoog.nl/wp-content/uploads/2015/10/Dijkstra-K.-Verkoeijen-P.-Van-Kuijk-I.-Soke-Yee-Chow-Bakker-A.-Zwaan-R.-2015.-Leidt-het-lezen-van-literaire-fictie-tot-meer-emphatie.-De-Psycholoog-10-10-21..pdf</t>
+  </si>
+  <si>
+    <t>Dijkstra, K., Verkoeijen, P., van Kuijk, I., Yee Chow, S., Bakker, A., &amp; Zwaan, R. (2015). Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013). De Psycholoog, 50(10), 10–21. Retrieved from http://hdl.handle.net/1765/98670</t>
+  </si>
+  <si>
+    <t>@article{dijkstra_verkoeijen_vankuijk_yeechow_bakker_zwaan_2015,
   title={Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013)},
   author={Dijkstra, K. and Verkoeijen, P. and van Kuijk, I. and Yee Chow, S. and Bakker, A. and Zwaan, R.},
   journal={De Psycholoog},
@@ -390,13 +398,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://datacolada.org/89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [89] Data Replicada #6: The Problem of (Weird) Differential Attrition. Data Colada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_89,
+    <t>https://datacolada.org/89</t>
+  </si>
+  <si>
+    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [89] Data Replicada #6: The Problem of (Weird) Differential Attrition. Data Colada.</t>
+  </si>
+  <si>
+    <t>@misc{simmons_nelson_2020_datacolada_89,
   title={[89] Data Replicada #6: The Problem of (Weird) Differential Attrition},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -405,13 +413,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://docs.google.com/document/d/1hW5moEcdB-U0Ud-MNOB5iYSkeQL60SqVekufodODxDQ/edit?tab=t.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hongye, L., &amp; Feldman, G. (2020). Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{hongye_feldman_2020_revisiting,
+    <t>https://docs.google.com/document/d/1hW5moEcdB-U0Ud-MNOB5iYSkeQL60SqVekufodODxDQ/edit?tab=t.0</t>
+  </si>
+  <si>
+    <t>Hongye, L., &amp; Feldman, G. (2020). Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986).</t>
+  </si>
+  <si>
+    <t>@misc{hongye_feldman_2020_revisiting,
   title={Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986)},
   author={Hongye, L. and Feldman, G.},
   year={2020},
@@ -419,19 +427,19 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ht4d5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCORE replication of Nyhan, B., &amp; Reifler, J. (2015). Displacing Misinformation about Events: An Experimental Test of Causal Corrections. Journal of Experimental Political Science, 2(1), 81–93. https://doi.org/10.1017/xps.2014.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/9hjxc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baskin, E., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Hahn, K. (2025, November 18). Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12. Retrieved from osf.io/cwmb5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{baskin_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_2025,
+    <t>https://osf.io/ht4d5</t>
+  </si>
+  <si>
+    <t>SCORE replication of Nyhan, B., &amp; Reifler, J. (2015). Displacing Misinformation about Events: An Experimental Test of Causal Corrections. Journal of Experimental Political Science, 2(1), 81–93. https://doi.org/10.1017/xps.2014.22</t>
+  </si>
+  <si>
+    <t>https://osf.io/9hjxc</t>
+  </si>
+  <si>
+    <t>Baskin, E., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Hahn, K. (2025, November 18). Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12. Retrieved from osf.io/cwmb5</t>
+  </si>
+  <si>
+    <t>@misc{baskin_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_2025,
  title={Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12},
  url={osf.io/cwmb5},
  publisher={OSF},
@@ -441,13 +449,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/36w4c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442. Retrieved from osf.io/23ghe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/36w4c</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442. Retrieved from osf.io/23ghe</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442},
  url={osf.io/23ghe},
  publisher={OSF},
@@ -457,13 +465,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/r58ch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56. Retrieved from osf.io/n35c2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/r58ch</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56. Retrieved from osf.io/n35c2</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56},
  url={osf.io/n35c2},
  publisher={OSF},
@@ -473,13 +481,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ahgfx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2. Retrieved from osf.io/ujg2c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/ahgfx</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2. Retrieved from osf.io/ujg2c</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2},
  url={osf.io/ujg2c},
  publisher={OSF},
@@ -489,13 +497,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/gyse6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2. Retrieved from osf.io/vhu2x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/gyse6</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2. Retrieved from osf.io/vhu2x</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2},
  url={osf.io/vhu2x},
  publisher={OSF},
@@ -505,13 +513,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/kpn34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6. Retrieved from osf.io/5k6jg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/kpn34</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6. Retrieved from osf.io/5k6jg</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6},
  url={osf.io/5k6jg},
  publisher={OSF},
@@ -521,13 +529,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/28mjt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2. Retrieved from osf.io/wjh3c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t>https://osf.io/28mjt</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2. Retrieved from osf.io/wjh3c</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2},
  url={osf.io/wjh3c},
  publisher={OSF},
@@ -537,13 +545,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/x9j47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoon, S., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k. Retrieved from osf.io/e9y6b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{yoon_tyner_loomas_miske_luis_2025,
+    <t>https://osf.io/x9j47</t>
+  </si>
+  <si>
+    <t>Yoon, S., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k. Retrieved from osf.io/e9y6b</t>
+  </si>
+  <si>
+    <t>@misc{yoon_tyner_loomas_miske_luis_2025,
  title={LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k},
  url={osf.io/e9y6b},
  publisher={OSF},
@@ -553,13 +561,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dnqrv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">de Leeuw, J. R., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Ostrowski, R. P. (2025, November 18). Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6. Retrieved from osf.io/ty5be</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{de leeuw_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_bader_et al._2025,
+    <t>https://osf.io/dnqrv</t>
+  </si>
+  <si>
+    <t>de Leeuw, J. R., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Ostrowski, R. P. (2025, November 18). Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6. Retrieved from osf.io/ty5be</t>
+  </si>
+  <si>
+    <t>@misc{de leeuw_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_bader_et al._2025,
  title={Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6},
  url={osf.io/ty5be},
  publisher={OSF},
@@ -569,13 +577,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/3u8x9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16. Retrieved from osf.io/er54t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/3u8x9</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16. Retrieved from osf.io/er54t</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16},
  url={osf.io/er54t},
  publisher={OSF},
@@ -585,13 +593,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/4usmq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6. Retrieved from osf.io/9mx5w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/4usmq</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6. Retrieved from osf.io/9mx5w</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6},
  url={osf.io/9mx5w},
  publisher={OSF},
@@ -601,13 +609,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/3d97y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2. Retrieved from osf.io/rywgh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_hong_duan_reed_2025,
+    <t>https://osf.io/3d97y</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2. Retrieved from osf.io/rywgh</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_hong_duan_reed_2025,
  title={Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2},
  url={osf.io/rywgh},
  publisher={OSF},
@@ -617,13 +625,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/x46bu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6. Retrieved from osf.io/bawh3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/x46bu</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6. Retrieved from osf.io/bawh3</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6},
  url={osf.io/bawh3},
  publisher={OSF},
@@ -633,13 +641,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/n6jca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Bonfiglio, D. B. V. (2025, December 1). Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2. Retrieved from osf.io/vg6zy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_mallik_bonfiglio_2025,
+    <t>https://osf.io/n6jca</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Bonfiglio, D. B. V. (2025, December 1). Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2. Retrieved from osf.io/vg6zy</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_mallik_bonfiglio_2025,
  title={Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2},
  url={osf.io/vg6zy},
  publisher={OSF},
@@ -649,13 +657,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/7qjzp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OYEBANJO, A., Adeyemi, A. F., Loomas, Z., Miske, O., Luis, B., Tyner, A. H., … Parsons, E. S. (2025, November 18). Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81. Retrieved from osf.io/en9md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{oyebanjo_adeyemi_loomas_miske_luis_tyner_kline struhl_parsons_2025,
+    <t>https://osf.io/7qjzp</t>
+  </si>
+  <si>
+    <t>OYEBANJO, A., Adeyemi, A. F., Loomas, Z., Miske, O., Luis, B., Tyner, A. H., … Parsons, E. S. (2025, November 18). Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81. Retrieved from osf.io/en9md</t>
+  </si>
+  <si>
+    <t>@misc{oyebanjo_adeyemi_loomas_miske_luis_tyner_kline struhl_parsons_2025,
  title={Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81},
  url={osf.io/en9md},
  publisher={OSF},
@@ -665,13 +673,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/cdrmk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Mallinson, D. J. (2025, November 18). Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182. Retrieved from osf.io/h7av9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_mallinson_2025,
+    <t>https://osf.io/cdrmk</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Mallinson, D. J. (2025, November 18). Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182. Retrieved from osf.io/h7av9</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_mallinson_2025,
  title={Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182},
  url={osf.io/h7av9},
  publisher={OSF},
@@ -681,13 +689,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/39upt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w. Retrieved from osf.io/bmzuf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t>https://osf.io/39upt</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w. Retrieved from osf.io/bmzuf</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w},
  url={osf.io/bmzuf},
  publisher={OSF},
@@ -697,13 +705,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/nbc6v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Berry, Z. (2025, December 14). Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2. Retrieved from osf.io/tmn3q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_berry_2025,
+    <t>https://osf.io/nbc6v</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Berry, Z. (2025, December 14). Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2. Retrieved from osf.io/tmn3q</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_berry_2025,
  title={Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2},
  url={osf.io/tmn3q},
  publisher={OSF},
@@ -713,13 +721,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/gn3vj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6. Retrieved from osf.io/uwnya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/gn3vj</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6. Retrieved from osf.io/uwnya</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6},
  url={osf.io/uwnya},
  publisher={OSF},
@@ -729,13 +737,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qev3x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Tomašević, A. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6. Retrieved from osf.io/e48gd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_kołczyńska_silverstein_et al._2025,
+    <t>https://osf.io/qev3x</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Tomašević, A. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6. Retrieved from osf.io/e48gd</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_kołczyńska_silverstein_et al._2025,
  title={McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6},
  url={osf.io/e48gd},
  publisher={OSF},
@@ -745,13 +753,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/e9j6y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96. Retrieved from osf.io/qgm2c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/e9j6y</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96. Retrieved from osf.io/qgm2c</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96},
  url={osf.io/qgm2c},
  publisher={OSF},
@@ -761,13 +769,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/srk8q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg. Retrieved from osf.io/xwthk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/srk8q</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg. Retrieved from osf.io/xwthk</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg},
  url={osf.io/xwthk},
  publisher={OSF},
@@ -777,13 +785,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qfh2r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m. Retrieved from osf.io/n7m39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/qfh2r</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m. Retrieved from osf.io/n7m39</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m},
  url={osf.io/n7m39},
  publisher={OSF},
@@ -793,13 +801,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8mqzu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Zhang, Y. (2025, November 18). Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky. Retrieved from osf.io/bcqem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_zhang_2025,
+    <t>https://osf.io/8mqzu</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Zhang, Y. (2025, November 18). Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky. Retrieved from osf.io/bcqem</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_zhang_2025,
  title={Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky},
  url={osf.io/bcqem},
  publisher={OSF},
@@ -809,13 +817,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/syq4e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok. Retrieved from osf.io/gk92w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/syq4e</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok. Retrieved from osf.io/gk92w</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok},
  url={osf.io/gk92w},
  publisher={OSF},
@@ -825,13 +833,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/6rpxu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y. Retrieved from osf.io/tz9ef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/6rpxu</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y. Retrieved from osf.io/tz9ef</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y},
  url={osf.io/tz9ef},
  publisher={OSF},
@@ -841,13 +849,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/u58za</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9. Retrieved from osf.io/qxk38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t>https://osf.io/u58za</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9. Retrieved from osf.io/qxk38</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9},
  url={osf.io/qxk38},
  publisher={OSF},
@@ -857,13 +865,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/b2xma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6. Retrieved from osf.io/shvdk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/b2xma</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6. Retrieved from osf.io/shvdk</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6},
  url={osf.io/shvdk},
  publisher={OSF},
@@ -873,13 +881,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/gvayj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12. Retrieved from osf.io/ub4c6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/gvayj</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12. Retrieved from osf.io/ub4c6</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12},
  url={osf.io/ub4c6},
  publisher={OSF},
@@ -889,13 +897,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ck8aq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2. Retrieved from osf.io/df36m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/ck8aq</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2. Retrieved from osf.io/df36m</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2},
  url={osf.io/df36m},
  publisher={OSF},
@@ -905,13 +913,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/c6a8e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16. Retrieved from osf.io/as7te</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t>https://osf.io/c6a8e</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16. Retrieved from osf.io/as7te</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16},
  url={osf.io/as7te},
  publisher={OSF},
@@ -921,13 +929,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/skwev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7. Retrieved from osf.io/yv2am</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
+    <t>https://osf.io/skwev</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7. Retrieved from osf.io/yv2am</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
  title={Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7},
  url={osf.io/yv2am},
  publisher={OSF},
@@ -937,13 +945,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/yd9bg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Vermeulen, J. (2025, November 18). van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487. Retrieved from osf.io/697dv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_vargo_vermeulen_2025,
+    <t>https://osf.io/yd9bg</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Vermeulen, J. (2025, November 18). van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487. Retrieved from osf.io/697dv</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_vargo_vermeulen_2025,
  title={van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487},
  url={osf.io/697dv},
  publisher={OSF},
@@ -953,13 +961,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/2f35a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chartier, C. R., Lewis, S. C., Kline Struhl, M., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189. Retrieved from osf.io/agv64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{chartier_lewis_kline struhl_miske_luis_loomas_2025,
+    <t>https://osf.io/2f35a</t>
+  </si>
+  <si>
+    <t>Chartier, C. R., Lewis, S. C., Kline Struhl, M., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189. Retrieved from osf.io/agv64</t>
+  </si>
+  <si>
+    <t>@misc{chartier_lewis_kline struhl_miske_luis_loomas_2025,
  title={Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189},
  url={osf.io/agv64},
  publisher={OSF},
@@ -969,13 +977,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/cnbt5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Ramljak, M. (2025, November 18). Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2. Retrieved from osf.io/em34f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_ramljak_2025,
+    <t>https://osf.io/cnbt5</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Ramljak, M. (2025, November 18). Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2. Retrieved from osf.io/em34f</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_ramljak_2025,
  title={Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2},
  url={osf.io/em34f},
  publisher={OSF},
@@ -985,13 +993,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/a6nsp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field, S., Loomas, Z., Miske, O., Luis, B., &amp; Jarke-Neuert, J. (2025, November 18). Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182. Retrieved from osf.io/p9k76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{field_loomas_miske_luis_jarke-neuert_2025,
+    <t>https://osf.io/a6nsp</t>
+  </si>
+  <si>
+    <t>Field, S., Loomas, Z., Miske, O., Luis, B., &amp; Jarke-Neuert, J. (2025, November 18). Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182. Retrieved from osf.io/p9k76</t>
+  </si>
+  <si>
+    <t>@misc{field_loomas_miske_luis_jarke-neuert_2025,
  title={Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182},
  url={osf.io/p9k76},
  publisher={OSF},
@@ -1001,13 +1009,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/5869t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Baník, G. (2025, November 18). BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k. Retrieved from osf.io/8ndcx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_adamkovic_ropovik_baník_2025,
+    <t>https://osf.io/5869t</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Baník, G. (2025, November 18). BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k. Retrieved from osf.io/8ndcx</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_adamkovic_ropovik_baník_2025,
  title={BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k},
  url={osf.io/8ndcx},
  publisher={OSF},
@@ -1017,13 +1025,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xkwj9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molden, D. C. (2025, November 18). Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g. Retrieved from osf.io/w8xun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{molden_2025,
+    <t>https://osf.io/xkwj9</t>
+  </si>
+  <si>
+    <t>Molden, D. C. (2025, November 18). Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g. Retrieved from osf.io/w8xun</t>
+  </si>
+  <si>
+    <t>@misc{molden_2025,
  title={Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g},
  url={osf.io/w8xun},
  publisher={OSF},
@@ -1033,13 +1041,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xyrv6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Gooty, J. (2025, November 18). Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12. Retrieved from osf.io/7k8sy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_sargent_gooty_2025,
+    <t>https://osf.io/xyrv6</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Gooty, J. (2025, November 18). Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12. Retrieved from osf.io/7k8sy</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_sargent_gooty_2025,
  title={Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12},
  url={osf.io/7k8sy},
  publisher={OSF},
@@ -1049,13 +1057,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/phz9x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96. Retrieved from osf.io/q7hpx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
+    <t>https://osf.io/phz9x</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96. Retrieved from osf.io/q7hpx</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
  title={Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96},
  url={osf.io/q7hpx},
  publisher={OSF},
@@ -1065,13 +1073,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/zybuc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1. Retrieved from osf.io/u5d2y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t>https://osf.io/zybuc</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1. Retrieved from osf.io/u5d2y</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1},
  url={osf.io/u5d2y},
  publisher={OSF},
@@ -1081,13 +1089,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dkcu6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7. Retrieved from osf.io/h8ecm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
+    <t>https://osf.io/dkcu6</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7. Retrieved from osf.io/h8ecm</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
  title={Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7},
  url={osf.io/h8ecm},
  publisher={OSF},
@@ -1097,13 +1105,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qmbxr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6. Retrieved from osf.io/p2st5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
+    <t>https://osf.io/qmbxr</t>
+  </si>
+  <si>
+    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6. Retrieved from osf.io/p2st5</t>
+  </si>
+  <si>
+    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
  title={Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6},
  url={osf.io/p2st5},
  publisher={OSF},
@@ -1113,13 +1121,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/udbnf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syed, M., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26. Retrieved from osf.io/f5b6c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{syed_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/udbnf</t>
+  </si>
+  <si>
+    <t>Syed, M., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26. Retrieved from osf.io/f5b6c</t>
+  </si>
+  <si>
+    <t>@misc{syed_fox_loomas_miske_luis_2025,
  title={Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26},
  url={osf.io/f5b6c},
  publisher={OSF},
@@ -1129,13 +1137,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qu793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17. Retrieved from osf.io/8qkrx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
+    <t>https://osf.io/qu793</t>
+  </si>
+  <si>
+    <t>Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17. Retrieved from osf.io/8qkrx</t>
+  </si>
+  <si>
+    <t>@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
  title={Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17},
  url={osf.io/8qkrx},
  publisher={OSF},
@@ -1145,13 +1153,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/5r28d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Kačmár, P. (2025, November 18). Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3. Retrieved from osf.io/h37zx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_kačmár_2025,
+    <t>https://osf.io/5r28d</t>
+  </si>
+  <si>
+    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Kačmár, P. (2025, November 18). Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3. Retrieved from osf.io/h37zx</t>
+  </si>
+  <si>
+    <t>@misc{loomas_miske_luis_fox_tyner_hahn_kačmár_2025,
  title={Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3},
  url={osf.io/h37zx},
  publisher={OSF},
@@ -1161,13 +1169,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dyn6j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edlund, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk. Retrieved from osf.io/9qjhf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{edlund_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/dyn6j</t>
+  </si>
+  <si>
+    <t>Edlund, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk. Retrieved from osf.io/9qjhf</t>
+  </si>
+  <si>
+    <t>@misc{edlund_fox_loomas_miske_luis_2025,
  title={Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk},
  url={osf.io/9qjhf},
  publisher={OSF},
@@ -1177,13 +1185,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8hnxg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liu, A., Fox, N. W., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142. Retrieved from osf.io/nse8t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{liu_fox_tyner_loomas_miske_luis_2025,
+    <t>https://osf.io/8hnxg</t>
+  </si>
+  <si>
+    <t>Liu, A., Fox, N. W., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142. Retrieved from osf.io/nse8t</t>
+  </si>
+  <si>
+    <t>@misc{liu_fox_tyner_loomas_miske_luis_2025,
  title={Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142},
  url={osf.io/nse8t},
  publisher={OSF},
@@ -1193,13 +1201,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/9t4nh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Méndez-Chacón, E., Tutor, M., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496. Retrieved from osf.io/q4fpr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{méndez-chacón_tutor_tyner_abatayo_loomas_miske_luis_2025,
+    <t>https://osf.io/9t4nh</t>
+  </si>
+  <si>
+    <t>Méndez-Chacón, E., Tutor, M., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496. Retrieved from osf.io/q4fpr</t>
+  </si>
+  <si>
+    <t>@misc{méndez-chacón_tutor_tyner_abatayo_loomas_miske_luis_2025,
  title={Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496},
  url={osf.io/q4fpr},
  publisher={OSF},
@@ -1209,13 +1217,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/jx64p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gooty, J., McBride, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Arendt, B. (2025, November 18). Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y. Retrieved from osf.io/sv4e8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{gooty_mcbride_tyner_loomas_miske_luis_arendt_2025,
+    <t>https://osf.io/jx64p</t>
+  </si>
+  <si>
+    <t>Gooty, J., McBride, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Arendt, B. (2025, November 18). Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y. Retrieved from osf.io/sv4e8</t>
+  </si>
+  <si>
+    <t>@misc{gooty_mcbride_tyner_loomas_miske_luis_arendt_2025,
  title={Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y},
  url={osf.io/sv4e8},
  publisher={OSF},
@@ -1225,13 +1233,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/h7jfv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axxe, E., Ramljak, M., Tyner, A. H., Loomas, Z., Luis, B., Miske, O., … Parsons, E. S. (2025, November 18). O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7. Retrieved from osf.io/7qnrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{axxe_ramljak_tyner_loomas_luis_miske_abatayo_parsons_2025,
+    <t>https://osf.io/h7jfv</t>
+  </si>
+  <si>
+    <t>Axxe, E., Ramljak, M., Tyner, A. H., Loomas, Z., Luis, B., Miske, O., … Parsons, E. S. (2025, November 18). O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7. Retrieved from osf.io/7qnrs</t>
+  </si>
+  <si>
+    <t>@misc{axxe_ramljak_tyner_loomas_luis_miske_abatayo_parsons_2025,
  title={O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7},
  url={osf.io/7qnrs},
  publisher={OSF},
@@ -1241,13 +1249,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ab762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554. Retrieved from osf.io/afznv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
+    <t>https://osf.io/ab762</t>
+  </si>
+  <si>
+    <t>Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554. Retrieved from osf.io/afznv</t>
+  </si>
+  <si>
+    <t>@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
  title={Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554},
  url={osf.io/afznv},
  publisher={OSF},
@@ -1257,13 +1265,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/b9rcg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baskin, E., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m. Retrieved from osf.io/sw67c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{baskin_tyner_miske_loomas_2025,
+    <t>https://osf.io/b9rcg</t>
+  </si>
+  <si>
+    <t>Baskin, E., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m. Retrieved from osf.io/sw67c</t>
+  </si>
+  <si>
+    <t>@misc{baskin_tyner_miske_loomas_2025,
  title={Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m},
  url={osf.io/sw67c},
  publisher={OSF},
@@ -1273,13 +1281,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/k79vj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Méndez-Chacón, E., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Abatayo, A. (2025, November 18). Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945. Retrieved from osf.io/tacvb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{méndez-chacón_tyner_loomas_miske_luis_abatayo_2025,
+    <t>https://osf.io/k79vj</t>
+  </si>
+  <si>
+    <t>Méndez-Chacón, E., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Abatayo, A. (2025, November 18). Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945. Retrieved from osf.io/tacvb</t>
+  </si>
+  <si>
+    <t>@misc{méndez-chacón_tyner_loomas_miske_luis_abatayo_2025,
  title={Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945},
  url={osf.io/tacvb},
  publisher={OSF},
@@ -1289,13 +1297,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/vekdm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leahy, K. E., Purol, M., Oh, J., Chopik, W. J., Kline Struhl, M., Miske, O., &amp; Loomas, Z. (2025, November 18). Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67. Retrieved from osf.io/8hp5j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{leahy_purol_oh_chopik_kline struhl_miske_loomas_2025,
+    <t>https://osf.io/vekdm</t>
+  </si>
+  <si>
+    <t>Leahy, K. E., Purol, M., Oh, J., Chopik, W. J., Kline Struhl, M., Miske, O., &amp; Loomas, Z. (2025, November 18). Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67. Retrieved from osf.io/8hp5j</t>
+  </si>
+  <si>
+    <t>@misc{leahy_purol_oh_chopik_kline struhl_miske_loomas_2025,
  title={Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67},
  url={osf.io/8hp5j},
  publisher={OSF},
@@ -1305,13 +1313,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fzut6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baskin, E., Kline Struhl, M., Miske, O., Luis, B., Loomas, Z., &amp; Parsons, E. S. (2025, November 18). Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1. Retrieved from osf.io/e52qx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{baskin_kline struhl_miske_luis_loomas_parsons_2025,
+    <t>https://osf.io/fzut6</t>
+  </si>
+  <si>
+    <t>Baskin, E., Kline Struhl, M., Miske, O., Luis, B., Loomas, Z., &amp; Parsons, E. S. (2025, November 18). Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1. Retrieved from osf.io/e52qx</t>
+  </si>
+  <si>
+    <t>@misc{baskin_kline struhl_miske_luis_loomas_parsons_2025,
  title={Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1},
  url={osf.io/e52qx},
  publisher={OSF},
@@ -1321,13 +1329,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/q4e35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aczel, B., Szaszi, B., Bognar, M., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91. Retrieved from osf.io/2cjuw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{aczel_szaszi_bognar_kline struhl_miske_loomas_luis_2025,
+    <t>https://osf.io/q4e35</t>
+  </si>
+  <si>
+    <t>Aczel, B., Szaszi, B., Bognar, M., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91. Retrieved from osf.io/2cjuw</t>
+  </si>
+  <si>
+    <t>@misc{aczel_szaszi_bognar_kline struhl_miske_loomas_luis_2025,
  title={Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91},
  url={osf.io/2cjuw},
  publisher={OSF},
@@ -1337,13 +1345,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xe3d2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilbiks, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z. Retrieved from osf.io/qtv6j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{wilbiks_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/xe3d2</t>
+  </si>
+  <si>
+    <t>Wilbiks, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z. Retrieved from osf.io/qtv6j</t>
+  </si>
+  <si>
+    <t>@misc{wilbiks_fox_loomas_miske_luis_2025,
  title={Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z},
  url={osf.io/qtv6j},
  publisher={OSF},
@@ -1353,13 +1361,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/2vmgw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m. Retrieved from osf.io/mjfwp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t>https://osf.io/2vmgw</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m. Retrieved from osf.io/mjfwp</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m},
  url={osf.io/mjfwp},
  publisher={OSF},
@@ -1369,13 +1377,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/3cp2d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le Forestier, J. M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., Loomas, Z., &amp; Ray, N. (2025, November 18). Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3. Retrieved from osf.io/tvhma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{le forestier_tyner_miske_luis_parsons_loomas_ray_2025,
+    <t>https://osf.io/3cp2d</t>
+  </si>
+  <si>
+    <t>Le Forestier, J. M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., Loomas, Z., &amp; Ray, N. (2025, November 18). Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3. Retrieved from osf.io/tvhma</t>
+  </si>
+  <si>
+    <t>@misc{le forestier_tyner_miske_luis_parsons_loomas_ray_2025,
  title={Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3},
  url={osf.io/tvhma},
  publisher={OSF},
@@ -1385,13 +1393,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8npm5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allen, P., Dujmović, M., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8. Retrieved from osf.io/834de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{allen_dujmović_kline struhl_loomas_miske_luis_2025,
+    <t>https://osf.io/8npm5</t>
+  </si>
+  <si>
+    <t>Allen, P., Dujmović, M., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8. Retrieved from osf.io/834de</t>
+  </si>
+  <si>
+    <t>@misc{allen_dujmović_kline struhl_loomas_miske_luis_2025,
  title={Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8},
  url={osf.io/834de},
  publisher={OSF},
@@ -1401,13 +1409,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/hmune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szabelska, A., Ghasemi, O., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796. Retrieved from osf.io/su48v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{szabelska_ghasemi_tyner_abatayo_loomas_miske_luis_2025,
+    <t>https://osf.io/hmune</t>
+  </si>
+  <si>
+    <t>Szabelska, A., Ghasemi, O., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796. Retrieved from osf.io/su48v</t>
+  </si>
+  <si>
+    <t>@misc{szabelska_ghasemi_tyner_abatayo_loomas_miske_luis_2025,
  title={Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796},
  url={osf.io/su48v},
  publisher={OSF},
@@ -1417,13 +1425,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/9s4e6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steffens, N. K., Munt, K. A., Peters, K. O., Fox, N. W., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g. Retrieved from osf.io/ty9du</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{steffens_munt_peters_fox_miske_loomas_luis_2025,
+    <t>https://osf.io/9s4e6</t>
+  </si>
+  <si>
+    <t>Steffens, N. K., Munt, K. A., Peters, K. O., Fox, N. W., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g. Retrieved from osf.io/ty9du</t>
+  </si>
+  <si>
+    <t>@misc{steffens_munt_peters_fox_miske_loomas_luis_2025,
  title={Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g},
  url={osf.io/ty9du},
  publisher={OSF},
@@ -1433,13 +1441,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fqdh4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weller, N., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Landgrave, M. G. (2025, November 18). Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m. Retrieved from osf.io/2ug8x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{weller_tyner_loomas_miske_luis_landgrave_2025,
+    <t>https://osf.io/fqdh4</t>
+  </si>
+  <si>
+    <t>Weller, N., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Landgrave, M. G. (2025, November 18). Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m. Retrieved from osf.io/2ug8x</t>
+  </si>
+  <si>
+    <t>@misc{weller_tyner_loomas_miske_luis_landgrave_2025,
  title={Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m},
  url={osf.io/2ug8x},
  publisher={OSF},
@@ -1449,13 +1457,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/tywer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mallik, P. R., Metzger, M., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Final Report. Retrieved from osf.io/4hau3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{mallik_metzger_kline struhl_loomas_miske_2025,
+    <t>https://osf.io/tywer</t>
+  </si>
+  <si>
+    <t>Mallik, P. R., Metzger, M., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Final Report. Retrieved from osf.io/4hau3</t>
+  </si>
+  <si>
+    <t>@misc{mallik_metzger_kline struhl_loomas_miske_2025,
  title={Final Report},
  url={osf.io/4hau3},
  publisher={OSF},
@@ -1465,13 +1473,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/9bkuf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0. Retrieved from osf.io/ndbrp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t>https://osf.io/9bkuf</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0. Retrieved from osf.io/ndbrp</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0},
  url={osf.io/ndbrp},
  publisher={OSF},
@@ -1481,13 +1489,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/rzny2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Abatayo, A., Fiala, N., … Fong, C. Y. M. (2025, November 18). Analysis. Retrieved from osf.io/9v6er</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_abatayo_fiala_volkman_fong_2025,
+    <t>https://osf.io/rzny2</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Abatayo, A., Fiala, N., … Fong, C. Y. M. (2025, November 18). Analysis. Retrieved from osf.io/9v6er</t>
+  </si>
+  <si>
+    <t>@misc{tyner_loomas_miske_luis_abatayo_fiala_volkman_fong_2025,
  title={Analysis},
  url={osf.io/9v6er},
  publisher={OSF},
@@ -1497,13 +1505,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/7efsw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OYEBANJO, A., Ramljak, M., Tyner, A. H., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51. Retrieved from osf.io/zt5y2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{oyebanjo_ramljak_tyner_fox_loomas_miske_luis_2025,
+    <t>https://osf.io/7efsw</t>
+  </si>
+  <si>
+    <t>OYEBANJO, A., Ramljak, M., Tyner, A. H., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51. Retrieved from osf.io/zt5y2</t>
+  </si>
+  <si>
+    <t>@misc{oyebanjo_ramljak_tyner_fox_loomas_miske_luis_2025,
  title={Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51},
  url={osf.io/zt5y2},
  publisher={OSF},
@@ -1513,13 +1521,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fr6g8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vargo, E., Tyner, A. H., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2. Retrieved from osf.io/kvsa6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{vargo_tyner_miske_luis_loomas_2025,
+    <t>https://osf.io/fr6g8</t>
+  </si>
+  <si>
+    <t>Vargo, E., Tyner, A. H., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2. Retrieved from osf.io/kvsa6</t>
+  </si>
+  <si>
+    <t>@misc{vargo_tyner_miske_luis_loomas_2025,
  title={Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2},
  url={osf.io/kvsa6},
  publisher={OSF},
@@ -1529,13 +1537,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/yva89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Luis, B., Harper, S., Nandi, A., &amp; Loomas, Z. (2025, November 18). Analysis. Retrieved from osf.io/b6kfm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_luis_harper_nandi_loomas_2025,
+    <t>https://osf.io/yva89</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Luis, B., Harper, S., Nandi, A., &amp; Loomas, Z. (2025, November 18). Analysis. Retrieved from osf.io/b6kfm</t>
+  </si>
+  <si>
+    <t>@misc{tyner_luis_harper_nandi_loomas_2025,
  title={Analysis},
  url={osf.io/b6kfm},
  publisher={OSF},
@@ -1545,13 +1553,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ftv7q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Held, M. J., Schütz, A., Loomas, Z., Fox, N. W., Luis, B., &amp; Miske, O. (2025, November 18). Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308. Retrieved from osf.io/hd3vf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{held_schütz_loomas_fox_luis_miske_2025,
+    <t>https://osf.io/ftv7q</t>
+  </si>
+  <si>
+    <t>Held, M. J., Schütz, A., Loomas, Z., Fox, N. W., Luis, B., &amp; Miske, O. (2025, November 18). Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308. Retrieved from osf.io/hd3vf</t>
+  </si>
+  <si>
+    <t>@misc{held_schütz_loomas_fox_luis_miske_2025,
  title={Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308},
  url={osf.io/hd3vf},
  publisher={OSF},
@@ -1561,13 +1569,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ceaq3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szabelska, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Parsons, E. S. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7. Retrieved from osf.io/ta5vh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{szabelska_tyner_loomas_miske_luis_parsons_2025,
+    <t>https://osf.io/ceaq3</t>
+  </si>
+  <si>
+    <t>Szabelska, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Parsons, E. S. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7. Retrieved from osf.io/ta5vh</t>
+  </si>
+  <si>
+    <t>@misc{szabelska_tyner_loomas_miske_luis_parsons_2025,
  title={BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7},
  url={osf.io/ta5vh},
  publisher={OSF},
@@ -1577,13 +1585,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/fgdxs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonseca, M., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964. Retrieved from osf.io/t9h6p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{fonseca_tyner_loomas_miske_luis_2025,
+    <t>https://osf.io/fgdxs</t>
+  </si>
+  <si>
+    <t>Fonseca, M., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964. Retrieved from osf.io/t9h6p</t>
+  </si>
+  <si>
+    <t>@misc{fonseca_tyner_loomas_miske_luis_2025,
  title={Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964},
  url={osf.io/t9h6p},
  publisher={OSF},
@@ -1593,13 +1601,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xr32n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cummins, J. (2025, November 18). Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130. Retrieved from osf.io/h24z8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{cummins_2025,
+    <t>https://osf.io/xr32n</t>
+  </si>
+  <si>
+    <t>Cummins, J. (2025, November 18). Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130. Retrieved from osf.io/h24z8</t>
+  </si>
+  <si>
+    <t>@misc{cummins_2025,
  title={Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130},
  url={osf.io/h24z8},
  publisher={OSF},
@@ -1609,13 +1617,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/kw5tv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kołczyńska, M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., &amp; Loomas, Z. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634. Retrieved from osf.io/rpumq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{kołczyńska_tyner_miske_luis_parsons_loomas_2025,
+    <t>https://osf.io/kw5tv</t>
+  </si>
+  <si>
+    <t>Kołczyńska, M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., &amp; Loomas, Z. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634. Retrieved from osf.io/rpumq</t>
+  </si>
+  <si>
+    <t>@misc{kołczyńska_tyner_miske_luis_parsons_loomas_2025,
  title={McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634},
  url={osf.io/rpumq},
  publisher={OSF},
@@ -1625,13 +1633,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/c2hry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hostler, T., Persson, S., &amp; Fox, N. W. (2025, November 18). Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z. Retrieved from osf.io/a8eg9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{hostler_persson_fox_2025,
+    <t>https://osf.io/c2hry</t>
+  </si>
+  <si>
+    <t>Hostler, T., Persson, S., &amp; Fox, N. W. (2025, November 18). Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z. Retrieved from osf.io/a8eg9</t>
+  </si>
+  <si>
+    <t>@misc{hostler_persson_fox_2025,
  title={Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z},
  url={osf.io/a8eg9},
  publisher={OSF},
@@ -1641,13 +1649,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/ybzev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azevedo, F., Micheli, L., Wagner, D., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16. Retrieved from osf.io/8feku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{azevedo_micheli_wagner_tyner_miske_loomas_2025,
+    <t>https://osf.io/ybzev</t>
+  </si>
+  <si>
+    <t>Azevedo, F., Micheli, L., Wagner, D., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16. Retrieved from osf.io/8feku</t>
+  </si>
+  <si>
+    <t>@misc{azevedo_micheli_wagner_tyner_miske_loomas_2025,
  title={Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16},
  url={osf.io/8feku},
  publisher={OSF},
@@ -1657,13 +1665,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/8rwkn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capitán, T., Nast, C., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Mallinson, D. J. (2025, November 18). Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762. Retrieved from osf.io/j8en2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{capitán_nast_tyner_loomas_miske_luis_abatayo_wintermantel_mallinson_2025,
+    <t>https://osf.io/8rwkn</t>
+  </si>
+  <si>
+    <t>Capitán, T., Nast, C., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Mallinson, D. J. (2025, November 18). Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762. Retrieved from osf.io/j8en2</t>
+  </si>
+  <si>
+    <t>@misc{capitán_nast_tyner_loomas_miske_luis_abatayo_wintermantel_mallinson_2025,
  title={Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762},
  url={osf.io/j8en2},
  publisher={OSF},
@@ -1673,13 +1681,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/esw45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyner, A. H., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930. Retrieved from osf.io/g6fkp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{tyner_miske_luis_kline struhl_2025,
+    <t>https://osf.io/esw45</t>
+  </si>
+  <si>
+    <t>Tyner, A. H., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930. Retrieved from osf.io/g6fkp</t>
+  </si>
+  <si>
+    <t>@misc{tyner_miske_luis_kline struhl_2025,
  title={Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930},
  url={osf.io/g6fkp},
  publisher={OSF},
@@ -1689,13 +1697,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/2wfgv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bokhove, C., Nast, C., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., … Bokhove, C. (2025, November 18). Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6. Retrieved from osf.io/u52y3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{bokhove_nast_tyner_abatayo_loomas_miske_luis_bokhove_2025,
+    <t>https://osf.io/2wfgv</t>
+  </si>
+  <si>
+    <t>Bokhove, C., Nast, C., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., … Bokhove, C. (2025, November 18). Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6. Retrieved from osf.io/u52y3</t>
+  </si>
+  <si>
+    <t>@misc{bokhove_nast_tyner_abatayo_loomas_miske_luis_bokhove_2025,
  title={Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6},
  url={osf.io/u52y3},
  publisher={OSF},
@@ -1705,13 +1713,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/hzg3j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Röer, J. P., Fox, N. W., Loomas, Z., Miske, O., Luis, B., Ostermann, T., … Parsons, E. S. (2025, November 18). Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38. Retrieved from osf.io/apv5t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{röer_fox_loomas_miske_luis_ostermann_michalak_parsons_2025,
+    <t>https://osf.io/hzg3j</t>
+  </si>
+  <si>
+    <t>Röer, J. P., Fox, N. W., Loomas, Z., Miske, O., Luis, B., Ostermann, T., … Parsons, E. S. (2025, November 18). Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38. Retrieved from osf.io/apv5t</t>
+  </si>
+  <si>
+    <t>@misc{röer_fox_loomas_miske_luis_ostermann_michalak_parsons_2025,
  title={Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38},
  url={osf.io/apv5t},
  publisher={OSF},
@@ -1721,13 +1729,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/r6ynf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colvin, V., Smith, C., Fox, N. W., Miske, O., &amp; Loomas, Z. (2025, November 18). Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9. Retrieved from osf.io/etfqz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{colvin_smith_fox_miske_loomas_2025,
+    <t>https://osf.io/r6ynf</t>
+  </si>
+  <si>
+    <t>Colvin, V., Smith, C., Fox, N. W., Miske, O., &amp; Loomas, Z. (2025, November 18). Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9. Retrieved from osf.io/etfqz</t>
+  </si>
+  <si>
+    <t>@misc{colvin_smith_fox_miske_loomas_2025,
  title={Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9},
  url={osf.io/etfqz},
  publisher={OSF},
@@ -1737,13 +1745,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/dscfg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slevc, L. R., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02. Retrieved from osf.io/78fvn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{slevc_kline struhl_loomas_miske_2025,
+    <t>https://osf.io/dscfg</t>
+  </si>
+  <si>
+    <t>Slevc, L. R., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02. Retrieved from osf.io/78fvn</t>
+  </si>
+  <si>
+    <t>@misc{slevc_kline struhl_loomas_miske_2025,
  title={Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02},
  url={osf.io/78fvn},
  publisher={OSF},
@@ -1753,13 +1761,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/nuzh2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Coupe, T., Tyner, A. H., Loomas, Z., … Kline Struhl, M. (2025, November 18). Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7. Retrieved from osf.io/62xh4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{reed_duan_hong_coupe_tyner_loomas_miske_luis_vo_kline struhl_2025,
+    <t>https://osf.io/nuzh2</t>
+  </si>
+  <si>
+    <t>Reed, W. R., Duan, J., Hong, S., Coupe, T., Tyner, A. H., Loomas, Z., … Kline Struhl, M. (2025, November 18). Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7. Retrieved from osf.io/62xh4</t>
+  </si>
+  <si>
+    <t>@misc{reed_duan_hong_coupe_tyner_loomas_miske_luis_vo_kline struhl_2025,
  title={Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7},
  url={osf.io/62xh4},
  publisher={OSF},
@@ -1769,13 +1777,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/pex6u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Tyner, A. H., Loomas, Z., Miske, O., … Vo, D. T. H. (2025, November 18). Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz. Retrieved from osf.io/925nz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{reed_duan_hong_tyner_loomas_miske_luis_coupe_vo_2025,
+    <t>https://osf.io/pex6u</t>
+  </si>
+  <si>
+    <t>Reed, W. R., Duan, J., Hong, S., Tyner, A. H., Loomas, Z., Miske, O., … Vo, D. T. H. (2025, November 18). Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz. Retrieved from osf.io/925nz</t>
+  </si>
+  <si>
+    <t>@misc{reed_duan_hong_tyner_loomas_miske_luis_coupe_vo_2025,
  title={Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz},
  url={osf.io/925nz},
  publisher={OSF},
@@ -1785,13 +1793,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/xg6q5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Loomas, Z., Miske, O., Luis, B., … Vo, D. T. H. (2025, November 18). Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz. Retrieved from osf.io/devn8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{reed_duan_hong_loomas_miske_luis_tyner_abatayo_coupe_vo_2025,
+    <t>https://osf.io/xg6q5</t>
+  </si>
+  <si>
+    <t>Reed, W. R., Duan, J., Hong, S., Loomas, Z., Miske, O., Luis, B., … Vo, D. T. H. (2025, November 18). Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz. Retrieved from osf.io/devn8</t>
+  </si>
+  <si>
+    <t>@misc{reed_duan_hong_loomas_miske_luis_tyner_abatayo_coupe_vo_2025,
  title={Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz},
  url={osf.io/devn8},
  publisher={OSF},
@@ -1801,13 +1809,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/qk34m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smalarz, L., Parsons, E. S., &amp; Hahn, K. (2025, November 18). Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707. Retrieved from osf.io/dhg3q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{smalarz_parsons_hahn_2025,
+    <t>https://osf.io/qk34m</t>
+  </si>
+  <si>
+    <t>Smalarz, L., Parsons, E. S., &amp; Hahn, K. (2025, November 18). Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707. Retrieved from osf.io/dhg3q</t>
+  </si>
+  <si>
+    <t>@misc{smalarz_parsons_hahn_2025,
  title={Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707},
  url={osf.io/dhg3q},
  publisher={OSF},
@@ -1817,49 +1825,49 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">osf.io/y2emk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pavlov, Y. G. (2023, June 20). Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4. Retrieved from osf.io/y2emk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pavlov_2023,\n title={Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4},\n url={osf.io/y2emk},\n publisher={OSF},\n author={Pavlov, Yuri G},\n year={2023},\n month={Jun}\n}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">latham_2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latham, O. (2013). Bias at the Beeb? A quantitative study of slant in BBC online reporting. Centre for Policy Studies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@techreport{latham2013bias, author = {Latham, Oliver}, title = {Bias at the Beeb? {A} quantitative study of slant in {BBC} online reporting}, institution = {Centre for Policy Studies}, year = {2013}, type = {Pointmaker}, url = {https://cps.org.uk/research/bias-at-the-beeb-a-quantitative-study-of-slant-in-bbc-online-reporting/} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">djaerv_2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Djärv, K., Zehr, J., &amp; Schwarz, F. (2018). Cognitive vs. emotive factives: An experimental differentiation. Proceedings of Sinn und Bedeutung, 21(1), 367–386.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@inproceedings{djarv2018cognitive, author = {Dj{\"a}rv, Kajsa and Zehr, Jeremy and Schwarz, Florian}, title = {Cognitive vs. emotive factives: {A}n experimental differentiation}, booktitle = {Proceedings of Sinn und Bedeutung}, volume = {21}, number = {1}, pages = {367--386}, year = {2018} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">escholarship.orgucitem39d347bk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chopra, S., Tessler, M. H., &amp; Goodman, N. D. (2019, July). The first crank of the cultural ratchet: Learning and transmitting concepts through language. In Proceedings of the 41st Annual Conference of the Cognitive Science Society (pp. 226–232). Cognitive Science Society.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@inproceedings{chopra2019first, author = {Chopra, Sahil and Tessler, Michael Henry and Goodman, Noah D}, booktitle = {Proceedings of the 41st Annual Meeting of the Cognitive Science Society}, date-added = {2020-09-05 00:50:14 +0000}, date-modified = {2020-09-05 01:32:38 +0000}, pages = {226--232}, title = {The first crank of the cultural ratchet: Learning and transmitting concepts through language}, website = {https://cogsci.mindmodeling.org/2019/papers/0060/0060.pdf}, year = {2019} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">art00005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reuter, K. (2011). Distinguishing the appearance from the reality of pain. Journal of Consciousness Studies, 18(9-10), 94-109.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{reuter2011distinguishing,
+    <t>osf.io/y2emk</t>
+  </si>
+  <si>
+    <t>Pavlov, Y. G. (2023, June 20). Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4. Retrieved from osf.io/y2emk</t>
+  </si>
+  <si>
+    <t>@misc{pavlov_2023,\n title={Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4},\n url={osf.io/y2emk},\n publisher={OSF},\n author={Pavlov, Yuri G},\n year={2023},\n month={Jun}\n}</t>
+  </si>
+  <si>
+    <t>latham_2012</t>
+  </si>
+  <si>
+    <t>Latham, O. (2013). Bias at the Beeb? A quantitative study of slant in BBC online reporting. Centre for Policy Studies.</t>
+  </si>
+  <si>
+    <t>@techreport{latham2013bias, author = {Latham, Oliver}, title = {Bias at the Beeb? {A} quantitative study of slant in {BBC} online reporting}, institution = {Centre for Policy Studies}, year = {2013}, type = {Pointmaker}, url = {https://cps.org.uk/research/bias-at-the-beeb-a-quantitative-study-of-slant-in-bbc-online-reporting/} }</t>
+  </si>
+  <si>
+    <t>djaerv_2018</t>
+  </si>
+  <si>
+    <t>Djärv, K., Zehr, J., &amp; Schwarz, F. (2018). Cognitive vs. emotive factives: An experimental differentiation. Proceedings of Sinn und Bedeutung, 21(1), 367–386.</t>
+  </si>
+  <si>
+    <t>@inproceedings{djarv2018cognitive, author = {Dj{\"a}rv, Kajsa and Zehr, Jeremy and Schwarz, Florian}, title = {Cognitive vs. emotive factives: {A}n experimental differentiation}, booktitle = {Proceedings of Sinn und Bedeutung}, volume = {21}, number = {1}, pages = {367--386}, year = {2018} }</t>
+  </si>
+  <si>
+    <t>escholarship.orgucitem39d347bk</t>
+  </si>
+  <si>
+    <t>Chopra, S., Tessler, M. H., &amp; Goodman, N. D. (2019, July). The first crank of the cultural ratchet: Learning and transmitting concepts through language. In Proceedings of the 41st Annual Conference of the Cognitive Science Society (pp. 226–232). Cognitive Science Society.</t>
+  </si>
+  <si>
+    <t>@inproceedings{chopra2019first, author = {Chopra, Sahil and Tessler, Michael Henry and Goodman, Noah D}, booktitle = {Proceedings of the 41st Annual Meeting of the Cognitive Science Society}, date-added = {2020-09-05 00:50:14 +0000}, date-modified = {2020-09-05 01:32:38 +0000}, pages = {226--232}, title = {The first crank of the cultural ratchet: Learning and transmitting concepts through language}, website = {https://cogsci.mindmodeling.org/2019/papers/0060/0060.pdf}, year = {2019} }</t>
+  </si>
+  <si>
+    <t>art00005</t>
+  </si>
+  <si>
+    <t>Reuter, K. (2011). Distinguishing the appearance from the reality of pain. Journal of Consciousness Studies, 18(9-10), 94-109.</t>
+  </si>
+  <si>
+    <t>@article{reuter2011distinguishing,
   title={Distinguishing the appearance from the reality of pain},
   author={Reuter, K.},
   journal={Journal of Consciousness Studies},
@@ -1870,13 +1878,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">scholars.indianastate.eduetds--2136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilfong, R. (2021). The mattering model: The foundational elements of mattering for K-12 educators (Order No. 28319407) [Doctoral dissertation, Indiana State University]. ProQuest Dissertations &amp; Theses Global. https://www.proquest.com/dissertations-theses/mattering-model-foundational-elements-k-12/docview/2537966312/se-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@phdthesis{wilfong2021mattering,
+    <t>scholars.indianastate.eduetds--2136</t>
+  </si>
+  <si>
+    <t>Wilfong, R. (2021). The mattering model: The foundational elements of mattering for K-12 educators (Order No. 28319407) [Doctoral dissertation, Indiana State University]. ProQuest Dissertations &amp; Theses Global. https://www.proquest.com/dissertations-theses/mattering-model-foundational-elements-k-12/docview/2537966312/se-2</t>
+  </si>
+  <si>
+    <t>@phdthesis{wilfong2021mattering,
   title={The mattering model: The foundational elements of mattering for K-12 educators},
   author={Wilfong, R.},
   year={2021},
@@ -1886,13 +1894,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">thekeep.eiu.edu/theses/4783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burback, S. (2020). Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/4783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{burback2020construct,
+    <t>thekeep.eiu.edu/theses/4783</t>
+  </si>
+  <si>
+    <t>Burback, S. (2020). Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/4783</t>
+  </si>
+  <si>
+    <t>@mastersthesis{burback2020construct,
   title={Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Burback, Shannon},
   year={2020},
@@ -1902,13 +1910,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wiebe_2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiebe, R. P. (2004). Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape. Individual Differences Research, 2, 38-62.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{wiebe2004delinquent,
+    <t>wiebe_2004</t>
+  </si>
+  <si>
+    <t>Wiebe, R. P. (2004). Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape. Individual Differences Research, 2, 38-62.</t>
+  </si>
+  <si>
+    <t>@article{wiebe2004delinquent,
   title={Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape},
   author={Wiebe, R. P.},
   journal={Individual Differences Research},
@@ -1918,13 +1926,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">pashler_2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N. (2011, September 15). Elderly-related words prime slow walking. PsychFileDrawer. Retrieved September 23, 2017, from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pashler_harris_coburn_2011_psychfiledrawer,
+    <t>pashler_2011</t>
+  </si>
+  <si>
+    <t>Pashler, H., Harris, C., &amp; Coburn, N. (2011, September 15). Elderly-related words prime slow walking. PsychFileDrawer. Retrieved September 23, 2017, from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>@misc{pashler_harris_coburn_2011_psychfiledrawer,
   title={Elderly-related words prime slow walking},
   author={Pashler, H. and Harris, C. and Coburn, N.},
   year={2011},
@@ -1935,13 +1943,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">murtagh_2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51. (Study 2).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{murtagh_todd_2004_strength,
+    <t>murtagh_2004</t>
+  </si>
+  <si>
+    <t>Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51. (Study 2).</t>
+  </si>
+  <si>
+    <t>@article{murtagh_todd_2004_strength,
   title={Self-regulation: A challenge to the strength model},
   author={Murtagh, Andrew M. and Todd, Sandra A.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -1953,13 +1961,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">korbmacher_2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Korbmacher, M., Kwan, C. I., &amp; Feldman, G. (2022). Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects. https://hdl.handle.net/11250/2990125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{korbmacher_kwan_feldman_2022_abovebelow,
+    <t>korbmacher_2022</t>
+  </si>
+  <si>
+    <t>Korbmacher, M., Kwan, C. I., &amp; Feldman, G. (2022). Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects. https://hdl.handle.net/11250/2990125</t>
+  </si>
+  <si>
+    <t>@misc{korbmacher_kwan_feldman_2022_abovebelow,
   title={Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects},
   author={Korbmacher, M. and Kwan, C. I. and Feldman, G.},
   year={2022},
@@ -1967,13 +1975,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">ferrell_2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ferrell, J. D., Gosling, S. D., &amp; Donnellan, M. B. (2014). Showering and loneliness: Participants from the University of Texas, Austin. PsychFileDrawer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{ferrell_gosling_donnellan_2014_showering,
+    <t>ferrell_2013</t>
+  </si>
+  <si>
+    <t>Ferrell, J. D., Gosling, S. D., &amp; Donnellan, M. B. (2014). Showering and loneliness: Participants from the University of Texas, Austin. PsychFileDrawer.</t>
+  </si>
+  <si>
+    <t>@misc{ferrell_gosling_donnellan_2014_showering,
   title={Showering and loneliness: Participants from the University of Texas, Austin},
   author={Ferrell, J. D. and Gosling, S. D. and Donnellan, M. B.},
   year={2014},
@@ -1982,13 +1990,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">lee_2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lee, F. (2013). Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@unpublished{lee2013clean,
+    <t>lee_2013</t>
+  </si>
+  <si>
+    <t>Lee, F. (2013). Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
+  </si>
+  <si>
+    <t>@unpublished{lee2013clean,
   title={Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science)},
   author={Lee, F.},
   year={2013},
@@ -1996,13 +2004,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">fayard_2009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6. (Study 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{fayard_bassi_bernstein_roberts_2009_cleanliness,
+    <t>fayard_2009</t>
+  </si>
+  <si>
+    <t>Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6. (Study 1).</t>
+  </si>
+  <si>
+    <t>@article{fayard_bassi_bernstein_roberts_2009_cleanliness,
   title={Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006)},
   author={Fayard, Jennifer V. and Bassi, Alana K. and Bernstein, Daniel M. and Roberts, Brent W.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -2012,13 +2020,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">vonpruski_2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruski, S. M. (2024). The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study (Bachelor's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@thesis{pruski2024impact,
+    <t>vonpruski_2024</t>
+  </si>
+  <si>
+    <t>Pruski, S. M. (2024). The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study (Bachelor's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100459</t>
+  </si>
+  <si>
+    <t>@thesis{pruski2024impact,
   title={The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study},
   author={Pruski, S. M.},
   year={2024},
@@ -2028,13 +2036,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">digitalcommons.memphis.edu--etd--3538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thornton, K. B. (2024). Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T) [Doctoral dissertation, University of Memphis]. Digital Commons @ University of Memphis. https://digitalcommons.memphis.edu/etd/3538/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@phdthesis{thornton2024perceptions,
+    <t>digitalcommons.memphis.edu--etd--3538</t>
+  </si>
+  <si>
+    <t>Thornton, K. B. (2024). Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T) [Doctoral dissertation, University of Memphis]. Digital Commons @ University of Memphis. https://digitalcommons.memphis.edu/etd/3538/</t>
+  </si>
+  <si>
+    <t>@phdthesis{thornton2024perceptions,
   title={Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T)},
   author={Thornton, K. B.},
   year={2024},
@@ -2043,13 +2051,13 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katla, J. (2024). Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{katla2024replication_basc,
+    <t>thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>Katla, J. (2024). Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t>@mastersthesis{katla2024replication_basc,
   title={Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Katla, J.},
   year={2024},
@@ -2058,58 +2066,58 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">https://osf.io/7jy4e/files/u93pc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lacko, D., &amp; Prošek, T. (2025). A comment on Combs et al. (2023) “Reducing political polarization in the United States with a mobile chat platform”. I4R Report.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{lacko2025comment, title={A comment on Combs et al. (2023) "Reducing political polarization in the United States with a mobile chat platform"}, author={Lacko, Daniel and Prošek, Tomáš}, journal={I4R Report}, year={2025}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/7qv89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créchet, J., Cui, J., Sabada, B., &amp; Sawyer, A. (2024). Why don’t firms hire young workers during recessions? A replication of Forsythe (The Economic Journal, 2022). (I4R Discussion Paper Series No. 163)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@techreport{crechet2024youngworkers, title={Why Don't Firms Hire Young Workers During Recessions? A Replication of Forsythe (The Economic Journal, 2022)}, author={Créchet, Jonathan and Cui, Jing and Sabada, Barbara and Sawyer, Antoine}, institution={The Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={163}, keywords={Worker flows; business cycles; life cycle}, url={https://ideas.repec.org/p/zbw/i4rdps/163.html}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/txqjw/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hallman, A., Johannesson, M., &amp; Kujansuu, E. (2024). Robustness Reproducibility of" Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention". (No. 118), I4R Discussion Paper Series.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@techreport{hallman2024robustness, title={Robustness Reproducibility of "Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention"}, author={Hallman, Alice and Johannesson, Magnus and Kujansuu, Essi}, institution={Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={118}, url={https://hdl.handle.net/10419/295247}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/8rb5k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brodeur, A. (2024). Reproduction of  "Who Chooses Commitment? Evidence and Welfare Implications".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{brodeur2024reproduction, author={Brodeur, Abel}, title={Reproduction of "Who Chooses Commitment? Evidence and Welfare Implications"}, year={2024}, month={July}, day={22}, howpublished={OSF}, url={https://osf.io/752q9}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/9erj6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kjelsrud, A., Kotsadam, A., Rogeberg, O., &amp; Brodeur, A. (2025, February 22). A comment on “Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India” by Siddique et al. (2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@book{kjelsrud2025comment, title={A Comment on "Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India" by Siddique et al. (2024)}, author={Kjelsrud, Anders and Kotsadam, Andreas and Rogeberg, Ole and Brodeur, Abel}, year={2025}, publisher={JSTOR}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/82bwv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lewis, M., &amp; Pitts, M. (2023). Replication of Hajcak &amp; Foti (2008, PS, Study 1). OSF. Retrieved from https://osf.io/82bwv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{lewis_pitts_2023,
+    <t>https://osf.io/7jy4e/files/u93pc</t>
+  </si>
+  <si>
+    <t>Lacko, D., &amp; Prošek, T. (2025). A comment on Combs et al. (2023) “Reducing political polarization in the United States with a mobile chat platform”. I4R Report.</t>
+  </si>
+  <si>
+    <t>@article{lacko2025comment, title={A comment on Combs et al. (2023) "Reducing political polarization in the United States with a mobile chat platform"}, author={Lacko, Daniel and Prošek, Tomáš}, journal={I4R Report}, year={2025}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/7qv89</t>
+  </si>
+  <si>
+    <t>Créchet, J., Cui, J., Sabada, B., &amp; Sawyer, A. (2024). Why don’t firms hire young workers during recessions? A replication of Forsythe (The Economic Journal, 2022). (I4R Discussion Paper Series No. 163)</t>
+  </si>
+  <si>
+    <t>@techreport{crechet2024youngworkers, title={Why Don't Firms Hire Young Workers During Recessions? A Replication of Forsythe (The Economic Journal, 2022)}, author={Créchet, Jonathan and Cui, Jing and Sabada, Barbara and Sawyer, Antoine}, institution={The Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={163}, keywords={Worker flows; business cycles; life cycle}, url={https://ideas.repec.org/p/zbw/i4rdps/163.html}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/txqjw/</t>
+  </si>
+  <si>
+    <t>Hallman, A., Johannesson, M., &amp; Kujansuu, E. (2024). Robustness Reproducibility of" Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention". (No. 118), I4R Discussion Paper Series.</t>
+  </si>
+  <si>
+    <t>@techreport{hallman2024robustness, title={Robustness Reproducibility of "Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention"}, author={Hallman, Alice and Johannesson, Magnus and Kujansuu, Essi}, institution={Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={118}, url={https://hdl.handle.net/10419/295247}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/8rb5k</t>
+  </si>
+  <si>
+    <t>Brodeur, A. (2024). Reproduction of  "Who Chooses Commitment? Evidence and Welfare Implications".</t>
+  </si>
+  <si>
+    <t>@misc{brodeur2024reproduction, author={Brodeur, Abel}, title={Reproduction of "Who Chooses Commitment? Evidence and Welfare Implications"}, year={2024}, month={July}, day={22}, howpublished={OSF}, url={https://osf.io/752q9}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/9erj6</t>
+  </si>
+  <si>
+    <t>Kjelsrud, A., Kotsadam, A., Rogeberg, O., &amp; Brodeur, A. (2025, February 22). A comment on “Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India” by Siddique et al. (2024)</t>
+  </si>
+  <si>
+    <t>@book{kjelsrud2025comment, title={A Comment on "Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India" by Siddique et al. (2024)}, author={Kjelsrud, Anders and Kotsadam, Andreas and Rogeberg, Ole and Brodeur, Abel}, year={2025}, publisher={JSTOR}}</t>
+  </si>
+  <si>
+    <t>https://osf.io/82bwv</t>
+  </si>
+  <si>
+    <t>Lewis, M., &amp; Pitts, M. (2023). Replication of Hajcak &amp; Foti (2008, PS, Study 1). OSF. Retrieved from https://osf.io/82bwv</t>
+  </si>
+  <si>
+    <t>@misc{lewis_pitts_2023,
  title={Replication of Hajcak &amp; Foti (2008, PS, Study 1)},
  url={osf.io/73pnd},
  DOI={10.17605/OSF.IO/73PND},
@@ -2120,19 +2128,19 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">Replication of Hajcak &amp; Foti  (2008, PS, Study 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/aaudl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chandler, J. J. (2023). Replication of Janiszewski &amp; Uy (2008, PS, Study 4b). OSF. Retrieved from https://osf.io/aaudl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{chandler_2023,
+    <t>Replication of Hajcak &amp; Foti  (2008, PS, Study 1)</t>
+  </si>
+  <si>
+    <t>OSF</t>
+  </si>
+  <si>
+    <t>https://osf.io/aaudl</t>
+  </si>
+  <si>
+    <t>Chandler, J. J. (2023). Replication of Janiszewski &amp; Uy (2008, PS, Study 4b). OSF. Retrieved from https://osf.io/aaudl</t>
+  </si>
+  <si>
+    <t>@misc{chandler_2023,
  title={Replication of Janiszewski &amp; Uy (2008, PS, Study 4b)},
  url={osf.io/aaudl},
  publisher={OSF},
@@ -2142,16 +2150,16 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">Replication of Janiszewski &amp; Uy  (2008, PS, Study 4b)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://osf.io/nxp9w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer, J. S., Rigney, A. E., &amp; Flagan, T. (2016). Replication of G Tabibnia, AB Satpute, MD Lieberman (2008, PS 19(4)). OSF. Retrieved from https://osf.io/nxp9w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{beer_rigney_flagan_2016,
+    <t>Replication of Janiszewski &amp; Uy  (2008, PS, Study 4b)</t>
+  </si>
+  <si>
+    <t>https://osf.io/nxp9w</t>
+  </si>
+  <si>
+    <t>Beer, J. S., Rigney, A. E., &amp; Flagan, T. (2016). Replication of G Tabibnia, AB Satpute, MD Lieberman (2008, PS 19(4)). OSF. Retrieved from https://osf.io/nxp9w</t>
+  </si>
+  <si>
+    <t>@misc{beer_rigney_flagan_2016,
  title={Replication of G Tabibnia, AB Satpute, MD Lieberman (2008, PS 19(4))},
  url={osf.io/94j6h},
  publisher={OSF},
@@ -2161,103 +2169,103 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">Replication of G Tabibnia, AB Satpute, MD Lieberman  (2008, PS 19 (4))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@article{findlay_santos_2012, title={Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli}, volume={9}, number={2}, journal={Econ Journal Watch}, author={Findlay, David W. and Santos, John M.}, year={2012}, pages={122-140}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Econ Journal Watch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122-140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramsay, G. (2013, September 10). The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed. LSE Impact Blog. Retrieved from https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{ramsay_2013, title={The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed}, author={Ramsay, Gordon}, year={2013}, month={Sep}, day={10}, howpublished={LSE Impact Blog}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSE Impact Blog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://purl.utwente.nl/essays/100571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bischoff, M. (2024). Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study (Master's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{bischoff_2024, title={Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study}, author={Bischoff, Milan}, year={2024}, school={University of Twente}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">University of Twente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arbesfeld, J., Collins, T., Baldwin, D., &amp; Daubman, K. (2014). Clean thoughts lead to less severe moral judgment [Replication of Schnall, Benton, &amp; Harvey, 2008]. PsychFileDrawer.org. Retrieved from https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{arbesfeld_2014, title={Clean thoughts lead to less severe moral judgment}, author={Arbesfeld, Julia and Collins, Tricia and Baldwin, Demetrius and Daubman, Kimberly}, year={2014}, howpublished={PsychFileDrawer.org}, note={Replication of Schnall, Benton, and Harvey (2008)}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean thoughts lead to less severe moral judgment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PsychFileDrawer.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siev, J. (2012). Unpublished replication of Zhong &amp; Liljenquist (2006). Retrieved from https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@unpublished{siev_2012, title={Unpublished replication of Zhong and Liljenquist (2006)}, author={Siev, Jedediah}, year={2012}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unpublished replication of Zhong &amp; Liljenquist (2006)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kontkanen_jaakko_thesis_2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontkanen, J. (2024). Investigating the effect of proficiency level on the acquisition order of morphemes for L2 English learners: A replication of a corpus-based SLA study using Interlanguage Annotation [Master’s thesis, University of Helsinki]. Retrieved from http://hdl.handle.net/10138/576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@mastersthesis{kontkanen2024investigating,
+    <t>Replication of G Tabibnia, AB Satpute, MD Lieberman  (2008, PS 19 (4))</t>
+  </si>
+  <si>
+    <t>https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
+  </si>
+  <si>
+    <t>Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
+  </si>
+  <si>
+    <t>@article{findlay_santos_2012, title={Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli}, volume={9}, number={2}, journal={Econ Journal Watch}, author={Findlay, David W. and Santos, John M.}, year={2012}, pages={122-140}}</t>
+  </si>
+  <si>
+    <t>Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli</t>
+  </si>
+  <si>
+    <t>Econ Journal Watch</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>122-140</t>
+  </si>
+  <si>
+    <t>https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
+  </si>
+  <si>
+    <t>Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
+  </si>
+  <si>
+    <t>https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
+  </si>
+  <si>
+    <t>Ramsay, G. (2013, September 10). The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed. LSE Impact Blog. Retrieved from https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
+  </si>
+  <si>
+    <t>@misc{ramsay_2013, title={The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed}, author={Ramsay, Gordon}, year={2013}, month={Sep}, day={10}, howpublished={LSE Impact Blog}}</t>
+  </si>
+  <si>
+    <t>The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed</t>
+  </si>
+  <si>
+    <t>LSE Impact Blog</t>
+  </si>
+  <si>
+    <t>https://purl.utwente.nl/essays/100571</t>
+  </si>
+  <si>
+    <t>Bischoff, M. (2024). Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study (Master's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100571</t>
+  </si>
+  <si>
+    <t>@mastersthesis{bischoff_2024, title={Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study}, author={Bischoff, Milan}, year={2024}, school={University of Twente}}</t>
+  </si>
+  <si>
+    <t>Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study</t>
+  </si>
+  <si>
+    <t>University of Twente</t>
+  </si>
+  <si>
+    <t>https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
+  </si>
+  <si>
+    <t>Arbesfeld, J., Collins, T., Baldwin, D., &amp; Daubman, K. (2014). Clean thoughts lead to less severe moral judgment [Replication of Schnall, Benton, &amp; Harvey, 2008]. PsychFileDrawer.org. Retrieved from https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
+  </si>
+  <si>
+    <t>@misc{arbesfeld_2014, title={Clean thoughts lead to less severe moral judgment}, author={Arbesfeld, Julia and Collins, Tricia and Baldwin, Demetrius and Daubman, Kimberly}, year={2014}, howpublished={PsychFileDrawer.org}, note={Replication of Schnall, Benton, and Harvey (2008)}}</t>
+  </si>
+  <si>
+    <t>Clean thoughts lead to less severe moral judgment</t>
+  </si>
+  <si>
+    <t>PsychFileDrawer.org</t>
+  </si>
+  <si>
+    <t>https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
+  </si>
+  <si>
+    <t>Siev, J. (2012). Unpublished replication of Zhong &amp; Liljenquist (2006). Retrieved from https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
+  </si>
+  <si>
+    <t>@unpublished{siev_2012, title={Unpublished replication of Zhong and Liljenquist (2006)}, author={Siev, Jedediah}, year={2012}}</t>
+  </si>
+  <si>
+    <t>Unpublished replication of Zhong &amp; Liljenquist (2006)</t>
+  </si>
+  <si>
+    <t>kontkanen_jaakko_thesis_2024</t>
+  </si>
+  <si>
+    <t>Kontkanen, J. (2024). Investigating the effect of proficiency level on the acquisition order of morphemes for L2 English learners: A replication of a corpus-based SLA study using Interlanguage Annotation [Master’s thesis, University of Helsinki]. Retrieved from http://hdl.handle.net/10138/576172</t>
+  </si>
+  <si>
+    <t>@mastersthesis{kontkanen2024investigating,
   author  = {Kontkanen, Jaakko},
   title   = {Investigating the effect of proficiency level on the acquisition order of morphemes for L2 English learners: A replication of a corpus-based SLA study using Interlanguage Annotation},
   school  = {University of Helsinki},
@@ -2269,22 +2277,22 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking. (2011, September 15). Retrieved September 23, 2017 from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@misc{pashler2011elderly, author = {Pashler, H. and Harris, C. and Coburn, N.}, title = {Elderly-Related Words Prime Slow Walking}, year = {2011}, month = {September 15}, howpublished = {\url{http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D}}, note = {Retrieved September 23, 2017} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4324/9781032633275-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tversky, A., &amp; Gati, I. (1978). Studies of similarity. In E. Rosch &amp; B. B. Lloyd (Eds.), Cognition and categorization (pp. 79–98). Lawrence Erlbaum Associates.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@incollection{tversky1978studies,
+    <t>http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking. (2011, September 15). Retrieved September 23, 2017 from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t>@misc{pashler2011elderly, author = {Pashler, H. and Harris, C. and Coburn, N.}, title = {Elderly-Related Words Prime Slow Walking}, year = {2011}, month = {September 15}, howpublished = {\url{http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D}}, note = {Retrieved September 23, 2017} }</t>
+  </si>
+  <si>
+    <t>10.4324/9781032633275-7</t>
+  </si>
+  <si>
+    <t>Tversky, A., &amp; Gati, I. (1978). Studies of similarity. In E. Rosch &amp; B. B. Lloyd (Eds.), Cognition and categorization (pp. 79–98). Lawrence Erlbaum Associates.</t>
+  </si>
+  <si>
+    <t>@incollection{tversky1978studies,
   author = {Tversky, Amos and Gati, Itamar},
   title = {Studies of Similarity},
   booktitle = {Cognition and Categorization},
@@ -2296,19 +2304,19 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">Studies of Similarity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79-98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.18574/nyu/9780814788912.003.0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simpson, A. Y. (1998). Identity and integration: The liberals. In The tie that binds: Identity and political attitudes in the post-civil rights generation (pp. 105–144). New York University Press. https://doi.org/10.18574/nyu/9780814788912.003.0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@incollection{simpson1998identity,
+    <t>Studies of Similarity</t>
+  </si>
+  <si>
+    <t>79-98</t>
+  </si>
+  <si>
+    <t>10.18574/nyu/9780814788912.003.0009</t>
+  </si>
+  <si>
+    <t>Simpson, A. Y. (1998). Identity and integration: The liberals. In The tie that binds: Identity and political attitudes in the post-civil rights generation (pp. 105–144). New York University Press. https://doi.org/10.18574/nyu/9780814788912.003.0009</t>
+  </si>
+  <si>
+    <t>@incollection{simpson1998identity,
   author = {Simpson, Andrea Y.},
   title = {Identity and Integration: {The} Liberals},
   booktitle = {The Tie That Binds: Identity and Political Attitudes in the Post-Civil Rights Generation},
@@ -2320,21 +2328,51 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">Identity and Integration: The Liberals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105-144</t>
+    <t>Identity and Integration: The Liberals</t>
+  </si>
+  <si>
+    <t>105-144</t>
+  </si>
+  <si>
+    <t>10.1126/science.aac4716</t>
+  </si>
+  <si>
+    <t>Open Science Collaboration</t>
+  </si>
+  <si>
+    <t>Open Science Collaboration (2015). Estimating the reproducibility of psychological science. Science 349(6251).</t>
+  </si>
+  <si>
+    <t>@article{OpenScienceCollaboration2015,
+  author = {{Open Science Collaboration}},
+  title = {Estimating the reproducibility of psychological science},
+  journal = {Science},
+  year = {2015},
+  volume = {349},
+  number = {6251},
+  pages = {aac4716},
+  doi = {10.1126/science.aac4716}}</t>
+  </si>
+  <si>
+    <t>Science</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2357,16 +2395,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2648,11 +2699,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J186"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2684,7 +2735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2694,15 +2745,8 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2712,15 +2756,8 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3"/>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2730,15 +2767,8 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2748,15 +2778,8 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2766,15 +2789,8 @@
       <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2784,15 +2800,8 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2802,15 +2811,8 @@
       <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="D8"/>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2820,15 +2822,8 @@
       <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -2838,15 +2833,8 @@
       <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2856,15 +2844,8 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-    </row>
-    <row r="12">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -2874,15 +2855,8 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-    </row>
-    <row r="13">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -2892,15 +2866,8 @@
       <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-      <c r="J13"/>
-    </row>
-    <row r="14">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -2910,15 +2877,8 @@
       <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-    </row>
-    <row r="15">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2928,15 +2888,8 @@
       <c r="C15" t="s">
         <v>51</v>
       </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -2946,15 +2899,8 @@
       <c r="C16" t="s">
         <v>54</v>
       </c>
-      <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2964,15 +2910,8 @@
       <c r="C17" t="s">
         <v>57</v>
       </c>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -2982,15 +2921,8 @@
       <c r="C18" t="s">
         <v>60</v>
       </c>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
-    </row>
-    <row r="19">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -3000,15 +2932,8 @@
       <c r="C19" t="s">
         <v>63</v>
       </c>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -3018,15 +2943,8 @@
       <c r="C20" t="s">
         <v>66</v>
       </c>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-    </row>
-    <row r="21">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -3036,15 +2954,8 @@
       <c r="C21" t="s">
         <v>69</v>
       </c>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-    </row>
-    <row r="22">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -3054,15 +2965,8 @@
       <c r="C22" t="s">
         <v>72</v>
       </c>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-    </row>
-    <row r="23">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -3072,15 +2976,8 @@
       <c r="C23" t="s">
         <v>75</v>
       </c>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-    </row>
-    <row r="24">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -3090,15 +2987,8 @@
       <c r="C24" t="s">
         <v>78</v>
       </c>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
-      <c r="J24"/>
-    </row>
-    <row r="25">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -3108,31 +2998,16 @@
       <c r="C25" t="s">
         <v>81</v>
       </c>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-    </row>
-    <row r="26">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>82</v>
       </c>
       <c r="B26" t="s">
         <v>83</v>
       </c>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-    </row>
-    <row r="27">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -3142,15 +3017,8 @@
       <c r="C27" t="s">
         <v>86</v>
       </c>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27"/>
-      <c r="J27"/>
-    </row>
-    <row r="28">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -3160,15 +3028,8 @@
       <c r="C28" t="s">
         <v>89</v>
       </c>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28"/>
-      <c r="J28"/>
-    </row>
-    <row r="29">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -3178,15 +3039,8 @@
       <c r="C29" t="s">
         <v>92</v>
       </c>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
-    </row>
-    <row r="30">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -3196,15 +3050,8 @@
       <c r="C30" t="s">
         <v>95</v>
       </c>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-    </row>
-    <row r="31">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -3214,15 +3061,8 @@
       <c r="C31" t="s">
         <v>98</v>
       </c>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31"/>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
-    </row>
-    <row r="32">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -3232,15 +3072,8 @@
       <c r="C32" t="s">
         <v>101</v>
       </c>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-    </row>
-    <row r="33">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -3250,15 +3083,8 @@
       <c r="C33" t="s">
         <v>104</v>
       </c>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-      <c r="I33"/>
-      <c r="J33"/>
-    </row>
-    <row r="34">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -3268,15 +3094,8 @@
       <c r="C34" t="s">
         <v>107</v>
       </c>
-      <c r="D34"/>
-      <c r="E34"/>
-      <c r="F34"/>
-      <c r="G34"/>
-      <c r="H34"/>
-      <c r="I34"/>
-      <c r="J34"/>
-    </row>
-    <row r="35">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -3286,15 +3105,8 @@
       <c r="C35" t="s">
         <v>110</v>
       </c>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35"/>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>111</v>
       </c>
@@ -3304,15 +3116,8 @@
       <c r="C36" t="s">
         <v>113</v>
       </c>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-    </row>
-    <row r="37">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -3322,15 +3127,8 @@
       <c r="C37" t="s">
         <v>116</v>
       </c>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
-    </row>
-    <row r="38">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -3340,15 +3138,8 @@
       <c r="C38" t="s">
         <v>119</v>
       </c>
-      <c r="D38"/>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
-      <c r="I38"/>
-      <c r="J38"/>
-    </row>
-    <row r="39">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -3358,15 +3149,8 @@
       <c r="C39" t="s">
         <v>122</v>
       </c>
-      <c r="D39"/>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39"/>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -3376,15 +3160,8 @@
       <c r="C40" t="s">
         <v>125</v>
       </c>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40"/>
-      <c r="J40"/>
-    </row>
-    <row r="41">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -3394,15 +3171,8 @@
       <c r="C41" t="s">
         <v>128</v>
       </c>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
-      <c r="I41"/>
-      <c r="J41"/>
-    </row>
-    <row r="42">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -3412,15 +3182,8 @@
       <c r="C42" t="s">
         <v>131</v>
       </c>
-      <c r="D42"/>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
-      <c r="I42"/>
-      <c r="J42"/>
-    </row>
-    <row r="43">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -3430,15 +3193,8 @@
       <c r="C43" t="s">
         <v>131</v>
       </c>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-    </row>
-    <row r="44">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -3448,15 +3204,8 @@
       <c r="C44" t="s">
         <v>131</v>
       </c>
-      <c r="D44"/>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
-      <c r="J44"/>
-    </row>
-    <row r="45">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>129</v>
       </c>
@@ -3466,15 +3215,8 @@
       <c r="C45" t="s">
         <v>131</v>
       </c>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45"/>
-      <c r="J45"/>
-    </row>
-    <row r="46">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -3484,15 +3226,8 @@
       <c r="C46" t="s">
         <v>134</v>
       </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46"/>
-      <c r="J46"/>
-    </row>
-    <row r="47">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>135</v>
       </c>
@@ -3502,15 +3237,8 @@
       <c r="C47" t="s">
         <v>137</v>
       </c>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
-      <c r="I47"/>
-      <c r="J47"/>
-    </row>
-    <row r="48">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -3520,15 +3248,8 @@
       <c r="C48" t="s">
         <v>137</v>
       </c>
-      <c r="D48"/>
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
-      <c r="I48"/>
-      <c r="J48"/>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>135</v>
       </c>
@@ -3538,15 +3259,8 @@
       <c r="C49" t="s">
         <v>137</v>
       </c>
-      <c r="D49"/>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
-      <c r="I49"/>
-      <c r="J49"/>
-    </row>
-    <row r="50">
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -3556,15 +3270,8 @@
       <c r="C50" t="s">
         <v>140</v>
       </c>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -3574,15 +3281,8 @@
       <c r="C51" t="s">
         <v>140</v>
       </c>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51"/>
-    </row>
-    <row r="52">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>138</v>
       </c>
@@ -3592,15 +3292,8 @@
       <c r="C52" t="s">
         <v>140</v>
       </c>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-    </row>
-    <row r="53">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>141</v>
       </c>
@@ -3610,15 +3303,8 @@
       <c r="C53" t="s">
         <v>143</v>
       </c>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-    </row>
-    <row r="54">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>144</v>
       </c>
@@ -3628,15 +3314,8 @@
       <c r="C54" t="s">
         <v>146</v>
       </c>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-    </row>
-    <row r="55">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>144</v>
       </c>
@@ -3646,15 +3325,8 @@
       <c r="C55" t="s">
         <v>146</v>
       </c>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-    </row>
-    <row r="56">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -3664,15 +3336,8 @@
       <c r="C56" t="s">
         <v>146</v>
       </c>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56"/>
-      <c r="J56"/>
-    </row>
-    <row r="57">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>147</v>
       </c>
@@ -3682,15 +3347,8 @@
       <c r="C57" t="s">
         <v>149</v>
       </c>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-    </row>
-    <row r="58">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -3700,15 +3358,8 @@
       <c r="C58" t="s">
         <v>149</v>
       </c>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
-      <c r="I58"/>
-      <c r="J58"/>
-    </row>
-    <row r="59">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>147</v>
       </c>
@@ -3718,15 +3369,8 @@
       <c r="C59" t="s">
         <v>149</v>
       </c>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
-      <c r="I59"/>
-      <c r="J59"/>
-    </row>
-    <row r="60">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -3736,15 +3380,8 @@
       <c r="C60" t="s">
         <v>149</v>
       </c>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
-      <c r="I60"/>
-      <c r="J60"/>
-    </row>
-    <row r="61">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -3754,15 +3391,8 @@
       <c r="C61" t="s">
         <v>152</v>
       </c>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
-      <c r="I61"/>
-      <c r="J61"/>
-    </row>
-    <row r="62">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>153</v>
       </c>
@@ -3772,15 +3402,8 @@
       <c r="C62" t="s">
         <v>155</v>
       </c>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
-      <c r="I62"/>
-      <c r="J62"/>
-    </row>
-    <row r="63">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -3790,15 +3413,8 @@
       <c r="C63" t="s">
         <v>155</v>
       </c>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
-      <c r="I63"/>
-      <c r="J63"/>
-    </row>
-    <row r="64">
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -3808,15 +3424,8 @@
       <c r="C64" t="s">
         <v>158</v>
       </c>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
-      <c r="I64"/>
-      <c r="J64"/>
-    </row>
-    <row r="65">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>156</v>
       </c>
@@ -3826,15 +3435,8 @@
       <c r="C65" t="s">
         <v>158</v>
       </c>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
-      <c r="I65"/>
-      <c r="J65"/>
-    </row>
-    <row r="66">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>156</v>
       </c>
@@ -3844,15 +3446,8 @@
       <c r="C66" t="s">
         <v>158</v>
       </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
-      <c r="I66"/>
-      <c r="J66"/>
-    </row>
-    <row r="67">
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>159</v>
       </c>
@@ -3862,15 +3457,8 @@
       <c r="C67" t="s">
         <v>161</v>
       </c>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
-      <c r="I67"/>
-      <c r="J67"/>
-    </row>
-    <row r="68">
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>159</v>
       </c>
@@ -3880,15 +3468,8 @@
       <c r="C68" t="s">
         <v>161</v>
       </c>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-    </row>
-    <row r="69">
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>159</v>
       </c>
@@ -3898,15 +3479,8 @@
       <c r="C69" t="s">
         <v>161</v>
       </c>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-    </row>
-    <row r="70">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -3916,15 +3490,8 @@
       <c r="C70" t="s">
         <v>164</v>
       </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>162</v>
       </c>
@@ -3934,15 +3501,8 @@
       <c r="C71" t="s">
         <v>164</v>
       </c>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
-      <c r="I71"/>
-      <c r="J71"/>
-    </row>
-    <row r="72">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>162</v>
       </c>
@@ -3952,15 +3512,8 @@
       <c r="C72" t="s">
         <v>164</v>
       </c>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
-      <c r="I72"/>
-      <c r="J72"/>
-    </row>
-    <row r="73">
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -3970,15 +3523,8 @@
       <c r="C73" t="s">
         <v>167</v>
       </c>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
-      <c r="G73"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-    </row>
-    <row r="74">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -3988,15 +3534,8 @@
       <c r="C74" t="s">
         <v>170</v>
       </c>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
-      <c r="G74"/>
-      <c r="H74"/>
-      <c r="I74"/>
-      <c r="J74"/>
-    </row>
-    <row r="75">
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>168</v>
       </c>
@@ -4006,15 +3545,8 @@
       <c r="C75" t="s">
         <v>170</v>
       </c>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
-      <c r="G75"/>
-      <c r="H75"/>
-      <c r="I75"/>
-      <c r="J75"/>
-    </row>
-    <row r="76">
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>171</v>
       </c>
@@ -4024,15 +3556,8 @@
       <c r="C76" t="s">
         <v>173</v>
       </c>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76"/>
-      <c r="H76"/>
-      <c r="I76"/>
-      <c r="J76"/>
-    </row>
-    <row r="77">
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>171</v>
       </c>
@@ -4042,15 +3567,8 @@
       <c r="C77" t="s">
         <v>173</v>
       </c>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
-      <c r="J77"/>
-    </row>
-    <row r="78">
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -4060,15 +3578,8 @@
       <c r="C78" t="s">
         <v>176</v>
       </c>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-      <c r="I78"/>
-      <c r="J78"/>
-    </row>
-    <row r="79">
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>174</v>
       </c>
@@ -4078,15 +3589,8 @@
       <c r="C79" t="s">
         <v>176</v>
       </c>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
-      <c r="G79"/>
-      <c r="H79"/>
-      <c r="I79"/>
-      <c r="J79"/>
-    </row>
-    <row r="80">
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -4096,15 +3600,8 @@
       <c r="C80" t="s">
         <v>176</v>
       </c>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
-      <c r="G80"/>
-      <c r="H80"/>
-      <c r="I80"/>
-      <c r="J80"/>
-    </row>
-    <row r="81">
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>177</v>
       </c>
@@ -4114,15 +3611,8 @@
       <c r="C81" t="s">
         <v>179</v>
       </c>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
-      <c r="G81"/>
-      <c r="H81"/>
-      <c r="I81"/>
-      <c r="J81"/>
-    </row>
-    <row r="82">
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>177</v>
       </c>
@@ -4132,15 +3622,8 @@
       <c r="C82" t="s">
         <v>179</v>
       </c>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
-      <c r="I82"/>
-      <c r="J82"/>
-    </row>
-    <row r="83">
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>177</v>
       </c>
@@ -4150,15 +3633,8 @@
       <c r="C83" t="s">
         <v>179</v>
       </c>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
-      <c r="I83"/>
-      <c r="J83"/>
-    </row>
-    <row r="84">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>180</v>
       </c>
@@ -4168,15 +3644,8 @@
       <c r="C84" t="s">
         <v>182</v>
       </c>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-      <c r="I84"/>
-      <c r="J84"/>
-    </row>
-    <row r="85">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>183</v>
       </c>
@@ -4186,15 +3655,8 @@
       <c r="C85" t="s">
         <v>185</v>
       </c>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
-      <c r="I85"/>
-      <c r="J85"/>
-    </row>
-    <row r="86">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>186</v>
       </c>
@@ -4204,15 +3666,8 @@
       <c r="C86" t="s">
         <v>188</v>
       </c>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-      <c r="J86"/>
-    </row>
-    <row r="87">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>186</v>
       </c>
@@ -4222,15 +3677,8 @@
       <c r="C87" t="s">
         <v>188</v>
       </c>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
-    </row>
-    <row r="88">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>189</v>
       </c>
@@ -4240,15 +3688,8 @@
       <c r="C88" t="s">
         <v>191</v>
       </c>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88"/>
-      <c r="J88"/>
-    </row>
-    <row r="89">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -4258,15 +3699,8 @@
       <c r="C89" t="s">
         <v>194</v>
       </c>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89"/>
-      <c r="I89"/>
-      <c r="J89"/>
-    </row>
-    <row r="90">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>195</v>
       </c>
@@ -4276,15 +3710,8 @@
       <c r="C90" t="s">
         <v>197</v>
       </c>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
-      <c r="I90"/>
-      <c r="J90"/>
-    </row>
-    <row r="91">
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -4294,15 +3721,8 @@
       <c r="C91" t="s">
         <v>200</v>
       </c>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91"/>
-      <c r="I91"/>
-      <c r="J91"/>
-    </row>
-    <row r="92">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>201</v>
       </c>
@@ -4312,15 +3732,8 @@
       <c r="C92" t="s">
         <v>203</v>
       </c>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
-      <c r="I92"/>
-      <c r="J92"/>
-    </row>
-    <row r="93">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>201</v>
       </c>
@@ -4330,15 +3743,8 @@
       <c r="C93" t="s">
         <v>203</v>
       </c>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
-      <c r="G93"/>
-      <c r="H93"/>
-      <c r="I93"/>
-      <c r="J93"/>
-    </row>
-    <row r="94">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -4348,15 +3754,8 @@
       <c r="C94" t="s">
         <v>203</v>
       </c>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
-      <c r="I94"/>
-      <c r="J94"/>
-    </row>
-    <row r="95">
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>201</v>
       </c>
@@ -4366,15 +3765,8 @@
       <c r="C95" t="s">
         <v>203</v>
       </c>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
-      <c r="G95"/>
-      <c r="H95"/>
-      <c r="I95"/>
-      <c r="J95"/>
-    </row>
-    <row r="96">
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -4384,15 +3776,8 @@
       <c r="C96" t="s">
         <v>203</v>
       </c>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
-      <c r="I96"/>
-      <c r="J96"/>
-    </row>
-    <row r="97">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>201</v>
       </c>
@@ -4402,15 +3787,8 @@
       <c r="C97" t="s">
         <v>203</v>
       </c>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-      <c r="H97"/>
-      <c r="I97"/>
-      <c r="J97"/>
-    </row>
-    <row r="98">
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -4420,15 +3798,8 @@
       <c r="C98" t="s">
         <v>203</v>
       </c>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98"/>
-      <c r="H98"/>
-      <c r="I98"/>
-      <c r="J98"/>
-    </row>
-    <row r="99">
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>201</v>
       </c>
@@ -4438,15 +3809,8 @@
       <c r="C99" t="s">
         <v>203</v>
       </c>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
-      <c r="I99"/>
-      <c r="J99"/>
-    </row>
-    <row r="100">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -4456,15 +3820,8 @@
       <c r="C100" t="s">
         <v>206</v>
       </c>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100"/>
-      <c r="H100"/>
-      <c r="I100"/>
-      <c r="J100"/>
-    </row>
-    <row r="101">
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -4474,15 +3831,8 @@
       <c r="C101" t="s">
         <v>209</v>
       </c>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-      <c r="I101"/>
-      <c r="J101"/>
-    </row>
-    <row r="102">
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>207</v>
       </c>
@@ -4492,15 +3842,8 @@
       <c r="C102" t="s">
         <v>209</v>
       </c>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-    </row>
-    <row r="103">
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -4510,15 +3853,8 @@
       <c r="C103" t="s">
         <v>212</v>
       </c>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
-      <c r="I103"/>
-      <c r="J103"/>
-    </row>
-    <row r="104">
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -4528,15 +3864,8 @@
       <c r="C104" t="s">
         <v>215</v>
       </c>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
-      <c r="I104"/>
-      <c r="J104"/>
-    </row>
-    <row r="105">
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -4546,15 +3875,8 @@
       <c r="C105" t="s">
         <v>218</v>
       </c>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
-      <c r="I105"/>
-      <c r="J105"/>
-    </row>
-    <row r="106">
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>219</v>
       </c>
@@ -4564,15 +3886,8 @@
       <c r="C106" t="s">
         <v>221</v>
       </c>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-      <c r="I106"/>
-      <c r="J106"/>
-    </row>
-    <row r="107">
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -4582,15 +3897,8 @@
       <c r="C107" t="s">
         <v>221</v>
       </c>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
-      <c r="I107"/>
-      <c r="J107"/>
-    </row>
-    <row r="108">
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>219</v>
       </c>
@@ -4600,15 +3908,8 @@
       <c r="C108" t="s">
         <v>221</v>
       </c>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-      <c r="I108"/>
-      <c r="J108"/>
-    </row>
-    <row r="109">
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>219</v>
       </c>
@@ -4618,15 +3919,8 @@
       <c r="C109" t="s">
         <v>221</v>
       </c>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
-      <c r="I109"/>
-      <c r="J109"/>
-    </row>
-    <row r="110">
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>222</v>
       </c>
@@ -4636,15 +3930,8 @@
       <c r="C110" t="s">
         <v>224</v>
       </c>
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110"/>
-      <c r="G110"/>
-      <c r="H110"/>
-      <c r="I110"/>
-      <c r="J110"/>
-    </row>
-    <row r="111">
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>225</v>
       </c>
@@ -4654,15 +3941,8 @@
       <c r="C111" t="s">
         <v>227</v>
       </c>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-      <c r="J111"/>
-    </row>
-    <row r="112">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>228</v>
       </c>
@@ -4672,15 +3952,8 @@
       <c r="C112" t="s">
         <v>230</v>
       </c>
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
-      <c r="G112"/>
-      <c r="H112"/>
-      <c r="I112"/>
-      <c r="J112"/>
-    </row>
-    <row r="113">
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -4690,15 +3963,8 @@
       <c r="C113" t="s">
         <v>233</v>
       </c>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
-      <c r="I113"/>
-      <c r="J113"/>
-    </row>
-    <row r="114">
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>234</v>
       </c>
@@ -4708,15 +3974,8 @@
       <c r="C114" t="s">
         <v>236</v>
       </c>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
-      <c r="I114"/>
-      <c r="J114"/>
-    </row>
-    <row r="115">
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>237</v>
       </c>
@@ -4726,15 +3985,8 @@
       <c r="C115" t="s">
         <v>239</v>
       </c>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
-      <c r="G115"/>
-      <c r="H115"/>
-      <c r="I115"/>
-      <c r="J115"/>
-    </row>
-    <row r="116">
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>240</v>
       </c>
@@ -4744,15 +3996,8 @@
       <c r="C116" t="s">
         <v>242</v>
       </c>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
-      <c r="G116"/>
-      <c r="H116"/>
-      <c r="I116"/>
-      <c r="J116"/>
-    </row>
-    <row r="117">
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>243</v>
       </c>
@@ -4762,15 +4007,8 @@
       <c r="C117" t="s">
         <v>245</v>
       </c>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
-      <c r="G117"/>
-      <c r="H117"/>
-      <c r="I117"/>
-      <c r="J117"/>
-    </row>
-    <row r="118">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>246</v>
       </c>
@@ -4780,15 +4018,8 @@
       <c r="C118" t="s">
         <v>248</v>
       </c>
-      <c r="D118"/>
-      <c r="E118"/>
-      <c r="F118"/>
-      <c r="G118"/>
-      <c r="H118"/>
-      <c r="I118"/>
-      <c r="J118"/>
-    </row>
-    <row r="119">
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>249</v>
       </c>
@@ -4798,15 +4029,8 @@
       <c r="C119" t="s">
         <v>251</v>
       </c>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
-      <c r="G119"/>
-      <c r="H119"/>
-      <c r="I119"/>
-      <c r="J119"/>
-    </row>
-    <row r="120">
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>252</v>
       </c>
@@ -4816,15 +4040,8 @@
       <c r="C120" t="s">
         <v>254</v>
       </c>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120"/>
-      <c r="H120"/>
-      <c r="I120"/>
-      <c r="J120"/>
-    </row>
-    <row r="121">
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>255</v>
       </c>
@@ -4834,15 +4051,8 @@
       <c r="C121" t="s">
         <v>257</v>
       </c>
-      <c r="D121"/>
-      <c r="E121"/>
-      <c r="F121"/>
-      <c r="G121"/>
-      <c r="H121"/>
-      <c r="I121"/>
-      <c r="J121"/>
-    </row>
-    <row r="122">
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>258</v>
       </c>
@@ -4852,15 +4062,8 @@
       <c r="C122" t="s">
         <v>260</v>
       </c>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
-      <c r="G122"/>
-      <c r="H122"/>
-      <c r="I122"/>
-      <c r="J122"/>
-    </row>
-    <row r="123">
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>261</v>
       </c>
@@ -4870,15 +4073,8 @@
       <c r="C123" t="s">
         <v>263</v>
       </c>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-      <c r="I123"/>
-      <c r="J123"/>
-    </row>
-    <row r="124">
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>264</v>
       </c>
@@ -4888,15 +4084,8 @@
       <c r="C124" t="s">
         <v>266</v>
       </c>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
-      <c r="G124"/>
-      <c r="H124"/>
-      <c r="I124"/>
-      <c r="J124"/>
-    </row>
-    <row r="125">
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -4906,15 +4095,8 @@
       <c r="C125" t="s">
         <v>269</v>
       </c>
-      <c r="D125"/>
-      <c r="E125"/>
-      <c r="F125"/>
-      <c r="G125"/>
-      <c r="H125"/>
-      <c r="I125"/>
-      <c r="J125"/>
-    </row>
-    <row r="126">
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>270</v>
       </c>
@@ -4924,15 +4106,8 @@
       <c r="C126" t="s">
         <v>272</v>
       </c>
-      <c r="D126"/>
-      <c r="E126"/>
-      <c r="F126"/>
-      <c r="G126"/>
-      <c r="H126"/>
-      <c r="I126"/>
-      <c r="J126"/>
-    </row>
-    <row r="127">
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -4942,15 +4117,8 @@
       <c r="C127" t="s">
         <v>275</v>
       </c>
-      <c r="D127"/>
-      <c r="E127"/>
-      <c r="F127"/>
-      <c r="G127"/>
-      <c r="H127"/>
-      <c r="I127"/>
-      <c r="J127"/>
-    </row>
-    <row r="128">
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>276</v>
       </c>
@@ -4960,15 +4128,8 @@
       <c r="C128" t="s">
         <v>278</v>
       </c>
-      <c r="D128"/>
-      <c r="E128"/>
-      <c r="F128"/>
-      <c r="G128"/>
-      <c r="H128"/>
-      <c r="I128"/>
-      <c r="J128"/>
-    </row>
-    <row r="129">
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>279</v>
       </c>
@@ -4978,15 +4139,8 @@
       <c r="C129" t="s">
         <v>281</v>
       </c>
-      <c r="D129"/>
-      <c r="E129"/>
-      <c r="F129"/>
-      <c r="G129"/>
-      <c r="H129"/>
-      <c r="I129"/>
-      <c r="J129"/>
-    </row>
-    <row r="130">
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>282</v>
       </c>
@@ -4996,15 +4150,8 @@
       <c r="C130" t="s">
         <v>284</v>
       </c>
-      <c r="D130"/>
-      <c r="E130"/>
-      <c r="F130"/>
-      <c r="G130"/>
-      <c r="H130"/>
-      <c r="I130"/>
-      <c r="J130"/>
-    </row>
-    <row r="131">
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>285</v>
       </c>
@@ -5014,15 +4161,8 @@
       <c r="C131" t="s">
         <v>287</v>
       </c>
-      <c r="D131"/>
-      <c r="E131"/>
-      <c r="F131"/>
-      <c r="G131"/>
-      <c r="H131"/>
-      <c r="I131"/>
-      <c r="J131"/>
-    </row>
-    <row r="132">
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>288</v>
       </c>
@@ -5032,15 +4172,8 @@
       <c r="C132" t="s">
         <v>290</v>
       </c>
-      <c r="D132"/>
-      <c r="E132"/>
-      <c r="F132"/>
-      <c r="G132"/>
-      <c r="H132"/>
-      <c r="I132"/>
-      <c r="J132"/>
-    </row>
-    <row r="133">
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>291</v>
       </c>
@@ -5050,15 +4183,8 @@
       <c r="C133" t="s">
         <v>293</v>
       </c>
-      <c r="D133"/>
-      <c r="E133"/>
-      <c r="F133"/>
-      <c r="G133"/>
-      <c r="H133"/>
-      <c r="I133"/>
-      <c r="J133"/>
-    </row>
-    <row r="134">
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>294</v>
       </c>
@@ -5068,15 +4194,8 @@
       <c r="C134" t="s">
         <v>296</v>
       </c>
-      <c r="D134"/>
-      <c r="E134"/>
-      <c r="F134"/>
-      <c r="G134"/>
-      <c r="H134"/>
-      <c r="I134"/>
-      <c r="J134"/>
-    </row>
-    <row r="135">
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>297</v>
       </c>
@@ -5086,15 +4205,8 @@
       <c r="C135" t="s">
         <v>299</v>
       </c>
-      <c r="D135"/>
-      <c r="E135"/>
-      <c r="F135"/>
-      <c r="G135"/>
-      <c r="H135"/>
-      <c r="I135"/>
-      <c r="J135"/>
-    </row>
-    <row r="136">
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>300</v>
       </c>
@@ -5104,15 +4216,8 @@
       <c r="C136" t="s">
         <v>302</v>
       </c>
-      <c r="D136"/>
-      <c r="E136"/>
-      <c r="F136"/>
-      <c r="G136"/>
-      <c r="H136"/>
-      <c r="I136"/>
-      <c r="J136"/>
-    </row>
-    <row r="137">
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>303</v>
       </c>
@@ -5122,15 +4227,8 @@
       <c r="C137" t="s">
         <v>305</v>
       </c>
-      <c r="D137"/>
-      <c r="E137"/>
-      <c r="F137"/>
-      <c r="G137"/>
-      <c r="H137"/>
-      <c r="I137"/>
-      <c r="J137"/>
-    </row>
-    <row r="138">
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>306</v>
       </c>
@@ -5140,15 +4238,8 @@
       <c r="C138" t="s">
         <v>308</v>
       </c>
-      <c r="D138"/>
-      <c r="E138"/>
-      <c r="F138"/>
-      <c r="G138"/>
-      <c r="H138"/>
-      <c r="I138"/>
-      <c r="J138"/>
-    </row>
-    <row r="139">
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>309</v>
       </c>
@@ -5158,15 +4249,8 @@
       <c r="C139" t="s">
         <v>311</v>
       </c>
-      <c r="D139"/>
-      <c r="E139"/>
-      <c r="F139"/>
-      <c r="G139"/>
-      <c r="H139"/>
-      <c r="I139"/>
-      <c r="J139"/>
-    </row>
-    <row r="140">
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>312</v>
       </c>
@@ -5176,15 +4260,8 @@
       <c r="C140" t="s">
         <v>314</v>
       </c>
-      <c r="D140"/>
-      <c r="E140"/>
-      <c r="F140"/>
-      <c r="G140"/>
-      <c r="H140"/>
-      <c r="I140"/>
-      <c r="J140"/>
-    </row>
-    <row r="141">
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>315</v>
       </c>
@@ -5194,15 +4271,8 @@
       <c r="C141" t="s">
         <v>317</v>
       </c>
-      <c r="D141"/>
-      <c r="E141"/>
-      <c r="F141"/>
-      <c r="G141"/>
-      <c r="H141"/>
-      <c r="I141"/>
-      <c r="J141"/>
-    </row>
-    <row r="142">
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>318</v>
       </c>
@@ -5212,15 +4282,8 @@
       <c r="C142" t="s">
         <v>320</v>
       </c>
-      <c r="D142"/>
-      <c r="E142"/>
-      <c r="F142"/>
-      <c r="G142"/>
-      <c r="H142"/>
-      <c r="I142"/>
-      <c r="J142"/>
-    </row>
-    <row r="143">
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>321</v>
       </c>
@@ -5230,15 +4293,8 @@
       <c r="C143" t="s">
         <v>323</v>
       </c>
-      <c r="D143"/>
-      <c r="E143"/>
-      <c r="F143"/>
-      <c r="G143"/>
-      <c r="H143"/>
-      <c r="I143"/>
-      <c r="J143"/>
-    </row>
-    <row r="144">
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>324</v>
       </c>
@@ -5248,15 +4304,8 @@
       <c r="C144" t="s">
         <v>326</v>
       </c>
-      <c r="D144"/>
-      <c r="E144"/>
-      <c r="F144"/>
-      <c r="G144"/>
-      <c r="H144"/>
-      <c r="I144"/>
-      <c r="J144"/>
-    </row>
-    <row r="145">
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>327</v>
       </c>
@@ -5266,15 +4315,8 @@
       <c r="C145" t="s">
         <v>329</v>
       </c>
-      <c r="D145"/>
-      <c r="E145"/>
-      <c r="F145"/>
-      <c r="G145"/>
-      <c r="H145"/>
-      <c r="I145"/>
-      <c r="J145"/>
-    </row>
-    <row r="146">
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -5284,15 +4326,8 @@
       <c r="C146" t="s">
         <v>332</v>
       </c>
-      <c r="D146"/>
-      <c r="E146"/>
-      <c r="F146"/>
-      <c r="G146"/>
-      <c r="H146"/>
-      <c r="I146"/>
-      <c r="J146"/>
-    </row>
-    <row r="147">
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>333</v>
       </c>
@@ -5302,15 +4337,8 @@
       <c r="C147" t="s">
         <v>335</v>
       </c>
-      <c r="D147"/>
-      <c r="E147"/>
-      <c r="F147"/>
-      <c r="G147"/>
-      <c r="H147"/>
-      <c r="I147"/>
-      <c r="J147"/>
-    </row>
-    <row r="148">
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>336</v>
       </c>
@@ -5320,15 +4348,8 @@
       <c r="C148" t="s">
         <v>338</v>
       </c>
-      <c r="D148"/>
-      <c r="E148"/>
-      <c r="F148"/>
-      <c r="G148"/>
-      <c r="H148"/>
-      <c r="I148"/>
-      <c r="J148"/>
-    </row>
-    <row r="149">
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>339</v>
       </c>
@@ -5338,15 +4359,8 @@
       <c r="C149" t="s">
         <v>341</v>
       </c>
-      <c r="D149"/>
-      <c r="E149"/>
-      <c r="F149"/>
-      <c r="G149"/>
-      <c r="H149"/>
-      <c r="I149"/>
-      <c r="J149"/>
-    </row>
-    <row r="150">
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>342</v>
       </c>
@@ -5356,15 +4370,8 @@
       <c r="C150" t="s">
         <v>344</v>
       </c>
-      <c r="D150"/>
-      <c r="E150"/>
-      <c r="F150"/>
-      <c r="G150"/>
-      <c r="H150"/>
-      <c r="I150"/>
-      <c r="J150"/>
-    </row>
-    <row r="151">
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>345</v>
       </c>
@@ -5374,15 +4381,8 @@
       <c r="C151" t="s">
         <v>347</v>
       </c>
-      <c r="D151"/>
-      <c r="E151"/>
-      <c r="F151"/>
-      <c r="G151"/>
-      <c r="H151"/>
-      <c r="I151"/>
-      <c r="J151"/>
-    </row>
-    <row r="152">
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>348</v>
       </c>
@@ -5392,15 +4392,8 @@
       <c r="C152" t="s">
         <v>350</v>
       </c>
-      <c r="D152"/>
-      <c r="E152"/>
-      <c r="F152"/>
-      <c r="G152"/>
-      <c r="H152"/>
-      <c r="I152"/>
-      <c r="J152"/>
-    </row>
-    <row r="153">
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>351</v>
       </c>
@@ -5410,15 +4403,8 @@
       <c r="C153" t="s">
         <v>353</v>
       </c>
-      <c r="D153"/>
-      <c r="E153"/>
-      <c r="F153"/>
-      <c r="G153"/>
-      <c r="H153"/>
-      <c r="I153"/>
-      <c r="J153"/>
-    </row>
-    <row r="154">
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>354</v>
       </c>
@@ -5428,15 +4414,8 @@
       <c r="C154" t="s">
         <v>356</v>
       </c>
-      <c r="D154"/>
-      <c r="E154"/>
-      <c r="F154"/>
-      <c r="G154"/>
-      <c r="H154"/>
-      <c r="I154"/>
-      <c r="J154"/>
-    </row>
-    <row r="155">
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>357</v>
       </c>
@@ -5446,15 +4425,8 @@
       <c r="C155" t="s">
         <v>359</v>
       </c>
-      <c r="D155"/>
-      <c r="E155"/>
-      <c r="F155"/>
-      <c r="G155"/>
-      <c r="H155"/>
-      <c r="I155"/>
-      <c r="J155"/>
-    </row>
-    <row r="156">
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>360</v>
       </c>
@@ -5464,15 +4436,8 @@
       <c r="C156" t="s">
         <v>362</v>
       </c>
-      <c r="D156"/>
-      <c r="E156"/>
-      <c r="F156"/>
-      <c r="G156"/>
-      <c r="H156"/>
-      <c r="I156"/>
-      <c r="J156"/>
-    </row>
-    <row r="157">
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>363</v>
       </c>
@@ -5482,15 +4447,8 @@
       <c r="C157" t="s">
         <v>365</v>
       </c>
-      <c r="D157"/>
-      <c r="E157"/>
-      <c r="F157"/>
-      <c r="G157"/>
-      <c r="H157"/>
-      <c r="I157"/>
-      <c r="J157"/>
-    </row>
-    <row r="158">
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>366</v>
       </c>
@@ -5500,15 +4458,8 @@
       <c r="C158" t="s">
         <v>368</v>
       </c>
-      <c r="D158"/>
-      <c r="E158"/>
-      <c r="F158"/>
-      <c r="G158"/>
-      <c r="H158"/>
-      <c r="I158"/>
-      <c r="J158"/>
-    </row>
-    <row r="159">
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>369</v>
       </c>
@@ -5518,15 +4469,8 @@
       <c r="C159" t="s">
         <v>371</v>
       </c>
-      <c r="D159"/>
-      <c r="E159"/>
-      <c r="F159"/>
-      <c r="G159"/>
-      <c r="H159"/>
-      <c r="I159"/>
-      <c r="J159"/>
-    </row>
-    <row r="160">
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>372</v>
       </c>
@@ -5536,15 +4480,8 @@
       <c r="C160" t="s">
         <v>374</v>
       </c>
-      <c r="D160"/>
-      <c r="E160"/>
-      <c r="F160"/>
-      <c r="G160"/>
-      <c r="H160"/>
-      <c r="I160"/>
-      <c r="J160"/>
-    </row>
-    <row r="161">
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>375</v>
       </c>
@@ -5554,15 +4491,8 @@
       <c r="C161" t="s">
         <v>377</v>
       </c>
-      <c r="D161"/>
-      <c r="E161"/>
-      <c r="F161"/>
-      <c r="G161"/>
-      <c r="H161"/>
-      <c r="I161"/>
-      <c r="J161"/>
-    </row>
-    <row r="162">
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>378</v>
       </c>
@@ -5572,15 +4502,8 @@
       <c r="C162" t="s">
         <v>380</v>
       </c>
-      <c r="D162"/>
-      <c r="E162"/>
-      <c r="F162"/>
-      <c r="G162"/>
-      <c r="H162"/>
-      <c r="I162"/>
-      <c r="J162"/>
-    </row>
-    <row r="163">
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>381</v>
       </c>
@@ -5590,15 +4513,8 @@
       <c r="C163" t="s">
         <v>383</v>
       </c>
-      <c r="D163"/>
-      <c r="E163"/>
-      <c r="F163"/>
-      <c r="G163"/>
-      <c r="H163"/>
-      <c r="I163"/>
-      <c r="J163"/>
-    </row>
-    <row r="164">
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>384</v>
       </c>
@@ -5608,15 +4524,8 @@
       <c r="C164" t="s">
         <v>386</v>
       </c>
-      <c r="D164"/>
-      <c r="E164"/>
-      <c r="F164"/>
-      <c r="G164"/>
-      <c r="H164"/>
-      <c r="I164"/>
-      <c r="J164"/>
-    </row>
-    <row r="165">
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>387</v>
       </c>
@@ -5626,15 +4535,8 @@
       <c r="C165" t="s">
         <v>389</v>
       </c>
-      <c r="D165"/>
-      <c r="E165"/>
-      <c r="F165"/>
-      <c r="G165"/>
-      <c r="H165"/>
-      <c r="I165"/>
-      <c r="J165"/>
-    </row>
-    <row r="166">
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>390</v>
       </c>
@@ -5644,15 +4546,8 @@
       <c r="C166" t="s">
         <v>392</v>
       </c>
-      <c r="D166"/>
-      <c r="E166"/>
-      <c r="F166"/>
-      <c r="G166"/>
-      <c r="H166"/>
-      <c r="I166"/>
-      <c r="J166"/>
-    </row>
-    <row r="167">
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -5662,15 +4557,8 @@
       <c r="C167" t="s">
         <v>395</v>
       </c>
-      <c r="D167"/>
-      <c r="E167"/>
-      <c r="F167"/>
-      <c r="G167"/>
-      <c r="H167"/>
-      <c r="I167"/>
-      <c r="J167"/>
-    </row>
-    <row r="168">
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>396</v>
       </c>
@@ -5680,15 +4568,8 @@
       <c r="C168" t="s">
         <v>398</v>
       </c>
-      <c r="D168"/>
-      <c r="E168"/>
-      <c r="F168"/>
-      <c r="G168"/>
-      <c r="H168"/>
-      <c r="I168"/>
-      <c r="J168"/>
-    </row>
-    <row r="169">
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>399</v>
       </c>
@@ -5698,15 +4579,8 @@
       <c r="C169" t="s">
         <v>401</v>
       </c>
-      <c r="D169"/>
-      <c r="E169"/>
-      <c r="F169"/>
-      <c r="G169"/>
-      <c r="H169"/>
-      <c r="I169"/>
-      <c r="J169"/>
-    </row>
-    <row r="170">
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -5716,15 +4590,8 @@
       <c r="C170" t="s">
         <v>404</v>
       </c>
-      <c r="D170"/>
-      <c r="E170"/>
-      <c r="F170"/>
-      <c r="G170"/>
-      <c r="H170"/>
-      <c r="I170"/>
-      <c r="J170"/>
-    </row>
-    <row r="171">
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>405</v>
       </c>
@@ -5734,15 +4601,8 @@
       <c r="C171" t="s">
         <v>407</v>
       </c>
-      <c r="D171"/>
-      <c r="E171"/>
-      <c r="F171"/>
-      <c r="G171"/>
-      <c r="H171"/>
-      <c r="I171"/>
-      <c r="J171"/>
-    </row>
-    <row r="172">
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>408</v>
       </c>
@@ -5752,15 +4612,8 @@
       <c r="C172" t="s">
         <v>410</v>
       </c>
-      <c r="D172"/>
-      <c r="E172"/>
-      <c r="F172"/>
-      <c r="G172"/>
-      <c r="H172"/>
-      <c r="I172"/>
-      <c r="J172"/>
-    </row>
-    <row r="173">
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>411</v>
       </c>
@@ -5773,18 +4626,14 @@
       <c r="D173" t="s">
         <v>414</v>
       </c>
-      <c r="E173"/>
       <c r="F173" t="s">
         <v>415</v>
       </c>
-      <c r="G173" t="n">
+      <c r="G173">
         <v>2023</v>
       </c>
-      <c r="H173"/>
-      <c r="I173"/>
-      <c r="J173"/>
-    </row>
-    <row r="174">
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>416</v>
       </c>
@@ -5797,18 +4646,14 @@
       <c r="D174" t="s">
         <v>419</v>
       </c>
-      <c r="E174"/>
       <c r="F174" t="s">
         <v>415</v>
       </c>
-      <c r="G174" t="n">
+      <c r="G174">
         <v>2023</v>
       </c>
-      <c r="H174"/>
-      <c r="I174"/>
-      <c r="J174"/>
-    </row>
-    <row r="175">
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>420</v>
       </c>
@@ -5821,18 +4666,14 @@
       <c r="D175" t="s">
         <v>423</v>
       </c>
-      <c r="E175"/>
       <c r="F175" t="s">
         <v>415</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G175">
         <v>2016</v>
       </c>
-      <c r="H175"/>
-      <c r="I175"/>
-      <c r="J175"/>
-    </row>
-    <row r="176">
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>424</v>
       </c>
@@ -5845,11 +4686,10 @@
       <c r="D176" t="s">
         <v>427</v>
       </c>
-      <c r="E176"/>
       <c r="F176" t="s">
         <v>428</v>
       </c>
-      <c r="G176" t="n">
+      <c r="G176">
         <v>2012</v>
       </c>
       <c r="H176" t="s">
@@ -5862,7 +4702,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>432</v>
       </c>
@@ -5875,11 +4715,10 @@
       <c r="D177" t="s">
         <v>427</v>
       </c>
-      <c r="E177"/>
       <c r="F177" t="s">
         <v>428</v>
       </c>
-      <c r="G177" t="n">
+      <c r="G177">
         <v>2012</v>
       </c>
       <c r="H177" t="s">
@@ -5892,7 +4731,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>434</v>
       </c>
@@ -5905,18 +4744,14 @@
       <c r="D178" t="s">
         <v>437</v>
       </c>
-      <c r="E178"/>
       <c r="F178" t="s">
         <v>438</v>
       </c>
-      <c r="G178" t="n">
+      <c r="G178">
         <v>2013</v>
       </c>
-      <c r="H178"/>
-      <c r="I178"/>
-      <c r="J178"/>
-    </row>
-    <row r="179">
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>439</v>
       </c>
@@ -5929,18 +4764,14 @@
       <c r="D179" t="s">
         <v>442</v>
       </c>
-      <c r="E179"/>
       <c r="F179" t="s">
         <v>443</v>
       </c>
-      <c r="G179" t="n">
+      <c r="G179">
         <v>2024</v>
       </c>
-      <c r="H179"/>
-      <c r="I179"/>
-      <c r="J179"/>
-    </row>
-    <row r="180">
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>444</v>
       </c>
@@ -5953,18 +4784,14 @@
       <c r="D180" t="s">
         <v>447</v>
       </c>
-      <c r="E180"/>
       <c r="F180" t="s">
         <v>448</v>
       </c>
-      <c r="G180" t="n">
+      <c r="G180">
         <v>2014</v>
       </c>
-      <c r="H180"/>
-      <c r="I180"/>
-      <c r="J180"/>
-    </row>
-    <row r="181">
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>449</v>
       </c>
@@ -5977,16 +4804,11 @@
       <c r="D181" t="s">
         <v>452</v>
       </c>
-      <c r="E181"/>
-      <c r="F181"/>
-      <c r="G181" t="n">
+      <c r="G181">
         <v>2012</v>
       </c>
-      <c r="H181"/>
-      <c r="I181"/>
-      <c r="J181"/>
-    </row>
-    <row r="182">
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>453</v>
       </c>
@@ -5996,15 +4818,8 @@
       <c r="C182" t="s">
         <v>455</v>
       </c>
-      <c r="D182"/>
-      <c r="E182"/>
-      <c r="F182"/>
-      <c r="G182"/>
-      <c r="H182"/>
-      <c r="I182"/>
-      <c r="J182"/>
-    </row>
-    <row r="183">
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>456</v>
       </c>
@@ -6014,15 +4829,8 @@
       <c r="C183" t="s">
         <v>458</v>
       </c>
-      <c r="D183"/>
-      <c r="E183"/>
-      <c r="F183"/>
-      <c r="G183"/>
-      <c r="H183"/>
-      <c r="I183"/>
-      <c r="J183"/>
-    </row>
-    <row r="184">
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>459</v>
       </c>
@@ -6035,18 +4843,14 @@
       <c r="D184" t="s">
         <v>462</v>
       </c>
-      <c r="E184"/>
-      <c r="F184"/>
-      <c r="G184" t="n">
+      <c r="G184">
         <v>1978</v>
       </c>
-      <c r="H184"/>
-      <c r="I184"/>
       <c r="J184" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>464</v>
       </c>
@@ -6059,19 +4863,44 @@
       <c r="D185" t="s">
         <v>467</v>
       </c>
-      <c r="E185"/>
-      <c r="F185"/>
-      <c r="G185" t="n">
+      <c r="G185">
         <v>1998</v>
       </c>
-      <c r="H185"/>
-      <c r="I185"/>
       <c r="J185" t="s">
         <v>468</v>
       </c>
     </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B186" t="s">
+        <v>471</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E186" t="s">
+        <v>470</v>
+      </c>
+      <c r="F186" t="s">
+        <v>473</v>
+      </c>
+      <c r="G186">
+        <v>2015</v>
+      </c>
+      <c r="H186">
+        <v>349</v>
+      </c>
+      <c r="I186">
+        <v>6251</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A186" r:id="rId1" display="https://doi.org/10.1126/science.aac4716" xr:uid="{C3963564-FE82-1142-BE0D-26BD87AE3BF2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/cache/manual_references.xlsx
+++ b/cache/manual_references.xlsx
@@ -1,64 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukaswallrich/Documents/Coding/fred_data/cache/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6E3F6D-7EC2-7049-BA71-B917D2255443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" calcCompleted="0" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="474">
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>reference_apa</t>
-  </si>
-  <si>
-    <t>reference_bibtex</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>journal</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>issue</t>
-  </si>
-  <si>
-    <t>pages</t>
-  </si>
-  <si>
-    <t>10.1177/2f10986111211035002</t>
-  </si>
-  <si>
-    <t>Lum, C., Koper, C. S., &amp; Wu, X. (2021). Can we really defund the police? A nine-agency study of police response to calls for service. Police Quarterly.</t>
-  </si>
-  <si>
-    <t>@article{Lum_2021,
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="677">
+  <si>
+    <t xml:space="preserve">key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference_apa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference_bibtex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">journal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1177/2f10986111211035002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lum, C., Koper, C. S., &amp; Wu, X. (2021). Can we really defund the police? A nine-agency study of police response to calls for service. Police Quarterly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{Lum_2021,
   title={Can We Really Defund the Police? A Nine-Agency Study of Police Response to Calls for Service},
   author={Lum, Cynthia and Koper, Christopher S. and Wu, Xiaoyun},
   journal={Police Quarterly},
@@ -73,13 +65,13 @@
 }</t>
   </si>
   <si>
-    <t>https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t>Katla, J. (2024). Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA). https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t>@mastersthesis{katla2024replication,
+    <t xml:space="preserve">https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katla, J. (2024). Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA). https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@mastersthesis{katla2024replication,
   title={Replication of Construct Validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Katla, J.},
   year={2024},
@@ -88,13 +80,13 @@
 }</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1DDCuEgQah24QordxkRGO0EIt6Q681jyL/view</t>
-  </si>
-  <si>
-    <t>Lee, F. (2013). Replication of “With a clean conscience: Cleanliness reduces the severity of moral judgments” by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
-  </si>
-  <si>
-    <t>@unpublished{lee2013replication,
+    <t xml:space="preserve">https://drive.google.com/file/d/1DDCuEgQah24QordxkRGO0EIt6Q681jyL/view</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee, F. (2013). Replication of “With a clean conscience: Cleanliness reduces the severity of moral judgments” by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@unpublished{lee2013replication,
   title={Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science)},
   author={Lee, F.},
   year={2013},
@@ -103,13 +95,13 @@
 }</t>
   </si>
   <si>
-    <t>https://www.jasnh.com/a14.htm</t>
-  </si>
-  <si>
-    <t>Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51.</t>
-  </si>
-  <si>
-    <t>@article{murtagh_todd_2004,
+    <t xml:space="preserve">https://www.jasnh.com/a14.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{murtagh_todd_2004,
   title={Self-regulation: A challenge to the strength model},
   author={Murtagh, Andrew M. and Todd, Sandra A.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -121,13 +113,13 @@
 }</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1i2aa1erQ9i9knP8Z5bgGiSt6DXX7U7Fa/view?usp=drivesdk</t>
-  </si>
-  <si>
-    <t>Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking . (2011, September 15). Retrieved from https://web.archive.org/web/20191117063540/http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t>@misc{pashler_harris_coburn_2011,
+    <t xml:space="preserve">https://drive.google.com/file/d/1i2aa1erQ9i9knP8Z5bgGiSt6DXX7U7Fa/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking . (2011, September 15). Retrieved from https://web.archive.org/web/20191117063540/http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{pashler_harris_coburn_2011,
   title={Elderly-Related Words Prime Slow Walking},
   author={Pashler, H. and Harris, C. and Coburn, N.},
   year={2011},
@@ -138,13 +130,13 @@
 }</t>
   </si>
   <si>
-    <t>https://www.jasnh.com/pdf/Vol6-No2.pdf</t>
-  </si>
-  <si>
-    <t>Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6(2).</t>
-  </si>
-  <si>
-    <t>@article{fayard_bassi_bernstein_roberts_2009,
+    <t xml:space="preserve">https://www.jasnh.com/pdf/Vol6-No2.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6(2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{fayard_bassi_bernstein_roberts_2009,
   title={Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006)},
   author={Fayard, Jennifer V. and Bassi, Alana K. and Bernstein, Daniel M. and Roberts, Brent W.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -155,13 +147,13 @@
 }</t>
   </si>
   <si>
-    <t>https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
-  </si>
-  <si>
-    <t>Besman, M., Dubensky, C., Dunsmore, L., &amp; Daubman, K. (2013). Cleanliness primes less severe moral judgments. Retrieved from: https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
-  </si>
-  <si>
-    <t>@misc{besman_dubensky_dunsmore_daubman_2013,
+    <t xml:space="preserve">https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besman, M., Dubensky, C., Dunsmore, L., &amp; Daubman, K. (2013). Cleanliness primes less severe moral judgments. Retrieved from: https://web.archive.org/web/20191117063540/http://www.psychfiledrawer.org/replication.php?attempt=MTQ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{besman_dubensky_dunsmore_daubman_2013,
   title={Cleanliness primes less severe moral judgments},
   author={Besman, M. and Dubensky, C. and Dunsmore, L. and Daubman, K.},
   year={2013},
@@ -170,13 +162,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/97</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2021, May 4). [97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure? Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2021_datacolada_97,
+    <t xml:space="preserve">https://datacolada.org/97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2021, May 4). [97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure? Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2021_datacolada_97,
   title={[97] Data Replicada #10: Does Goal Conflict Affect Time Spent on Work and Leisure?},
   author={Simmons, J. and Nelson, L. D.},
   year={2021},
@@ -187,13 +179,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/83</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group? Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2020_datacolada_83,
+    <t xml:space="preserve">https://datacolada.org/83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group? Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_83,
   title={[83] Data Replicada #2: Do Self-Construal and Group Size Influence How People Make Choices on Behalf of a Group?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -202,13 +194,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/84</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice? Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2020_datacolada_84,
+    <t xml:space="preserve">https://datacolada.org/84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice? Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_84,
   title={[84] Data Replicada #3: Does Self-Concept Uncertainty Influence Magazine Subscription Choice?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -217,13 +209,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/90</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness? Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2020_datacolada_90,
+    <t xml:space="preserve">https://datacolada.org/90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness? Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_90,
   title={[90] Data Replicada #7: Does Displaying Multiple Copies of a Product Increase Its Perceived Effectiveness?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -232,13 +224,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/aczvt</t>
-  </si>
-  <si>
-    <t>Brown, B. T., Kleinberg, B., Hicks, G., Bentley, H., Attridge, P. R., Eboigbe, S., … Brown, K. (2023, September 28). Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1). Retrieved from osf.io/aczvt</t>
-  </si>
-  <si>
-    <t>@misc{brown_kleinberg_hicks_bentley_attridge_eboigbe_devitt_vazquez_beyan_brown_2023,
+    <t xml:space="preserve">https://osf.io/aczvt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown, B. T., Kleinberg, B., Hicks, G., Bentley, H., Attridge, P. R., Eboigbe, S., … Brown, K. (2023, September 28). Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1). Retrieved from osf.io/aczvt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{brown_kleinberg_hicks_bentley_attridge_eboigbe_devitt_vazquez_beyan_brown_2023,
  title={Replication of Nurmsoo &amp; Bloom (2008, PS, Study 1)},
  url={osf.io/aczvt},
  publisher={OSF},
@@ -248,13 +240,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/8nzfm/</t>
-  </si>
-  <si>
-    <t>Papenmeier, F., &amp; Rebholz, T. R. (2023, September). Bimodal Flanker: Audio vs. Visual. Retrieved from https://osf.io/8nzfm/</t>
-  </si>
-  <si>
-    <t>@misc{papenmeier_rebholz_2023,
+    <t xml:space="preserve">https://osf.io/8nzfm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papenmeier, F., &amp; Rebholz, T. R. (2023, September). Bimodal Flanker: Audio vs. Visual. Retrieved from https://osf.io/8nzfm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{papenmeier_rebholz_2023,
  title={Bimodal Flanker: Audio vs. Visual},
  url={osf.io/8nzfm},
  publisher={OSF},
@@ -264,13 +256,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/92</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side? Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2020_datacolada_92,
+    <t xml:space="preserve">https://datacolada.org/92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side? Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_92,
   title={[92] Data Replicada #8: Is The Left-Digit Bias Stronger When Prices Are Presented Side-By-Side?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -279,13 +271,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/94</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [94] Data Replicada #9: Are Progression Ads More Credible? Data Colada. https://datacolada.org/94</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2020_datacolada_94,
+    <t xml:space="preserve">https://datacolada.org/94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [94] Data Replicada #9: Are Progression Ads More Credible? Data Colada. https://datacolada.org/94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_94,
   title={[94] Data Replicada #9: Are Progression Ads More Credible?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -294,22 +286,22 @@
 }</t>
   </si>
   <si>
-    <t>https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
-  </si>
-  <si>
-    <t>Chan, C. H. &amp; Feldman, G. Weinstein (1984): Replication and extension. [Unpublished manuscript]. Retrieved from https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
-  </si>
-  <si>
-    <t>@misc{Chan2020Weinstein, author = {Chan, Chun Him and Feldman, Gilad}, title = {Weinstein (1984): Replication and extension}, year = {2020}, howpublished = {Unpublished manuscript}, url = {https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk} }</t>
-  </si>
-  <si>
-    <t>https://datacolada.org/82</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2019). [82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking? Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2019_datacolada_82,
+    <t xml:space="preserve">https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chan, C. H. &amp; Feldman, G. Weinstein (1984): Replication and extension. [Unpublished manuscript]. Retrieved from https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{Chan2020Weinstein, author = {Chan, Chun Him and Feldman, Gilad}, title = {Weinstein (1984): Replication and extension}, year = {2020}, howpublished = {Unpublished manuscript}, url = {https://docs.google.com/document/d/10OKLI0-Kw2D7SDyLU_Ieql88gLtbnYGSyZhCBqsEAyk} }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://datacolada.org/82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2019). [82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking? Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2019_datacolada_82,
   title={[82] Data Replicada #1: Do Elevated Viewpoints Increase Risk Taking?},
   author={Simmons, J. and Nelson, L. D.},
   year={2019},
@@ -318,13 +310,13 @@
 }</t>
   </si>
   <si>
-    <t>https://replications.clearerthinking.org/replication-2022psci33-8</t>
-  </si>
-  <si>
-    <t>Transparent Replications by Clearer Thinking. (2024). Report #11: Replication of a study from “Changes in the prevalence of thin bodies bias young women’s judgments about body size” (Psychological Science | Devine et al., 2022) https://replications.clearerthinking.org/replication-2022psci33-8</t>
-  </si>
-  <si>
-    <t>@misc{clearer_thinking_2024_report11,
+    <t xml:space="preserve">https://replications.clearerthinking.org/replication-2022psci33-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparent Replications by Clearer Thinking. (2024). Report #11: Replication of a study from “Changes in the prevalence of thin bodies bias young women’s judgments about body size” (Psychological Science | Devine et al., 2022) https://replications.clearerthinking.org/replication-2022psci33-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{clearer_thinking_2024_report11,
   title={Report #11: Replication of a study from "Changes in the prevalence of thin bodies bias young women's judgments about body size" (Psychological Science | Devine et al., 2022)},
   author={{Transparent Replications by Clearer Thinking}},
   year={2024},
@@ -333,13 +325,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/74892/</t>
-  </si>
-  <si>
-    <t>Pavlović, Z. (2023, April 8). First impression replication study (Asch, 1945, Experiment 1).</t>
-  </si>
-  <si>
-    <t>@misc{pavlović_kaiser_2024,
+    <t xml:space="preserve">https://osf.io/74892/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavlović, Z. (2023, April 8). First impression replication study (Asch, 1945, Experiment 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{pavlović_kaiser_2024,
  title={First impression replication study (Asch, 1945, Experiment 1)},
  url={osf.io/74892},
  publisher={OSF},
@@ -349,13 +341,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ns26x</t>
-  </si>
-  <si>
-    <t>Lau &amp; Feldman, Van Boven and Ashworth (2007): Replication and extension</t>
-  </si>
-  <si>
-    <t>@misc{chin_feldman_2025,
+    <t xml:space="preserve">https://osf.io/ns26x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lau &amp; Feldman, Van Boven and Ashworth (2007): Replication and extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{chin_feldman_2025,
  title={Revisiting the past-future emotional asymmetry:  Replication and extensions of Van Boven and Ashworth (2007)},
  url={osf.io/gcf3v},
  publisher={OSF},
@@ -365,13 +357,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/87</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments? Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2020_datacolada_87,
+    <t xml:space="preserve">https://datacolada.org/87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments? Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_87,
   title={[87] Data Replicada #5: Do Human-Like Products Inspire More Holistic Judgments?},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -380,13 +372,13 @@
 }</t>
   </si>
   <si>
-    <t>https://www.tijdschriftdepsycholoog.nl/wp-content/uploads/2015/10/Dijkstra-K.-Verkoeijen-P.-Van-Kuijk-I.-Soke-Yee-Chow-Bakker-A.-Zwaan-R.-2015.-Leidt-het-lezen-van-literaire-fictie-tot-meer-emphatie.-De-Psycholoog-10-10-21..pdf</t>
-  </si>
-  <si>
-    <t>Dijkstra, K., Verkoeijen, P., van Kuijk, I., Yee Chow, S., Bakker, A., &amp; Zwaan, R. (2015). Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013). De Psycholoog, 50(10), 10–21. Retrieved from http://hdl.handle.net/1765/98670</t>
-  </si>
-  <si>
-    <t>@article{dijkstra_verkoeijen_vankuijk_yeechow_bakker_zwaan_2015,
+    <t xml:space="preserve">https://www.tijdschriftdepsycholoog.nl/wp-content/uploads/2015/10/Dijkstra-K.-Verkoeijen-P.-Van-Kuijk-I.-Soke-Yee-Chow-Bakker-A.-Zwaan-R.-2015.-Leidt-het-lezen-van-literaire-fictie-tot-meer-emphatie.-De-Psycholoog-10-10-21..pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijkstra, K., Verkoeijen, P., van Kuijk, I., Yee Chow, S., Bakker, A., &amp; Zwaan, R. (2015). Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013). De Psycholoog, 50(10), 10–21. Retrieved from http://hdl.handle.net/1765/98670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{dijkstra_verkoeijen_vankuijk_yeechow_bakker_zwaan_2015,
   title={Leidt het lezen van literaire fictie tot meer empathie? : een replicatiestudie van Kidd en Castano (2013)},
   author={Dijkstra, K. and Verkoeijen, P. and van Kuijk, I. and Yee Chow, S. and Bakker, A. and Zwaan, R.},
   journal={De Psycholoog},
@@ -398,13 +390,13 @@
 }</t>
   </si>
   <si>
-    <t>https://datacolada.org/89</t>
-  </si>
-  <si>
-    <t>Simmons, J. &amp;. Nelson, L.D. (2020). [89] Data Replicada #6: The Problem of (Weird) Differential Attrition. Data Colada.</t>
-  </si>
-  <si>
-    <t>@misc{simmons_nelson_2020_datacolada_89,
+    <t xml:space="preserve">https://datacolada.org/89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simmons, J. &amp;. Nelson, L.D. (2020). [89] Data Replicada #6: The Problem of (Weird) Differential Attrition. Data Colada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{simmons_nelson_2020_datacolada_89,
   title={[89] Data Replicada #6: The Problem of (Weird) Differential Attrition},
   author={Simmons, J. and Nelson, L. D.},
   year={2020},
@@ -413,13 +405,13 @@
 }</t>
   </si>
   <si>
-    <t>https://docs.google.com/document/d/1hW5moEcdB-U0Ud-MNOB5iYSkeQL60SqVekufodODxDQ/edit?tab=t.0</t>
-  </si>
-  <si>
-    <t>Hongye, L., &amp; Feldman, G. (2020). Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986).</t>
-  </si>
-  <si>
-    <t>@misc{hongye_feldman_2020_revisiting,
+    <t xml:space="preserve">https://docs.google.com/document/d/1hW5moEcdB-U0Ud-MNOB5iYSkeQL60SqVekufodODxDQ/edit?tab=t.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hongye, L., &amp; Feldman, G. (2020). Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{hongye_feldman_2020_revisiting,
   title={Revisiting Illusion of Invulnerability effect: Replication and extension of Perloff and Fetzer (1986)},
   author={Hongye, L. and Feldman, G.},
   year={2020},
@@ -427,19 +419,19 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ht4d5</t>
-  </si>
-  <si>
-    <t>SCORE replication of Nyhan, B., &amp; Reifler, J. (2015). Displacing Misinformation about Events: An Experimental Test of Causal Corrections. Journal of Experimental Political Science, 2(1), 81–93. https://doi.org/10.1017/xps.2014.22</t>
-  </si>
-  <si>
-    <t>https://osf.io/9hjxc</t>
-  </si>
-  <si>
-    <t>Baskin, E., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Hahn, K. (2025, November 18). Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12. Retrieved from osf.io/cwmb5</t>
-  </si>
-  <si>
-    <t>@misc{baskin_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_2025,
+    <t xml:space="preserve">https://osf.io/ht4d5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCORE replication of Nyhan, B., &amp; Reifler, J. (2015). Displacing Misinformation about Events: An Experimental Test of Causal Corrections. Journal of Experimental Political Science, 2(1), 81–93. https://doi.org/10.1017/xps.2014.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/9hjxc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baskin, E., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Hahn, K. (2025, November 18). Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12. Retrieved from osf.io/cwmb5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{baskin_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_2025,
  title={Ritov_OrgBehavior_2014_d24p - Baskin - New Data Replication - 67z12},
  url={osf.io/cwmb5},
  publisher={OSF},
@@ -449,13 +441,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/36w4c</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442. Retrieved from osf.io/23ghe</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t xml:space="preserve">https://osf.io/36w4c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442. Retrieved from osf.io/23ghe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Lammers_JournPerSocPsy_2018_e3G7 - Baskin - New Data Replication - 6o442},
  url={osf.io/23ghe},
  publisher={OSF},
@@ -465,13 +457,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/r58ch</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56. Retrieved from osf.io/n35c2</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t xml:space="preserve">https://osf.io/r58ch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56. Retrieved from osf.io/n35c2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Kausel_OrgBehavior_2015_5XEE - Baskin - New Data Replication - 21z56},
  url={osf.io/n35c2},
  publisher={OSF},
@@ -481,13 +473,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ahgfx</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2. Retrieved from osf.io/ujg2c</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t xml:space="preserve">https://osf.io/ahgfx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2. Retrieved from osf.io/ujg2c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Lu_OrgBehavior_2017_N8pB - Baskin - New Data Replication - 2ggz2},
  url={osf.io/ujg2c},
  publisher={OSF},
@@ -497,13 +489,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/gyse6</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2. Retrieved from osf.io/vhu2x</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t xml:space="preserve">https://osf.io/gyse6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2. Retrieved from osf.io/vhu2x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Ready_AmEduResJourn_2011_bY2A - Reed - Secondary Data Replication - 6zoo2},
  url={osf.io/vhu2x},
  publisher={OSF},
@@ -513,13 +505,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/kpn34</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6. Retrieved from osf.io/5k6jg</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t xml:space="preserve">https://osf.io/kpn34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6. Retrieved from osf.io/5k6jg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Wilcox_JournMarketRes_2009_OKRy - Baskin - New Data Replication - 281g6},
  url={osf.io/5k6jg},
  publisher={OSF},
@@ -529,13 +521,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/28mjt</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2. Retrieved from osf.io/wjh3c</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
+    <t xml:space="preserve">https://osf.io/28mjt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2025, November 18). Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2. Retrieved from osf.io/wjh3c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2025,
  title={Etkin_JournMarketRes_2015_aag9 - Baskin - New Data Replication - 6z1o2},
  url={osf.io/wjh3c},
  publisher={OSF},
@@ -545,13 +537,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/x9j47</t>
-  </si>
-  <si>
-    <t>Yoon, S., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k. Retrieved from osf.io/e9y6b</t>
-  </si>
-  <si>
-    <t>@misc{yoon_tyner_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/x9j47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoon, S., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k. Retrieved from osf.io/e9y6b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{yoon_tyner_loomas_miske_luis_2025,
  title={LeBoeuf_JournMarketRes_2010_EKBZ - Yoon - New Data Replication - 618k},
  url={osf.io/e9y6b},
  publisher={OSF},
@@ -561,13 +553,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/dnqrv</t>
-  </si>
-  <si>
-    <t>de Leeuw, J. R., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Ostrowski, R. P. (2025, November 18). Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6. Retrieved from osf.io/ty5be</t>
-  </si>
-  <si>
-    <t>@misc{de leeuw_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_bader_et al._2025,
+    <t xml:space="preserve">https://osf.io/dnqrv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de Leeuw, J. R., Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., … Ostrowski, R. P. (2025, November 18). Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6. Retrieved from osf.io/ty5be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{de leeuw_parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_bader_et al._2025,
  title={Rich_JournExPsychGen_2018_LbEB - deLeeuw - New Data Replication - 6zzo6},
  url={osf.io/ty5be},
  publisher={OSF},
@@ -577,13 +569,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/3u8x9</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16. Retrieved from osf.io/er54t</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t xml:space="preserve">https://osf.io/3u8x9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16. Retrieved from osf.io/er54t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Tai_EurSocioRev_2013_vGqL - Reed - Secondary Data Replication - 67y16},
  url={osf.io/er54t},
  publisher={OSF},
@@ -593,13 +585,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/4usmq</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6. Retrieved from osf.io/9mx5w</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t xml:space="preserve">https://osf.io/4usmq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6. Retrieved from osf.io/9mx5w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Brons_EurSocioRev_2017_e227 - Reed - Secondary Data Replication - 24yw6},
  url={osf.io/9mx5w},
  publisher={OSF},
@@ -609,13 +601,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/3d97y</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2. Retrieved from osf.io/rywgh</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_hong_duan_reed_2025,
+    <t xml:space="preserve">https://osf.io/3d97y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2. Retrieved from osf.io/rywgh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_hong_duan_reed_2025,
  title={Humphrey_SocSciMed_2017_Eb2N - Reed - Secondary Data Replication - 23yw2},
  url={osf.io/rywgh},
  publisher={OSF},
@@ -625,13 +617,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/x46bu</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6. Retrieved from osf.io/bawh3</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t xml:space="preserve">https://osf.io/x46bu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6. Retrieved from osf.io/bawh3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Bollerslev_RevFinStudies_2009_QllV - Reed - Secondary Data Replication - 249w6},
  url={osf.io/bawh3},
  publisher={OSF},
@@ -641,13 +633,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/n6jca</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Bonfiglio, D. B. V. (2025, December 1). Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2. Retrieved from osf.io/vg6zy</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_mallik_bonfiglio_2025,
+    <t xml:space="preserve">https://osf.io/n6jca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Bonfiglio, D. B. V. (2025, December 1). Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2. Retrieved from osf.io/vg6zy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_mallik_bonfiglio_2025,
  title={Bursztyn_AmEcoRev_2017_VB9K - Mallik - New Data Replication - 2g7z2},
  url={osf.io/vg6zy},
  publisher={OSF},
@@ -657,13 +649,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/7qjzp</t>
-  </si>
-  <si>
-    <t>OYEBANJO, A., Adeyemi, A. F., Loomas, Z., Miske, O., Luis, B., Tyner, A. H., … Parsons, E. S. (2025, November 18). Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81. Retrieved from osf.io/en9md</t>
-  </si>
-  <si>
-    <t>@misc{oyebanjo_adeyemi_loomas_miske_luis_tyner_kline struhl_parsons_2025,
+    <t xml:space="preserve">https://osf.io/7qjzp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OYEBANJO, A., Adeyemi, A. F., Loomas, Z., Miske, O., Luis, B., Tyner, A. H., … Parsons, E. S. (2025, November 18). Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81. Retrieved from osf.io/en9md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{oyebanjo_adeyemi_loomas_miske_luis_tyner_kline struhl_parsons_2025,
  title={Andrew_SocialForces_2014_x0pA - Festus &amp; Oyebanjo - Secondary Data Replication - 8z81},
  url={osf.io/en9md},
  publisher={OSF},
@@ -673,13 +665,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/cdrmk</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Mallinson, D. J. (2025, November 18). Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182. Retrieved from osf.io/h7av9</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_mallinson_2025,
+    <t xml:space="preserve">https://osf.io/cdrmk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Mallinson, D. J. (2025, November 18). Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182. Retrieved from osf.io/h7av9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_mallinson_2025,
  title={Denson_AmEduResJourn_2009_zb3Y - Méndez-Chacón - Secondary Data Replication - 2y182},
  url={osf.io/h7av9},
  publisher={OSF},
@@ -689,13 +681,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/39upt</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w. Retrieved from osf.io/bmzuf</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
+    <t xml:space="preserve">https://osf.io/39upt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2025, November 18). Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w. Retrieved from osf.io/bmzuf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2025,
  title={Kieffer_AmEduResJourn_2011_Kybl - Reed - Secondary Data Replication - 23w8w},
  url={osf.io/bmzuf},
  publisher={OSF},
@@ -705,13 +697,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/nbc6v</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Berry, Z. (2025, December 14). Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2. Retrieved from osf.io/tmn3q</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_berry_2025,
+    <t xml:space="preserve">https://osf.io/nbc6v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Berry, Z. (2025, December 14). Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2. Retrieved from osf.io/tmn3q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_berry_2025,
  title={Bhattacharjee_JournPerSocPsy_2017_Br0x - Berry - New Data Replication - 658m2},
  url={osf.io/tmn3q},
  publisher={OSF},
@@ -721,13 +713,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/gn3vj</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6. Retrieved from osf.io/uwnya</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t xml:space="preserve">https://osf.io/gn3vj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6. Retrieved from osf.io/uwnya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Boehm_PsychologSci_2015_zlBL - Méndez-Chacón - Secondary Data Replication - 651m6},
  url={osf.io/uwnya},
  publisher={OSF},
@@ -737,13 +729,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/qev3x</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Tomašević, A. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6. Retrieved from osf.io/e48gd</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_kołczyńska_silverstein_et al._2025,
+    <t xml:space="preserve">https://osf.io/qev3x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Tomašević, A. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6. Retrieved from osf.io/e48gd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_kołczyńska_silverstein_et al._2025,
  title={McLaren_WorldPolitics_2012_wRvv - Urbanska/Kolczynska - Secondary Data Replication - 65wm6},
  url={osf.io/e48gd},
  publisher={OSF},
@@ -753,13 +745,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/e9j6y</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96. Retrieved from osf.io/qgm2c</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t xml:space="preserve">https://osf.io/e9j6y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96. Retrieved from osf.io/qgm2c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Raley_JournMarFam_2012_D2LY - Méndez-Chacón - Secondary Data Replication - 65o96},
  url={osf.io/qgm2c},
  publisher={OSF},
@@ -769,13 +761,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/srk8q</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg. Retrieved from osf.io/xwthk</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
+    <t xml:space="preserve">https://osf.io/srk8q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Méndez-Chacón, E. (2025, November 18). Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg. Retrieved from osf.io/xwthk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_méndez-chacón_2025,
  title={Welzel_BritJournPoliSci_2012_qgWj - Méndez-Chacón - Secondary Data Replication - 23wwg},
  url={osf.io/xwthk},
  publisher={OSF},
@@ -785,13 +777,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/qfh2r</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m. Retrieved from osf.io/n7m39</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t xml:space="preserve">https://osf.io/qfh2r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m. Retrieved from osf.io/n7m39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Hiskey_CompPolitStu_2018_AYQG - Méndez-Chacón - Secondary Data Replication - 6m33m},
  url={osf.io/n7m39},
  publisher={OSF},
@@ -801,13 +793,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/8mqzu</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Zhang, Y. (2025, November 18). Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky. Retrieved from osf.io/bcqem</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_zhang_2025,
+    <t xml:space="preserve">https://osf.io/8mqzu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Zhang, Y. (2025, November 18). Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky. Retrieved from osf.io/bcqem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_zhang_2025,
  title={Weidmann_BritJournPoliSci_2013_JRpA - Zhang - Secondary Data Replication - 2g7ky},
  url={osf.io/bcqem},
  publisher={OSF},
@@ -817,13 +809,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/syq4e</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok. Retrieved from osf.io/gk92w</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t xml:space="preserve">https://osf.io/syq4e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok. Retrieved from osf.io/gk92w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Kollmeyer_AmJournSocio_2009_EJpm - Méndez-Chacón - Secondary Data Replication - 288ok},
  url={osf.io/gk92w},
  publisher={OSF},
@@ -833,13 +825,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/6rpxu</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y. Retrieved from osf.io/tz9ef</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t xml:space="preserve">https://osf.io/6rpxu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y. Retrieved from osf.io/tz9ef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Karraker_JournMarFam_2013_Vj0p - Méndez-Chacón - Secondary Data Replication - 2g79y},
  url={osf.io/tz9ef},
  publisher={OSF},
@@ -849,13 +841,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/u58za</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9. Retrieved from osf.io/qxk38</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
+    <t xml:space="preserve">https://osf.io/u58za</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Méndez-Chacón, E. (2025, November 18). Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9. Retrieved from osf.io/qxk38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_méndez-chacón_2025,
  title={Zakharova_CompPolitStu_2014_qYr7 - Méndez-Chacón - Secondary Data Replication - 675m9},
  url={osf.io/qxk38},
  publisher={OSF},
@@ -865,13 +857,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/b2xma</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6. Retrieved from osf.io/shvdk</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t xml:space="preserve">https://osf.io/b2xma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6. Retrieved from osf.io/shvdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={Ahlerup_WorldDev_2016_E5qr - Boxell - Secondary Data Replication - 65gm6},
  url={osf.io/shvdk},
  publisher={OSF},
@@ -881,13 +873,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/gvayj</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12. Retrieved from osf.io/ub4c6</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t xml:space="preserve">https://osf.io/gvayj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12. Retrieved from osf.io/ub4c6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={Liang_JournPoliEco_2018_q8xv - Boxell - Secondary Data Replication - 23g12},
  url={osf.io/ub4c6},
  publisher={OSF},
@@ -897,13 +889,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ck8aq</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2. Retrieved from osf.io/df36m</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t xml:space="preserve">https://osf.io/ck8aq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2. Retrieved from osf.io/df36m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={BATESON_AmPoliSciRev_2012_RYKv - Boxell - Secondary Data Replication - 2k5g2},
  url={osf.io/df36m},
  publisher={OSF},
@@ -913,13 +905,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/c6a8e</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16. Retrieved from osf.io/as7te</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
+    <t xml:space="preserve">https://osf.io/c6a8e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Boxell, L. (2025, November 18). LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16. Retrieved from osf.io/as7te</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_boxell_2025,
  title={LINDQVIST_AmPoliSciRev_2010_OeGv - Boxell - Secondary Data Replication - 24m16},
  url={osf.io/as7te},
  publisher={OSF},
@@ -929,13 +921,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/skwev</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7. Retrieved from osf.io/yv2am</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
+    <t xml:space="preserve">https://osf.io/skwev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7. Retrieved from osf.io/yv2am</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
  title={Roberts_JournEduPsych_2010_OYX0 - Szabelska - Secondary Data Replication - 658y7},
  url={osf.io/yv2am},
  publisher={OSF},
@@ -945,13 +937,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/yd9bg</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Vermeulen, J. (2025, November 18). van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487. Retrieved from osf.io/697dv</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_vargo_vermeulen_2025,
+    <t xml:space="preserve">https://osf.io/yd9bg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Vermeulen, J. (2025, November 18). van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487. Retrieved from osf.io/697dv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_vargo_vermeulen_2025,
  title={van Gastel_PsychMed_2013_AOQj - Vargo - Secondary Data Replication - 21487},
  url={osf.io/697dv},
  publisher={OSF},
@@ -961,13 +953,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/2f35a</t>
-  </si>
-  <si>
-    <t>Chartier, C. R., Lewis, S. C., Kline Struhl, M., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189. Retrieved from osf.io/agv64</t>
-  </si>
-  <si>
-    <t>@misc{chartier_lewis_kline struhl_miske_luis_loomas_2025,
+    <t xml:space="preserve">https://osf.io/2f35a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chartier, C. R., Lewis, S. C., Kline Struhl, M., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189. Retrieved from osf.io/agv64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{chartier_lewis_kline struhl_miske_luis_loomas_2025,
  title={Rozenkrants_JournConsRes_2017_5JE - Chartier - New Data Replication - z189},
  url={osf.io/agv64},
  publisher={OSF},
@@ -977,13 +969,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/cnbt5</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Ramljak, M. (2025, November 18). Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2. Retrieved from osf.io/em34f</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_fox_tyner_hahn_ramljak_2025,
+    <t xml:space="preserve">https://osf.io/cnbt5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Ramljak, M. (2025, November 18). Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2. Retrieved from osf.io/em34f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_ramljak_2025,
  title={Seaton_AmEduResJourn_2010_Blxd - Ramljak - Secondary Data Replication - 6z3o2},
  url={osf.io/em34f},
  publisher={OSF},
@@ -993,13 +985,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/a6nsp</t>
-  </si>
-  <si>
-    <t>Field, S., Loomas, Z., Miske, O., Luis, B., &amp; Jarke-Neuert, J. (2025, November 18). Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182. Retrieved from osf.io/p9k76</t>
-  </si>
-  <si>
-    <t>@misc{field_loomas_miske_luis_jarke-neuert_2025,
+    <t xml:space="preserve">https://osf.io/a6nsp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field, S., Loomas, Z., Miske, O., Luis, B., &amp; Jarke-Neuert, J. (2025, November 18). Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182. Retrieved from osf.io/p9k76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{field_loomas_miske_luis_jarke-neuert_2025,
  title={Janssen_ExpEco_2011_VvZX - Jarke-Neuert - New Data Replication - 4182},
  url={osf.io/p9k76},
  publisher={OSF},
@@ -1009,13 +1001,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/5869t</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Baník, G. (2025, November 18). BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k. Retrieved from osf.io/8ndcx</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_adamkovic_ropovik_baník_2025,
+    <t xml:space="preserve">https://osf.io/5869t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., … Baník, G. (2025, November 18). BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k. Retrieved from osf.io/8ndcx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_adamkovic_ropovik_baník_2025,
  title={BERSANI_Criminology_2013_zmYY - Adamkovic - Secondary Data Replication - 6zz3k},
  url={osf.io/8ndcx},
  publisher={OSF},
@@ -1025,13 +1017,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/xkwj9</t>
-  </si>
-  <si>
-    <t>Molden, D. C. (2025, November 18). Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g. Retrieved from osf.io/w8xun</t>
-  </si>
-  <si>
-    <t>@misc{molden_2025,
+    <t xml:space="preserve">https://osf.io/xkwj9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molden, D. C. (2025, November 18). Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g. Retrieved from osf.io/w8xun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{molden_2025,
  title={Sandra_Cognition_2018_0qar - Molden - New Data Replication - 20g},
  url={osf.io/w8xun},
  publisher={OSF},
@@ -1041,13 +1033,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/xyrv6</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Gooty, J. (2025, November 18). Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12. Retrieved from osf.io/7k8sy</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_sargent_gooty_2025,
+    <t xml:space="preserve">https://osf.io/xyrv6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Gooty, J. (2025, November 18). Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12. Retrieved from osf.io/7k8sy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_sargent_gooty_2025,
  title={Popper_LeadQuart_2009_aYyR - Gooty - New Data Replication - 23w12},
  url={osf.io/7k8sy},
  publisher={OSF},
@@ -1057,13 +1049,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/phz9x</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96. Retrieved from osf.io/q7hpx</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
+    <t xml:space="preserve">https://osf.io/phz9x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96. Retrieved from osf.io/q7hpx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
  title={Vermeulen_EurJournPersonality_2010_7RR2 - Wilbiks - New Data Replication - 86m96},
  url={osf.io/q7hpx},
  publisher={OSF},
@@ -1073,13 +1065,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/zybuc</t>
-  </si>
-  <si>
-    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1. Retrieved from osf.io/u5d2y</t>
-  </si>
-  <si>
-    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t xml:space="preserve">https://osf.io/zybuc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1. Retrieved from osf.io/u5d2y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={Armon_EurJournPersonality_2013_mJDj - COS - Secondary Data Replication - y7g1},
  url={osf.io/u5d2y},
  publisher={OSF},
@@ -1089,13 +1081,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/dkcu6</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7. Retrieved from osf.io/h8ecm</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
+    <t xml:space="preserve">https://osf.io/dkcu6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Szabelska, A. (2025, November 18). Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7. Retrieved from osf.io/h8ecm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_szabelska_2025,
  title={Barsbai_AmEcoJourn_2017_9OK1 - Szabelska - Secondary Data Replication - 658g7},
  url={osf.io/h8ecm},
  publisher={OSF},
@@ -1105,13 +1097,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/qmbxr</t>
-  </si>
-  <si>
-    <t>Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6. Retrieved from osf.io/p2st5</t>
-  </si>
-  <si>
-    <t>@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
+    <t xml:space="preserve">https://osf.io/qmbxr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Wilbiks, J. (2025, November 18). Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6. Retrieved from osf.io/p2st5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_wilbiks_2025,
  title={Yiend_ClinPsychSci_2015_LmBx - Wilbiks - New Data Replication - y2gz6},
  url={osf.io/p2st5},
  publisher={OSF},
@@ -1121,13 +1113,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/udbnf</t>
-  </si>
-  <si>
-    <t>Syed, M., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26. Retrieved from osf.io/f5b6c</t>
-  </si>
-  <si>
-    <t>@misc{syed_fox_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/udbnf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syed, M., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26. Retrieved from osf.io/f5b6c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{syed_fox_loomas_miske_luis_2025,
  title={Wetzel_EurJournPersonality_2016_Ovkm - Syed - New Data Replication - zz26},
  url={osf.io/f5b6c},
  publisher={OSF},
@@ -1137,13 +1129,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/qu793</t>
-  </si>
-  <si>
-    <t>Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17. Retrieved from osf.io/8qkrx</t>
-  </si>
-  <si>
-    <t>@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
+    <t xml:space="preserve">https://osf.io/qu793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17. Retrieved from osf.io/8qkrx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
  title={Ballard_JournAppPsych_2016_mBL1 - Safin - New Data Replication - 8m17},
  url={osf.io/8qkrx},
  publisher={OSF},
@@ -1153,13 +1145,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/5r28d</t>
-  </si>
-  <si>
-    <t>Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Kačmár, P. (2025, November 18). Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3. Retrieved from osf.io/h37zx</t>
-  </si>
-  <si>
-    <t>@misc{loomas_miske_luis_fox_tyner_hahn_kačmár_2025,
+    <t xml:space="preserve">https://osf.io/5r28d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Fox, N. W., Tyner, A. H., Hahn, K., &amp; Kačmár, P. (2025, November 18). Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3. Retrieved from osf.io/h37zx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_fox_tyner_hahn_kačmár_2025,
  title={Vadillo_JournExPsychGen_2016_BrGp - Kačmár - Secondary Data Replication - 247z3},
  url={osf.io/h37zx},
  publisher={OSF},
@@ -1169,13 +1161,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/dyn6j</t>
-  </si>
-  <si>
-    <t>Edlund, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk. Retrieved from osf.io/9qjhf</t>
-  </si>
-  <si>
-    <t>@misc{edlund_fox_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/dyn6j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edlund, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk. Retrieved from osf.io/9qjhf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{edlund_fox_loomas_miske_luis_2025,
  title={Navarrete_EvoHumanBehavior_2010_1X9W - Edlund - New Data Replication - 32mk},
  url={osf.io/9qjhf},
  publisher={OSF},
@@ -1185,13 +1177,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/8hnxg</t>
-  </si>
-  <si>
-    <t>Liu, A., Fox, N. W., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142. Retrieved from osf.io/nse8t</t>
-  </si>
-  <si>
-    <t>@misc{liu_fox_tyner_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/8hnxg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liu, A., Fox, N. W., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142. Retrieved from osf.io/nse8t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{liu_fox_tyner_loomas_miske_luis_2025,
  title={Li_WorldDev_2011_2GKO - Liu - Secondary Data Replication - 4142},
  url={osf.io/nse8t},
  publisher={OSF},
@@ -1201,13 +1193,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/9t4nh</t>
-  </si>
-  <si>
-    <t>Méndez-Chacón, E., Tutor, M., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496. Retrieved from osf.io/q4fpr</t>
-  </si>
-  <si>
-    <t>@misc{méndez-chacón_tutor_tyner_abatayo_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/9t4nh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Méndez-Chacón, E., Tutor, M., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496. Retrieved from osf.io/q4fpr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{méndez-chacón_tutor_tyner_abatayo_loomas_miske_luis_2025,
  title={Cohen_AmEcoRev_2015_2lb5 - Tutor/Méndez-Chacón - Secondary Data Replication - y496},
  url={osf.io/q4fpr},
  publisher={OSF},
@@ -1217,13 +1209,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/jx64p</t>
-  </si>
-  <si>
-    <t>Gooty, J., McBride, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Arendt, B. (2025, November 18). Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y. Retrieved from osf.io/sv4e8</t>
-  </si>
-  <si>
-    <t>@misc{gooty_mcbride_tyner_loomas_miske_luis_arendt_2025,
+    <t xml:space="preserve">https://osf.io/jx64p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gooty, J., McBride, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Arendt, B. (2025, November 18). Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y. Retrieved from osf.io/sv4e8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{gooty_mcbride_tyner_loomas_miske_luis_arendt_2025,
  title={Dumas_AcaManageJourn_2018_5KrD - Gooty - New Data Replication - 935y},
  url={osf.io/sv4e8},
  publisher={OSF},
@@ -1233,13 +1225,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/h7jfv</t>
-  </si>
-  <si>
-    <t>Axxe, E., Ramljak, M., Tyner, A. H., Loomas, Z., Luis, B., Miske, O., … Parsons, E. S. (2025, November 18). O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7. Retrieved from osf.io/7qnrs</t>
-  </si>
-  <si>
-    <t>@misc{axxe_ramljak_tyner_loomas_luis_miske_abatayo_parsons_2025,
+    <t xml:space="preserve">https://osf.io/h7jfv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axxe, E., Ramljak, M., Tyner, A. H., Loomas, Z., Luis, B., Miske, O., … Parsons, E. S. (2025, November 18). O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7. Retrieved from osf.io/7qnrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{axxe_ramljak_tyner_loomas_luis_miske_abatayo_parsons_2025,
  title={O’Brien_AmSocioRev_2015_7X54 - Ramljak/Axxe - Secondary Data Replication - 93k7},
  url={osf.io/7qnrs},
  publisher={OSF},
@@ -1249,13 +1241,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ab762</t>
-  </si>
-  <si>
-    <t>Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554. Retrieved from osf.io/afznv</t>
-  </si>
-  <si>
-    <t>@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
+    <t xml:space="preserve">https://osf.io/ab762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safin, V., Kline Struhl, M., Miske, O., Loomas, Z., Luis, B., Losi, M., &amp; Yttredahl, A. (2025, November 18). Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554. Retrieved from osf.io/afznv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{safin_kline struhl_miske_loomas_luis_losi_yttredahl_2025,
  title={Savani_PsychologSci_2010_88xa - Safin - New Data Replication - 1554},
  url={osf.io/afznv},
  publisher={OSF},
@@ -1265,13 +1257,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/b9rcg</t>
-  </si>
-  <si>
-    <t>Baskin, E., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m. Retrieved from osf.io/sw67c</t>
-  </si>
-  <si>
-    <t>@misc{baskin_tyner_miske_loomas_2025,
+    <t xml:space="preserve">https://osf.io/b9rcg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baskin, E., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m. Retrieved from osf.io/sw67c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{baskin_tyner_miske_loomas_2025,
  title={Zhu_JournMarketRes_2009_8w97 - Baskin - New Data Replication - gz2m},
  url={osf.io/sw67c},
  publisher={OSF},
@@ -1281,13 +1273,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/k79vj</t>
-  </si>
-  <si>
-    <t>Méndez-Chacón, E., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Abatayo, A. (2025, November 18). Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945. Retrieved from osf.io/tacvb</t>
-  </si>
-  <si>
-    <t>@misc{méndez-chacón_tyner_loomas_miske_luis_abatayo_2025,
+    <t xml:space="preserve">https://osf.io/k79vj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Méndez-Chacón, E., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Abatayo, A. (2025, November 18). Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945. Retrieved from osf.io/tacvb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{méndez-chacón_tyner_loomas_miske_luis_abatayo_2025,
  title={Kim_SocSciMed_2016_AqDO - Méndez-Chacón - Secondary Data Replication - 7945},
  url={osf.io/tacvb},
  publisher={OSF},
@@ -1297,13 +1289,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/vekdm</t>
-  </si>
-  <si>
-    <t>Leahy, K. E., Purol, M., Oh, J., Chopik, W. J., Kline Struhl, M., Miske, O., &amp; Loomas, Z. (2025, November 18). Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67. Retrieved from osf.io/8hp5j</t>
-  </si>
-  <si>
-    <t>@misc{leahy_purol_oh_chopik_kline struhl_miske_loomas_2025,
+    <t xml:space="preserve">https://osf.io/vekdm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leahy, K. E., Purol, M., Oh, J., Chopik, W. J., Kline Struhl, M., Miske, O., &amp; Loomas, Z. (2025, November 18). Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67. Retrieved from osf.io/8hp5j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{leahy_purol_oh_chopik_kline struhl_miske_loomas_2025,
  title={Nelson_JournConsRes_2009_eg1q - Chopik - New Data Replication - 6g67},
  url={osf.io/8hp5j},
  publisher={OSF},
@@ -1313,13 +1305,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/fzut6</t>
-  </si>
-  <si>
-    <t>Baskin, E., Kline Struhl, M., Miske, O., Luis, B., Loomas, Z., &amp; Parsons, E. S. (2025, November 18). Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1. Retrieved from osf.io/e52qx</t>
-  </si>
-  <si>
-    <t>@misc{baskin_kline struhl_miske_luis_loomas_parsons_2025,
+    <t xml:space="preserve">https://osf.io/fzut6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baskin, E., Kline Struhl, M., Miske, O., Luis, B., Loomas, Z., &amp; Parsons, E. S. (2025, November 18). Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1. Retrieved from osf.io/e52qx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{baskin_kline struhl_miske_luis_loomas_parsons_2025,
  title={Cutright_JournConsRes_2011_eg3p - Baskin - New Data Replication - yyy1},
  url={osf.io/e52qx},
  publisher={OSF},
@@ -1329,13 +1321,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/q4e35</t>
-  </si>
-  <si>
-    <t>Aczel, B., Szaszi, B., Bognar, M., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91. Retrieved from osf.io/2cjuw</t>
-  </si>
-  <si>
-    <t>@misc{aczel_szaszi_bognar_kline struhl_miske_loomas_luis_2025,
+    <t xml:space="preserve">https://osf.io/q4e35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aczel, B., Szaszi, B., Bognar, M., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91. Retrieved from osf.io/2cjuw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{aczel_szaszi_bognar_kline struhl_miske_loomas_luis_2025,
  title={Mason_JournExPsychGen_2012_eOQm - Bognar - New Data Replication - yk91},
  url={osf.io/2cjuw},
  publisher={OSF},
@@ -1345,13 +1337,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/xe3d2</t>
-  </si>
-  <si>
-    <t>Wilbiks, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z. Retrieved from osf.io/qtv6j</t>
-  </si>
-  <si>
-    <t>@misc{wilbiks_fox_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/xe3d2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilbiks, J., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z. Retrieved from osf.io/qtv6j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{wilbiks_fox_loomas_miske_luis_2025,
  title={Tsay_OrgBehavior_2014_exd7 - Wilbiks - New Data Replication - 318z},
  url={osf.io/qtv6j},
  publisher={OSF},
@@ -1361,13 +1353,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/2vmgw</t>
-  </si>
-  <si>
-    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m. Retrieved from osf.io/mjfwp</t>
-  </si>
-  <si>
-    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t xml:space="preserve">https://osf.io/2vmgw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m. Retrieved from osf.io/mjfwp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={Yang_JournMarketRes_2013_G1Lr - COS - New Data Replication - gz9m},
  url={osf.io/mjfwp},
  publisher={OSF},
@@ -1377,13 +1369,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/3cp2d</t>
-  </si>
-  <si>
-    <t>Le Forestier, J. M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., Loomas, Z., &amp; Ray, N. (2025, November 18). Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3. Retrieved from osf.io/tvhma</t>
-  </si>
-  <si>
-    <t>@misc{le forestier_tyner_miske_luis_parsons_loomas_ray_2025,
+    <t xml:space="preserve">https://osf.io/3cp2d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Forestier, J. M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., Loomas, Z., &amp; Ray, N. (2025, November 18). Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3. Retrieved from osf.io/tvhma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{le forestier_tyner_miske_luis_parsons_loomas_ray_2025,
  title={Calzo_HealthPsych_2013_gRWz - Le Forestier - New Data Replication - m5k3},
  url={osf.io/tvhma},
  publisher={OSF},
@@ -1393,13 +1385,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/8npm5</t>
-  </si>
-  <si>
-    <t>Allen, P., Dujmović, M., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8. Retrieved from osf.io/834de</t>
-  </si>
-  <si>
-    <t>@misc{allen_dujmović_kline struhl_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/8npm5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allen, P., Dujmović, M., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8. Retrieved from osf.io/834de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{allen_dujmović_kline struhl_loomas_miske_luis_2025,
  title={Srinivasan_Cognition_2010_GXEW - Allen - New Data Replication - 67g8},
  url={osf.io/834de},
  publisher={OSF},
@@ -1409,13 +1401,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/hmune</t>
-  </si>
-  <si>
-    <t>Szabelska, A., Ghasemi, O., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796. Retrieved from osf.io/su48v</t>
-  </si>
-  <si>
-    <t>@misc{szabelska_ghasemi_tyner_abatayo_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/hmune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szabelska, A., Ghasemi, O., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796. Retrieved from osf.io/su48v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{szabelska_ghasemi_tyner_abatayo_loomas_miske_luis_2025,
  title={Buchner_EvoHumanBehavior_2009_j2yd - Ghasemi/Szabelska - Secondary Data Replication - 5796},
  url={osf.io/su48v},
  publisher={OSF},
@@ -1425,13 +1417,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/9s4e6</t>
-  </si>
-  <si>
-    <t>Steffens, N. K., Munt, K. A., Peters, K. O., Fox, N. W., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g. Retrieved from osf.io/ty9du</t>
-  </si>
-  <si>
-    <t>@misc{steffens_munt_peters_fox_miske_loomas_luis_2025,
+    <t xml:space="preserve">https://osf.io/9s4e6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steffens, N. K., Munt, K. A., Peters, K. O., Fox, N. W., Miske, O., Loomas, Z., &amp; Luis, B. (2025, November 18). Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g. Retrieved from osf.io/ty9du</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{steffens_munt_peters_fox_miske_loomas_luis_2025,
  title={Rubin_LeadQuart_2010_lJ0w - Steffens - New Data Replication - 931g},
  url={osf.io/ty9du},
  publisher={OSF},
@@ -1441,13 +1433,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/fqdh4</t>
-  </si>
-  <si>
-    <t>Weller, N., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Landgrave, M. G. (2025, November 18). Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m. Retrieved from osf.io/2ug8x</t>
-  </si>
-  <si>
-    <t>@misc{weller_tyner_loomas_miske_luis_landgrave_2025,
+    <t xml:space="preserve">https://osf.io/fqdh4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weller, N., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Landgrave, M. G. (2025, November 18). Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m. Retrieved from osf.io/2ug8x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{weller_tyner_loomas_miske_luis_landgrave_2025,
  title={Einstein_AmJourPoliSci_2017_mxyQ - Weller - New Data Replication - g77m},
  url={osf.io/2ug8x},
  publisher={OSF},
@@ -1457,13 +1449,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/tywer</t>
-  </si>
-  <si>
-    <t>Mallik, P. R., Metzger, M., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Final Report. Retrieved from osf.io/4hau3</t>
-  </si>
-  <si>
-    <t>@misc{mallik_metzger_kline struhl_loomas_miske_2025,
+    <t xml:space="preserve">https://osf.io/tywer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mallik, P. R., Metzger, M., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Final Report. Retrieved from osf.io/4hau3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{mallik_metzger_kline struhl_loomas_miske_2025,
  title={Final Report},
  url={osf.io/4hau3},
  publisher={OSF},
@@ -1473,13 +1465,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/9bkuf</t>
-  </si>
-  <si>
-    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0. Retrieved from osf.io/ndbrp</t>
-  </si>
-  <si>
-    <t>@misc{tyner_loomas_miske_luis_kline struhl_2025,
+    <t xml:space="preserve">https://osf.io/9bkuf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0. Retrieved from osf.io/ndbrp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_2025,
  title={King_JournOrgBehavior_2017_Q1dl - COS - New Data Replication - 40z0},
  url={osf.io/ndbrp},
  publisher={OSF},
@@ -1489,13 +1481,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/rzny2</t>
-  </si>
-  <si>
-    <t>Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Abatayo, A., Fiala, N., … Fong, C. Y. M. (2025, November 18). Analysis. Retrieved from osf.io/9v6er</t>
-  </si>
-  <si>
-    <t>@misc{tyner_loomas_miske_luis_abatayo_fiala_volkman_fong_2025,
+    <t xml:space="preserve">https://osf.io/rzny2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Abatayo, A., Fiala, N., … Fong, C. Y. M. (2025, November 18). Analysis. Retrieved from osf.io/9v6er</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_abatayo_fiala_volkman_fong_2025,
  title={Analysis},
  url={osf.io/9v6er},
  publisher={OSF},
@@ -1505,13 +1497,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/7efsw</t>
-  </si>
-  <si>
-    <t>OYEBANJO, A., Ramljak, M., Tyner, A. H., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51. Retrieved from osf.io/zt5y2</t>
-  </si>
-  <si>
-    <t>@misc{oyebanjo_ramljak_tyner_fox_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/7efsw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OYEBANJO, A., Ramljak, M., Tyner, A. H., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51. Retrieved from osf.io/zt5y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{oyebanjo_ramljak_tyner_fox_loomas_miske_luis_2025,
  title={Teney_EurSocioRev_2016_qXX2 - Ramljak/Oyebanjo - Secondary Data Replication - gz51},
  url={osf.io/zt5y2},
  publisher={OSF},
@@ -1521,13 +1513,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/fr6g8</t>
-  </si>
-  <si>
-    <t>Vargo, E., Tyner, A. H., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2. Retrieved from osf.io/kvsa6</t>
-  </si>
-  <si>
-    <t>@misc{vargo_tyner_miske_luis_loomas_2025,
+    <t xml:space="preserve">https://osf.io/fr6g8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vargo, E., Tyner, A. H., Miske, O., Luis, B., &amp; Loomas, Z. (2025, November 18). Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2. Retrieved from osf.io/kvsa6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{vargo_tyner_miske_luis_loomas_2025,
  title={Usta_JournMarketRes_2011_R8RN - Vargo - New Data Replication - 1yz2},
  url={osf.io/kvsa6},
  publisher={OSF},
@@ -1537,13 +1529,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/yva89</t>
-  </si>
-  <si>
-    <t>Tyner, A. H., Luis, B., Harper, S., Nandi, A., &amp; Loomas, Z. (2025, November 18). Analysis. Retrieved from osf.io/b6kfm</t>
-  </si>
-  <si>
-    <t>@misc{tyner_luis_harper_nandi_loomas_2025,
+    <t xml:space="preserve">https://osf.io/yva89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Luis, B., Harper, S., Nandi, A., &amp; Loomas, Z. (2025, November 18). Analysis. Retrieved from osf.io/b6kfm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_luis_harper_nandi_loomas_2025,
  title={Analysis},
  url={osf.io/b6kfm},
  publisher={OSF},
@@ -1553,13 +1545,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ftv7q</t>
-  </si>
-  <si>
-    <t>Held, M. J., Schütz, A., Loomas, Z., Fox, N. W., Luis, B., &amp; Miske, O. (2025, November 18). Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308. Retrieved from osf.io/hd3vf</t>
-  </si>
-  <si>
-    <t>@misc{held_schütz_loomas_fox_luis_miske_2025,
+    <t xml:space="preserve">https://osf.io/ftv7q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Held, M. J., Schütz, A., Loomas, Z., Fox, N. W., Luis, B., &amp; Miske, O. (2025, November 18). Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308. Retrieved from osf.io/hd3vf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{held_schütz_loomas_fox_luis_miske_2025,
  title={Kang_JournExpSocPsych_2009_rpq - Held - New Data Replication - 308},
  url={osf.io/hd3vf},
  publisher={OSF},
@@ -1569,13 +1561,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ceaq3</t>
-  </si>
-  <si>
-    <t>Szabelska, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Parsons, E. S. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7. Retrieved from osf.io/ta5vh</t>
-  </si>
-  <si>
-    <t>@misc{szabelska_tyner_loomas_miske_luis_parsons_2025,
+    <t xml:space="preserve">https://osf.io/ceaq3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szabelska, A., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Parsons, E. S. (2025, November 18). BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7. Retrieved from osf.io/ta5vh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{szabelska_tyner_loomas_miske_luis_parsons_2025,
  title={BATESON_AmPoliSciRev_2012_RYKv - Szabelska - Secondary Data Replication - mkz7},
  url={osf.io/ta5vh},
  publisher={OSF},
@@ -1585,13 +1577,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/fgdxs</t>
-  </si>
-  <si>
-    <t>Fonseca, M., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964. Retrieved from osf.io/t9h6p</t>
-  </si>
-  <si>
-    <t>@misc{fonseca_tyner_loomas_miske_luis_2025,
+    <t xml:space="preserve">https://osf.io/fgdxs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonseca, M., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2025, November 18). Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964. Retrieved from osf.io/t9h6p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{fonseca_tyner_loomas_miske_luis_2025,
  title={Goerg_JournLabEco_2010_WLpV - Fonseca - New Data Replication - 1964},
  url={osf.io/t9h6p},
  publisher={OSF},
@@ -1601,13 +1593,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/xr32n</t>
-  </si>
-  <si>
-    <t>Cummins, J. (2025, November 18). Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130. Retrieved from osf.io/h24z8</t>
-  </si>
-  <si>
-    <t>@misc{cummins_2025,
+    <t xml:space="preserve">https://osf.io/xr32n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cummins, J. (2025, November 18). Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130. Retrieved from osf.io/h24z8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{cummins_2025,
  title={Woltin_JournExpSocPsych_2011_Wre - Cummins - New Data Replication - 4130},
  url={osf.io/h24z8},
  publisher={OSF},
@@ -1617,13 +1609,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/kw5tv</t>
-  </si>
-  <si>
-    <t>Kołczyńska, M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., &amp; Loomas, Z. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634. Retrieved from osf.io/rpumq</t>
-  </si>
-  <si>
-    <t>@misc{kołczyńska_tyner_miske_luis_parsons_loomas_2025,
+    <t xml:space="preserve">https://osf.io/kw5tv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kołczyńska, M., Tyner, A. H., Miske, O., Luis, B., Parsons, E. S., &amp; Loomas, Z. (2025, November 18). McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634. Retrieved from osf.io/rpumq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{kołczyńska_tyner_miske_luis_parsons_loomas_2025,
  title={McLaren_WorldPolitics_2012_wRvv - Kołczyńska - Secondary Data Replication - 1634},
  url={osf.io/rpumq},
  publisher={OSF},
@@ -1633,13 +1625,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/c2hry</t>
-  </si>
-  <si>
-    <t>Hostler, T., Persson, S., &amp; Fox, N. W. (2025, November 18). Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z. Retrieved from osf.io/a8eg9</t>
-  </si>
-  <si>
-    <t>@misc{hostler_persson_fox_2025,
+    <t xml:space="preserve">https://osf.io/c2hry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hostler, T., Persson, S., &amp; Fox, N. W. (2025, November 18). Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z. Retrieved from osf.io/a8eg9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{hostler_persson_fox_2025,
  title={Vollmann_EurJournPersonality_2011_x3KP - Hostler - New Data Replication - k5z},
  url={osf.io/a8eg9},
  publisher={OSF},
@@ -1649,13 +1641,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/ybzev</t>
-  </si>
-  <si>
-    <t>Azevedo, F., Micheli, L., Wagner, D., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16. Retrieved from osf.io/8feku</t>
-  </si>
-  <si>
-    <t>@misc{azevedo_micheli_wagner_tyner_miske_loomas_2025,
+    <t xml:space="preserve">https://osf.io/ybzev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azevedo, F., Micheli, L., Wagner, D., Tyner, A. H., Miske, O., &amp; Loomas, Z. (2025, November 18). Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16. Retrieved from osf.io/8feku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{azevedo_micheli_wagner_tyner_miske_loomas_2025,
  title={Ihme_JournExpPoliSci_2018_xYbO - Azevedo - New Data Replication - yk16},
  url={osf.io/8feku},
  publisher={OSF},
@@ -1665,13 +1657,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/8rwkn</t>
-  </si>
-  <si>
-    <t>Capitán, T., Nast, C., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Mallinson, D. J. (2025, November 18). Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762. Retrieved from osf.io/j8en2</t>
-  </si>
-  <si>
-    <t>@misc{capitán_nast_tyner_loomas_miske_luis_abatayo_wintermantel_mallinson_2025,
+    <t xml:space="preserve">https://osf.io/8rwkn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitán, T., Nast, C., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Mallinson, D. J. (2025, November 18). Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762. Retrieved from osf.io/j8en2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{capitán_nast_tyner_loomas_miske_luis_abatayo_wintermantel_mallinson_2025,
  title={Chen_Demography_2018_yAPR - Nast/Capitán - Secondary Data Replication - 1762},
  url={osf.io/j8en2},
  publisher={OSF},
@@ -1681,13 +1673,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/esw45</t>
-  </si>
-  <si>
-    <t>Tyner, A. H., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930. Retrieved from osf.io/g6fkp</t>
-  </si>
-  <si>
-    <t>@misc{tyner_miske_luis_kline struhl_2025,
+    <t xml:space="preserve">https://osf.io/esw45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Miske, O., Luis, B., &amp; Kline Struhl, M. (2025, November 18). Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930. Retrieved from osf.io/g6fkp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_miske_luis_kline struhl_2025,
  title={Ku_JournEnvPsych_2014_YpZZ - COS - New Data Replication - 4930},
  url={osf.io/g6fkp},
  publisher={OSF},
@@ -1697,13 +1689,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/2wfgv</t>
-  </si>
-  <si>
-    <t>Bokhove, C., Nast, C., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., … Bokhove, C. (2025, November 18). Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6. Retrieved from osf.io/u52y3</t>
-  </si>
-  <si>
-    <t>@misc{bokhove_nast_tyner_abatayo_loomas_miske_luis_bokhove_2025,
+    <t xml:space="preserve">https://osf.io/2wfgv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bokhove, C., Nast, C., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., … Bokhove, C. (2025, November 18). Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6. Retrieved from osf.io/u52y3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{bokhove_nast_tyner_abatayo_loomas_miske_luis_bokhove_2025,
  title={Kim_CompEdu_2014_YWep - Nast/Bokhove - Secondary Data Replication - 75g6},
  url={osf.io/u52y3},
  publisher={OSF},
@@ -1713,13 +1705,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/hzg3j</t>
-  </si>
-  <si>
-    <t>Röer, J. P., Fox, N. W., Loomas, Z., Miske, O., Luis, B., Ostermann, T., … Parsons, E. S. (2025, November 18). Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38. Retrieved from osf.io/apv5t</t>
-  </si>
-  <si>
-    <t>@misc{röer_fox_loomas_miske_luis_ostermann_michalak_parsons_2025,
+    <t xml:space="preserve">https://osf.io/hzg3j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Röer, J. P., Fox, N. W., Loomas, Z., Miske, O., Luis, B., Ostermann, T., … Parsons, E. S. (2025, November 18). Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38. Retrieved from osf.io/apv5t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{röer_fox_loomas_miske_luis_ostermann_michalak_parsons_2025,
  title={Hurst_EvoHumanBehavior_2017_yypJ - Röer - New Data Replication - 6g38},
  url={osf.io/apv5t},
  publisher={OSF},
@@ -1729,13 +1721,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/r6ynf</t>
-  </si>
-  <si>
-    <t>Colvin, V., Smith, C., Fox, N. W., Miske, O., &amp; Loomas, Z. (2025, November 18). Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9. Retrieved from osf.io/etfqz</t>
-  </si>
-  <si>
-    <t>@misc{colvin_smith_fox_miske_loomas_2025,
+    <t xml:space="preserve">https://osf.io/r6ynf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colvin, V., Smith, C., Fox, N. W., Miske, O., &amp; Loomas, Z. (2025, November 18). Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9. Retrieved from osf.io/etfqz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{colvin_smith_fox_miske_loomas_2025,
  title={Axt_JournExpSocPsych_2018_zK2 - Colvin_Smith - New Data Replication - m5g9},
  url={osf.io/etfqz},
  publisher={OSF},
@@ -1745,13 +1737,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/dscfg</t>
-  </si>
-  <si>
-    <t>Slevc, L. R., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02. Retrieved from osf.io/78fvn</t>
-  </si>
-  <si>
-    <t>@misc{slevc_kline struhl_loomas_miske_2025,
+    <t xml:space="preserve">https://osf.io/dscfg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slevc, L. R., Kline Struhl, M., Loomas, Z., &amp; Miske, O. (2025, November 18). Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02. Retrieved from osf.io/78fvn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{slevc_kline struhl_loomas_miske_2025,
  title={Lai_Cognition_2011_zNEm - Slevc - New Data Replication - 1y02},
  url={osf.io/78fvn},
  publisher={OSF},
@@ -1761,13 +1753,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/nuzh2</t>
-  </si>
-  <si>
-    <t>Reed, W. R., Duan, J., Hong, S., Coupe, T., Tyner, A. H., Loomas, Z., … Kline Struhl, M. (2025, November 18). Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7. Retrieved from osf.io/62xh4</t>
-  </si>
-  <si>
-    <t>@misc{reed_duan_hong_coupe_tyner_loomas_miske_luis_vo_kline struhl_2025,
+    <t xml:space="preserve">https://osf.io/nuzh2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Coupe, T., Tyner, A. H., Loomas, Z., … Kline Struhl, M. (2025, November 18). Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7. Retrieved from osf.io/62xh4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{reed_duan_hong_coupe_tyner_loomas_miske_luis_vo_kline struhl_2025,
  title={Case_Demography_2011_5Kgq - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - k6y7},
  url={osf.io/62xh4},
  publisher={OSF},
@@ -1777,13 +1769,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/pex6u</t>
-  </si>
-  <si>
-    <t>Reed, W. R., Duan, J., Hong, S., Tyner, A. H., Loomas, Z., Miske, O., … Vo, D. T. H. (2025, November 18). Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz. Retrieved from osf.io/925nz</t>
-  </si>
-  <si>
-    <t>@misc{reed_duan_hong_tyner_loomas_miske_luis_coupe_vo_2025,
+    <t xml:space="preserve">https://osf.io/pex6u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Tyner, A. H., Loomas, Z., Miske, O., … Vo, D. T. H. (2025, November 18). Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz. Retrieved from osf.io/925nz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{reed_duan_hong_tyner_loomas_miske_luis_coupe_vo_2025,
  title={Chittoor_OrgSci_2009_kXp8 - Duan &amp; Hong/Reed &amp; Coupe - Secondary Data Replication - kzyz},
  url={osf.io/925nz},
  publisher={OSF},
@@ -1793,13 +1785,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/xg6q5</t>
-  </si>
-  <si>
-    <t>Reed, W. R., Duan, J., Hong, S., Loomas, Z., Miske, O., Luis, B., … Vo, D. T. H. (2025, November 18). Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz. Retrieved from osf.io/devn8</t>
-  </si>
-  <si>
-    <t>@misc{reed_duan_hong_loomas_miske_luis_tyner_abatayo_coupe_vo_2025,
+    <t xml:space="preserve">https://osf.io/xg6q5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Loomas, Z., Miske, O., Luis, B., … Vo, D. T. H. (2025, November 18). Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz. Retrieved from osf.io/devn8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{reed_duan_hong_loomas_miske_luis_tyner_abatayo_coupe_vo_2025,
  title={Chung_JournFinEco_2014_RrOb - Hong &amp; Duan/Reed - Secondary Data Replication - 19gz},
  url={osf.io/devn8},
  publisher={OSF},
@@ -1809,13 +1801,13 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/qk34m</t>
-  </si>
-  <si>
-    <t>Smalarz, L., Parsons, E. S., &amp; Hahn, K. (2025, November 18). Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707. Retrieved from osf.io/dhg3q</t>
-  </si>
-  <si>
-    <t>@misc{smalarz_parsons_hahn_2025,
+    <t xml:space="preserve">https://osf.io/qk34m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smalarz, L., Parsons, E. S., &amp; Hahn, K. (2025, November 18). Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707. Retrieved from osf.io/dhg3q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{smalarz_parsons_hahn_2025,
  title={Biernat_JournExpSocPsych_2013_jLr - Smalarz - New Data Replication - m707},
  url={osf.io/dhg3q},
  publisher={OSF},
@@ -1825,49 +1817,49 @@
 }</t>
   </si>
   <si>
-    <t>osf.io/y2emk</t>
-  </si>
-  <si>
-    <t>Pavlov, Y. G. (2023, June 20). Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4. Retrieved from osf.io/y2emk</t>
-  </si>
-  <si>
-    <t>@misc{pavlov_2023,\n title={Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4},\n url={osf.io/y2emk},\n publisher={OSF},\n author={Pavlov, Yuri G},\n year={2023},\n month={Jun}\n}</t>
-  </si>
-  <si>
-    <t>latham_2012</t>
-  </si>
-  <si>
-    <t>Latham, O. (2013). Bias at the Beeb? A quantitative study of slant in BBC online reporting. Centre for Policy Studies.</t>
-  </si>
-  <si>
-    <t>@techreport{latham2013bias, author = {Latham, Oliver}, title = {Bias at the Beeb? {A} quantitative study of slant in {BBC} online reporting}, institution = {Centre for Policy Studies}, year = {2013}, type = {Pointmaker}, url = {https://cps.org.uk/research/bias-at-the-beeb-a-quantitative-study-of-slant-in-bbc-online-reporting/} }</t>
-  </si>
-  <si>
-    <t>djaerv_2018</t>
-  </si>
-  <si>
-    <t>Djärv, K., Zehr, J., &amp; Schwarz, F. (2018). Cognitive vs. emotive factives: An experimental differentiation. Proceedings of Sinn und Bedeutung, 21(1), 367–386.</t>
-  </si>
-  <si>
-    <t>@inproceedings{djarv2018cognitive, author = {Dj{\"a}rv, Kajsa and Zehr, Jeremy and Schwarz, Florian}, title = {Cognitive vs. emotive factives: {A}n experimental differentiation}, booktitle = {Proceedings of Sinn und Bedeutung}, volume = {21}, number = {1}, pages = {367--386}, year = {2018} }</t>
-  </si>
-  <si>
-    <t>escholarship.orgucitem39d347bk</t>
-  </si>
-  <si>
-    <t>Chopra, S., Tessler, M. H., &amp; Goodman, N. D. (2019, July). The first crank of the cultural ratchet: Learning and transmitting concepts through language. In Proceedings of the 41st Annual Conference of the Cognitive Science Society (pp. 226–232). Cognitive Science Society.</t>
-  </si>
-  <si>
-    <t>@inproceedings{chopra2019first, author = {Chopra, Sahil and Tessler, Michael Henry and Goodman, Noah D}, booktitle = {Proceedings of the 41st Annual Meeting of the Cognitive Science Society}, date-added = {2020-09-05 00:50:14 +0000}, date-modified = {2020-09-05 01:32:38 +0000}, pages = {226--232}, title = {The first crank of the cultural ratchet: Learning and transmitting concepts through language}, website = {https://cogsci.mindmodeling.org/2019/papers/0060/0060.pdf}, year = {2019} }</t>
-  </si>
-  <si>
-    <t>art00005</t>
-  </si>
-  <si>
-    <t>Reuter, K. (2011). Distinguishing the appearance from the reality of pain. Journal of Consciousness Studies, 18(9-10), 94-109.</t>
-  </si>
-  <si>
-    <t>@article{reuter2011distinguishing,
+    <t xml:space="preserve">osf.io/y2emk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavlov, Y. G. (2023, June 20). Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4. Retrieved from osf.io/y2emk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{pavlov_2023,\n title={Replication of Kotchoubey &amp; Pavlov, 2017, Experiment 4},\n url={osf.io/y2emk},\n publisher={OSF},\n author={Pavlov, Yuri G},\n year={2023},\n month={Jun}\n}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">latham_2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latham, O. (2013). Bias at the Beeb? A quantitative study of slant in BBC online reporting. Centre for Policy Studies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@techreport{latham2013bias, author = {Latham, Oliver}, title = {Bias at the Beeb? {A} quantitative study of slant in {BBC} online reporting}, institution = {Centre for Policy Studies}, year = {2013}, type = {Pointmaker}, url = {https://cps.org.uk/research/bias-at-the-beeb-a-quantitative-study-of-slant-in-bbc-online-reporting/} }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">djaerv_2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Djärv, K., Zehr, J., &amp; Schwarz, F. (2018). Cognitive vs. emotive factives: An experimental differentiation. Proceedings of Sinn und Bedeutung, 21(1), 367–386.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@inproceedings{djarv2018cognitive, author = {Dj{\"a}rv, Kajsa and Zehr, Jeremy and Schwarz, Florian}, title = {Cognitive vs. emotive factives: {A}n experimental differentiation}, booktitle = {Proceedings of Sinn und Bedeutung}, volume = {21}, number = {1}, pages = {367--386}, year = {2018} }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">escholarship.orgucitem39d347bk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chopra, S., Tessler, M. H., &amp; Goodman, N. D. (2019, July). The first crank of the cultural ratchet: Learning and transmitting concepts through language. In Proceedings of the 41st Annual Conference of the Cognitive Science Society (pp. 226–232). Cognitive Science Society.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@inproceedings{chopra2019first, author = {Chopra, Sahil and Tessler, Michael Henry and Goodman, Noah D}, booktitle = {Proceedings of the 41st Annual Meeting of the Cognitive Science Society}, date-added = {2020-09-05 00:50:14 +0000}, date-modified = {2020-09-05 01:32:38 +0000}, pages = {226--232}, title = {The first crank of the cultural ratchet: Learning and transmitting concepts through language}, website = {https://cogsci.mindmodeling.org/2019/papers/0060/0060.pdf}, year = {2019} }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">art00005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reuter, K. (2011). Distinguishing the appearance from the reality of pain. Journal of Consciousness Studies, 18(9-10), 94-109.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{reuter2011distinguishing,
   title={Distinguishing the appearance from the reality of pain},
   author={Reuter, K.},
   journal={Journal of Consciousness Studies},
@@ -1878,13 +1870,13 @@
 }</t>
   </si>
   <si>
-    <t>scholars.indianastate.eduetds--2136</t>
-  </si>
-  <si>
-    <t>Wilfong, R. (2021). The mattering model: The foundational elements of mattering for K-12 educators (Order No. 28319407) [Doctoral dissertation, Indiana State University]. ProQuest Dissertations &amp; Theses Global. https://www.proquest.com/dissertations-theses/mattering-model-foundational-elements-k-12/docview/2537966312/se-2</t>
-  </si>
-  <si>
-    <t>@phdthesis{wilfong2021mattering,
+    <t xml:space="preserve">scholars.indianastate.eduetds--2136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilfong, R. (2021). The mattering model: The foundational elements of mattering for K-12 educators (Order No. 28319407) [Doctoral dissertation, Indiana State University]. ProQuest Dissertations &amp; Theses Global. https://www.proquest.com/dissertations-theses/mattering-model-foundational-elements-k-12/docview/2537966312/se-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@phdthesis{wilfong2021mattering,
   title={The mattering model: The foundational elements of mattering for K-12 educators},
   author={Wilfong, R.},
   year={2021},
@@ -1894,13 +1886,13 @@
 }</t>
   </si>
   <si>
-    <t>thekeep.eiu.edu/theses/4783</t>
-  </si>
-  <si>
-    <t>Burback, S. (2020). Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/4783</t>
-  </si>
-  <si>
-    <t>@mastersthesis{burback2020construct,
+    <t xml:space="preserve">thekeep.eiu.edu/theses/4783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burback, S. (2020). Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/4783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@mastersthesis{burback2020construct,
   title={Construct validity of the Behavior Assessment System for Children--Third Edition Teacher Rating Scales (BASC-3 TRS): Comparisons with the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Burback, Shannon},
   year={2020},
@@ -1910,13 +1902,13 @@
 }</t>
   </si>
   <si>
-    <t>wiebe_2004</t>
-  </si>
-  <si>
-    <t>Wiebe, R. P. (2004). Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape. Individual Differences Research, 2, 38-62.</t>
-  </si>
-  <si>
-    <t>@article{wiebe2004delinquent,
+    <t xml:space="preserve">wiebe_2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiebe, R. P. (2004). Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape. Individual Differences Research, 2, 38-62.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{wiebe2004delinquent,
   title={Delinquent behavior and the Five-Factor Model: Hiding in the adaptive landscape},
   author={Wiebe, R. P.},
   journal={Individual Differences Research},
@@ -1926,13 +1918,13 @@
 }</t>
   </si>
   <si>
-    <t>pashler_2011</t>
-  </si>
-  <si>
-    <t>Pashler, H., Harris, C., &amp; Coburn, N. (2011, September 15). Elderly-related words prime slow walking. PsychFileDrawer. Retrieved September 23, 2017, from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t>@misc{pashler_harris_coburn_2011_psychfiledrawer,
+    <t xml:space="preserve">pashler_2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N. (2011, September 15). Elderly-related words prime slow walking. PsychFileDrawer. Retrieved September 23, 2017, from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{pashler_harris_coburn_2011_psychfiledrawer,
   title={Elderly-related words prime slow walking},
   author={Pashler, H. and Harris, C. and Coburn, N.},
   year={2011},
@@ -1943,13 +1935,13 @@
 }</t>
   </si>
   <si>
-    <t>murtagh_2004</t>
-  </si>
-  <si>
-    <t>Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51. (Study 2).</t>
-  </si>
-  <si>
-    <t>@article{murtagh_todd_2004_strength,
+    <t xml:space="preserve">murtagh_2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murtagh, A. M., &amp; Todd, S. A. (2004). Self-regulation: A challenge to the strength model. Journal of Articles in Support of the Null Hypothesis, 3(1), 19-51. (Study 2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{murtagh_todd_2004_strength,
   title={Self-regulation: A challenge to the strength model},
   author={Murtagh, Andrew M. and Todd, Sandra A.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -1961,13 +1953,13 @@
 }</t>
   </si>
   <si>
-    <t>korbmacher_2022</t>
-  </si>
-  <si>
-    <t>Korbmacher, M., Kwan, C. I., &amp; Feldman, G. (2022). Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects. https://hdl.handle.net/11250/2990125</t>
-  </si>
-  <si>
-    <t>@misc{korbmacher_kwan_feldman_2022_abovebelow,
+    <t xml:space="preserve">korbmacher_2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korbmacher, M., Kwan, C. I., &amp; Feldman, G. (2022). Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects. https://hdl.handle.net/11250/2990125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{korbmacher_kwan_feldman_2022_abovebelow,
   title={Both better and worse than others depending on difficulty: Replication and extensions of Kruger's (1999) above- and below-average effects},
   author={Korbmacher, M. and Kwan, C. I. and Feldman, G.},
   year={2022},
@@ -1975,13 +1967,13 @@
 }</t>
   </si>
   <si>
-    <t>ferrell_2013</t>
-  </si>
-  <si>
-    <t>Ferrell, J. D., Gosling, S. D., &amp; Donnellan, M. B. (2014). Showering and loneliness: Participants from the University of Texas, Austin. PsychFileDrawer.</t>
-  </si>
-  <si>
-    <t>@misc{ferrell_gosling_donnellan_2014_showering,
+    <t xml:space="preserve">ferrell_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferrell, J. D., Gosling, S. D., &amp; Donnellan, M. B. (2014). Showering and loneliness: Participants from the University of Texas, Austin. PsychFileDrawer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{ferrell_gosling_donnellan_2014_showering,
   title={Showering and loneliness: Participants from the University of Texas, Austin},
   author={Ferrell, J. D. and Gosling, S. D. and Donnellan, M. B.},
   year={2014},
@@ -1990,13 +1982,13 @@
 }</t>
   </si>
   <si>
-    <t>lee_2013</t>
-  </si>
-  <si>
-    <t>Lee, F. (2013). Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
-  </si>
-  <si>
-    <t>@unpublished{lee2013clean,
+    <t xml:space="preserve">lee_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee, F. (2013). Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science) [Unpublished manuscript].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@unpublished{lee2013clean,
   title={Replication of "With a clean conscience: Cleanliness reduces the severity of moral judgments" by Schnall, Benton, and Harvey (2008, Psychological Science)},
   author={Lee, F.},
   year={2013},
@@ -2004,13 +1996,13 @@
 }</t>
   </si>
   <si>
-    <t>fayard_2009</t>
-  </si>
-  <si>
-    <t>Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6. (Study 1).</t>
-  </si>
-  <si>
-    <t>@article{fayard_bassi_bernstein_roberts_2009_cleanliness,
+    <t xml:space="preserve">fayard_2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fayard, J. V., Bassi, A. K., Bernstein, D. M., &amp; Roberts, B. W. (2009). Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006). Journal of Articles in Support of the Null Hypothesis, 6. (Study 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{fayard_bassi_bernstein_roberts_2009_cleanliness,
   title={Is cleanliness next to godliness? Dispelling old wives' tales: Failure to replicate Zhong and Liljenquist (2006)},
   author={Fayard, Jennifer V. and Bassi, Alana K. and Bernstein, Daniel M. and Roberts, Brent W.},
   journal={Journal of Articles in Support of the Null Hypothesis},
@@ -2020,13 +2012,13 @@
 }</t>
   </si>
   <si>
-    <t>vonpruski_2024</t>
-  </si>
-  <si>
-    <t>Pruski, S. M. (2024). The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study (Bachelor's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100459</t>
-  </si>
-  <si>
-    <t>@thesis{pruski2024impact,
+    <t xml:space="preserve">vonpruski_2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruski, S. M. (2024). The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study (Bachelor's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@thesis{pruski2024impact,
   title={The impact of screen time, social media use and extraversion on life satisfaction among university students: An extended replication study},
   author={Pruski, S. M.},
   year={2024},
@@ -2036,13 +2028,13 @@
 }</t>
   </si>
   <si>
-    <t>digitalcommons.memphis.edu--etd--3538</t>
-  </si>
-  <si>
-    <t>Thornton, K. B. (2024). Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T) [Doctoral dissertation, University of Memphis]. Digital Commons @ University of Memphis. https://digitalcommons.memphis.edu/etd/3538/</t>
-  </si>
-  <si>
-    <t>@phdthesis{thornton2024perceptions,
+    <t xml:space="preserve">digitalcommons.memphis.edu--etd--3538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thornton, K. B. (2024). Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T) [Doctoral dissertation, University of Memphis]. Digital Commons @ University of Memphis. https://digitalcommons.memphis.edu/etd/3538/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@phdthesis{thornton2024perceptions,
   title={Perceptions of mattering among general education teachers: Replication, validation, and extension of the Fundamental Elements of Mattering Scale for Teachers (FEMS-T)},
   author={Thornton, K. B.},
   year={2024},
@@ -2051,13 +2043,13 @@
 }</t>
   </si>
   <si>
-    <t>thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t>Katla, J. (2024). Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/5025</t>
-  </si>
-  <si>
-    <t>@mastersthesis{katla2024replication_basc,
+    <t xml:space="preserve">thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katla, J. (2024). Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA) [Master's thesis, Eastern Illinois University]. The Keep. https://thekeep.eiu.edu/theses/5025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@mastersthesis{katla2024replication_basc,
   title={Replication of construct validity of the Behavior Assessment System for Children-Teacher Rating Scales (BASC-3 TRS) and the Adjustment Scales for Children and Adolescents (ASCA)},
   author={Katla, J.},
   year={2024},
@@ -2066,58 +2058,58 @@
 }</t>
   </si>
   <si>
-    <t>https://osf.io/7jy4e/files/u93pc</t>
-  </si>
-  <si>
-    <t>Lacko, D., &amp; Prošek, T. (2025). A comment on Combs et al. (2023) “Reducing political polarization in the United States with a mobile chat platform”. I4R Report.</t>
-  </si>
-  <si>
-    <t>@article{lacko2025comment, title={A comment on Combs et al. (2023) "Reducing political polarization in the United States with a mobile chat platform"}, author={Lacko, Daniel and Prošek, Tomáš}, journal={I4R Report}, year={2025}}</t>
-  </si>
-  <si>
-    <t>https://osf.io/7qv89</t>
-  </si>
-  <si>
-    <t>Créchet, J., Cui, J., Sabada, B., &amp; Sawyer, A. (2024). Why don’t firms hire young workers during recessions? A replication of Forsythe (The Economic Journal, 2022). (I4R Discussion Paper Series No. 163)</t>
-  </si>
-  <si>
-    <t>@techreport{crechet2024youngworkers, title={Why Don't Firms Hire Young Workers During Recessions? A Replication of Forsythe (The Economic Journal, 2022)}, author={Créchet, Jonathan and Cui, Jing and Sabada, Barbara and Sawyer, Antoine}, institution={The Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={163}, keywords={Worker flows; business cycles; life cycle}, url={https://ideas.repec.org/p/zbw/i4rdps/163.html}}</t>
-  </si>
-  <si>
-    <t>https://osf.io/txqjw/</t>
-  </si>
-  <si>
-    <t>Hallman, A., Johannesson, M., &amp; Kujansuu, E. (2024). Robustness Reproducibility of" Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention". (No. 118), I4R Discussion Paper Series.</t>
-  </si>
-  <si>
-    <t>@techreport{hallman2024robustness, title={Robustness Reproducibility of "Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention"}, author={Hallman, Alice and Johannesson, Magnus and Kujansuu, Essi}, institution={Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={118}, url={https://hdl.handle.net/10419/295247}}</t>
-  </si>
-  <si>
-    <t>https://osf.io/8rb5k</t>
-  </si>
-  <si>
-    <t>Brodeur, A. (2024). Reproduction of  "Who Chooses Commitment? Evidence and Welfare Implications".</t>
-  </si>
-  <si>
-    <t>@misc{brodeur2024reproduction, author={Brodeur, Abel}, title={Reproduction of "Who Chooses Commitment? Evidence and Welfare Implications"}, year={2024}, month={July}, day={22}, howpublished={OSF}, url={https://osf.io/752q9}}</t>
-  </si>
-  <si>
-    <t>https://osf.io/9erj6</t>
-  </si>
-  <si>
-    <t>Kjelsrud, A., Kotsadam, A., Rogeberg, O., &amp; Brodeur, A. (2025, February 22). A comment on “Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India” by Siddique et al. (2024)</t>
-  </si>
-  <si>
-    <t>@book{kjelsrud2025comment, title={A Comment on "Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India" by Siddique et al. (2024)}, author={Kjelsrud, Anders and Kotsadam, Andreas and Rogeberg, Ole and Brodeur, Abel}, year={2025}, publisher={JSTOR}}</t>
-  </si>
-  <si>
-    <t>https://osf.io/82bwv</t>
-  </si>
-  <si>
-    <t>Lewis, M., &amp; Pitts, M. (2023). Replication of Hajcak &amp; Foti (2008, PS, Study 1). OSF. Retrieved from https://osf.io/82bwv</t>
-  </si>
-  <si>
-    <t>@misc{lewis_pitts_2023,
+    <t xml:space="preserve">https://osf.io/7jy4e/files/u93pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lacko, D., &amp; Prošek, T. (2025). A comment on Combs et al. (2023) “Reducing political polarization in the United States with a mobile chat platform”. I4R Report.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{lacko2025comment, title={A comment on Combs et al. (2023) "Reducing political polarization in the United States with a mobile chat platform"}, author={Lacko, Daniel and Prošek, Tomáš}, journal={I4R Report}, year={2025}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/7qv89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créchet, J., Cui, J., Sabada, B., &amp; Sawyer, A. (2024). Why don’t firms hire young workers during recessions? A replication of Forsythe (The Economic Journal, 2022). (I4R Discussion Paper Series No. 163)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@techreport{crechet2024youngworkers, title={Why Don't Firms Hire Young Workers During Recessions? A Replication of Forsythe (The Economic Journal, 2022)}, author={Créchet, Jonathan and Cui, Jing and Sabada, Barbara and Sawyer, Antoine}, institution={The Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={163}, keywords={Worker flows; business cycles; life cycle}, url={https://ideas.repec.org/p/zbw/i4rdps/163.html}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/txqjw/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallman, A., Johannesson, M., &amp; Kujansuu, E. (2024). Robustness Reproducibility of" Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention". (No. 118), I4R Discussion Paper Series.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@techreport{hallman2024robustness, title={Robustness Reproducibility of "Improving Workplace Climate in Large Corporations: A Clustered Randomized Intervention"}, author={Hallman, Alice and Johannesson, Magnus and Kujansuu, Essi}, institution={Institute for Replication (I4R)}, type={I4R Discussion Paper Series}, year={2024}, number={118}, url={https://hdl.handle.net/10419/295247}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/8rb5k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brodeur, A. (2024). Reproduction of  "Who Chooses Commitment? Evidence and Welfare Implications".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{brodeur2024reproduction, author={Brodeur, Abel}, title={Reproduction of "Who Chooses Commitment? Evidence and Welfare Implications"}, year={2024}, month={July}, day={22}, howpublished={OSF}, url={https://osf.io/752q9}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/9erj6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kjelsrud, A., Kotsadam, A., Rogeberg, O., &amp; Brodeur, A. (2025, February 22). A comment on “Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India” by Siddique et al. (2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@book{kjelsrud2025comment, title={A Comment on "Raising Health Awareness in Rural Communities: A Randomized Experiment in Bangladesh and India" by Siddique et al. (2024)}, author={Kjelsrud, Anders and Kotsadam, Andreas and Rogeberg, Ole and Brodeur, Abel}, year={2025}, publisher={JSTOR}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/82bwv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lewis, M., &amp; Pitts, M. (2023). Replication of Hajcak &amp; Foti (2008, PS, Study 1). OSF. Retrieved from https://osf.io/82bwv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{lewis_pitts_2023,
  title={Replication of Hajcak &amp; Foti (2008, PS, Study 1)},
  url={osf.io/73pnd},
  DOI={10.17605/OSF.IO/73PND},
@@ -2128,19 +2120,19 @@
 }</t>
   </si>
   <si>
-    <t>Replication of Hajcak &amp; Foti  (2008, PS, Study 1)</t>
-  </si>
-  <si>
-    <t>OSF</t>
-  </si>
-  <si>
-    <t>https://osf.io/aaudl</t>
-  </si>
-  <si>
-    <t>Chandler, J. J. (2023). Replication of Janiszewski &amp; Uy (2008, PS, Study 4b). OSF. Retrieved from https://osf.io/aaudl</t>
-  </si>
-  <si>
-    <t>@misc{chandler_2023,
+    <t xml:space="preserve">Replication of Hajcak &amp; Foti  (2008, PS, Study 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/aaudl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chandler, J. J. (2023). Replication of Janiszewski &amp; Uy (2008, PS, Study 4b). OSF. Retrieved from https://osf.io/aaudl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{chandler_2023,
  title={Replication of Janiszewski &amp; Uy (2008, PS, Study 4b)},
  url={osf.io/aaudl},
  publisher={OSF},
@@ -2150,16 +2142,16 @@
 }</t>
   </si>
   <si>
-    <t>Replication of Janiszewski &amp; Uy  (2008, PS, Study 4b)</t>
-  </si>
-  <si>
-    <t>https://osf.io/nxp9w</t>
-  </si>
-  <si>
-    <t>Beer, J. S., Rigney, A. E., &amp; Flagan, T. (2016). Replication of G Tabibnia, AB Satpute, MD Lieberman (2008, PS 19(4)). OSF. Retrieved from https://osf.io/nxp9w</t>
-  </si>
-  <si>
-    <t>@misc{beer_rigney_flagan_2016,
+    <t xml:space="preserve">Replication of Janiszewski &amp; Uy  (2008, PS, Study 4b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/nxp9w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer, J. S., Rigney, A. E., &amp; Flagan, T. (2016). Replication of G Tabibnia, AB Satpute, MD Lieberman (2008, PS 19(4)). OSF. Retrieved from https://osf.io/nxp9w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{beer_rigney_flagan_2016,
  title={Replication of G Tabibnia, AB Satpute, MD Lieberman (2008, PS 19(4))},
  url={osf.io/94j6h},
  publisher={OSF},
@@ -2169,103 +2161,103 @@
 }</t>
   </si>
   <si>
-    <t>Replication of G Tabibnia, AB Satpute, MD Lieberman  (2008, PS 19 (4))</t>
-  </si>
-  <si>
-    <t>https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
-  </si>
-  <si>
-    <t>Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
-  </si>
-  <si>
-    <t>@article{findlay_santos_2012, title={Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli}, volume={9}, number={2}, journal={Econ Journal Watch}, author={Findlay, David W. and Santos, John M.}, year={2012}, pages={122-140}}</t>
-  </si>
-  <si>
-    <t>Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli</t>
-  </si>
-  <si>
-    <t>Econ Journal Watch</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>122-140</t>
-  </si>
-  <si>
-    <t>https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
-  </si>
-  <si>
-    <t>Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
-  </si>
-  <si>
-    <t>https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
-  </si>
-  <si>
-    <t>Ramsay, G. (2013, September 10). The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed. LSE Impact Blog. Retrieved from https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
-  </si>
-  <si>
-    <t>@misc{ramsay_2013, title={The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed}, author={Ramsay, Gordon}, year={2013}, month={Sep}, day={10}, howpublished={LSE Impact Blog}}</t>
-  </si>
-  <si>
-    <t>The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed</t>
-  </si>
-  <si>
-    <t>LSE Impact Blog</t>
-  </si>
-  <si>
-    <t>https://purl.utwente.nl/essays/100571</t>
-  </si>
-  <si>
-    <t>Bischoff, M. (2024). Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study (Master's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100571</t>
-  </si>
-  <si>
-    <t>@mastersthesis{bischoff_2024, title={Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study}, author={Bischoff, Milan}, year={2024}, school={University of Twente}}</t>
-  </si>
-  <si>
-    <t>Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study</t>
-  </si>
-  <si>
-    <t>University of Twente</t>
-  </si>
-  <si>
-    <t>https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
-  </si>
-  <si>
-    <t>Arbesfeld, J., Collins, T., Baldwin, D., &amp; Daubman, K. (2014). Clean thoughts lead to less severe moral judgment [Replication of Schnall, Benton, &amp; Harvey, 2008]. PsychFileDrawer.org. Retrieved from https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
-  </si>
-  <si>
-    <t>@misc{arbesfeld_2014, title={Clean thoughts lead to less severe moral judgment}, author={Arbesfeld, Julia and Collins, Tricia and Baldwin, Demetrius and Daubman, Kimberly}, year={2014}, howpublished={PsychFileDrawer.org}, note={Replication of Schnall, Benton, and Harvey (2008)}}</t>
-  </si>
-  <si>
-    <t>Clean thoughts lead to less severe moral judgment</t>
-  </si>
-  <si>
-    <t>PsychFileDrawer.org</t>
-  </si>
-  <si>
-    <t>https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
-  </si>
-  <si>
-    <t>Siev, J. (2012). Unpublished replication of Zhong &amp; Liljenquist (2006). Retrieved from https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
-  </si>
-  <si>
-    <t>@unpublished{siev_2012, title={Unpublished replication of Zhong and Liljenquist (2006)}, author={Siev, Jedediah}, year={2012}}</t>
-  </si>
-  <si>
-    <t>Unpublished replication of Zhong &amp; Liljenquist (2006)</t>
-  </si>
-  <si>
-    <t>kontkanen_jaakko_thesis_2024</t>
-  </si>
-  <si>
-    <t>Kontkanen, J. (2024). Investigating the effect of proficiency level on the acquisition order of morphemes for L2 English learners: A replication of a corpus-based SLA study using Interlanguage Annotation [Master’s thesis, University of Helsinki]. Retrieved from http://hdl.handle.net/10138/576172</t>
-  </si>
-  <si>
-    <t>@mastersthesis{kontkanen2024investigating,
+    <t xml:space="preserve">Replication of G Tabibnia, AB Satpute, MD Lieberman  (2008, PS 19 (4))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/articles/race-ethnicity-and-baseball-card-prices-a-replication-correction-and-extension-of-hewitt-munoz-oliver-and-regoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{findlay_santos_2012, title={Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli}, volume={9}, number={2}, journal={Econ Journal Watch}, author={Findlay, David W. and Santos, John M.}, year={2012}, pages={122-140}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Race, Ethnicity, and Baseball Card Prices: A Replication, Correction, and Extension of Hewitt, Munoz, Oliver, and Regoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Econ Journal Watch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122-140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Findlay, D. W., &amp; Santos, J. M. (2012). Race, ethnicity, and baseball card prices: A replication, correction, and extension of Hewitt, Munoz, Oliver, and Regoli. Econ Journal Watch, 9(2), 122-140. Retrieved from https://econjwatch.org/File+download/538/FindlaySantosMay2012.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramsay, G. (2013, September 10). The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed. LSE Impact Blog. Retrieved from https://blogs.lse.ac.uk/impactofsocialsciences/2013/09/10/bias-at-the-bbc-replicating-the-cps-analysis/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{ramsay_2013, title={The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed}, author={Ramsay, Gordon}, year={2013}, month={Sep}, day={10}, howpublished={LSE Impact Blog}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CPS claims that the BBC has a left-of-centre bias in its coverage of Think Tanks, but closer analysis shows that it is much more even handed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSE Impact Blog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://purl.utwente.nl/essays/100571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bischoff, M. (2024). Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study (Master's thesis, University of Twente). Retrieved from https://purl.utwente.nl/essays/100571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@mastersthesis{bischoff_2024, title={Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study}, author={Bischoff, Milan}, year={2024}, school={University of Twente}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluating the reliability of relative frontal alpha asymmetry as a state-dependent correlate of the stress response in a mixed-sex sample: A replication study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University of Twente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbesfeld, J., Collins, T., Baldwin, D., &amp; Daubman, K. (2014). Clean thoughts lead to less severe moral judgment [Replication of Schnall, Benton, &amp; Harvey, 2008]. PsychFileDrawer.org. Retrieved from https://web.archive.org/web/20191201181415/http://psychfiledrawer.org/replication.php?attempt=MTc3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{arbesfeld_2014, title={Clean thoughts lead to less severe moral judgment}, author={Arbesfeld, Julia and Collins, Tricia and Baldwin, Demetrius and Daubman, Kimberly}, year={2014}, howpublished={PsychFileDrawer.org}, note={Replication of Schnall, Benton, and Harvey (2008)}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean thoughts lead to less severe moral judgment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PsychFileDrawer.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siev, J. (2012). Unpublished replication of Zhong &amp; Liljenquist (2006). Retrieved from https://github.com/eplebel/science-commons/blob/master/curated/z%26l/Siev%20(2012).pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@unpublished{siev_2012, title={Unpublished replication of Zhong and Liljenquist (2006)}, author={Siev, Jedediah}, year={2012}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpublished replication of Zhong &amp; Liljenquist (2006)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kontkanen_jaakko_thesis_2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontkanen, J. (2024). Investigating the effect of proficiency level on the acquisition order of morphemes for L2 English learners: A replication of a corpus-based SLA study using Interlanguage Annotation [Master’s thesis, University of Helsinki]. Retrieved from http://hdl.handle.net/10138/576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@mastersthesis{kontkanen2024investigating,
   author  = {Kontkanen, Jaakko},
   title   = {Investigating the effect of proficiency level on the acquisition order of morphemes for L2 English learners: A replication of a corpus-based SLA study using Interlanguage Annotation},
   school  = {University of Helsinki},
@@ -2277,22 +2269,22 @@
 }</t>
   </si>
   <si>
-    <t>http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t>Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking. (2011, September 15). Retrieved September 23, 2017 from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
-  </si>
-  <si>
-    <t>@misc{pashler2011elderly, author = {Pashler, H. and Harris, C. and Coburn, N.}, title = {Elderly-Related Words Prime Slow Walking}, year = {2011}, month = {September 15}, howpublished = {\url{http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D}}, note = {Retrieved September 23, 2017} }</t>
-  </si>
-  <si>
-    <t>10.4324/9781032633275-7</t>
-  </si>
-  <si>
-    <t>Tversky, A., &amp; Gati, I. (1978). Studies of similarity. In E. Rosch &amp; B. B. Lloyd (Eds.), Cognition and categorization (pp. 79–98). Lawrence Erlbaum Associates.</t>
-  </si>
-  <si>
-    <t>@incollection{tversky1978studies,
+    <t xml:space="preserve">http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pashler, H., Harris, C., &amp; Coburn, N.. Elderly-Related Words Prime Slow Walking. (2011, September 15). Retrieved September 23, 2017 from http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{pashler2011elderly, author = {Pashler, H. and Harris, C. and Coburn, N.}, title = {Elderly-Related Words Prime Slow Walking}, year = {2011}, month = {September 15}, howpublished = {\url{http://www.PsychFileDrawer.org/replication.php?attempt=MTU%3D}}, note = {Retrieved September 23, 2017} }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4324/9781032633275-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tversky, A., &amp; Gati, I. (1978). Studies of similarity. In E. Rosch &amp; B. B. Lloyd (Eds.), Cognition and categorization (pp. 79–98). Lawrence Erlbaum Associates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@incollection{tversky1978studies,
   author = {Tversky, Amos and Gati, Itamar},
   title = {Studies of Similarity},
   booktitle = {Cognition and Categorization},
@@ -2304,19 +2296,19 @@
 }</t>
   </si>
   <si>
-    <t>Studies of Similarity</t>
-  </si>
-  <si>
-    <t>79-98</t>
-  </si>
-  <si>
-    <t>10.18574/nyu/9780814788912.003.0009</t>
-  </si>
-  <si>
-    <t>Simpson, A. Y. (1998). Identity and integration: The liberals. In The tie that binds: Identity and political attitudes in the post-civil rights generation (pp. 105–144). New York University Press. https://doi.org/10.18574/nyu/9780814788912.003.0009</t>
-  </si>
-  <si>
-    <t>@incollection{simpson1998identity,
+    <t xml:space="preserve">Studies of Similarity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79-98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.18574/nyu/9780814788912.003.0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simpson, A. Y. (1998). Identity and integration: The liberals. In The tie that binds: Identity and political attitudes in the post-civil rights generation (pp. 105–144). New York University Press. https://doi.org/10.18574/nyu/9780814788912.003.0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@incollection{simpson1998identity,
   author = {Simpson, Andrea Y.},
   title = {Identity and Integration: {The} Liberals},
   booktitle = {The Tie That Binds: Identity and Political Attitudes in the Post-Civil Rights Generation},
@@ -2328,22 +2320,19 @@
 }</t>
   </si>
   <si>
-    <t>Identity and Integration: The Liberals</t>
-  </si>
-  <si>
-    <t>105-144</t>
-  </si>
-  <si>
-    <t>10.1126/science.aac4716</t>
-  </si>
-  <si>
-    <t>Open Science Collaboration</t>
-  </si>
-  <si>
-    <t>Open Science Collaboration (2015). Estimating the reproducibility of psychological science. Science 349(6251).</t>
-  </si>
-  <si>
-    <t>@article{OpenScienceCollaboration2015,
+    <t xml:space="preserve">Identity and Integration: The Liberals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105-144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1126/science.aac4716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Science Collaboration (2015). Estimating the reproducibility of psychological science. Science 349(6251).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@article{OpenScienceCollaboration2015,
   author = {{Open Science Collaboration}},
   title = {Estimating the reproducibility of psychological science},
   journal = {Science},
@@ -2354,25 +2343,1161 @@
   doi = {10.1126/science.aac4716}}</t>
   </si>
   <si>
-    <t>Science</t>
+    <t xml:space="preserve">Open Science Collaboration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/5xr92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2026, February 27). Allendorf_Demography_2013_Y8Yx - Reed - Secondary Data Replication - 21wg2. https://doi.org/10.17605/OSF.IO/USV5K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2026,
+ title={Allendorf_Demography_2013_Y8Yx - Reed - Secondary Data Replication - 21wg2},
+ url={osf.io/usv5k},
+ DOI={10.17605/OSF.IO/USV5K},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Duan, Jianhua and Hong, Sanghyun and Reed, W. R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/m8bpk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Fonseca, M. (2026, February 27). Altmann_JournLabEco_2012_WLkV - Fonseca - New Data Replication - 67516. https://doi.org/10.17605/OSF.IO/Q7JK4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_fonseca_2026,
+ title={Altmann_JournLabEco_2012_WLkV - Fonseca - New Data Replication - 67516},
+ url={osf.io/q7jk4},
+ DOI={10.17605/OSF.IO/Q7JK4},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Fonseca, Miguel},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/kcegt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Abatayo, A., Porter, N. D., … Tagat, A. (2026, February 27). Anderson_AmEcoJourn_2011_bLe8 - Tagat/Porter - Secondary Data Replication - 329k. https://doi.org/10.17605/OSF.IO/T95K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_abatayo_porter_geng_tagat_2026,
+ title={Anderson_AmEcoJourn_2011_bLe8 - Tagat/Porter - Secondary Data Replication - 329k},
+ url={osf.io/t95k2},
+ DOI={10.17605/OSF.IO/T95K2},
+ publisher={OSF},
+ author={Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Abatayo, Anna Lou and Porter, Nathaniel D and Geng, Jing and Tagat, Anirudh},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/hefyp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Koirala, S. (2026, February 12). Banerjee_ExpEco_2016_J4W9 - Fiala - New Data Replication - y2312. Retrieved from osf.io/yg7d2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_fiala_neubauer_et al._2026,
+ title={Banerjee_ExpEco_2016_J4W9 - Fiala - New Data Replication - y2312},
+ url={osf.io/yg7d2},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Fiala, Nathan and Neubauer, Florian and et al.},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/gu26j</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chandler, J. J., &amp; Kline Struhl, M. (2026, February 27). Bartels_JournConsRes_2015_mrZ - Chandler - New Data Replication - 579. https://doi.org/10.17605/OSF.IO/NA3MH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{chandler_kline struhl_2026,
+ title={Bartels_JournConsRes_2015_mrZ - Chandler - New Data Replication - 579},
+ url={osf.io/na3mh},
+ DOI={10.17605/OSF.IO/NA3MH},
+ publisher={OSF},
+ author={Chandler, Jesse J and Kline Struhl, Melissa},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/pdurj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiala, N., Volkman, V., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2026, March 20). Benjamin_AmEcoRev_2010_WaYe - Fiala - New Data Replication - 556. https://doi.org/10.17605/OSF.IO/FGX67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{fiala_volkman_abatayo_loomas_miske_luis_2026,
+ title={Benjamin_AmEcoRev_2010_WaYe - Fiala - New Data Replication - 556},
+ url={osf.io/fgx67},
+ DOI={10.17605/OSF.IO/FGX67},
+ publisher={OSF},
+ author={Fiala, Nathan and Volkman, Victor and Abatayo, Anna Lou and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Mar}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/675hz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2026, February 27). Burgoon_WorldPolitics_2014_5Q82 - Reed - Secondary Data Replication - 6zy82. https://doi.org/10.17605/OSF.IO/GUEN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2026,
+ title={Burgoon_WorldPolitics_2014_5Q82 - Reed - Secondary Data Replication - 6zy82},
+ url={osf.io/guen5},
+ DOI={10.17605/OSF.IO/GUEN5},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Duan, Jianhua and Hong, Sanghyun and Reed, W. R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/nr64y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Vargo, E. (2026, February 27). BUTTON_Criminology_2017_pN7E - Vargo - Secondary Data Replication - 69812. https://doi.org/10.17605/OSF.IO/F49UQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_vargo_2026,
+ title={BUTTON_Criminology_2017_pN7E - Vargo - Secondary Data Replication - 69812},
+ url={osf.io/f49uq},
+ DOI={10.17605/OSF.IO/F49UQ},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Vargo, Elisabeth Julie},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/d5ezq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2026, February 27). Chudgar_AmEduResJourn_2009_pw3m - Reed - Secondary Data Replication - 2kwg2. https://doi.org/10.17605/OSF.IO/68X45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_hong_duan_reed_2026,
+ title={Chudgar_AmEduResJourn_2009_pw3m - Reed - Secondary Data Replication - 2kwg2},
+ url={osf.io/68x45},
+ DOI={10.17605/OSF.IO/68X45},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Hong, Sanghyun and Duan, Jianhua and Reed, W. R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/dtkjc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Emery, C. (2026, February 27). Crossley_OrgBehavior_2009_5Xaw - Peters - New Data Replication - 69y36. https://doi.org/10.17605/OSF.IO/7VTY6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_peters_emery_2026,
+ title={Crossley_OrgBehavior_2009_5Xaw - Peters - New Data Replication - 69y36},
+ url={osf.io/7vty6},
+ DOI={10.17605/OSF.IO/7VTY6},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Peters, Kim O and Emery, Cécile},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/q7yc5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Soderberg, C. K., Kline Struhl, M., Tyner, A. H., … Parsons, E. S. (2026, February 27). Da_JournFinEco_2009_BKxK - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - 4zz0. https://doi.org/10.17605/OSF.IO/ND87T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_soderberg_kline struhl_tyner_duan_hong_reed_coupe_et al._2026,
+ title={Da_JournFinEco_2009_BKxK - Hong &amp; Duan/Reed &amp; Coupe - Secondary Data Replication - 4zz0},
+ url={osf.io/nd87t},
+ DOI={10.17605/OSF.IO/ND87T},
+ publisher={OSF},
+ author={Loomas, Zachary and Miske, Olivia and Luis, Brianna and Soderberg, Courtney K and Kline Struhl, Melissa and Tyner, Andrew H and Duan, Jianhua and Hong, Sanghyun and Reed, W. R and Coupe, Tom and et al.},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/wygup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Urbanska, K. (2026, February 27). Duriez_EurJournPersonality_2012_d5v3 - Urbanska - Secondary Data Replication - 6m492. https://doi.org/10.17605/OSF.IO/VCJF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_2026,
+ title={Duriez_EurJournPersonality_2012_d5v3 - Urbanska - Secondary Data Replication - 6m492},
+ url={osf.io/vcjf6},
+ DOI={10.17605/OSF.IO/VCJF6},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Urbanska, Karolina},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/gsw9a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milyavskaya, M., McMillan, G., Fox, N. W., Miske, O., Loomas, Z., Luis, B., &amp; Yee, J. (2026, February 27). Kappes_JournExpSocPsych_2012_9J1 - Milyavskaya - New Data Replication - g9mm. https://doi.org/10.17605/OSF.IO/RQWJU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{milyavskaya_mcmillan_fox_miske_loomas_luis_yee_2026,
+ title={Kappes_JournExpSocPsych_2012_9J1 - Milyavskaya - New Data Replication - g9mm},
+ url={osf.io/rqwju},
+ DOI={10.17605/OSF.IO/RQWJU},
+ publisher={OSF},
+ author={Milyavskaya, Marina and McMillan, Gail and Fox, Nicholas W and Miske, Olivia and Loomas, Zachary and Luis, Brianna and Yee, Jasmin},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/s2hez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Loomas, Z., Miske, O., Luis, B., Kline Struhl, M., Duan, J., … Reed, W. R. (2026, February 27). Kuo_Demography_2016_JWzJ - Duan &amp; Hong - Secondary Data Replication - 6547. https://doi.org/10.17605/OSF.IO/U8X9S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_loomas_miske_luis_kline struhl_duan_hong_fox_parsons_reed_2026,
+ title={Kuo_Demography_2016_JWzJ - Duan &amp; Hong - Secondary Data Replication - 6547},
+ url={osf.io/u8x9s},
+ DOI={10.17605/OSF.IO/U8X9S},
+ publisher={OSF},
+ author={Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Kline Struhl, Melissa and Duan, Jianhua and Hong, Sanghyun and Fox, Nicholas W and Parsons, Elan S and Reed, W. R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/957xr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2026, February 27). Kupor_OrgBehavior_2018_y3R4 - Baskin - New Data Replication - 2wgk2. https://doi.org/10.17605/OSF.IO/P7MEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2026,
+ title={Kupor_OrgBehavior_2018_y3R4 - Baskin - New Data Replication - 2wgk2},
+ url={osf.io/p7mex},
+ DOI={10.17605/OSF.IO/P7MEX},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Baskin, Ernest},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/j24ts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szumowska, E., Czernatowicz-Kukuczka, A., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 11). Lee_EvoHumanBehavior_2018_AvWY - Szumowska - New Data Replication - 8g91. Retrieved from osf.io/uyt9p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{szumowska_czernatowicz-kukuczka_fox_loomas_miske_luis_2026,
+ title={Lee_EvoHumanBehavior_2018_AvWY - Szumowska - New Data Replication - 8g91},
+ url={osf.io/uyt9p},
+ publisher={OSF},
+ author={Szumowska, Ewa and Czernatowicz-Kukuczka, Aneta and Fox, Nicholas W and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/ad9jm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brady, T. F., Williams, J. R., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Fox, N. W. (2026, February 11). Linkenauger_PsychologSci_2009_7WjP - Brady - New Data Replication - 7976. Retrieved from osf.io/md84s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{brady_williams_kline struhl_loomas_miske_fox_2026,
+ title={Linkenauger_PsychologSci_2009_7WjP - Brady - New Data Replication - 7976},
+ url={osf.io/md84s},
+ publisher={OSF},
+ author={Brady, Timothy F and Williams, Jamal R and Kline Struhl, Melissa and Loomas, Zachary and Miske, Olivia and Fox, Nicholas W},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/fngwe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hannon, E., Getz, L. M., Leslie, J., Sanchez, M., &amp; Tyner, A. H. (2026, February 27). Lowe_JournMarketRes_2017_VGAe - Hannon - New Data Replication - 4z32. https://doi.org/10.17605/OSF.IO/DK3XZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{hannon_getz_leslie_sanchez_tyner_2026,
+ title={Lowe_JournMarketRes_2017_VGAe - Hannon - New Data Replication - 4z32},
+ url={osf.io/dk3xz},
+ DOI={10.17605/OSF.IO/DK3XZ},
+ publisher={OSF},
+ author={Hannon, Erin and Getz, Laura M and Leslie, Jared and Sanchez, Mary and Tyner, Andrew H},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/yfd5b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talhelm, T., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Ma-Kellams_PsychologSci_2011_lkBL - Talhelm - New Data Replication - 618. https://doi.org/10.17605/OSF.IO/CR6ZM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{talhelm_kline struhl_loomas_miske_luis_2026,
+ title={Ma-Kellams_PsychologSci_2011_lkBL - Talhelm - New Data Replication - 618},
+ url={osf.io/cr6zm},
+ DOI={10.17605/OSF.IO/CR6ZM},
+ publisher={OSF},
+ author={Talhelm, Thomas and Kline Struhl, Melissa and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/snrcv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyner, A. H., Miske, O., Loomas, Z., Schroeder, A., Luis, B., &amp; Bricka, T. (2026, February 12). Analysis. Retrieved from osf.io/kg7ae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{tyner_miske_loomas_schroeder_luis_bricka_2026,
+ title={Analysis},
+ url={osf.io/kg7ae},
+ publisher={OSF},
+ author={Tyner, Andrew H and Miske, Olivia and Loomas, Zachary and Schroeder, Amber and Luis, Brianna and Bricka, Traci},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/vu8nb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Edlund, J. (2026, March 24). Petit_JournBusRes_2017_9R9X - Edlund - New Data Replication - 2kkg2. https://doi.org/10.17605/OSF.IO/TUY3F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_edlund_2026,
+ title={Petit_JournBusRes_2017_9R9X - Edlund - New Data Replication - 2kkg2},
+ url={osf.io/tuy3f},
+ DOI={10.17605/OSF.IO/TUY3F},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Edlund, John},
+ year={2026},
+ month={Mar}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/6aefs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaki, S., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2026, February 27). Rinaldi_Cognition_2016_Kj9d - Shaki - New Data Replication - 16yz. https://doi.org/10.17605/OSF.IO/5DU7F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{shaki_kline struhl_miske_loomas_luis_2026,
+ title={Rinaldi_Cognition_2016_Kj9d - Shaki - New Data Replication - 16yz},
+ url={osf.io/5du7f},
+ DOI={10.17605/OSF.IO/5DU7F},
+ publisher={OSF},
+ author={Shaki, Samuel and Kline Struhl, Melissa and Miske, Olivia and Loomas, Zachary and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/mb5fp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adamkovic, M., Baník, G., &amp; Ropovik, I. (2026, February 27). Stahl_JournPerSocPsy_2012_gbl9 - Ropovik - New Data Replication - 393. https://doi.org/10.17605/OSF.IO/VCFSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{adamkovic_baník_ropovik_2026,
+ title={Stahl_JournPerSocPsy_2012_gbl9 - Ropovik - New Data Replication - 393},
+ url={osf.io/vcfsg},
+ DOI={10.17605/OSF.IO/VCFSG},
+ publisher={OSF},
+ author={Adamkovic, Matus and Baník, Gabriel and Ropovik, Ivan},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/uvgp5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wulff, J. N., Abatayo, A., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Subramanian_ManagementSci_2013_VOwm - Wulff - Secondary Data Replication - ykk0. https://doi.org/10.17605/OSF.IO/82G9J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{wulff_abatayo_tyner_loomas_miske_luis_2026,
+ title={Subramanian_ManagementSci_2013_VOwm - Wulff - Secondary Data Replication - ykk0},
+ url={osf.io/82g9j},
+ DOI={10.17605/OSF.IO/82G9J},
+ publisher={OSF},
+ author={Wulff, Jesper N and Abatayo, Anna Lou and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/4bckg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Druckman, J., Freese, J., Rothschild, J., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). TOMZ_AmPoliSciRev_2009_Pb9K - Druckman - New Data Replication - 7g95. https://doi.org/10.17605/OSF.IO/RVS4Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{druckman_freese_rothschild_tyner_loomas_miske_luis_2026,
+ title={TOMZ_AmPoliSciRev_2009_Pb9K - Druckman - New Data Replication - 7g95},
+ url={osf.io/rvs4q},
+ DOI={10.17605/OSF.IO/RVS4Q},
+ publisher={OSF},
+ author={Druckman, James and Freese, Jeremy and Rothschild, Jacob and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/4gd23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Kouroupaki, D. (2026, February 27). Torelli_JournPerSocPsy_2010_gbAY - Vargo - New Data Replication - 165m6. https://doi.org/10.17605/OSF.IO/8QUJB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_vargo_kouroupaki_2026,
+ title={Torelli_JournPerSocPsy_2010_gbAY - Vargo - New Data Replication - 165m6},
+ url={osf.io/8qujb},
+ DOI={10.17605/OSF.IO/8QUJB},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Vargo, Elisabeth Julie and Kouroupaki, Dimitra},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/wgznk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2026, February 27). Umashankar_JournMarket_2017_Ej3y - Baskin - New Data Replication - 65km6. https://doi.org/10.17605/OSF.IO/SKJ4C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2026,
+ title={Umashankar_JournMarket_2017_Ej3y - Baskin - New Data Replication - 65km6},
+ url={osf.io/skj4c},
+ DOI={10.17605/OSF.IO/SKJ4C},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Baskin, Ernest},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/bnauj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de Leeuw, J. R., Charles, T., Ritzau, M., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). van Dijck_Cognition_2009_zN22 - de Leeuw - New Data Replication - m63. https://doi.org/10.17605/OSF.IO/5QWDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{de leeuw_charles_ritzau_kline struhl_loomas_miske_luis_2026,
+ title={van Dijck_Cognition_2009_zN22 - de Leeuw - New Data Replication - m63},
+ url={osf.io/5qwdh},
+ DOI={10.17605/OSF.IO/5QWDH},
+ publisher={OSF},
+ author={de Leeuw, Joshua R and Charles, Tessa and Ritzau, Margaret and Kline Struhl, Melissa and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/4w3dy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2026, February 27). Weijters_JournConsRes_2013_Rvb - Baskin - New Data Replication - 2y582. https://doi.org/10.17605/OSF.IO/EBAF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2026,
+ title={Weijters_JournConsRes_2013_Rvb - Baskin - New Data Replication - 2y582},
+ url={osf.io/ebaf2},
+ DOI={10.17605/OSF.IO/EBAF2},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Baskin, Ernest},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/jmdsy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baskin, E., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2026, April 1). Wentzel_JournAcaMarkSci_2009_Nj8V - Baskin - New Data Replication - 746. https://doi.org/10.17605/OSF.IO/2DX54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{baskin_fox_loomas_miske_luis_2026,
+ title={Wentzel_JournAcaMarkSci_2009_Nj8V - Baskin - New Data Replication - 746},
+ url={osf.io/2dx54},
+ DOI={10.17605/OSF.IO/2DX54},
+ publisher={OSF},
+ author={Baskin, Ernest and Fox, Nicholas W and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Apr}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/bfs6p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Edlund, J. (2026, February 27). Wurst_JournPerSocPsy_2017_qPxQ - Edlund - New Data Replication - 69136. https://doi.org/10.17605/OSF.IO/2BE7N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_edlund_2026,
+ title={Wurst_JournPerSocPsy_2017_qPxQ - Edlund - New Data Replication - 69136},
+ url={osf.io/2be7n},
+ DOI={10.17605/OSF.IO/2BE7N},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Edlund, John},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/zcjx7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fong, N., Field, S., Miske, O., Yoon, S., &amp; Loomas, Z. (2026, February 27). Zhang_ExpEco_2009_1VeW - Fong - New Data Replication - g941. https://doi.org/10.17605/OSF.IO/3TCZS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{fong_field_miske_yoon_loomas_2026,
+ title={Zhang_ExpEco_2009_1VeW - Fong - New Data Replication - g941},
+ url={osf.io/3tczs},
+ DOI={10.17605/OSF.IO/3TCZS},
+ publisher={OSF},
+ author={Fong, Nathan and Field, Samuel and Miske, Olivia and Yoon, Sangsuk and Loomas, Zachary},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/tybxg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Clark, B. (2026, April 1). Alves_PsychologSci_2018_AvOr - Schmidt - New Data Replication - 24716. https://doi.org/10.17605/OSF.IO/BX4HY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_schmidt_clark_2026,
+ title={Alves_PsychologSci_2018_AvOr - Schmidt - New Data Replication - 24716},
+ url={osf.io/bx4hy},
+ DOI={10.17605/OSF.IO/BX4HY},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Schmidt, Kathleen and Clark, Bruce},
+ year={2026},
+ month={Apr}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/zr7dw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Baskin, E. (2026, February 27). Amira_JournExpPoliSci_2018_a8jQ - Baskin - New Data Replication - 6mz92. https://doi.org/10.17605/OSF.IO/3G74A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_baskin_2026,
+ title={Amira_JournExpPoliSci_2018_a8jQ - Baskin - New Data Replication - 6mz92},
+ url={osf.io/3g74a},
+ DOI={10.17605/OSF.IO/3G74A},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Baskin, Ernest},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/7qnxh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chen, J., Dr., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (Cecilia), D., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B.  (2026, February 27). Baillon_Econometrica_2018_QYNq - Chen - New Data Replication - kk47. https://doi.org/10.17605/OSF.IO/5FJD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{chen_tyner_loomas_miske_luis_2026,
+ title={Baillon_Econometrica_2018_QYNq - Chen - New Data Replication - kk47},
+ url={osf.io/5fjd4},
+ DOI={10.17605/OSF.IO/5FJD4},
+ publisher={OSF},
+ author={Chen, Jingnan (Cecilia), Dr. and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/nftez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baskin, E., Kline Struhl, M., Miske, O., Loomas, Z., &amp; Luis, B. (2026, April 1). Brough_JournConsRes_2016_9ey - Baskin - New Data Replication - z161. https://doi.org/10.17605/OSF.IO/FTBMK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{baskin_kline struhl_miske_loomas_luis_2026,
+ title={Brough_JournConsRes_2016_9ey - Baskin - New Data Replication - z161},
+ url={osf.io/ftbmk},
+ DOI={10.17605/OSF.IO/FTBMK},
+ publisher={OSF},
+ author={Baskin, Ernest and Kline Struhl, Melissa and Miske, Olivia and Loomas, Zachary and Luis, Brianna},
+ year={2026},
+ month={Apr}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/fxwt7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitán, T., Capitán, S., Méndez-Chacón, E., Field, S., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Bruner_ExpEco_2017_amYY - Capitán - New Data Replication - 6mz8. https://doi.org/10.17605/OSF.IO/H2CQ7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{capitán_capitán_méndez-chacón_field_loomas_miske_luis_2026,
+ title={Bruner_ExpEco_2017_amYY - Capitán - New Data Replication - 6mz8},
+ url={osf.io/h2cq7},
+ DOI={10.17605/OSF.IO/H2CQ7},
+ publisher={OSF},
+ author={Capitán, Tabaré and Capitán, Sara and Méndez-Chacón, Esteban and Field, Samuel and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/dp4xv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braithwaite, S. R., Baldwin, S., Fox, N. W., Miske, O., Loomas, Z., &amp; Luis, B. (2026, February 27). Campbell_JournPerSocPsy_2013_gbg4 - Braithwaite - New Data Replication - 8z7g. https://doi.org/10.17605/OSF.IO/NPJU2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{braithwaite_baldwin_fox_miske_loomas_luis_2026,
+ title={Campbell_JournPerSocPsy_2013_gbg4 - Braithwaite - New Data Replication - 8z7g},
+ url={osf.io/npju2},
+ DOI={10.17605/OSF.IO/NPJU2},
+ publisher={OSF},
+ author={Braithwaite, Scott R and Baldwin, Scott and Fox, Nicholas W and Miske, Olivia and Loomas, Zachary and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/n4kby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costantini, G., Perugini, M., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., &amp; Fox, N. W. (2026, February 27). Christensen_EurJournPersonality_2018_8R9d - Costantini &amp; Perugini - New Data Replication - 9kgg. https://doi.org/10.17605/OSF.IO/MP3AK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{costantini_perugini_tyner_loomas_miske_luis_fox_2026,
+ title={Christensen_EurJournPersonality_2018_8R9d - Costantini &amp; Perugini - New Data Replication - 9kgg},
+ url={osf.io/mp3ak},
+ DOI={10.17605/OSF.IO/MP3AK},
+ publisher={OSF},
+ author={Costantini, Giulio and Perugini, Marco and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Fox, Nicholas W},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/4rch2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2026, February 27). Datar_SocSciMed_2017_RZdL - Reed - Secondary Data Replication - 6o946. https://doi.org/10.17605/OSF.IO/C9N5X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2026,
+ title={Datar_SocSciMed_2017_RZdL - Reed - Secondary Data Replication - 6o946},
+ url={osf.io/c9n5x},
+ DOI={10.17605/OSF.IO/C9N5X},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Duan, Jianhua and Hong, Sanghyun and Reed, W. R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/kms49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludvig, E. A., Walasek, L., Wort, F., &amp; Brown, G. D. A. (2026, February 27). de Langhe_JournConsRes_2014_RJb - Ludvig - New Data Replication - 6m4k. https://doi.org/10.17605/OSF.IO/VNGZ9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{ludvig_walasek_wort_brown_2026,
+ title={de Langhe_JournConsRes_2014_RJb - Ludvig - New Data Replication - 6m4k},
+ url={osf.io/vngz9},
+ DOI={10.17605/OSF.IO/VNGZ9},
+ publisher={OSF},
+ author={Ludvig, Elliot A and Walasek, Lukasz and Wort, Finn and Brown, Gordon D A},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/2zv6n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2026, February 27). Echávarri_WorldDev_2016_YmQR - Reed - Secondary Data Replication - 69412. https://doi.org/10.17605/OSF.IO/C6PKB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_porter_et al._2026,
+ title={Echávarri_WorldDev_2016_YmQR - Reed - Secondary Data Replication - 69412},
+ url={osf.io/c6pkb},
+ DOI={10.17605/OSF.IO/C6PKB},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Duan, Jianhua and Hong, Sanghyun and Porter, Nathaniel D and et al.},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/dw4mf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mallinson, D. J., Cheng, K. G., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Hahn, K. (2026, February 27). Fitzgerald_SocialForces_2018_4q0L - Cheng/Mallinson - Secondary Data Replication - 3z5z. https://doi.org/10.17605/OSF.IO/M4YSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{mallinson_cheng_tyner_loomas_miske_luis_houlihan_hahn_2026,
+ title={Fitzgerald_SocialForces_2018_4q0L - Cheng/Mallinson - Secondary Data Replication - 3z5z},
+ url={osf.io/m4yse},
+ DOI={10.17605/OSF.IO/M4YSE},
+ publisher={OSF},
+ author={Mallinson, Daniel J and Cheng, Kent Jason G and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Houlihan, Sean Dae and Hahn, Krystal},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/up8xs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kline Struhl, M., Loomas, Z., Miske, O., Luis, B., Hickman, L., Thapa, S., &amp; Tay, L. (2026, February 12). Analysis. Retrieved from osf.io/r8ehb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{kline struhl_loomas_miske_luis_hickman_thapa_tay_2026,
+ title={Analysis},
+ url={osf.io/r8ehb},
+ publisher={OSF},
+ author={Kline Struhl, Melissa and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Hickman, Louis and Thapa, Stuti and Tay, Louis},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/jqrde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed, W. R., Duan, J., Bialkowski, J., Tyner, A. H., Abatayo, A., Loomas, Z., … Vo, D. T. H. (2026, February 27). Gârleanu_RevFinStudies_2011_PlDa - Duan &amp; Bialkowski/Reed &amp; Coupe - Secondary Data Replication - 786. https://doi.org/10.17605/OSF.IO/HUAVW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{reed_duan_bialkowski_tyner_abatayo_loomas_miske_luis_coupe_vo_2026,
+ title={Gârleanu_RevFinStudies_2011_PlDa - Duan &amp; Bialkowski/Reed &amp; Coupe - Secondary Data Replication - 786},
+ url={osf.io/huavw},
+ DOI={10.17605/OSF.IO/HUAVW},
+ publisher={OSF},
+ author={Reed, W. R and Duan, Jianhua and Bialkowski, Jedrzej and Tyner, Andrew H and Abatayo, Anna Lou and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Coupe, Tom and Vo, Diem T H},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/dh3ae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Kline Struhl, M., Fox, N. W., … Fonseca, M. (2026, February 27). Goeree_Econometrica_2011_1574 - Fonseca - New Data Replication - 2w9k2. https://doi.org/10.17605/OSF.IO/MZTKR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_kline struhl_fox_tyner_hahn_fonseca_2026,
+ title={Goeree_Econometrica_2011_1574 - Fonseca - New Data Replication - 2w9k2},
+ url={osf.io/mztkr},
+ DOI={10.17605/OSF.IO/MZTKR},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Kline Struhl, Melissa and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Fonseca, Miguel},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/5qet4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavlov, Y. G., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Hurst_JournEnvPsych_2013_Vpgm - Pavlov - Secondary Data Replication - m7m3. https://doi.org/10.17605/OSF.IO/HZ97D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{pavlov_tyner_loomas_miske_luis_2026,
+ title={Hurst_JournEnvPsych_2013_Vpgm - Pavlov - Secondary Data Replication - m7m3},
+ url={osf.io/hz97d},
+ DOI={10.17605/OSF.IO/HZ97D},
+ publisher={OSF},
+ author={Pavlov, Yuri G and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/n8tds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evans, T. R. (2026, February 27). Lefevre_EurJournPersonality_2013_GNjz - Evans - New Data Replication - y60. https://doi.org/10.17605/OSF.IO/M36Y2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{evans_2026,
+ title={Lefevre_EurJournPersonality_2013_GNjz - Evans - New Data Replication - y60},
+ url={osf.io/m36y2},
+ DOI={10.17605/OSF.IO/M36Y2},
+ publisher={OSF},
+ author={Evans, Thomas R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/eq96h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banks, G. C., Sargent, A., Stock, G., Fox, N. W., Loomas, Z., Luis, B., &amp; Miske, O. (2026, February 27). Liu_OrgBehavior_2016_jDWN - Banks - Secondary Data Replication - 0y38. https://doi.org/10.17605/OSF.IO/G9V87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{banks_sargent_stock_fox_loomas_luis_miske_2026,
+ title={Liu_OrgBehavior_2016_jDWN - Banks - Secondary Data Replication - 0y38},
+ url={osf.io/g9v87},
+ DOI={10.17605/OSF.IO/G9V87},
+ publisher={OSF},
+ author={Banks, George C and Sargent, Amanda and Stock, George and Fox, Nicholas W and Loomas, Zachary and Luis, Brianna and Miske, Olivia},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/5fvdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loomas, Z., Miske, O., Luis, B., Tyner, A. H., Abatayo, A., Ramljak, M., … Fox, N. W. (2026, February 27). Maluch_LearnInst_2015_5Awm - Ramljak/Fernández-Castilla &amp; Santos - Secondary Data Replication - 2y2g. https://doi.org/10.17605/OSF.IO/K6XM9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{loomas_miske_luis_tyner_abatayo_ramljak_fernández_santos_parsons_fox_2026,
+ title={Maluch_LearnInst_2015_5Awm - Ramljak/Fernández-Castilla &amp; Santos - Secondary Data Replication - 2y2g},
+ url={osf.io/k6xm9},
+ DOI={10.17605/OSF.IO/K6XM9},
+ publisher={OSF},
+ author={Loomas, Zachary and Miske, Olivia and Luis, Brianna and Tyner, Andrew H and Abatayo, Anna Lou and Ramljak, Marco and Fernández, Belén and Santos, David and Parsons, Elan S and Fox, Nicholas W},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/zhdtn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed, W. R., Duan, J., Hong, S., Coupe, T., Loomas, Z., Miske, O., … Vo, D. T. H. (2026, February 27). McDevitt_JournPoliEco_2014_yQeR - Duan, Coupe, &amp; Hong/Reed - Secondary Data Replication - 38. https://doi.org/10.17605/OSF.IO/4V7AX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{reed_duan_hong_coupe_loomas_miske_luis_tyner_abatayo_vo_2026,
+ title={McDevitt_JournPoliEco_2014_yQeR - Duan, Coupe, &amp; Hong/Reed - Secondary Data Replication - 38},
+ url={osf.io/4v7ax},
+ DOI={10.17605/OSF.IO/4V7AX},
+ publisher={OSF},
+ author={Reed, W. R and Duan, Jianhua and Hong, Sanghyun and Coupe, Tom and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Tyner, Andrew H and Abatayo, Anna Lou and Vo, Diem T H},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/y4tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OYEBANJO, A., Cheng, K. G., Tyner, A. H., Field, S., Loomas, Z., Miske, O., … Arendt, B. (2026, February 27). Montez_Demography_2014_3aPw - Cheng/Oyebanjo - Secondary Data Replication - 05g8. https://doi.org/10.17605/OSF.IO/QCZEU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{oyebanjo_cheng_tyner_field_loomas_miske_luis_arendt_2026,
+ title={Montez_Demography_2014_3aPw - Cheng/Oyebanjo - Secondary Data Replication - 05g8},
+ url={osf.io/qczeu},
+ DOI={10.17605/OSF.IO/QCZEU},
+ publisher={OSF},
+ author={OYEBANJO, Abiola and Cheng, Kent Jason G and Tyner, Andrew H and Field, Samuel and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Arendt, Beatrix},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/rg5vt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sommet, N., Batruch, A., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Mosimann_WorldPolitics_2017_z4dO - Sommet &amp; Batruch - Secondary Data Replication - yzz0. https://doi.org/10.17605/OSF.IO/RS7E9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{sommet_batruch_tyner_loomas_miske_luis_2026,
+ title={Mosimann_WorldPolitics_2017_z4dO - Sommet &amp; Batruch - Secondary Data Replication - yzz0},
+ url={osf.io/rs7e9},
+ DOI={10.17605/OSF.IO/RS7E9},
+ publisher={OSF},
+ author={Sommet, Nicolas and Batruch, Anatolia and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/f5esc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reed, W. R., Duan, J., Tyner, A. H., Loomas, Z., Miske, O., Luis, B., … Hahn, K. (2026, February 27). Niehaus_AmEduResJourn_2014_BlRQ - Duan/Reed &amp; Coupe - Secondary Data Replication - 546. https://doi.org/10.17605/OSF.IO/KR7WF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{reed_duan_tyner_loomas_miske_luis_abatayo_coupe_vo_kline struhl_et al._2026,
+ title={Niehaus_AmEduResJourn_2014_BlRQ - Duan/Reed &amp; Coupe - Secondary Data Replication - 546},
+ url={osf.io/kr7wf},
+ DOI={10.17605/OSF.IO/KR7WF},
+ publisher={OSF},
+ author={Reed, W. R and Duan, Jianhua and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Abatayo, Anna Lou and Coupe, Tom and Vo, Diem T H and Kline Struhl, Melissa and et al.},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/rak92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">van de Ven, N., Pieters, C., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Pappu_JournAcaMarkSci_2014_yDyG - van de Ven - New Data Replication - z106. https://doi.org/10.17605/OSF.IO/XTMY9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{van de ven_pieters_fox_loomas_miske_luis_2026,
+ title={Pappu_JournAcaMarkSci_2014_yDyG - van de Ven - New Data Replication - z106},
+ url={osf.io/xtmy9},
+ DOI={10.17605/OSF.IO/XTMY9},
+ publisher={OSF},
+ author={van de Ven, Niels and Pieters, Constant and Fox, Nicholas W and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/axph8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Higgins, N. C., Sanchez, M., Monjaras, A., Nave-Blodgett, J. E., Snyder, J. S., Kline Struhl, M., … Luis, B. (2026, February 27). Petersen_Cognition_2017_yJwG - Snyder - New Data Replication - 9ky. https://doi.org/10.17605/OSF.IO/WTM3E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{higgins_sanchez_monjaras_nave-blodgett_snyder_kline struhl_miske_luis_2026,
+ title={Petersen_Cognition_2017_yJwG - Snyder - New Data Replication - 9ky},
+ url={osf.io/wtm3e},
+ DOI={10.17605/OSF.IO/WTM3E},
+ publisher={OSF},
+ author={Higgins, Nathan C and Sanchez, Mary and Monjaras, Ambar and Nave-Blodgett, Jessica E and Snyder, Joel S and Kline Struhl, Melissa and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/7q5d4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2026, February 27). Pitts_PubAdminRev_2011_0wWk - Reed - Secondary Data Replication - 28yg6. https://doi.org/10.17605/OSF.IO/EFUHG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2026,
+ title={Pitts_PubAdminRev_2011_0wWk - Reed - Secondary Data Replication - 28yg6},
+ url={osf.io/efuhg},
+ DOI={10.17605/OSF.IO/EFUHG},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Duan, Jianhua and Hong, Sanghyun and Reed, W. R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/69zjt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Briker, R., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Walter, F. (2026, February 27). Reh_JournAppPsych_2018_K4ZD - Briker - New Data Replication - y071. https://doi.org/10.17605/OSF.IO/2JN6D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{briker_kline struhl_loomas_miske_walter_2026,
+ title={Reh_JournAppPsych_2018_K4ZD - Briker - New Data Replication - y071},
+ url={osf.io/2jn6d},
+ DOI={10.17605/OSF.IO/2JN6D},
+ publisher={OSF},
+ author={Briker, Roman and Kline Struhl, Melissa and Loomas, Zachary and Miske, Olivia and Walter, Frank},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/jtd7n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Urbanska, K. (2026, February 27). Robinson_EduRes_2011_NrrW - Urbanska - Secondary Data Replication - 24812. https://doi.org/10.17605/OSF.IO/9VXWZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_urbanska_2026,
+ title={Robinson_EduRes_2011_NrrW - Urbanska - Secondary Data Replication - 24812},
+ url={osf.io/9vxwz},
+ DOI={10.17605/OSF.IO/9VXWZ},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Urbanska, Karolina},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/6gpkx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schmidt, K., Hall, B. F., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Seuntjens_JournPerSocPsy_2015_PNPz - Schmidt - New Data Replication - 5zg9. https://doi.org/10.17605/OSF.IO/ER4GY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{schmidt_hall_fox_loomas_miske_luis_2026,
+ title={Seuntjens_JournPerSocPsy_2015_PNPz - Schmidt - New Data Replication - 5zg9},
+ url={osf.io/er4gy},
+ DOI={10.17605/OSF.IO/ER4GY},
+ publisher={OSF},
+ author={Schmidt, Kathleen and Hall, Braeden F and Fox, Nicholas W and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/d923e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peters, K. O., Fox, N. W., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Thomas_JournPerSocPsy_2014_xvrb - Peters - New Data Replication - z591. https://doi.org/10.17605/OSF.IO/XNH2R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{peters_fox_loomas_miske_luis_2026,
+ title={Thomas_JournPerSocPsy_2014_xvrb - Peters - New Data Replication - z591},
+ url={osf.io/xnh2r},
+ DOI={10.17605/OSF.IO/XNH2R},
+ publisher={OSF},
+ author={Peters, Kim O and Fox, Nicholas W and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/3ykw5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsons, E. S., Miske, O., Luis, B., Loomas, Z., Fox, N. W., Tyner, A. H., … Reed, W. R. (2026, February 27). Thomas_Demography_2012_dxQp - Reed - Secondary Data Replication - 2w5k2. https://doi.org/10.17605/OSF.IO/QRU6T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{parsons_miske_luis_loomas_fox_tyner_hahn_duan_hong_reed_2026,
+ title={Thomas_Demography_2012_dxQp - Reed - Secondary Data Replication - 2w5k2},
+ url={osf.io/qru6t},
+ DOI={10.17605/OSF.IO/QRU6T},
+ publisher={OSF},
+ author={Parsons, Elan S and Miske, Olivia and Luis, Brianna and Loomas, Zachary and Fox, Nicholas W and Tyner, Andrew H and Hahn, Krystal and Duan, Jianhua and Hong, Sanghyun and Reed, W. R},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/jr239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Méndez-Chacón, E., Sisco, M. R., Tyner, A. H., Abatayo, A., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Travers_ExChildren_2018_zqwm - Sisco/Méndez-Chacón - Secondary Data Replication - z4z9. https://doi.org/10.17605/OSF.IO/87QS6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{méndez-chacón_sisco_tyner_abatayo_loomas_miske_luis_2026,
+ title={Travers_ExChildren_2018_zqwm - Sisco/Méndez-Chacón - Secondary Data Replication - z4z9},
+ url={osf.io/87qs6},
+ DOI={10.17605/OSF.IO/87QS6},
+ publisher={OSF},
+ author={Méndez-Chacón, Esteban and Sisco, Matthew R and Tyner, Andrew H and Abatayo, Anna Lou and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/82z6a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oshana, A., Banks, G. C., &amp; Tyner, A. H. (2026, February 27). Triana_JournOrgBehavior_2009_347d - Banks - New Data Replication - m89. https://doi.org/10.17605/OSF.IO/56JQU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{oshana_banks_tyner_2026,
+ title={Triana_JournOrgBehavior_2009_347d - Banks - New Data Replication - m89},
+ url={osf.io/56jqu},
+ DOI={10.17605/OSF.IO/56JQU},
+ publisher={OSF},
+ author={Oshana, Adoril and Banks, George C and Tyner, Andrew H},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/f93t6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samaha, J., Kline Struhl, M., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Zhou_JournExPsychGen_2014_VjjX - Samaha - New Data Replication - 99m7. https://doi.org/10.17605/OSF.IO/9R2JW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{samaha_kline struhl_loomas_miske_luis_2026,
+ title={Zhou_JournExPsychGen_2014_VjjX - Samaha - New Data Replication - 99m7},
+ url={osf.io/9r2jw},
+ DOI={10.17605/OSF.IO/9R2JW},
+ publisher={OSF},
+ author={Samaha, Jason and Kline Struhl, Melissa and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/w9acu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michaelides, M., Durkee, P. K., Abatayo, A., Tyner, A. H., Loomas, Z., Miske, O., … Kline Struhl, M. (2026, February 27). Zimmerman_ContEduPsych_2014_EZ3x - Michaelides/Durkee - Secondary Data Replication - 8z2g. https://doi.org/10.17605/OSF.IO/A4SWD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{michaelides_durkee_abatayo_tyner_loomas_miske_luis_kline struhl_2026,
+ title={Zimmerman_ContEduPsych_2014_EZ3x - Michaelides/Durkee - Secondary Data Replication - 8z2g},
+ url={osf.io/a4swd},
+ DOI={10.17605/OSF.IO/A4SWD},
+ publisher={OSF},
+ author={Michaelides, Michalis and Durkee, Patrick K and Abatayo, Anna Lou and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna and Kline Struhl, Melissa},
+ year={2026},
+ month={Feb}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osf.io/8uc5z/files/jmk9d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andreychik, M., Tyner, A. H., Loomas, Z., Miske, O., &amp; Luis, B. (2026, February 27). Nyhan_JournExpPoliSci_2015_DEqr - Andreychik - New Data Replication - 61k8. https://doi.org/10.17605/OSF.IO/8UC5Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">@misc{andreychik_tyner_loomas_miske_luis_2026,
+ title={Nyhan_JournExpPoliSci_2015_DEqr - Andreychik - New Data Replication - 61k8},
+ url={osf.io/8uc5z},
+ DOI={10.17605/OSF.IO/8UC5Z},
+ publisher={OSF},
+ author={Andreychik, Michael and Tyner, Andrew H and Loomas, Zachary and Miske, Olivia and Luis, Brianna},
+ year={2026},
+ month={Feb}
+}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2395,29 +3520,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -2699,11 +3811,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J186"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2735,7 +3847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2745,8 +3857,15 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2756,8 +3875,15 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -2767,8 +3893,15 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -2778,8 +3911,15 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2789,8 +3929,15 @@
       <c r="C6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2800,8 +3947,15 @@
       <c r="C7" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2811,8 +3965,15 @@
       <c r="C8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2822,8 +3983,15 @@
       <c r="C9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -2833,8 +4001,15 @@
       <c r="C10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -2844,8 +4019,15 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -2855,8 +4037,15 @@
       <c r="C12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -2866,8 +4055,15 @@
       <c r="C13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -2877,8 +4073,15 @@
       <c r="C14" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2888,8 +4091,15 @@
       <c r="C15" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -2899,8 +4109,15 @@
       <c r="C16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2910,8 +4127,15 @@
       <c r="C17" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -2921,8 +4145,15 @@
       <c r="C18" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -2932,8 +4163,15 @@
       <c r="C19" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -2943,8 +4181,15 @@
       <c r="C20" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -2954,8 +4199,15 @@
       <c r="C21" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -2965,8 +4217,15 @@
       <c r="C22" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -2976,8 +4235,15 @@
       <c r="C23" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -2987,8 +4253,15 @@
       <c r="C24" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -2998,16 +4271,31 @@
       <c r="C25" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25"/>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>82</v>
       </c>
       <c r="B26" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -3017,8 +4305,15 @@
       <c r="C27" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -3028,8 +4323,15 @@
       <c r="C28" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -3039,8 +4341,15 @@
       <c r="C29" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="I29"/>
+      <c r="J29"/>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -3050,8 +4359,15 @@
       <c r="C30" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30"/>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -3061,8 +4377,15 @@
       <c r="C31" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -3072,8 +4395,15 @@
       <c r="C32" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="I32"/>
+      <c r="J32"/>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -3083,8 +4413,15 @@
       <c r="C33" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="I33"/>
+      <c r="J33"/>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -3094,8 +4431,15 @@
       <c r="C34" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="I34"/>
+      <c r="J34"/>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -3105,8 +4449,15 @@
       <c r="C35" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
         <v>111</v>
       </c>
@@ -3116,8 +4467,15 @@
       <c r="C36" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -3127,8 +4485,15 @@
       <c r="C37" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -3138,8 +4503,15 @@
       <c r="C38" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="I38"/>
+      <c r="J38"/>
+    </row>
+    <row r="39">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -3149,8 +4521,15 @@
       <c r="C39" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="I39"/>
+      <c r="J39"/>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -3160,8 +4539,15 @@
       <c r="C40" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40"/>
+      <c r="J40"/>
+    </row>
+    <row r="41">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -3171,8 +4557,15 @@
       <c r="C41" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -3182,8 +4575,15 @@
       <c r="C42" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -3193,8 +4593,15 @@
       <c r="C43" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="I43"/>
+      <c r="J43"/>
+    </row>
+    <row r="44">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -3204,8 +4611,15 @@
       <c r="C44" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
         <v>129</v>
       </c>
@@ -3215,8 +4629,15 @@
       <c r="C45" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45"/>
+      <c r="J45"/>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -3226,8 +4647,15 @@
       <c r="C46" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46"/>
+    </row>
+    <row r="47">
       <c r="A47" t="s">
         <v>135</v>
       </c>
@@ -3237,8 +4665,15 @@
       <c r="C47" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47"/>
+    </row>
+    <row r="48">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -3248,8 +4683,15 @@
       <c r="C48" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="I48"/>
+      <c r="J48"/>
+    </row>
+    <row r="49">
       <c r="A49" t="s">
         <v>135</v>
       </c>
@@ -3259,8 +4701,15 @@
       <c r="C49" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+    </row>
+    <row r="50">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -3270,8 +4719,15 @@
       <c r="C50" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+    </row>
+    <row r="51">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -3281,8 +4737,15 @@
       <c r="C51" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+    </row>
+    <row r="52">
       <c r="A52" t="s">
         <v>138</v>
       </c>
@@ -3292,8 +4755,15 @@
       <c r="C52" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+    </row>
+    <row r="53">
       <c r="A53" t="s">
         <v>141</v>
       </c>
@@ -3303,8 +4773,15 @@
       <c r="C53" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+    </row>
+    <row r="54">
       <c r="A54" t="s">
         <v>144</v>
       </c>
@@ -3314,8 +4791,15 @@
       <c r="C54" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+    </row>
+    <row r="55">
       <c r="A55" t="s">
         <v>144</v>
       </c>
@@ -3325,8 +4809,15 @@
       <c r="C55" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+    </row>
+    <row r="56">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -3336,8 +4827,15 @@
       <c r="C56" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+    </row>
+    <row r="57">
       <c r="A57" t="s">
         <v>147</v>
       </c>
@@ -3347,8 +4845,15 @@
       <c r="C57" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+    </row>
+    <row r="58">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -3358,8 +4863,15 @@
       <c r="C58" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+    </row>
+    <row r="59">
       <c r="A59" t="s">
         <v>147</v>
       </c>
@@ -3369,8 +4881,15 @@
       <c r="C59" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+    </row>
+    <row r="60">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -3380,8 +4899,15 @@
       <c r="C60" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+    </row>
+    <row r="61">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -3391,8 +4917,15 @@
       <c r="C61" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+    </row>
+    <row r="62">
       <c r="A62" t="s">
         <v>153</v>
       </c>
@@ -3402,8 +4935,15 @@
       <c r="C62" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+    </row>
+    <row r="63">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -3413,8 +4953,15 @@
       <c r="C63" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+    </row>
+    <row r="64">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -3424,8 +4971,15 @@
       <c r="C64" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+    </row>
+    <row r="65">
       <c r="A65" t="s">
         <v>156</v>
       </c>
@@ -3435,8 +4989,15 @@
       <c r="C65" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+    </row>
+    <row r="66">
       <c r="A66" t="s">
         <v>156</v>
       </c>
@@ -3446,8 +5007,15 @@
       <c r="C66" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+    </row>
+    <row r="67">
       <c r="A67" t="s">
         <v>159</v>
       </c>
@@ -3457,8 +5025,15 @@
       <c r="C67" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+    </row>
+    <row r="68">
       <c r="A68" t="s">
         <v>159</v>
       </c>
@@ -3468,8 +5043,15 @@
       <c r="C68" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+    </row>
+    <row r="69">
       <c r="A69" t="s">
         <v>159</v>
       </c>
@@ -3479,8 +5061,15 @@
       <c r="C69" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+    </row>
+    <row r="70">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -3490,8 +5079,15 @@
       <c r="C70" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+    </row>
+    <row r="71">
       <c r="A71" t="s">
         <v>162</v>
       </c>
@@ -3501,8 +5097,15 @@
       <c r="C71" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="I71"/>
+      <c r="J71"/>
+    </row>
+    <row r="72">
       <c r="A72" t="s">
         <v>162</v>
       </c>
@@ -3512,8 +5115,15 @@
       <c r="C72" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="I72"/>
+      <c r="J72"/>
+    </row>
+    <row r="73">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -3523,8 +5133,15 @@
       <c r="C73" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+    </row>
+    <row r="74">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -3534,8 +5151,15 @@
       <c r="C74" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="I74"/>
+      <c r="J74"/>
+    </row>
+    <row r="75">
       <c r="A75" t="s">
         <v>168</v>
       </c>
@@ -3545,8 +5169,15 @@
       <c r="C75" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75"/>
+      <c r="I75"/>
+      <c r="J75"/>
+    </row>
+    <row r="76">
       <c r="A76" t="s">
         <v>171</v>
       </c>
@@ -3556,8 +5187,15 @@
       <c r="C76" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76"/>
+      <c r="I76"/>
+      <c r="J76"/>
+    </row>
+    <row r="77">
       <c r="A77" t="s">
         <v>171</v>
       </c>
@@ -3567,8 +5205,15 @@
       <c r="C77" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="I77"/>
+      <c r="J77"/>
+    </row>
+    <row r="78">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -3578,8 +5223,15 @@
       <c r="C78" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
+      <c r="I78"/>
+      <c r="J78"/>
+    </row>
+    <row r="79">
       <c r="A79" t="s">
         <v>174</v>
       </c>
@@ -3589,8 +5241,15 @@
       <c r="C79" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79"/>
+      <c r="I79"/>
+      <c r="J79"/>
+    </row>
+    <row r="80">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -3600,8 +5259,15 @@
       <c r="C80" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="I80"/>
+      <c r="J80"/>
+    </row>
+    <row r="81">
       <c r="A81" t="s">
         <v>177</v>
       </c>
@@ -3611,8 +5277,15 @@
       <c r="C81" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="I81"/>
+      <c r="J81"/>
+    </row>
+    <row r="82">
       <c r="A82" t="s">
         <v>177</v>
       </c>
@@ -3622,8 +5295,15 @@
       <c r="C82" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="I82"/>
+      <c r="J82"/>
+    </row>
+    <row r="83">
       <c r="A83" t="s">
         <v>177</v>
       </c>
@@ -3633,8 +5313,15 @@
       <c r="C83" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="I83"/>
+      <c r="J83"/>
+    </row>
+    <row r="84">
       <c r="A84" t="s">
         <v>180</v>
       </c>
@@ -3644,8 +5331,15 @@
       <c r="C84" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="I84"/>
+      <c r="J84"/>
+    </row>
+    <row r="85">
       <c r="A85" t="s">
         <v>183</v>
       </c>
@@ -3655,8 +5349,15 @@
       <c r="C85" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+      <c r="I85"/>
+      <c r="J85"/>
+    </row>
+    <row r="86">
       <c r="A86" t="s">
         <v>186</v>
       </c>
@@ -3666,8 +5367,15 @@
       <c r="C86" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
+    </row>
+    <row r="87">
       <c r="A87" t="s">
         <v>186</v>
       </c>
@@ -3677,8 +5385,15 @@
       <c r="C87" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+    </row>
+    <row r="88">
       <c r="A88" t="s">
         <v>189</v>
       </c>
@@ -3688,8 +5403,15 @@
       <c r="C88" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+    </row>
+    <row r="89">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -3699,8 +5421,15 @@
       <c r="C89" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
+      <c r="I89"/>
+      <c r="J89"/>
+    </row>
+    <row r="90">
       <c r="A90" t="s">
         <v>195</v>
       </c>
@@ -3710,8 +5439,15 @@
       <c r="C90" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="I90"/>
+      <c r="J90"/>
+    </row>
+    <row r="91">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -3721,8 +5457,15 @@
       <c r="C91" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="I91"/>
+      <c r="J91"/>
+    </row>
+    <row r="92">
       <c r="A92" t="s">
         <v>201</v>
       </c>
@@ -3732,8 +5475,15 @@
       <c r="C92" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="I92"/>
+      <c r="J92"/>
+    </row>
+    <row r="93">
       <c r="A93" t="s">
         <v>201</v>
       </c>
@@ -3743,8 +5493,15 @@
       <c r="C93" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="H93"/>
+      <c r="I93"/>
+      <c r="J93"/>
+    </row>
+    <row r="94">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -3754,8 +5511,15 @@
       <c r="C94" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="I94"/>
+      <c r="J94"/>
+    </row>
+    <row r="95">
       <c r="A95" t="s">
         <v>201</v>
       </c>
@@ -3765,8 +5529,15 @@
       <c r="C95" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95"/>
+      <c r="I95"/>
+      <c r="J95"/>
+    </row>
+    <row r="96">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -3776,8 +5547,15 @@
       <c r="C96" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="H96"/>
+      <c r="I96"/>
+      <c r="J96"/>
+    </row>
+    <row r="97">
       <c r="A97" t="s">
         <v>201</v>
       </c>
@@ -3787,8 +5565,15 @@
       <c r="C97" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97"/>
+      <c r="I97"/>
+      <c r="J97"/>
+    </row>
+    <row r="98">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -3798,8 +5583,15 @@
       <c r="C98" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="H98"/>
+      <c r="I98"/>
+      <c r="J98"/>
+    </row>
+    <row r="99">
       <c r="A99" t="s">
         <v>201</v>
       </c>
@@ -3809,8 +5601,15 @@
       <c r="C99" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+    </row>
+    <row r="100">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -3820,8 +5619,15 @@
       <c r="C100" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+      <c r="I100"/>
+      <c r="J100"/>
+    </row>
+    <row r="101">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -3831,8 +5637,15 @@
       <c r="C101" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+    </row>
+    <row r="102">
       <c r="A102" t="s">
         <v>207</v>
       </c>
@@ -3842,8 +5655,15 @@
       <c r="C102" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+    </row>
+    <row r="103">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -3853,8 +5673,15 @@
       <c r="C103" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
+    </row>
+    <row r="104">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -3864,8 +5691,15 @@
       <c r="C104" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
+    </row>
+    <row r="105">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -3875,8 +5709,15 @@
       <c r="C105" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105"/>
+    </row>
+    <row r="106">
       <c r="A106" t="s">
         <v>219</v>
       </c>
@@ -3886,8 +5727,15 @@
       <c r="C106" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106"/>
+    </row>
+    <row r="107">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -3897,8 +5745,15 @@
       <c r="C107" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
+    </row>
+    <row r="108">
       <c r="A108" t="s">
         <v>219</v>
       </c>
@@ -3908,8 +5763,15 @@
       <c r="C108" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+    </row>
+    <row r="109">
       <c r="A109" t="s">
         <v>219</v>
       </c>
@@ -3919,8 +5781,15 @@
       <c r="C109" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109"/>
+    </row>
+    <row r="110">
       <c r="A110" t="s">
         <v>222</v>
       </c>
@@ -3930,8 +5799,15 @@
       <c r="C110" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+    </row>
+    <row r="111">
       <c r="A111" t="s">
         <v>225</v>
       </c>
@@ -3941,8 +5817,15 @@
       <c r="C111" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+    </row>
+    <row r="112">
       <c r="A112" t="s">
         <v>228</v>
       </c>
@@ -3952,8 +5835,15 @@
       <c r="C112" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="I112"/>
+      <c r="J112"/>
+    </row>
+    <row r="113">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -3963,8 +5853,15 @@
       <c r="C113" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+    </row>
+    <row r="114">
       <c r="A114" t="s">
         <v>234</v>
       </c>
@@ -3974,8 +5871,15 @@
       <c r="C114" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
+    </row>
+    <row r="115">
       <c r="A115" t="s">
         <v>237</v>
       </c>
@@ -3985,8 +5889,15 @@
       <c r="C115" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115"/>
+    </row>
+    <row r="116">
       <c r="A116" t="s">
         <v>240</v>
       </c>
@@ -3996,8 +5907,15 @@
       <c r="C116" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116"/>
+    </row>
+    <row r="117">
       <c r="A117" t="s">
         <v>243</v>
       </c>
@@ -4007,8 +5925,15 @@
       <c r="C117" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
+    </row>
+    <row r="118">
       <c r="A118" t="s">
         <v>246</v>
       </c>
@@ -4018,8 +5943,15 @@
       <c r="C118" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
+    </row>
+    <row r="119">
       <c r="A119" t="s">
         <v>249</v>
       </c>
@@ -4029,8 +5961,15 @@
       <c r="C119" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
+    </row>
+    <row r="120">
       <c r="A120" t="s">
         <v>252</v>
       </c>
@@ -4040,8 +5979,15 @@
       <c r="C120" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120"/>
+    </row>
+    <row r="121">
       <c r="A121" t="s">
         <v>255</v>
       </c>
@@ -4051,8 +5997,15 @@
       <c r="C121" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121"/>
+    </row>
+    <row r="122">
       <c r="A122" t="s">
         <v>258</v>
       </c>
@@ -4062,8 +6015,15 @@
       <c r="C122" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+    </row>
+    <row r="123">
       <c r="A123" t="s">
         <v>261</v>
       </c>
@@ -4073,8 +6033,15 @@
       <c r="C123" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123"/>
+      <c r="I123"/>
+      <c r="J123"/>
+    </row>
+    <row r="124">
       <c r="A124" t="s">
         <v>264</v>
       </c>
@@ -4084,8 +6051,15 @@
       <c r="C124" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="H124"/>
+      <c r="I124"/>
+      <c r="J124"/>
+    </row>
+    <row r="125">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -4095,8 +6069,15 @@
       <c r="C125" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="H125"/>
+      <c r="I125"/>
+      <c r="J125"/>
+    </row>
+    <row r="126">
       <c r="A126" t="s">
         <v>270</v>
       </c>
@@ -4106,8 +6087,15 @@
       <c r="C126" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="H126"/>
+      <c r="I126"/>
+      <c r="J126"/>
+    </row>
+    <row r="127">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -4117,8 +6105,15 @@
       <c r="C127" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="H127"/>
+      <c r="I127"/>
+      <c r="J127"/>
+    </row>
+    <row r="128">
       <c r="A128" t="s">
         <v>276</v>
       </c>
@@ -4128,8 +6123,15 @@
       <c r="C128" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D128"/>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="H128"/>
+      <c r="I128"/>
+      <c r="J128"/>
+    </row>
+    <row r="129">
       <c r="A129" t="s">
         <v>279</v>
       </c>
@@ -4139,8 +6141,15 @@
       <c r="C129" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="I129"/>
+      <c r="J129"/>
+    </row>
+    <row r="130">
       <c r="A130" t="s">
         <v>282</v>
       </c>
@@ -4150,8 +6159,15 @@
       <c r="C130" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
+    </row>
+    <row r="131">
       <c r="A131" t="s">
         <v>285</v>
       </c>
@@ -4161,8 +6177,15 @@
       <c r="C131" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+      <c r="J131"/>
+    </row>
+    <row r="132">
       <c r="A132" t="s">
         <v>288</v>
       </c>
@@ -4172,8 +6195,15 @@
       <c r="C132" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D132"/>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="H132"/>
+      <c r="I132"/>
+      <c r="J132"/>
+    </row>
+    <row r="133">
       <c r="A133" t="s">
         <v>291</v>
       </c>
@@ -4183,8 +6213,15 @@
       <c r="C133" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D133"/>
+      <c r="E133"/>
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="H133"/>
+      <c r="I133"/>
+      <c r="J133"/>
+    </row>
+    <row r="134">
       <c r="A134" t="s">
         <v>294</v>
       </c>
@@ -4194,8 +6231,15 @@
       <c r="C134" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
+      <c r="G134"/>
+      <c r="H134"/>
+      <c r="I134"/>
+      <c r="J134"/>
+    </row>
+    <row r="135">
       <c r="A135" t="s">
         <v>297</v>
       </c>
@@ -4205,8 +6249,15 @@
       <c r="C135" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D135"/>
+      <c r="E135"/>
+      <c r="F135"/>
+      <c r="G135"/>
+      <c r="H135"/>
+      <c r="I135"/>
+      <c r="J135"/>
+    </row>
+    <row r="136">
       <c r="A136" t="s">
         <v>300</v>
       </c>
@@ -4216,8 +6267,15 @@
       <c r="C136" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D136"/>
+      <c r="E136"/>
+      <c r="F136"/>
+      <c r="G136"/>
+      <c r="H136"/>
+      <c r="I136"/>
+      <c r="J136"/>
+    </row>
+    <row r="137">
       <c r="A137" t="s">
         <v>303</v>
       </c>
@@ -4227,8 +6285,15 @@
       <c r="C137" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D137"/>
+      <c r="E137"/>
+      <c r="F137"/>
+      <c r="G137"/>
+      <c r="H137"/>
+      <c r="I137"/>
+      <c r="J137"/>
+    </row>
+    <row r="138">
       <c r="A138" t="s">
         <v>306</v>
       </c>
@@ -4238,8 +6303,15 @@
       <c r="C138" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D138"/>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138"/>
+      <c r="I138"/>
+      <c r="J138"/>
+    </row>
+    <row r="139">
       <c r="A139" t="s">
         <v>309</v>
       </c>
@@ -4249,8 +6321,15 @@
       <c r="C139" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D139"/>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="H139"/>
+      <c r="I139"/>
+      <c r="J139"/>
+    </row>
+    <row r="140">
       <c r="A140" t="s">
         <v>312</v>
       </c>
@@ -4260,8 +6339,15 @@
       <c r="C140" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D140"/>
+      <c r="E140"/>
+      <c r="F140"/>
+      <c r="G140"/>
+      <c r="H140"/>
+      <c r="I140"/>
+      <c r="J140"/>
+    </row>
+    <row r="141">
       <c r="A141" t="s">
         <v>315</v>
       </c>
@@ -4271,8 +6357,15 @@
       <c r="C141" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D141"/>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141"/>
+      <c r="H141"/>
+      <c r="I141"/>
+      <c r="J141"/>
+    </row>
+    <row r="142">
       <c r="A142" t="s">
         <v>318</v>
       </c>
@@ -4282,8 +6375,15 @@
       <c r="C142" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D142"/>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142"/>
+      <c r="H142"/>
+      <c r="I142"/>
+      <c r="J142"/>
+    </row>
+    <row r="143">
       <c r="A143" t="s">
         <v>321</v>
       </c>
@@ -4293,8 +6393,15 @@
       <c r="C143" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D143"/>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143"/>
+      <c r="H143"/>
+      <c r="I143"/>
+      <c r="J143"/>
+    </row>
+    <row r="144">
       <c r="A144" t="s">
         <v>324</v>
       </c>
@@ -4304,8 +6411,15 @@
       <c r="C144" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D144"/>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="H144"/>
+      <c r="I144"/>
+      <c r="J144"/>
+    </row>
+    <row r="145">
       <c r="A145" t="s">
         <v>327</v>
       </c>
@@ -4315,8 +6429,15 @@
       <c r="C145" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="H145"/>
+      <c r="I145"/>
+      <c r="J145"/>
+    </row>
+    <row r="146">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -4326,8 +6447,15 @@
       <c r="C146" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="H146"/>
+      <c r="I146"/>
+      <c r="J146"/>
+    </row>
+    <row r="147">
       <c r="A147" t="s">
         <v>333</v>
       </c>
@@ -4337,8 +6465,15 @@
       <c r="C147" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147"/>
+      <c r="H147"/>
+      <c r="I147"/>
+      <c r="J147"/>
+    </row>
+    <row r="148">
       <c r="A148" t="s">
         <v>336</v>
       </c>
@@ -4348,8 +6483,15 @@
       <c r="C148" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D148"/>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148"/>
+      <c r="H148"/>
+      <c r="I148"/>
+      <c r="J148"/>
+    </row>
+    <row r="149">
       <c r="A149" t="s">
         <v>339</v>
       </c>
@@ -4359,8 +6501,15 @@
       <c r="C149" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D149"/>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149"/>
+      <c r="H149"/>
+      <c r="I149"/>
+      <c r="J149"/>
+    </row>
+    <row r="150">
       <c r="A150" t="s">
         <v>342</v>
       </c>
@@ -4370,8 +6519,15 @@
       <c r="C150" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D150"/>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150"/>
+      <c r="H150"/>
+      <c r="I150"/>
+      <c r="J150"/>
+    </row>
+    <row r="151">
       <c r="A151" t="s">
         <v>345</v>
       </c>
@@ -4381,8 +6537,15 @@
       <c r="C151" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D151"/>
+      <c r="E151"/>
+      <c r="F151"/>
+      <c r="G151"/>
+      <c r="H151"/>
+      <c r="I151"/>
+      <c r="J151"/>
+    </row>
+    <row r="152">
       <c r="A152" t="s">
         <v>348</v>
       </c>
@@ -4392,8 +6555,15 @@
       <c r="C152" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D152"/>
+      <c r="E152"/>
+      <c r="F152"/>
+      <c r="G152"/>
+      <c r="H152"/>
+      <c r="I152"/>
+      <c r="J152"/>
+    </row>
+    <row r="153">
       <c r="A153" t="s">
         <v>351</v>
       </c>
@@ -4403,8 +6573,15 @@
       <c r="C153" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D153"/>
+      <c r="E153"/>
+      <c r="F153"/>
+      <c r="G153"/>
+      <c r="H153"/>
+      <c r="I153"/>
+      <c r="J153"/>
+    </row>
+    <row r="154">
       <c r="A154" t="s">
         <v>354</v>
       </c>
@@ -4414,8 +6591,15 @@
       <c r="C154" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D154"/>
+      <c r="E154"/>
+      <c r="F154"/>
+      <c r="G154"/>
+      <c r="H154"/>
+      <c r="I154"/>
+      <c r="J154"/>
+    </row>
+    <row r="155">
       <c r="A155" t="s">
         <v>357</v>
       </c>
@@ -4425,8 +6609,15 @@
       <c r="C155" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D155"/>
+      <c r="E155"/>
+      <c r="F155"/>
+      <c r="G155"/>
+      <c r="H155"/>
+      <c r="I155"/>
+      <c r="J155"/>
+    </row>
+    <row r="156">
       <c r="A156" t="s">
         <v>360</v>
       </c>
@@ -4436,8 +6627,15 @@
       <c r="C156" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D156"/>
+      <c r="E156"/>
+      <c r="F156"/>
+      <c r="G156"/>
+      <c r="H156"/>
+      <c r="I156"/>
+      <c r="J156"/>
+    </row>
+    <row r="157">
       <c r="A157" t="s">
         <v>363</v>
       </c>
@@ -4447,8 +6645,15 @@
       <c r="C157" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D157"/>
+      <c r="E157"/>
+      <c r="F157"/>
+      <c r="G157"/>
+      <c r="H157"/>
+      <c r="I157"/>
+      <c r="J157"/>
+    </row>
+    <row r="158">
       <c r="A158" t="s">
         <v>366</v>
       </c>
@@ -4458,8 +6663,15 @@
       <c r="C158" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D158"/>
+      <c r="E158"/>
+      <c r="F158"/>
+      <c r="G158"/>
+      <c r="H158"/>
+      <c r="I158"/>
+      <c r="J158"/>
+    </row>
+    <row r="159">
       <c r="A159" t="s">
         <v>369</v>
       </c>
@@ -4469,8 +6681,15 @@
       <c r="C159" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D159"/>
+      <c r="E159"/>
+      <c r="F159"/>
+      <c r="G159"/>
+      <c r="H159"/>
+      <c r="I159"/>
+      <c r="J159"/>
+    </row>
+    <row r="160">
       <c r="A160" t="s">
         <v>372</v>
       </c>
@@ -4480,8 +6699,15 @@
       <c r="C160" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D160"/>
+      <c r="E160"/>
+      <c r="F160"/>
+      <c r="G160"/>
+      <c r="H160"/>
+      <c r="I160"/>
+      <c r="J160"/>
+    </row>
+    <row r="161">
       <c r="A161" t="s">
         <v>375</v>
       </c>
@@ -4491,8 +6717,15 @@
       <c r="C161" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D161"/>
+      <c r="E161"/>
+      <c r="F161"/>
+      <c r="G161"/>
+      <c r="H161"/>
+      <c r="I161"/>
+      <c r="J161"/>
+    </row>
+    <row r="162">
       <c r="A162" t="s">
         <v>378</v>
       </c>
@@ -4502,8 +6735,15 @@
       <c r="C162" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D162"/>
+      <c r="E162"/>
+      <c r="F162"/>
+      <c r="G162"/>
+      <c r="H162"/>
+      <c r="I162"/>
+      <c r="J162"/>
+    </row>
+    <row r="163">
       <c r="A163" t="s">
         <v>381</v>
       </c>
@@ -4513,8 +6753,15 @@
       <c r="C163" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D163"/>
+      <c r="E163"/>
+      <c r="F163"/>
+      <c r="G163"/>
+      <c r="H163"/>
+      <c r="I163"/>
+      <c r="J163"/>
+    </row>
+    <row r="164">
       <c r="A164" t="s">
         <v>384</v>
       </c>
@@ -4524,8 +6771,15 @@
       <c r="C164" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D164"/>
+      <c r="E164"/>
+      <c r="F164"/>
+      <c r="G164"/>
+      <c r="H164"/>
+      <c r="I164"/>
+      <c r="J164"/>
+    </row>
+    <row r="165">
       <c r="A165" t="s">
         <v>387</v>
       </c>
@@ -4535,8 +6789,15 @@
       <c r="C165" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D165"/>
+      <c r="E165"/>
+      <c r="F165"/>
+      <c r="G165"/>
+      <c r="H165"/>
+      <c r="I165"/>
+      <c r="J165"/>
+    </row>
+    <row r="166">
       <c r="A166" t="s">
         <v>390</v>
       </c>
@@ -4546,8 +6807,15 @@
       <c r="C166" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D166"/>
+      <c r="E166"/>
+      <c r="F166"/>
+      <c r="G166"/>
+      <c r="H166"/>
+      <c r="I166"/>
+      <c r="J166"/>
+    </row>
+    <row r="167">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -4557,8 +6825,15 @@
       <c r="C167" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D167"/>
+      <c r="E167"/>
+      <c r="F167"/>
+      <c r="G167"/>
+      <c r="H167"/>
+      <c r="I167"/>
+      <c r="J167"/>
+    </row>
+    <row r="168">
       <c r="A168" t="s">
         <v>396</v>
       </c>
@@ -4568,8 +6843,15 @@
       <c r="C168" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D168"/>
+      <c r="E168"/>
+      <c r="F168"/>
+      <c r="G168"/>
+      <c r="H168"/>
+      <c r="I168"/>
+      <c r="J168"/>
+    </row>
+    <row r="169">
       <c r="A169" t="s">
         <v>399</v>
       </c>
@@ -4579,8 +6861,15 @@
       <c r="C169" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D169"/>
+      <c r="E169"/>
+      <c r="F169"/>
+      <c r="G169"/>
+      <c r="H169"/>
+      <c r="I169"/>
+      <c r="J169"/>
+    </row>
+    <row r="170">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -4590,8 +6879,15 @@
       <c r="C170" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D170"/>
+      <c r="E170"/>
+      <c r="F170"/>
+      <c r="G170"/>
+      <c r="H170"/>
+      <c r="I170"/>
+      <c r="J170"/>
+    </row>
+    <row r="171">
       <c r="A171" t="s">
         <v>405</v>
       </c>
@@ -4601,8 +6897,15 @@
       <c r="C171" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D171"/>
+      <c r="E171"/>
+      <c r="F171"/>
+      <c r="G171"/>
+      <c r="H171"/>
+      <c r="I171"/>
+      <c r="J171"/>
+    </row>
+    <row r="172">
       <c r="A172" t="s">
         <v>408</v>
       </c>
@@ -4612,8 +6915,15 @@
       <c r="C172" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D172"/>
+      <c r="E172"/>
+      <c r="F172"/>
+      <c r="G172"/>
+      <c r="H172"/>
+      <c r="I172"/>
+      <c r="J172"/>
+    </row>
+    <row r="173">
       <c r="A173" t="s">
         <v>411</v>
       </c>
@@ -4626,14 +6936,18 @@
       <c r="D173" t="s">
         <v>414</v>
       </c>
+      <c r="E173"/>
       <c r="F173" t="s">
         <v>415</v>
       </c>
-      <c r="G173">
+      <c r="G173" t="n">
         <v>2023</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H173"/>
+      <c r="I173"/>
+      <c r="J173"/>
+    </row>
+    <row r="174">
       <c r="A174" t="s">
         <v>416</v>
       </c>
@@ -4646,14 +6960,18 @@
       <c r="D174" t="s">
         <v>419</v>
       </c>
+      <c r="E174"/>
       <c r="F174" t="s">
         <v>415</v>
       </c>
-      <c r="G174">
+      <c r="G174" t="n">
         <v>2023</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H174"/>
+      <c r="I174"/>
+      <c r="J174"/>
+    </row>
+    <row r="175">
       <c r="A175" t="s">
         <v>420</v>
       </c>
@@ -4666,14 +6984,18 @@
       <c r="D175" t="s">
         <v>423</v>
       </c>
+      <c r="E175"/>
       <c r="F175" t="s">
         <v>415</v>
       </c>
-      <c r="G175">
+      <c r="G175" t="n">
         <v>2016</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H175"/>
+      <c r="I175"/>
+      <c r="J175"/>
+    </row>
+    <row r="176">
       <c r="A176" t="s">
         <v>424</v>
       </c>
@@ -4686,10 +7008,11 @@
       <c r="D176" t="s">
         <v>427</v>
       </c>
+      <c r="E176"/>
       <c r="F176" t="s">
         <v>428</v>
       </c>
-      <c r="G176">
+      <c r="G176" t="n">
         <v>2012</v>
       </c>
       <c r="H176" t="s">
@@ -4702,7 +7025,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177">
       <c r="A177" t="s">
         <v>432</v>
       </c>
@@ -4715,10 +7038,11 @@
       <c r="D177" t="s">
         <v>427</v>
       </c>
+      <c r="E177"/>
       <c r="F177" t="s">
         <v>428</v>
       </c>
-      <c r="G177">
+      <c r="G177" t="n">
         <v>2012</v>
       </c>
       <c r="H177" t="s">
@@ -4731,7 +7055,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178">
       <c r="A178" t="s">
         <v>434</v>
       </c>
@@ -4744,14 +7068,18 @@
       <c r="D178" t="s">
         <v>437</v>
       </c>
+      <c r="E178"/>
       <c r="F178" t="s">
         <v>438</v>
       </c>
-      <c r="G178">
+      <c r="G178" t="n">
         <v>2013</v>
       </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H178"/>
+      <c r="I178"/>
+      <c r="J178"/>
+    </row>
+    <row r="179">
       <c r="A179" t="s">
         <v>439</v>
       </c>
@@ -4764,14 +7092,18 @@
       <c r="D179" t="s">
         <v>442</v>
       </c>
+      <c r="E179"/>
       <c r="F179" t="s">
         <v>443</v>
       </c>
-      <c r="G179">
+      <c r="G179" t="n">
         <v>2024</v>
       </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H179"/>
+      <c r="I179"/>
+      <c r="J179"/>
+    </row>
+    <row r="180">
       <c r="A180" t="s">
         <v>444</v>
       </c>
@@ -4784,14 +7116,18 @@
       <c r="D180" t="s">
         <v>447</v>
       </c>
+      <c r="E180"/>
       <c r="F180" t="s">
         <v>448</v>
       </c>
-      <c r="G180">
+      <c r="G180" t="n">
         <v>2014</v>
       </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H180"/>
+      <c r="I180"/>
+      <c r="J180"/>
+    </row>
+    <row r="181">
       <c r="A181" t="s">
         <v>449</v>
       </c>
@@ -4804,11 +7140,16 @@
       <c r="D181" t="s">
         <v>452</v>
       </c>
-      <c r="G181">
+      <c r="E181"/>
+      <c r="F181"/>
+      <c r="G181" t="n">
         <v>2012</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H181"/>
+      <c r="I181"/>
+      <c r="J181"/>
+    </row>
+    <row r="182">
       <c r="A182" t="s">
         <v>453</v>
       </c>
@@ -4818,8 +7159,15 @@
       <c r="C182" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D182"/>
+      <c r="E182"/>
+      <c r="F182"/>
+      <c r="G182"/>
+      <c r="H182"/>
+      <c r="I182"/>
+      <c r="J182"/>
+    </row>
+    <row r="183">
       <c r="A183" t="s">
         <v>456</v>
       </c>
@@ -4829,8 +7177,15 @@
       <c r="C183" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D183"/>
+      <c r="E183"/>
+      <c r="F183"/>
+      <c r="G183"/>
+      <c r="H183"/>
+      <c r="I183"/>
+      <c r="J183"/>
+    </row>
+    <row r="184">
       <c r="A184" t="s">
         <v>459</v>
       </c>
@@ -4843,14 +7198,18 @@
       <c r="D184" t="s">
         <v>462</v>
       </c>
-      <c r="G184">
+      <c r="E184"/>
+      <c r="F184"/>
+      <c r="G184" t="n">
         <v>1978</v>
       </c>
+      <c r="H184"/>
+      <c r="I184"/>
       <c r="J184" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="185">
       <c r="A185" t="s">
         <v>464</v>
       </c>
@@ -4863,44 +7222,1253 @@
       <c r="D185" t="s">
         <v>467</v>
       </c>
-      <c r="G185">
+      <c r="E185"/>
+      <c r="F185"/>
+      <c r="G185" t="n">
         <v>1998</v>
       </c>
+      <c r="H185"/>
+      <c r="I185"/>
       <c r="J185" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A186" s="1" t="s">
+    <row r="186">
+      <c r="A186" t="s">
         <v>469</v>
       </c>
       <c r="B186" t="s">
+        <v>470</v>
+      </c>
+      <c r="C186" t="s">
         <v>471</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="D186"/>
+      <c r="E186" t="s">
         <v>472</v>
-      </c>
-      <c r="E186" t="s">
-        <v>470</v>
       </c>
       <c r="F186" t="s">
         <v>473</v>
       </c>
-      <c r="G186">
+      <c r="G186" t="n">
         <v>2015</v>
       </c>
-      <c r="H186">
-        <v>349</v>
-      </c>
-      <c r="I186">
-        <v>6251</v>
-      </c>
+      <c r="H186" t="s">
+        <v>474</v>
+      </c>
+      <c r="I186" t="s">
+        <v>475</v>
+      </c>
+      <c r="J186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>476</v>
+      </c>
+      <c r="B187" t="s">
+        <v>477</v>
+      </c>
+      <c r="C187" t="s">
+        <v>478</v>
+      </c>
+      <c r="D187"/>
+      <c r="E187"/>
+      <c r="F187"/>
+      <c r="G187"/>
+      <c r="H187"/>
+      <c r="I187"/>
+      <c r="J187"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>479</v>
+      </c>
+      <c r="B188" t="s">
+        <v>480</v>
+      </c>
+      <c r="C188" t="s">
+        <v>481</v>
+      </c>
+      <c r="D188"/>
+      <c r="E188"/>
+      <c r="F188"/>
+      <c r="G188"/>
+      <c r="H188"/>
+      <c r="I188"/>
+      <c r="J188"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>482</v>
+      </c>
+      <c r="B189" t="s">
+        <v>483</v>
+      </c>
+      <c r="C189" t="s">
+        <v>484</v>
+      </c>
+      <c r="D189"/>
+      <c r="E189"/>
+      <c r="F189"/>
+      <c r="G189"/>
+      <c r="H189"/>
+      <c r="I189"/>
+      <c r="J189"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>485</v>
+      </c>
+      <c r="B190" t="s">
+        <v>486</v>
+      </c>
+      <c r="C190" t="s">
+        <v>487</v>
+      </c>
+      <c r="D190"/>
+      <c r="E190"/>
+      <c r="F190"/>
+      <c r="G190"/>
+      <c r="H190"/>
+      <c r="I190"/>
+      <c r="J190"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>488</v>
+      </c>
+      <c r="B191" t="s">
+        <v>489</v>
+      </c>
+      <c r="C191" t="s">
+        <v>490</v>
+      </c>
+      <c r="D191"/>
+      <c r="E191"/>
+      <c r="F191"/>
+      <c r="G191"/>
+      <c r="H191"/>
+      <c r="I191"/>
+      <c r="J191"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>491</v>
+      </c>
+      <c r="B192" t="s">
+        <v>492</v>
+      </c>
+      <c r="C192" t="s">
+        <v>493</v>
+      </c>
+      <c r="D192"/>
+      <c r="E192"/>
+      <c r="F192"/>
+      <c r="G192"/>
+      <c r="H192"/>
+      <c r="I192"/>
+      <c r="J192"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>494</v>
+      </c>
+      <c r="B193" t="s">
+        <v>495</v>
+      </c>
+      <c r="C193" t="s">
+        <v>496</v>
+      </c>
+      <c r="D193"/>
+      <c r="E193"/>
+      <c r="F193"/>
+      <c r="G193"/>
+      <c r="H193"/>
+      <c r="I193"/>
+      <c r="J193"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>497</v>
+      </c>
+      <c r="B194" t="s">
+        <v>498</v>
+      </c>
+      <c r="C194" t="s">
+        <v>499</v>
+      </c>
+      <c r="D194"/>
+      <c r="E194"/>
+      <c r="F194"/>
+      <c r="G194"/>
+      <c r="H194"/>
+      <c r="I194"/>
+      <c r="J194"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>500</v>
+      </c>
+      <c r="B195" t="s">
+        <v>501</v>
+      </c>
+      <c r="C195" t="s">
+        <v>502</v>
+      </c>
+      <c r="D195"/>
+      <c r="E195"/>
+      <c r="F195"/>
+      <c r="G195"/>
+      <c r="H195"/>
+      <c r="I195"/>
+      <c r="J195"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>503</v>
+      </c>
+      <c r="B196" t="s">
+        <v>504</v>
+      </c>
+      <c r="C196" t="s">
+        <v>505</v>
+      </c>
+      <c r="D196"/>
+      <c r="E196"/>
+      <c r="F196"/>
+      <c r="G196"/>
+      <c r="H196"/>
+      <c r="I196"/>
+      <c r="J196"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>506</v>
+      </c>
+      <c r="B197" t="s">
+        <v>507</v>
+      </c>
+      <c r="C197" t="s">
+        <v>508</v>
+      </c>
+      <c r="D197"/>
+      <c r="E197"/>
+      <c r="F197"/>
+      <c r="G197"/>
+      <c r="H197"/>
+      <c r="I197"/>
+      <c r="J197"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>509</v>
+      </c>
+      <c r="B198" t="s">
+        <v>510</v>
+      </c>
+      <c r="C198" t="s">
+        <v>511</v>
+      </c>
+      <c r="D198"/>
+      <c r="E198"/>
+      <c r="F198"/>
+      <c r="G198"/>
+      <c r="H198"/>
+      <c r="I198"/>
+      <c r="J198"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>512</v>
+      </c>
+      <c r="B199" t="s">
+        <v>513</v>
+      </c>
+      <c r="C199" t="s">
+        <v>514</v>
+      </c>
+      <c r="D199"/>
+      <c r="E199"/>
+      <c r="F199"/>
+      <c r="G199"/>
+      <c r="H199"/>
+      <c r="I199"/>
+      <c r="J199"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>515</v>
+      </c>
+      <c r="B200" t="s">
+        <v>516</v>
+      </c>
+      <c r="C200" t="s">
+        <v>517</v>
+      </c>
+      <c r="D200"/>
+      <c r="E200"/>
+      <c r="F200"/>
+      <c r="G200"/>
+      <c r="H200"/>
+      <c r="I200"/>
+      <c r="J200"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>518</v>
+      </c>
+      <c r="B201" t="s">
+        <v>519</v>
+      </c>
+      <c r="C201" t="s">
+        <v>520</v>
+      </c>
+      <c r="D201"/>
+      <c r="E201"/>
+      <c r="F201"/>
+      <c r="G201"/>
+      <c r="H201"/>
+      <c r="I201"/>
+      <c r="J201"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>521</v>
+      </c>
+      <c r="B202" t="s">
+        <v>522</v>
+      </c>
+      <c r="C202" t="s">
+        <v>523</v>
+      </c>
+      <c r="D202"/>
+      <c r="E202"/>
+      <c r="F202"/>
+      <c r="G202"/>
+      <c r="H202"/>
+      <c r="I202"/>
+      <c r="J202"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>524</v>
+      </c>
+      <c r="B203" t="s">
+        <v>525</v>
+      </c>
+      <c r="C203" t="s">
+        <v>526</v>
+      </c>
+      <c r="D203"/>
+      <c r="E203"/>
+      <c r="F203"/>
+      <c r="G203"/>
+      <c r="H203"/>
+      <c r="I203"/>
+      <c r="J203"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>527</v>
+      </c>
+      <c r="B204" t="s">
+        <v>528</v>
+      </c>
+      <c r="C204" t="s">
+        <v>529</v>
+      </c>
+      <c r="D204"/>
+      <c r="E204"/>
+      <c r="F204"/>
+      <c r="G204"/>
+      <c r="H204"/>
+      <c r="I204"/>
+      <c r="J204"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>530</v>
+      </c>
+      <c r="B205" t="s">
+        <v>531</v>
+      </c>
+      <c r="C205" t="s">
+        <v>532</v>
+      </c>
+      <c r="D205"/>
+      <c r="E205"/>
+      <c r="F205"/>
+      <c r="G205"/>
+      <c r="H205"/>
+      <c r="I205"/>
+      <c r="J205"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>533</v>
+      </c>
+      <c r="B206" t="s">
+        <v>534</v>
+      </c>
+      <c r="C206" t="s">
+        <v>535</v>
+      </c>
+      <c r="D206"/>
+      <c r="E206"/>
+      <c r="F206"/>
+      <c r="G206"/>
+      <c r="H206"/>
+      <c r="I206"/>
+      <c r="J206"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>536</v>
+      </c>
+      <c r="B207" t="s">
+        <v>537</v>
+      </c>
+      <c r="C207" t="s">
+        <v>538</v>
+      </c>
+      <c r="D207"/>
+      <c r="E207"/>
+      <c r="F207"/>
+      <c r="G207"/>
+      <c r="H207"/>
+      <c r="I207"/>
+      <c r="J207"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>539</v>
+      </c>
+      <c r="B208" t="s">
+        <v>540</v>
+      </c>
+      <c r="C208" t="s">
+        <v>541</v>
+      </c>
+      <c r="D208"/>
+      <c r="E208"/>
+      <c r="F208"/>
+      <c r="G208"/>
+      <c r="H208"/>
+      <c r="I208"/>
+      <c r="J208"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>542</v>
+      </c>
+      <c r="B209" t="s">
+        <v>543</v>
+      </c>
+      <c r="C209" t="s">
+        <v>544</v>
+      </c>
+      <c r="D209"/>
+      <c r="E209"/>
+      <c r="F209"/>
+      <c r="G209"/>
+      <c r="H209"/>
+      <c r="I209"/>
+      <c r="J209"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>545</v>
+      </c>
+      <c r="B210" t="s">
+        <v>546</v>
+      </c>
+      <c r="C210" t="s">
+        <v>547</v>
+      </c>
+      <c r="D210"/>
+      <c r="E210"/>
+      <c r="F210"/>
+      <c r="G210"/>
+      <c r="H210"/>
+      <c r="I210"/>
+      <c r="J210"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>548</v>
+      </c>
+      <c r="B211" t="s">
+        <v>549</v>
+      </c>
+      <c r="C211" t="s">
+        <v>550</v>
+      </c>
+      <c r="D211"/>
+      <c r="E211"/>
+      <c r="F211"/>
+      <c r="G211"/>
+      <c r="H211"/>
+      <c r="I211"/>
+      <c r="J211"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>551</v>
+      </c>
+      <c r="B212" t="s">
+        <v>552</v>
+      </c>
+      <c r="C212" t="s">
+        <v>553</v>
+      </c>
+      <c r="D212"/>
+      <c r="E212"/>
+      <c r="F212"/>
+      <c r="G212"/>
+      <c r="H212"/>
+      <c r="I212"/>
+      <c r="J212"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>554</v>
+      </c>
+      <c r="B213" t="s">
+        <v>555</v>
+      </c>
+      <c r="C213" t="s">
+        <v>556</v>
+      </c>
+      <c r="D213"/>
+      <c r="E213"/>
+      <c r="F213"/>
+      <c r="G213"/>
+      <c r="H213"/>
+      <c r="I213"/>
+      <c r="J213"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>557</v>
+      </c>
+      <c r="B214" t="s">
+        <v>558</v>
+      </c>
+      <c r="C214" t="s">
+        <v>559</v>
+      </c>
+      <c r="D214"/>
+      <c r="E214"/>
+      <c r="F214"/>
+      <c r="G214"/>
+      <c r="H214"/>
+      <c r="I214"/>
+      <c r="J214"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>560</v>
+      </c>
+      <c r="B215" t="s">
+        <v>561</v>
+      </c>
+      <c r="C215" t="s">
+        <v>562</v>
+      </c>
+      <c r="D215"/>
+      <c r="E215"/>
+      <c r="F215"/>
+      <c r="G215"/>
+      <c r="H215"/>
+      <c r="I215"/>
+      <c r="J215"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>563</v>
+      </c>
+      <c r="B216" t="s">
+        <v>564</v>
+      </c>
+      <c r="C216" t="s">
+        <v>565</v>
+      </c>
+      <c r="D216"/>
+      <c r="E216"/>
+      <c r="F216"/>
+      <c r="G216"/>
+      <c r="H216"/>
+      <c r="I216"/>
+      <c r="J216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>566</v>
+      </c>
+      <c r="B217" t="s">
+        <v>567</v>
+      </c>
+      <c r="C217" t="s">
+        <v>568</v>
+      </c>
+      <c r="D217"/>
+      <c r="E217"/>
+      <c r="F217"/>
+      <c r="G217"/>
+      <c r="H217"/>
+      <c r="I217"/>
+      <c r="J217"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>569</v>
+      </c>
+      <c r="B218" t="s">
+        <v>570</v>
+      </c>
+      <c r="C218" t="s">
+        <v>571</v>
+      </c>
+      <c r="D218"/>
+      <c r="E218"/>
+      <c r="F218"/>
+      <c r="G218"/>
+      <c r="H218"/>
+      <c r="I218"/>
+      <c r="J218"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>572</v>
+      </c>
+      <c r="B219" t="s">
+        <v>573</v>
+      </c>
+      <c r="C219" t="s">
+        <v>574</v>
+      </c>
+      <c r="D219"/>
+      <c r="E219"/>
+      <c r="F219"/>
+      <c r="G219"/>
+      <c r="H219"/>
+      <c r="I219"/>
+      <c r="J219"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>575</v>
+      </c>
+      <c r="B220" t="s">
+        <v>576</v>
+      </c>
+      <c r="C220" t="s">
+        <v>577</v>
+      </c>
+      <c r="D220"/>
+      <c r="E220"/>
+      <c r="F220"/>
+      <c r="G220"/>
+      <c r="H220"/>
+      <c r="I220"/>
+      <c r="J220"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>578</v>
+      </c>
+      <c r="B221" t="s">
+        <v>579</v>
+      </c>
+      <c r="C221" t="s">
+        <v>580</v>
+      </c>
+      <c r="D221"/>
+      <c r="E221"/>
+      <c r="F221"/>
+      <c r="G221"/>
+      <c r="H221"/>
+      <c r="I221"/>
+      <c r="J221"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>581</v>
+      </c>
+      <c r="B222" t="s">
+        <v>582</v>
+      </c>
+      <c r="C222" t="s">
+        <v>583</v>
+      </c>
+      <c r="D222"/>
+      <c r="E222"/>
+      <c r="F222"/>
+      <c r="G222"/>
+      <c r="H222"/>
+      <c r="I222"/>
+      <c r="J222"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>584</v>
+      </c>
+      <c r="B223" t="s">
+        <v>585</v>
+      </c>
+      <c r="C223" t="s">
+        <v>586</v>
+      </c>
+      <c r="D223"/>
+      <c r="E223"/>
+      <c r="F223"/>
+      <c r="G223"/>
+      <c r="H223"/>
+      <c r="I223"/>
+      <c r="J223"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>587</v>
+      </c>
+      <c r="B224" t="s">
+        <v>588</v>
+      </c>
+      <c r="C224" t="s">
+        <v>589</v>
+      </c>
+      <c r="D224"/>
+      <c r="E224"/>
+      <c r="F224"/>
+      <c r="G224"/>
+      <c r="H224"/>
+      <c r="I224"/>
+      <c r="J224"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>590</v>
+      </c>
+      <c r="B225" t="s">
+        <v>591</v>
+      </c>
+      <c r="C225" t="s">
+        <v>592</v>
+      </c>
+      <c r="D225"/>
+      <c r="E225"/>
+      <c r="F225"/>
+      <c r="G225"/>
+      <c r="H225"/>
+      <c r="I225"/>
+      <c r="J225"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>593</v>
+      </c>
+      <c r="B226" t="s">
+        <v>594</v>
+      </c>
+      <c r="C226" t="s">
+        <v>595</v>
+      </c>
+      <c r="D226"/>
+      <c r="E226"/>
+      <c r="F226"/>
+      <c r="G226"/>
+      <c r="H226"/>
+      <c r="I226"/>
+      <c r="J226"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>596</v>
+      </c>
+      <c r="B227" t="s">
+        <v>597</v>
+      </c>
+      <c r="C227" t="s">
+        <v>598</v>
+      </c>
+      <c r="D227"/>
+      <c r="E227"/>
+      <c r="F227"/>
+      <c r="G227"/>
+      <c r="H227"/>
+      <c r="I227"/>
+      <c r="J227"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>599</v>
+      </c>
+      <c r="B228" t="s">
+        <v>600</v>
+      </c>
+      <c r="C228" t="s">
+        <v>601</v>
+      </c>
+      <c r="D228"/>
+      <c r="E228"/>
+      <c r="F228"/>
+      <c r="G228"/>
+      <c r="H228"/>
+      <c r="I228"/>
+      <c r="J228"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>602</v>
+      </c>
+      <c r="B229" t="s">
+        <v>603</v>
+      </c>
+      <c r="C229" t="s">
+        <v>604</v>
+      </c>
+      <c r="D229"/>
+      <c r="E229"/>
+      <c r="F229"/>
+      <c r="G229"/>
+      <c r="H229"/>
+      <c r="I229"/>
+      <c r="J229"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>605</v>
+      </c>
+      <c r="B230" t="s">
+        <v>606</v>
+      </c>
+      <c r="C230" t="s">
+        <v>607</v>
+      </c>
+      <c r="D230"/>
+      <c r="E230"/>
+      <c r="F230"/>
+      <c r="G230"/>
+      <c r="H230"/>
+      <c r="I230"/>
+      <c r="J230"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>608</v>
+      </c>
+      <c r="B231" t="s">
+        <v>609</v>
+      </c>
+      <c r="C231" t="s">
+        <v>610</v>
+      </c>
+      <c r="D231"/>
+      <c r="E231"/>
+      <c r="F231"/>
+      <c r="G231"/>
+      <c r="H231"/>
+      <c r="I231"/>
+      <c r="J231"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>611</v>
+      </c>
+      <c r="B232" t="s">
+        <v>612</v>
+      </c>
+      <c r="C232" t="s">
+        <v>613</v>
+      </c>
+      <c r="D232"/>
+      <c r="E232"/>
+      <c r="F232"/>
+      <c r="G232"/>
+      <c r="H232"/>
+      <c r="I232"/>
+      <c r="J232"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>614</v>
+      </c>
+      <c r="B233" t="s">
+        <v>615</v>
+      </c>
+      <c r="C233" t="s">
+        <v>616</v>
+      </c>
+      <c r="D233"/>
+      <c r="E233"/>
+      <c r="F233"/>
+      <c r="G233"/>
+      <c r="H233"/>
+      <c r="I233"/>
+      <c r="J233"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>617</v>
+      </c>
+      <c r="B234" t="s">
+        <v>618</v>
+      </c>
+      <c r="C234" t="s">
+        <v>619</v>
+      </c>
+      <c r="D234"/>
+      <c r="E234"/>
+      <c r="F234"/>
+      <c r="G234"/>
+      <c r="H234"/>
+      <c r="I234"/>
+      <c r="J234"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>620</v>
+      </c>
+      <c r="B235" t="s">
+        <v>621</v>
+      </c>
+      <c r="C235" t="s">
+        <v>622</v>
+      </c>
+      <c r="D235"/>
+      <c r="E235"/>
+      <c r="F235"/>
+      <c r="G235"/>
+      <c r="H235"/>
+      <c r="I235"/>
+      <c r="J235"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>623</v>
+      </c>
+      <c r="B236" t="s">
+        <v>624</v>
+      </c>
+      <c r="C236" t="s">
+        <v>625</v>
+      </c>
+      <c r="D236"/>
+      <c r="E236"/>
+      <c r="F236"/>
+      <c r="G236"/>
+      <c r="H236"/>
+      <c r="I236"/>
+      <c r="J236"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>626</v>
+      </c>
+      <c r="B237" t="s">
+        <v>627</v>
+      </c>
+      <c r="C237" t="s">
+        <v>628</v>
+      </c>
+      <c r="D237"/>
+      <c r="E237"/>
+      <c r="F237"/>
+      <c r="G237"/>
+      <c r="H237"/>
+      <c r="I237"/>
+      <c r="J237"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>629</v>
+      </c>
+      <c r="B238" t="s">
+        <v>630</v>
+      </c>
+      <c r="C238" t="s">
+        <v>631</v>
+      </c>
+      <c r="D238"/>
+      <c r="E238"/>
+      <c r="F238"/>
+      <c r="G238"/>
+      <c r="H238"/>
+      <c r="I238"/>
+      <c r="J238"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>632</v>
+      </c>
+      <c r="B239" t="s">
+        <v>633</v>
+      </c>
+      <c r="C239" t="s">
+        <v>634</v>
+      </c>
+      <c r="D239"/>
+      <c r="E239"/>
+      <c r="F239"/>
+      <c r="G239"/>
+      <c r="H239"/>
+      <c r="I239"/>
+      <c r="J239"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>635</v>
+      </c>
+      <c r="B240" t="s">
+        <v>636</v>
+      </c>
+      <c r="C240" t="s">
+        <v>637</v>
+      </c>
+      <c r="D240"/>
+      <c r="E240"/>
+      <c r="F240"/>
+      <c r="G240"/>
+      <c r="H240"/>
+      <c r="I240"/>
+      <c r="J240"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>638</v>
+      </c>
+      <c r="B241" t="s">
+        <v>639</v>
+      </c>
+      <c r="C241" t="s">
+        <v>640</v>
+      </c>
+      <c r="D241"/>
+      <c r="E241"/>
+      <c r="F241"/>
+      <c r="G241"/>
+      <c r="H241"/>
+      <c r="I241"/>
+      <c r="J241"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>641</v>
+      </c>
+      <c r="B242" t="s">
+        <v>642</v>
+      </c>
+      <c r="C242" t="s">
+        <v>643</v>
+      </c>
+      <c r="D242"/>
+      <c r="E242"/>
+      <c r="F242"/>
+      <c r="G242"/>
+      <c r="H242"/>
+      <c r="I242"/>
+      <c r="J242"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>644</v>
+      </c>
+      <c r="B243" t="s">
+        <v>645</v>
+      </c>
+      <c r="C243" t="s">
+        <v>646</v>
+      </c>
+      <c r="D243"/>
+      <c r="E243"/>
+      <c r="F243"/>
+      <c r="G243"/>
+      <c r="H243"/>
+      <c r="I243"/>
+      <c r="J243"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>647</v>
+      </c>
+      <c r="B244" t="s">
+        <v>648</v>
+      </c>
+      <c r="C244" t="s">
+        <v>649</v>
+      </c>
+      <c r="D244"/>
+      <c r="E244"/>
+      <c r="F244"/>
+      <c r="G244"/>
+      <c r="H244"/>
+      <c r="I244"/>
+      <c r="J244"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>650</v>
+      </c>
+      <c r="B245" t="s">
+        <v>651</v>
+      </c>
+      <c r="C245" t="s">
+        <v>652</v>
+      </c>
+      <c r="D245"/>
+      <c r="E245"/>
+      <c r="F245"/>
+      <c r="G245"/>
+      <c r="H245"/>
+      <c r="I245"/>
+      <c r="J245"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>653</v>
+      </c>
+      <c r="B246" t="s">
+        <v>654</v>
+      </c>
+      <c r="C246" t="s">
+        <v>655</v>
+      </c>
+      <c r="D246"/>
+      <c r="E246"/>
+      <c r="F246"/>
+      <c r="G246"/>
+      <c r="H246"/>
+      <c r="I246"/>
+      <c r="J246"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>656</v>
+      </c>
+      <c r="B247" t="s">
+        <v>657</v>
+      </c>
+      <c r="C247" t="s">
+        <v>658</v>
+      </c>
+      <c r="D247"/>
+      <c r="E247"/>
+      <c r="F247"/>
+      <c r="G247"/>
+      <c r="H247"/>
+      <c r="I247"/>
+      <c r="J247"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>659</v>
+      </c>
+      <c r="B248" t="s">
+        <v>660</v>
+      </c>
+      <c r="C248" t="s">
+        <v>661</v>
+      </c>
+      <c r="D248"/>
+      <c r="E248"/>
+      <c r="F248"/>
+      <c r="G248"/>
+      <c r="H248"/>
+      <c r="I248"/>
+      <c r="J248"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>662</v>
+      </c>
+      <c r="B249" t="s">
+        <v>663</v>
+      </c>
+      <c r="C249" t="s">
+        <v>664</v>
+      </c>
+      <c r="D249"/>
+      <c r="E249"/>
+      <c r="F249"/>
+      <c r="G249"/>
+      <c r="H249"/>
+      <c r="I249"/>
+      <c r="J249"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>665</v>
+      </c>
+      <c r="B250" t="s">
+        <v>666</v>
+      </c>
+      <c r="C250" t="s">
+        <v>667</v>
+      </c>
+      <c r="D250"/>
+      <c r="E250"/>
+      <c r="F250"/>
+      <c r="G250"/>
+      <c r="H250"/>
+      <c r="I250"/>
+      <c r="J250"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>668</v>
+      </c>
+      <c r="B251" t="s">
+        <v>669</v>
+      </c>
+      <c r="C251" t="s">
+        <v>670</v>
+      </c>
+      <c r="D251"/>
+      <c r="E251"/>
+      <c r="F251"/>
+      <c r="G251"/>
+      <c r="H251"/>
+      <c r="I251"/>
+      <c r="J251"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>671</v>
+      </c>
+      <c r="B252" t="s">
+        <v>672</v>
+      </c>
+      <c r="C252" t="s">
+        <v>673</v>
+      </c>
+      <c r="D252"/>
+      <c r="E252"/>
+      <c r="F252"/>
+      <c r="G252"/>
+      <c r="H252"/>
+      <c r="I252"/>
+      <c r="J252"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>674</v>
+      </c>
+      <c r="B253" t="s">
+        <v>675</v>
+      </c>
+      <c r="C253" t="s">
+        <v>676</v>
+      </c>
+      <c r="D253"/>
+      <c r="E253"/>
+      <c r="F253"/>
+      <c r="G253"/>
+      <c r="H253"/>
+      <c r="I253"/>
+      <c r="J253"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A186" r:id="rId1" display="https://doi.org/10.1126/science.aac4716" xr:uid="{C3963564-FE82-1142-BE0D-26BD87AE3BF2}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/cache/manual_references.xlsx
+++ b/cache/manual_references.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hamidrezabehbood/Documents/GitHub/FReD-data/cache/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103F3E61-A99E-BD4F-8763-5166EDA9D16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CCF5C8-837C-CD4F-B1CA-2BC239980651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4300" yWindow="680" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="838">
   <si>
     <t>key</t>
   </si>
@@ -4970,6 +4970,27 @@
   </si>
   <si>
     <t>Article 13</t>
+  </si>
+  <si>
+    <t>10.1016/j.im.2015.06.009</t>
+  </si>
+  <si>
+    <t>Hsu, P.-F., Yen, H. R., &amp; Chung, J.-C. (2015). Assessing ERP post-implementation success at the individual level: Revisiting the role of service quality. Information &amp; Management, 52(8), 925–942. https://doi.org/10.1016/j.im.2015.06.009</t>
+  </si>
+  <si>
+    <t>@article{Hsu2015ERP, author={Pei-Fang Hsu and HsiuJu Rebecca Yen and Jung-Ching Chung}, title={Assessing ERP post-implementation success at the individual level: Revisiting the role of service quality}, journal={Information &amp; Management}, year={2015}, volume={52}, number={8}, pages={925--942}, doi={10.1016/j.im.2015.06.009} }</t>
+  </si>
+  <si>
+    <t>Assessing ERP post-implementation success at the individual level: Revisiting the role of service quality</t>
+  </si>
+  <si>
+    <t>Hsu, Pei-Fang; Yen, HsiuJu Rebecca; Chung, Jung-Ching</t>
+  </si>
+  <si>
+    <t>Information &amp; Management</t>
+  </si>
+  <si>
+    <t>925-942</t>
   </si>
 </sst>
 </file>
@@ -5322,7 +5343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J276"/>
+  <dimension ref="A1:J277"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -8862,6 +8883,38 @@
         <v>830</v>
       </c>
     </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>831</v>
+      </c>
+      <c r="B277" t="s">
+        <v>832</v>
+      </c>
+      <c r="C277" t="s">
+        <v>833</v>
+      </c>
+      <c r="D277" t="s">
+        <v>834</v>
+      </c>
+      <c r="E277" t="s">
+        <v>835</v>
+      </c>
+      <c r="F277" t="s">
+        <v>836</v>
+      </c>
+      <c r="G277">
+        <v>2015</v>
+      </c>
+      <c r="H277">
+        <v>52</v>
+      </c>
+      <c r="I277">
+        <v>8</v>
+      </c>
+      <c r="J277" t="s">
+        <v>837</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cache/manual_references.xlsx
+++ b/cache/manual_references.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hamidrezabehbood/Documents/GitHub/FReD-data/cache/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamid\Documents\GitHub\FReD-data\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CCF5C8-837C-CD4F-B1CA-2BC239980651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9CCA66-2D39-443F-90C4-180339AB495A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4300" yWindow="680" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="841">
   <si>
     <t>key</t>
   </si>
@@ -4992,12 +4992,21 @@
   <si>
     <t>925-942</t>
   </si>
+  <si>
+    <t>https://aisel.aisnet.org/trr/vol7/iss1/3</t>
+  </si>
+  <si>
+    <t>Kumar, M., &amp; Leroy, G. (2021). Factors Affecting Compliance with Alerts in the Context of Healthcare-related Emergencies. AIS Transactions on Replication Research, 7, Article 3. https://doi.org/10.17705/1atrr.00068</t>
+  </si>
+  <si>
+    <t>@article{kumar2021factors, title = {Factors Affecting Compliance with Alerts in the Context of Healthcare-related Emergencies}, author = {Kumar, Manasvi and Leroy, Gondy}, journal = {AIS Transactions on Replication Research}, year = {2021}, volume = {7}, number = {1}, note = {Article 3}, doi = {10.17705/1atrr.00068}, url = {https://aisel.aisnet.org/trr/vol7/iss1/3} }</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5009,6 +5018,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -5034,11 +5050,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5343,10 +5360,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J277"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:SF278"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5378,7 +5395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -5389,7 +5406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5400,7 +5417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5411,7 +5428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -5422,7 +5439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -5433,7 +5450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -5444,7 +5461,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -5455,7 +5472,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -5466,7 +5483,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -5477,7 +5494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -5488,7 +5505,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -5499,7 +5516,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -5510,7 +5527,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -5521,7 +5538,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -5532,7 +5549,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -5543,7 +5560,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -5554,7 +5571,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -5565,7 +5582,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -5576,7 +5593,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -5587,7 +5604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -5598,7 +5615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -5609,7 +5626,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -5620,7 +5637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -5631,7 +5648,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -5642,7 +5659,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -5650,7 +5667,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -5661,7 +5678,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -5672,7 +5689,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -5683,7 +5700,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -5694,7 +5711,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -5705,7 +5722,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -5716,7 +5733,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -5727,7 +5744,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -5738,7 +5755,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -5749,7 +5766,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>111</v>
       </c>
@@ -5760,7 +5777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -5771,7 +5788,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -5782,7 +5799,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -5793,7 +5810,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -5804,7 +5821,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -5815,7 +5832,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -5826,7 +5843,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -5837,7 +5854,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -5848,7 +5865,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>129</v>
       </c>
@@ -5859,7 +5876,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -5870,7 +5887,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>135</v>
       </c>
@@ -5881,7 +5898,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -5892,7 +5909,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>135</v>
       </c>
@@ -5903,7 +5920,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -5914,7 +5931,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -5925,7 +5942,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>138</v>
       </c>
@@ -5936,7 +5953,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>141</v>
       </c>
@@ -5947,7 +5964,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>144</v>
       </c>
@@ -5958,7 +5975,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>144</v>
       </c>
@@ -5969,7 +5986,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -5980,7 +5997,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>147</v>
       </c>
@@ -5991,7 +6008,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -6002,7 +6019,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>147</v>
       </c>
@@ -6013,7 +6030,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -6024,7 +6041,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -6035,7 +6052,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>153</v>
       </c>
@@ -6046,7 +6063,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -6057,7 +6074,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -6068,7 +6085,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>156</v>
       </c>
@@ -6079,7 +6096,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>156</v>
       </c>
@@ -6090,7 +6107,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>159</v>
       </c>
@@ -6101,7 +6118,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>159</v>
       </c>
@@ -6112,7 +6129,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>159</v>
       </c>
@@ -6123,7 +6140,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -6134,7 +6151,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>162</v>
       </c>
@@ -6145,7 +6162,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>162</v>
       </c>
@@ -6156,7 +6173,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -6167,7 +6184,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -6178,7 +6195,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>168</v>
       </c>
@@ -6189,7 +6206,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>171</v>
       </c>
@@ -6200,7 +6217,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>171</v>
       </c>
@@ -6211,7 +6228,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -6222,7 +6239,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>174</v>
       </c>
@@ -6233,7 +6250,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -6244,7 +6261,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>177</v>
       </c>
@@ -6255,7 +6272,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>177</v>
       </c>
@@ -6266,7 +6283,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>177</v>
       </c>
@@ -6277,7 +6294,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>180</v>
       </c>
@@ -6288,7 +6305,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>183</v>
       </c>
@@ -6299,7 +6316,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>186</v>
       </c>
@@ -6310,7 +6327,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>186</v>
       </c>
@@ -6321,7 +6338,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>189</v>
       </c>
@@ -6332,7 +6349,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -6343,7 +6360,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>195</v>
       </c>
@@ -6354,7 +6371,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -6365,7 +6382,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>201</v>
       </c>
@@ -6376,7 +6393,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>201</v>
       </c>
@@ -6387,7 +6404,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -6398,7 +6415,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>201</v>
       </c>
@@ -6409,7 +6426,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -6420,7 +6437,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>201</v>
       </c>
@@ -6431,7 +6448,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -6442,7 +6459,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>201</v>
       </c>
@@ -6453,7 +6470,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -6464,7 +6481,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -6475,7 +6492,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>207</v>
       </c>
@@ -6486,7 +6503,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -6497,7 +6514,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -6508,7 +6525,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -6519,7 +6536,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>219</v>
       </c>
@@ -6530,7 +6547,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -6541,7 +6558,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>219</v>
       </c>
@@ -6552,7 +6569,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>219</v>
       </c>
@@ -6563,7 +6580,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>222</v>
       </c>
@@ -6574,7 +6591,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>225</v>
       </c>
@@ -6585,7 +6602,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>228</v>
       </c>
@@ -6596,7 +6613,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -6607,7 +6624,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>234</v>
       </c>
@@ -6618,7 +6635,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>237</v>
       </c>
@@ -6629,7 +6646,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>240</v>
       </c>
@@ -6640,7 +6657,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>243</v>
       </c>
@@ -6651,7 +6668,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>246</v>
       </c>
@@ -6662,7 +6679,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>249</v>
       </c>
@@ -6673,7 +6690,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>252</v>
       </c>
@@ -6684,7 +6701,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>255</v>
       </c>
@@ -6695,7 +6712,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>258</v>
       </c>
@@ -6706,7 +6723,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>261</v>
       </c>
@@ -6717,7 +6734,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>264</v>
       </c>
@@ -6728,7 +6745,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -6739,7 +6756,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>270</v>
       </c>
@@ -6750,7 +6767,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -6761,7 +6778,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>276</v>
       </c>
@@ -6772,7 +6789,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>279</v>
       </c>
@@ -6783,7 +6800,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>282</v>
       </c>
@@ -6794,7 +6811,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>285</v>
       </c>
@@ -6805,7 +6822,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>288</v>
       </c>
@@ -6816,7 +6833,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>291</v>
       </c>
@@ -6827,7 +6844,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>294</v>
       </c>
@@ -6838,7 +6855,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>297</v>
       </c>
@@ -6849,7 +6866,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>300</v>
       </c>
@@ -6860,7 +6877,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>303</v>
       </c>
@@ -6871,7 +6888,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>306</v>
       </c>
@@ -6882,7 +6899,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>309</v>
       </c>
@@ -6893,7 +6910,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>312</v>
       </c>
@@ -6904,7 +6921,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>315</v>
       </c>
@@ -6915,7 +6932,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>318</v>
       </c>
@@ -6926,7 +6943,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>321</v>
       </c>
@@ -6937,7 +6954,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>324</v>
       </c>
@@ -6948,7 +6965,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>327</v>
       </c>
@@ -6959,7 +6976,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -6970,7 +6987,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>333</v>
       </c>
@@ -6981,7 +6998,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>336</v>
       </c>
@@ -6992,7 +7009,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>339</v>
       </c>
@@ -7003,7 +7020,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>342</v>
       </c>
@@ -7014,7 +7031,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>345</v>
       </c>
@@ -7025,7 +7042,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>348</v>
       </c>
@@ -7036,7 +7053,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>351</v>
       </c>
@@ -7047,7 +7064,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>354</v>
       </c>
@@ -7058,7 +7075,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>357</v>
       </c>
@@ -7069,7 +7086,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>360</v>
       </c>
@@ -7080,7 +7097,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>363</v>
       </c>
@@ -7091,7 +7108,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>366</v>
       </c>
@@ -7102,7 +7119,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>369</v>
       </c>
@@ -7113,7 +7130,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>372</v>
       </c>
@@ -7124,7 +7141,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>375</v>
       </c>
@@ -7135,7 +7152,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>378</v>
       </c>
@@ -7146,7 +7163,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>381</v>
       </c>
@@ -7157,7 +7174,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>384</v>
       </c>
@@ -7168,7 +7185,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>387</v>
       </c>
@@ -7179,7 +7196,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>390</v>
       </c>
@@ -7190,7 +7207,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -7201,7 +7218,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>396</v>
       </c>
@@ -7212,7 +7229,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>399</v>
       </c>
@@ -7223,7 +7240,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -7234,7 +7251,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>405</v>
       </c>
@@ -7245,7 +7262,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>408</v>
       </c>
@@ -7256,7 +7273,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>411</v>
       </c>
@@ -7276,7 +7293,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>416</v>
       </c>
@@ -7296,7 +7313,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>420</v>
       </c>
@@ -7316,7 +7333,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>424</v>
       </c>
@@ -7345,7 +7362,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>432</v>
       </c>
@@ -7374,7 +7391,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>434</v>
       </c>
@@ -7394,7 +7411,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>439</v>
       </c>
@@ -7414,7 +7431,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>444</v>
       </c>
@@ -7434,7 +7451,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>449</v>
       </c>
@@ -7451,7 +7468,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>453</v>
       </c>
@@ -7462,7 +7479,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>456</v>
       </c>
@@ -7473,7 +7490,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>459</v>
       </c>
@@ -7493,7 +7510,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>464</v>
       </c>
@@ -7513,7 +7530,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>469</v>
       </c>
@@ -7539,7 +7556,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>476</v>
       </c>
@@ -7550,7 +7567,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>479</v>
       </c>
@@ -7561,7 +7578,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>482</v>
       </c>
@@ -7572,7 +7589,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>485</v>
       </c>
@@ -7583,7 +7600,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>488</v>
       </c>
@@ -7594,7 +7611,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>491</v>
       </c>
@@ -7605,7 +7622,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>494</v>
       </c>
@@ -7616,7 +7633,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>497</v>
       </c>
@@ -7627,7 +7644,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>500</v>
       </c>
@@ -7638,7 +7655,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>503</v>
       </c>
@@ -7649,7 +7666,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>506</v>
       </c>
@@ -7660,7 +7677,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>509</v>
       </c>
@@ -7671,7 +7688,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>512</v>
       </c>
@@ -7682,7 +7699,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>515</v>
       </c>
@@ -7693,7 +7710,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>518</v>
       </c>
@@ -7704,7 +7721,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>521</v>
       </c>
@@ -7715,7 +7732,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>524</v>
       </c>
@@ -7726,7 +7743,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>527</v>
       </c>
@@ -7737,7 +7754,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>530</v>
       </c>
@@ -7748,7 +7765,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>533</v>
       </c>
@@ -7759,7 +7776,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>536</v>
       </c>
@@ -7770,7 +7787,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>539</v>
       </c>
@@ -7781,7 +7798,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>542</v>
       </c>
@@ -7792,7 +7809,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>545</v>
       </c>
@@ -7803,7 +7820,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>548</v>
       </c>
@@ -7814,7 +7831,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>551</v>
       </c>
@@ -7825,7 +7842,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>554</v>
       </c>
@@ -7836,7 +7853,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>557</v>
       </c>
@@ -7847,7 +7864,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>560</v>
       </c>
@@ -7858,7 +7875,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>563</v>
       </c>
@@ -7869,7 +7886,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>566</v>
       </c>
@@ -7880,7 +7897,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>569</v>
       </c>
@@ -7891,7 +7908,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>572</v>
       </c>
@@ -7902,7 +7919,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>575</v>
       </c>
@@ -7913,7 +7930,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>578</v>
       </c>
@@ -7924,7 +7941,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>581</v>
       </c>
@@ -7935,7 +7952,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>584</v>
       </c>
@@ -7946,7 +7963,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>587</v>
       </c>
@@ -7957,7 +7974,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>590</v>
       </c>
@@ -7968,7 +7985,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>593</v>
       </c>
@@ -7979,7 +7996,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>596</v>
       </c>
@@ -7990,7 +8007,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>599</v>
       </c>
@@ -8001,7 +8018,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>602</v>
       </c>
@@ -8012,7 +8029,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>605</v>
       </c>
@@ -8023,7 +8040,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>608</v>
       </c>
@@ -8034,7 +8051,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>611</v>
       </c>
@@ -8045,7 +8062,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>614</v>
       </c>
@@ -8056,7 +8073,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>617</v>
       </c>
@@ -8067,7 +8084,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>620</v>
       </c>
@@ -8078,7 +8095,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>623</v>
       </c>
@@ -8089,7 +8106,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>626</v>
       </c>
@@ -8100,7 +8117,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>629</v>
       </c>
@@ -8111,7 +8128,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>632</v>
       </c>
@@ -8122,7 +8139,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>635</v>
       </c>
@@ -8133,7 +8150,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>638</v>
       </c>
@@ -8144,7 +8161,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>641</v>
       </c>
@@ -8155,7 +8172,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>644</v>
       </c>
@@ -8166,7 +8183,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>647</v>
       </c>
@@ -8177,7 +8194,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>650</v>
       </c>
@@ -8188,7 +8205,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>653</v>
       </c>
@@ -8199,7 +8216,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>656</v>
       </c>
@@ -8210,7 +8227,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>659</v>
       </c>
@@ -8221,7 +8238,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>662</v>
       </c>
@@ -8232,7 +8249,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>665</v>
       </c>
@@ -8243,7 +8260,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>668</v>
       </c>
@@ -8254,7 +8271,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>671</v>
       </c>
@@ -8265,7 +8282,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>674</v>
       </c>
@@ -8276,7 +8293,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>677</v>
       </c>
@@ -8308,7 +8325,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>686</v>
       </c>
@@ -8340,7 +8357,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>694</v>
       </c>
@@ -8366,7 +8383,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>701</v>
       </c>
@@ -8392,7 +8409,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>708</v>
       </c>
@@ -8412,7 +8429,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>713</v>
       </c>
@@ -8432,7 +8449,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>718</v>
       </c>
@@ -8464,7 +8481,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>725</v>
       </c>
@@ -8487,7 +8504,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>731</v>
       </c>
@@ -8510,7 +8527,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>736</v>
       </c>
@@ -8530,7 +8547,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>741</v>
       </c>
@@ -8562,7 +8579,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>750</v>
       </c>
@@ -8594,7 +8611,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>758</v>
       </c>
@@ -8617,7 +8634,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>763</v>
       </c>
@@ -8646,7 +8663,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>771</v>
       </c>
@@ -8663,7 +8680,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>776</v>
       </c>
@@ -8686,7 +8703,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>782</v>
       </c>
@@ -8709,7 +8726,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>787</v>
       </c>
@@ -8729,7 +8746,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>792</v>
       </c>
@@ -8755,7 +8772,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:500" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>799</v>
       </c>
@@ -8787,7 +8804,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:500" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>807</v>
       </c>
@@ -8819,7 +8836,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:500" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>815</v>
       </c>
@@ -8851,7 +8868,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:500" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>824</v>
       </c>
@@ -8883,7 +8900,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:500" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>831</v>
       </c>
@@ -8914,6 +8931,528 @@
       <c r="J277" t="s">
         <v>837</v>
       </c>
+    </row>
+    <row r="278" spans="1:500" x14ac:dyDescent="0.45">
+      <c r="A278" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F278" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G278" s="2">
+        <v>2021</v>
+      </c>
+      <c r="H278" s="2">
+        <v>7</v>
+      </c>
+      <c r="I278" s="2">
+        <v>1</v>
+      </c>
+      <c r="J278" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="K278" s="2"/>
+      <c r="L278" s="2"/>
+      <c r="M278" s="2"/>
+      <c r="N278" s="2"/>
+      <c r="O278" s="2"/>
+      <c r="P278" s="2"/>
+      <c r="Q278" s="2"/>
+      <c r="R278" s="2"/>
+      <c r="S278" s="2"/>
+      <c r="T278" s="2"/>
+      <c r="U278" s="2"/>
+      <c r="V278" s="2"/>
+      <c r="W278" s="2"/>
+      <c r="X278" s="2"/>
+      <c r="Y278" s="2"/>
+      <c r="Z278" s="2"/>
+      <c r="AA278" s="2"/>
+      <c r="AB278" s="2"/>
+      <c r="AC278" s="2"/>
+      <c r="AD278" s="2"/>
+      <c r="AE278" s="2"/>
+      <c r="AF278" s="2"/>
+      <c r="AG278" s="2"/>
+      <c r="AH278" s="2"/>
+      <c r="AI278" s="2"/>
+      <c r="AJ278" s="2"/>
+      <c r="AK278" s="2"/>
+      <c r="AL278" s="2"/>
+      <c r="AM278" s="2"/>
+      <c r="AN278" s="2"/>
+      <c r="AO278" s="2"/>
+      <c r="AP278" s="2"/>
+      <c r="AQ278" s="2"/>
+      <c r="AR278" s="2"/>
+      <c r="AS278" s="2"/>
+      <c r="AT278" s="2"/>
+      <c r="AU278" s="2"/>
+      <c r="AV278" s="2"/>
+      <c r="AW278" s="2"/>
+      <c r="AX278" s="2"/>
+      <c r="AY278" s="2"/>
+      <c r="AZ278" s="2"/>
+      <c r="BA278" s="2"/>
+      <c r="BB278" s="2"/>
+      <c r="BC278" s="2"/>
+      <c r="BD278" s="2"/>
+      <c r="BE278" s="2"/>
+      <c r="BF278" s="2"/>
+      <c r="BG278" s="2"/>
+      <c r="BH278" s="2"/>
+      <c r="BI278" s="2"/>
+      <c r="BJ278" s="2"/>
+      <c r="BK278" s="2"/>
+      <c r="BL278" s="2"/>
+      <c r="BM278" s="2"/>
+      <c r="BN278" s="2"/>
+      <c r="BO278" s="2"/>
+      <c r="BP278" s="2"/>
+      <c r="BQ278" s="2"/>
+      <c r="BR278" s="2"/>
+      <c r="BS278" s="2"/>
+      <c r="BT278" s="2"/>
+      <c r="BU278" s="2"/>
+      <c r="BV278" s="2"/>
+      <c r="BW278" s="2"/>
+      <c r="BX278" s="2"/>
+      <c r="BY278" s="2"/>
+      <c r="BZ278" s="2"/>
+      <c r="CA278" s="2"/>
+      <c r="CB278" s="2"/>
+      <c r="CC278" s="2"/>
+      <c r="CD278" s="2"/>
+      <c r="CE278" s="2"/>
+      <c r="CF278" s="2"/>
+      <c r="CG278" s="2"/>
+      <c r="CH278" s="2"/>
+      <c r="CI278" s="2"/>
+      <c r="CJ278" s="2"/>
+      <c r="CK278" s="2"/>
+      <c r="CL278" s="2"/>
+      <c r="CM278" s="2"/>
+      <c r="CN278" s="2"/>
+      <c r="CO278" s="2"/>
+      <c r="CP278" s="2"/>
+      <c r="CQ278" s="2"/>
+      <c r="CR278" s="2"/>
+      <c r="CS278" s="2"/>
+      <c r="CT278" s="2"/>
+      <c r="CU278" s="2"/>
+      <c r="CV278" s="2"/>
+      <c r="CW278" s="2"/>
+      <c r="CX278" s="2"/>
+      <c r="CY278" s="2"/>
+      <c r="CZ278" s="2"/>
+      <c r="DA278" s="2"/>
+      <c r="DB278" s="2"/>
+      <c r="DC278" s="2"/>
+      <c r="DD278" s="2"/>
+      <c r="DE278" s="2"/>
+      <c r="DF278" s="2"/>
+      <c r="DG278" s="2"/>
+      <c r="DH278" s="2"/>
+      <c r="DI278" s="2"/>
+      <c r="DJ278" s="2"/>
+      <c r="DK278" s="2"/>
+      <c r="DL278" s="2"/>
+      <c r="DM278" s="2"/>
+      <c r="DN278" s="2"/>
+      <c r="DO278" s="2"/>
+      <c r="DP278" s="2"/>
+      <c r="DQ278" s="2"/>
+      <c r="DR278" s="2"/>
+      <c r="DS278" s="2"/>
+      <c r="DT278" s="2"/>
+      <c r="DU278" s="2"/>
+      <c r="DV278" s="2"/>
+      <c r="DW278" s="2"/>
+      <c r="DX278" s="2"/>
+      <c r="DY278" s="2"/>
+      <c r="DZ278" s="2"/>
+      <c r="EA278" s="2"/>
+      <c r="EB278" s="2"/>
+      <c r="EC278" s="2"/>
+      <c r="ED278" s="2"/>
+      <c r="EE278" s="2"/>
+      <c r="EF278" s="2"/>
+      <c r="EG278" s="2"/>
+      <c r="EH278" s="2"/>
+      <c r="EI278" s="2"/>
+      <c r="EJ278" s="2"/>
+      <c r="EK278" s="2"/>
+      <c r="EL278" s="2"/>
+      <c r="EM278" s="2"/>
+      <c r="EN278" s="2"/>
+      <c r="EO278" s="2"/>
+      <c r="EP278" s="2"/>
+      <c r="EQ278" s="2"/>
+      <c r="ER278" s="2"/>
+      <c r="ES278" s="2"/>
+      <c r="ET278" s="2"/>
+      <c r="EU278" s="2"/>
+      <c r="EV278" s="2"/>
+      <c r="EW278" s="2"/>
+      <c r="EX278" s="2"/>
+      <c r="EY278" s="2"/>
+      <c r="EZ278" s="2"/>
+      <c r="FA278" s="2"/>
+      <c r="FB278" s="2"/>
+      <c r="FC278" s="2"/>
+      <c r="FD278" s="2"/>
+      <c r="FE278" s="2"/>
+      <c r="FF278" s="2"/>
+      <c r="FG278" s="2"/>
+      <c r="FH278" s="2"/>
+      <c r="FI278" s="2"/>
+      <c r="FJ278" s="2"/>
+      <c r="FK278" s="2"/>
+      <c r="FL278" s="2"/>
+      <c r="FM278" s="2"/>
+      <c r="FN278" s="2"/>
+      <c r="FO278" s="2"/>
+      <c r="FP278" s="2"/>
+      <c r="FQ278" s="2"/>
+      <c r="FR278" s="2"/>
+      <c r="FS278" s="2"/>
+      <c r="FT278" s="2"/>
+      <c r="FU278" s="2"/>
+      <c r="FV278" s="2"/>
+      <c r="FW278" s="2"/>
+      <c r="FX278" s="2"/>
+      <c r="FY278" s="2"/>
+      <c r="FZ278" s="2"/>
+      <c r="GA278" s="2"/>
+      <c r="GB278" s="2"/>
+      <c r="GC278" s="2"/>
+      <c r="GD278" s="2"/>
+      <c r="GE278" s="2"/>
+      <c r="GF278" s="2"/>
+      <c r="GG278" s="2"/>
+      <c r="GH278" s="2"/>
+      <c r="GI278" s="2"/>
+      <c r="GJ278" s="2"/>
+      <c r="GK278" s="2"/>
+      <c r="GL278" s="2"/>
+      <c r="GM278" s="2"/>
+      <c r="GN278" s="2"/>
+      <c r="GO278" s="2"/>
+      <c r="GP278" s="2"/>
+      <c r="GQ278" s="2"/>
+      <c r="GR278" s="2"/>
+      <c r="GS278" s="2"/>
+      <c r="GT278" s="2"/>
+      <c r="GU278" s="2"/>
+      <c r="GV278" s="2"/>
+      <c r="GW278" s="2"/>
+      <c r="GX278" s="2"/>
+      <c r="GY278" s="2"/>
+      <c r="GZ278" s="2"/>
+      <c r="HA278" s="2"/>
+      <c r="HB278" s="2"/>
+      <c r="HC278" s="2"/>
+      <c r="HD278" s="2"/>
+      <c r="HE278" s="2"/>
+      <c r="HF278" s="2"/>
+      <c r="HG278" s="2"/>
+      <c r="HH278" s="2"/>
+      <c r="HI278" s="2"/>
+      <c r="HJ278" s="2"/>
+      <c r="HK278" s="2"/>
+      <c r="HL278" s="2"/>
+      <c r="HM278" s="2"/>
+      <c r="HN278" s="2"/>
+      <c r="HO278" s="2"/>
+      <c r="HP278" s="2"/>
+      <c r="HQ278" s="2"/>
+      <c r="HR278" s="2"/>
+      <c r="HS278" s="2"/>
+      <c r="HT278" s="2"/>
+      <c r="HU278" s="2"/>
+      <c r="HV278" s="2"/>
+      <c r="HW278" s="2"/>
+      <c r="HX278" s="2"/>
+      <c r="HY278" s="2"/>
+      <c r="HZ278" s="2"/>
+      <c r="IA278" s="2"/>
+      <c r="IB278" s="2"/>
+      <c r="IC278" s="2"/>
+      <c r="ID278" s="2"/>
+      <c r="IE278" s="2"/>
+      <c r="IF278" s="2"/>
+      <c r="IG278" s="2"/>
+      <c r="IH278" s="2"/>
+      <c r="II278" s="2"/>
+      <c r="IJ278" s="2"/>
+      <c r="IK278" s="2"/>
+      <c r="IL278" s="2"/>
+      <c r="IM278" s="2"/>
+      <c r="IN278" s="2"/>
+      <c r="IO278" s="2"/>
+      <c r="IP278" s="2"/>
+      <c r="IQ278" s="2"/>
+      <c r="IR278" s="2"/>
+      <c r="IS278" s="2"/>
+      <c r="IT278" s="2"/>
+      <c r="IU278" s="2"/>
+      <c r="IV278" s="2"/>
+      <c r="IW278" s="2"/>
+      <c r="IX278" s="2"/>
+      <c r="IY278" s="2"/>
+      <c r="IZ278" s="2"/>
+      <c r="JA278" s="2"/>
+      <c r="JB278" s="2"/>
+      <c r="JC278" s="2"/>
+      <c r="JD278" s="2"/>
+      <c r="JE278" s="2"/>
+      <c r="JF278" s="2"/>
+      <c r="JG278" s="2"/>
+      <c r="JH278" s="2"/>
+      <c r="JI278" s="2"/>
+      <c r="JJ278" s="2"/>
+      <c r="JK278" s="2"/>
+      <c r="JL278" s="2"/>
+      <c r="JM278" s="2"/>
+      <c r="JN278" s="2"/>
+      <c r="JO278" s="2"/>
+      <c r="JP278" s="2"/>
+      <c r="JQ278" s="2"/>
+      <c r="JR278" s="2"/>
+      <c r="JS278" s="2"/>
+      <c r="JT278" s="2"/>
+      <c r="JU278" s="2"/>
+      <c r="JV278" s="2"/>
+      <c r="JW278" s="2"/>
+      <c r="JX278" s="2"/>
+      <c r="JY278" s="2"/>
+      <c r="JZ278" s="2"/>
+      <c r="KA278" s="2"/>
+      <c r="KB278" s="2"/>
+      <c r="KC278" s="2"/>
+      <c r="KD278" s="2"/>
+      <c r="KE278" s="2"/>
+      <c r="KF278" s="2"/>
+      <c r="KG278" s="2"/>
+      <c r="KH278" s="2"/>
+      <c r="KI278" s="2"/>
+      <c r="KJ278" s="2"/>
+      <c r="KK278" s="2"/>
+      <c r="KL278" s="2"/>
+      <c r="KM278" s="2"/>
+      <c r="KN278" s="2"/>
+      <c r="KO278" s="2"/>
+      <c r="KP278" s="2"/>
+      <c r="KQ278" s="2"/>
+      <c r="KR278" s="2"/>
+      <c r="KS278" s="2"/>
+      <c r="KT278" s="2"/>
+      <c r="KU278" s="2"/>
+      <c r="KV278" s="2"/>
+      <c r="KW278" s="2"/>
+      <c r="KX278" s="2"/>
+      <c r="KY278" s="2"/>
+      <c r="KZ278" s="2"/>
+      <c r="LA278" s="2"/>
+      <c r="LB278" s="2"/>
+      <c r="LC278" s="2"/>
+      <c r="LD278" s="2"/>
+      <c r="LE278" s="2"/>
+      <c r="LF278" s="2"/>
+      <c r="LG278" s="2"/>
+      <c r="LH278" s="2"/>
+      <c r="LI278" s="2"/>
+      <c r="LJ278" s="2"/>
+      <c r="LK278" s="2"/>
+      <c r="LL278" s="2"/>
+      <c r="LM278" s="2"/>
+      <c r="LN278" s="2"/>
+      <c r="LO278" s="2"/>
+      <c r="LP278" s="2"/>
+      <c r="LQ278" s="2"/>
+      <c r="LR278" s="2"/>
+      <c r="LS278" s="2"/>
+      <c r="LT278" s="2"/>
+      <c r="LU278" s="2"/>
+      <c r="LV278" s="2"/>
+      <c r="LW278" s="2"/>
+      <c r="LX278" s="2"/>
+      <c r="LY278" s="2"/>
+      <c r="LZ278" s="2"/>
+      <c r="MA278" s="2"/>
+      <c r="MB278" s="2"/>
+      <c r="MC278" s="2"/>
+      <c r="MD278" s="2"/>
+      <c r="ME278" s="2"/>
+      <c r="MF278" s="2"/>
+      <c r="MG278" s="2"/>
+      <c r="MH278" s="2"/>
+      <c r="MI278" s="2"/>
+      <c r="MJ278" s="2"/>
+      <c r="MK278" s="2"/>
+      <c r="ML278" s="2"/>
+      <c r="MM278" s="2"/>
+      <c r="MN278" s="2"/>
+      <c r="MO278" s="2"/>
+      <c r="MP278" s="2"/>
+      <c r="MQ278" s="2"/>
+      <c r="MR278" s="2"/>
+      <c r="MS278" s="2"/>
+      <c r="MT278" s="2"/>
+      <c r="MU278" s="2"/>
+      <c r="MV278" s="2"/>
+      <c r="MW278" s="2"/>
+      <c r="MX278" s="2"/>
+      <c r="MY278" s="2"/>
+      <c r="MZ278" s="2"/>
+      <c r="NA278" s="2"/>
+      <c r="NB278" s="2"/>
+      <c r="NC278" s="2"/>
+      <c r="ND278" s="2"/>
+      <c r="NE278" s="2"/>
+      <c r="NF278" s="2"/>
+      <c r="NG278" s="2"/>
+      <c r="NH278" s="2"/>
+      <c r="NI278" s="2"/>
+      <c r="NJ278" s="2"/>
+      <c r="NK278" s="2"/>
+      <c r="NL278" s="2"/>
+      <c r="NM278" s="2"/>
+      <c r="NN278" s="2"/>
+      <c r="NO278" s="2"/>
+      <c r="NP278" s="2"/>
+      <c r="NQ278" s="2"/>
+      <c r="NR278" s="2"/>
+      <c r="NS278" s="2"/>
+      <c r="NT278" s="2"/>
+      <c r="NU278" s="2"/>
+      <c r="NV278" s="2"/>
+      <c r="NW278" s="2"/>
+      <c r="NX278" s="2"/>
+      <c r="NY278" s="2"/>
+      <c r="NZ278" s="2"/>
+      <c r="OA278" s="2"/>
+      <c r="OB278" s="2"/>
+      <c r="OC278" s="2"/>
+      <c r="OD278" s="2"/>
+      <c r="OE278" s="2"/>
+      <c r="OF278" s="2"/>
+      <c r="OG278" s="2"/>
+      <c r="OH278" s="2"/>
+      <c r="OI278" s="2"/>
+      <c r="OJ278" s="2"/>
+      <c r="OK278" s="2"/>
+      <c r="OL278" s="2"/>
+      <c r="OM278" s="2"/>
+      <c r="ON278" s="2"/>
+      <c r="OO278" s="2"/>
+      <c r="OP278" s="2"/>
+      <c r="OQ278" s="2"/>
+      <c r="OR278" s="2"/>
+      <c r="OS278" s="2"/>
+      <c r="OT278" s="2"/>
+      <c r="OU278" s="2"/>
+      <c r="OV278" s="2"/>
+      <c r="OW278" s="2"/>
+      <c r="OX278" s="2"/>
+      <c r="OY278" s="2"/>
+      <c r="OZ278" s="2"/>
+      <c r="PA278" s="2"/>
+      <c r="PB278" s="2"/>
+      <c r="PC278" s="2"/>
+      <c r="PD278" s="2"/>
+      <c r="PE278" s="2"/>
+      <c r="PF278" s="2"/>
+      <c r="PG278" s="2"/>
+      <c r="PH278" s="2"/>
+      <c r="PI278" s="2"/>
+      <c r="PJ278" s="2"/>
+      <c r="PK278" s="2"/>
+      <c r="PL278" s="2"/>
+      <c r="PM278" s="2"/>
+      <c r="PN278" s="2"/>
+      <c r="PO278" s="2"/>
+      <c r="PP278" s="2"/>
+      <c r="PQ278" s="2"/>
+      <c r="PR278" s="2"/>
+      <c r="PS278" s="2"/>
+      <c r="PT278" s="2"/>
+      <c r="PU278" s="2"/>
+      <c r="PV278" s="2"/>
+      <c r="PW278" s="2"/>
+      <c r="PX278" s="2"/>
+      <c r="PY278" s="2"/>
+      <c r="PZ278" s="2"/>
+      <c r="QA278" s="2"/>
+      <c r="QB278" s="2"/>
+      <c r="QC278" s="2"/>
+      <c r="QD278" s="2"/>
+      <c r="QE278" s="2"/>
+      <c r="QF278" s="2"/>
+      <c r="QG278" s="2"/>
+      <c r="QH278" s="2"/>
+      <c r="QI278" s="2"/>
+      <c r="QJ278" s="2"/>
+      <c r="QK278" s="2"/>
+      <c r="QL278" s="2"/>
+      <c r="QM278" s="2"/>
+      <c r="QN278" s="2"/>
+      <c r="QO278" s="2"/>
+      <c r="QP278" s="2"/>
+      <c r="QQ278" s="2"/>
+      <c r="QR278" s="2"/>
+      <c r="QS278" s="2"/>
+      <c r="QT278" s="2"/>
+      <c r="QU278" s="2"/>
+      <c r="QV278" s="2"/>
+      <c r="QW278" s="2"/>
+      <c r="QX278" s="2"/>
+      <c r="QY278" s="2"/>
+      <c r="QZ278" s="2"/>
+      <c r="RA278" s="2"/>
+      <c r="RB278" s="2"/>
+      <c r="RC278" s="2"/>
+      <c r="RD278" s="2"/>
+      <c r="RE278" s="2"/>
+      <c r="RF278" s="2"/>
+      <c r="RG278" s="2"/>
+      <c r="RH278" s="2"/>
+      <c r="RI278" s="2"/>
+      <c r="RJ278" s="2"/>
+      <c r="RK278" s="2"/>
+      <c r="RL278" s="2"/>
+      <c r="RM278" s="2"/>
+      <c r="RN278" s="2"/>
+      <c r="RO278" s="2"/>
+      <c r="RP278" s="2"/>
+      <c r="RQ278" s="2"/>
+      <c r="RR278" s="2"/>
+      <c r="RS278" s="2"/>
+      <c r="RT278" s="2"/>
+      <c r="RU278" s="2"/>
+      <c r="RV278" s="2"/>
+      <c r="RW278" s="2"/>
+      <c r="RX278" s="2"/>
+      <c r="RY278" s="2"/>
+      <c r="RZ278" s="2"/>
+      <c r="SA278" s="2"/>
+      <c r="SB278" s="2"/>
+      <c r="SC278" s="2"/>
+      <c r="SD278" s="2"/>
+      <c r="SE278" s="2"/>
+      <c r="SF278" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cache/manual_references.xlsx
+++ b/cache/manual_references.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamid\Documents\GitHub\FReD-data\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9CCA66-2D39-443F-90C4-180339AB495A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B31B9D-BF5A-4D77-AD69-BADCFDB9CC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="930">
   <si>
     <t>key</t>
   </si>
@@ -5001,12 +5001,401 @@
   <si>
     <t>@article{kumar2021factors, title = {Factors Affecting Compliance with Alerts in the Context of Healthcare-related Emergencies}, author = {Kumar, Manasvi and Leroy, Gondy}, journal = {AIS Transactions on Replication Research}, year = {2021}, volume = {7}, number = {1}, note = {Article 3}, doi = {10.17705/1atrr.00068}, url = {https://aisel.aisnet.org/trr/vol7/iss1/3} }</t>
   </si>
+  <si>
+    <t>10.1080/14616696.2017.1290265</t>
+  </si>
+  <si>
+    <t>Barone, C., &amp; Ruggera, L. (2018). Educational equalization stalled? Trends in inequality of educational opportunity between 1930 and 1980 across 26 European nations. European Societies, 20(1), 1–25. https://doi.org/10.1080/14616696.2017.1290265</t>
+  </si>
+  <si>
+    <t>@article{barone2018educational,
+  title={Educational equalization stalled? Trends in inequality of educational opportunity between 1930 and 1980 across 26 European nations},
+  author={Barone, Carlo and Ruggera, Lucia},
+  journal={European Societies},
+  year={2018},
+  volume={20},
+  number={1},
+  pages={1--25},
+  doi={10.1080/14616696.2017.1290265}
+}</t>
+  </si>
+  <si>
+    <t>Educational equalization stalled? Trends in inequality of educational opportunity between 1930 and 1980 across 26 European nations</t>
+  </si>
+  <si>
+    <t>Carlo Barone; Lucia Ruggera</t>
+  </si>
+  <si>
+    <t>European Societies</t>
+  </si>
+  <si>
+    <t>1–25</t>
+  </si>
+  <si>
+    <t>10.31234/osf.io/m6ghr</t>
+  </si>
+  <si>
+    <t>Tybur, J. M., Jones, B. C., DeBruine, L. M., Ackerman, J. M., &amp; Fasolt, V. (2020). Preregistered replication of “Sick body, vigilant mind: The biological immune system activates the behavioral immune system.” PsyArXiv. https://doi.org/10.31234/osf.io/m6ghr</t>
+  </si>
+  <si>
+    <t>@article{tybur2020preregistered,
+  title={Preregistered replication of Sick body, vigilant mind: The biological immune system activates the behavioral immune system},
+  author={Tybur, Joshua M. and Jones, Benedict C. and DeBruine, Lisa Marie and Ackerman, Joshua M. and Fasolt, Vanessa},
+  journal={PsyArXiv},
+  year={2020},
+  doi={10.31234/osf.io/m6ghr}
+}</t>
+  </si>
+  <si>
+    <t>Preregistered replication of “Sick body, vigilant mind: The biological immune system activates the behavioral immune system”</t>
+  </si>
+  <si>
+    <t>Joshua M. Tybur; Benedict C. Jones; Lisa Marie DeBruine; Joshua M. Ackerman; Vanessa Fasolt</t>
+  </si>
+  <si>
+    <t>PsyArXiv</t>
+  </si>
+  <si>
+    <t>10.17705/1atrr.00067</t>
+  </si>
+  <si>
+    <t>Kajtazi, M., Holmberg, N., Sarker, S., Keller, C., Johansson, B., &amp; Tona, O. (2021). Toward a unified model of information security policy compliance: A conceptual replication study. AIS Transactions on Replication Research, 7(2), 1–15. https://doi.org/10.17705/1atrr.00067</t>
+  </si>
+  <si>
+    <t>@article{kajtazi2021unified,
+  title={Toward a unified model of information security policy compliance: A conceptual replication study},
+  author={Kajtazi, Miranda and Holmberg, Nicklas and Sarker, Saonee and Keller, Christina and Johansson, Björn and Tona, Olgerta},
+  journal={AIS Transactions on Replication Research},
+  year={2021},
+  volume={7},
+  number={2},
+  pages={1--15},
+  doi={10.17705/1atrr.00067}
+}</t>
+  </si>
+  <si>
+    <t>Toward a Unified Model of Information Security Policy Compliance: A Conceptual Replication Study</t>
+  </si>
+  <si>
+    <t>Miranda Kajtazi; Nicklas Holmberg; Saonee Sarker; Christina Keller; Björn Johansson; Olgerta Tona</t>
+  </si>
+  <si>
+    <t>1–15</t>
+  </si>
+  <si>
+    <t>10.31219/osf.io/pzy5q</t>
+  </si>
+  <si>
+    <t>Quirk, C., Adam, K., &amp; Vogel, E. K. (2020). No evidence for an object working memory capacity benefit with extended viewing time. OSF Preprints. https://doi.org/10.31219/osf.io/pzy5q</t>
+  </si>
+  <si>
+    <t>@article{quirk2020object,
+  title={No Evidence for an Object Working Memory Capacity Benefit with Extended Viewing Time},
+  author={Quirk, Colin and Adam, Kirsten and Vogel, Edward K.},
+  journal={OSF Preprints},
+  year={2020},
+  doi={10.31219/osf.io/pzy5q}
+}</t>
+  </si>
+  <si>
+    <t>No Evidence for an Object Working Memory Capacity Benefit with Extended Viewing Time</t>
+  </si>
+  <si>
+    <t>Colin Quirk; Kirsten Adam; Edward K. Vogel</t>
+  </si>
+  <si>
+    <t>OSF Preprints</t>
+  </si>
+  <si>
+    <t>10.1111/lang.12393</t>
+  </si>
+  <si>
+    <t>Kim, Y., Skalicky, S., &amp; Jung, Y. (2020). The role of linguistic alignment on question development in face-to-face and synchronous computer-mediated communication contexts: A conceptual replication study. Language Learning, 70(3), 643–684. https://doi.org/10.1111/lang.12393</t>
+  </si>
+  <si>
+    <t>@article{kim2020alignment,
+  title={The Role of Linguistic Alignment on Question Development in Face-to-Face and Synchronous Computer-Mediated Communication Contexts: A Conceptual Replication Study},
+  author={Kim, YouJin and Skalicky, Stephen and Jung, Yeonjoo},
+  journal={Language Learning},
+  year={2020},
+  volume={70},
+  number={3},
+  pages={643--684},
+  doi={10.1111/lang.12393}
+}</t>
+  </si>
+  <si>
+    <t>The Role of Linguistic Alignment on Question Development in Face-to-Face and Synchronous Computer-Mediated Communication Contexts: A Conceptual Replication Study</t>
+  </si>
+  <si>
+    <t>YouJin Kim; Stephen Skalicky; Yeonjoo Jung</t>
+  </si>
+  <si>
+    <t>Language Learning</t>
+  </si>
+  <si>
+    <t>643–684</t>
+  </si>
+  <si>
+    <t>10.31234/osf.io/3fvyn</t>
+  </si>
+  <si>
+    <t>Ross, R. M., &amp; Levy, N. (2022). Expressive responding in support of Donald Trump: An extended replication of Schaffner and Luks (2018). PsyArXiv. https://doi.org/10.31234/osf.io/3fvyn</t>
+  </si>
+  <si>
+    <t>@article{ross2022expressive,
+  title={Expressive responding in support of Donald Trump: An extended replication of Schaffner and Luks (2018)},
+  author={Ross, Robert M. and Levy, Neil},
+  journal={PsyArXiv},
+  year={2022},
+  doi={10.31234/osf.io/3fvyn}
+}</t>
+  </si>
+  <si>
+    <t>Expressive responding in support of Donald Trump: An extended replication of Schaffner and Luks (2018)</t>
+  </si>
+  <si>
+    <t>Robert M. Ross; Neil Levy</t>
+  </si>
+  <si>
+    <t>10.5964/jnc.6063</t>
+  </si>
+  <si>
+    <t>Artemenko, C., Masson, N., Georges, C., Nuerk, H.-C., &amp; Cipora, K. (2021). Not all elementary school teachers are scared of math. Journal of Numerical Cognition, 7(3), Article e6063. https://doi.org/10.5964/jnc.6063</t>
+  </si>
+  <si>
+    <t>@article{artemenko2021teachers,
+  title={Not All Elementary School Teachers Are Scared of Math},
+  author={Artemenko, Christina and Masson, Nicolas and Georges, Carrie and Nuerk, Hans-Christoph and Cipora, Krzysztof},
+  journal={Journal of Numerical Cognition},
+  year={2021},
+  volume={7},
+  number={3},
+  pages={e6063},
+  doi={10.5964/jnc.6063}
+}</t>
+  </si>
+  <si>
+    <t>Not All Elementary School Teachers Are Scared of Math</t>
+  </si>
+  <si>
+    <t>Christina Artemenko; Nicolas Masson; Carrie Georges; Hans-Christoph Nuerk; Krzysztof Cipora</t>
+  </si>
+  <si>
+    <t>Journal of Numerical Cognition</t>
+  </si>
+  <si>
+    <t>e6063</t>
+  </si>
+  <si>
+    <t>@article{shin2023satisfaction,
+  title={Student satisfaction and perceived learning in an online second language learning environment: A replication of Gray and DiLoreto (2016)},
+  author={Shin, Hye Won and Sok, Sarah},
+  journal={ReCALL},
+  year={2023},
+  volume={35},
+  number={2},
+  pages={160--177},
+  doi={10.1017/S0958344023000034}
+}</t>
+  </si>
+  <si>
+    <t>160–177</t>
+  </si>
+  <si>
+    <t>10.31234/osf.io/6tn4f</t>
+  </si>
+  <si>
+    <t>Evans, T. R., Hughes, D. J., &amp; Steptoe-Warren, G. (2019). A conceptual replication of emotional intelligence as a second-stratum factor of intelligence. PsyArXiv. https://doi.org/10.31234/osf.io/6tn4f</t>
+  </si>
+  <si>
+    <t>@article{evans2019emotional,
+  title={A conceptual replication of emotional intelligence as a second-stratum factor of intelligence},
+  author={Evans, Thomas Rhys and Hughes, David J. and Steptoe-Warren, Gail},
+  journal={PsyArXiv},
+  year={2019},
+  doi={10.31234/osf.io/6tn4f}
+}</t>
+  </si>
+  <si>
+    <t>A conceptual replication of emotional intelligence as a second-stratum factor of intelligence</t>
+  </si>
+  <si>
+    <t>Thomas Rhys Evans; David J. Hughes; Gail Steptoe-Warren</t>
+  </si>
+  <si>
+    <t>https://aisel.aisnet.org/trr/vol6/iss1/13</t>
+  </si>
+  <si>
+    <t>Masuch, K., Hengstler, S., Trang, S., &amp; Brendel, A. B. (2020). Replication research of Moody, Siponen, and Pahnila’s unified model of information security policy compliance. AIS Transactions on Replication Research, 6, Article 13. https://doi.org/10.17705/1atrr.00056</t>
+  </si>
+  <si>
+    <t>@article{masuch2020replication,
+  title={Replication Research of Moody, Siponen, and Pahnila's Unified Model of Information Security Policy Compliance},
+  author={Masuch, Kristin and Hengstler, Sebastian and Trang, Simon and Brendel, Alfred Benedikt},
+  journal={AIS Transactions on Replication Research},
+  year={2020},
+  volume={6},
+  number={13},
+  doi={10.17705/1atrr.00056},
+  url={https://aisel.aisnet.org/trr/vol6/iss1/13}
+}</t>
+  </si>
+  <si>
+    <t>1–16</t>
+  </si>
+  <si>
+    <t>10.1503/jpn.120060</t>
+  </si>
+  <si>
+    <t>Stuhrmann, A., Dohm, K., Kugel, H., Zwanzger, P., Redlich, R., Grotegerd, D., Rauch, A. V., Arolt, V., Heindel, W., Suslow, T., Zwitserlood, P., &amp; Dannlowski, U. (2013). Mood-congruent amygdala responses to subliminally presented facial expressions in major depression: Associations with anhedonia. Journal of Psychiatry &amp; Neuroscience, 38(4), 249–258. https://doi.org/10.1503/jpn.120060</t>
+  </si>
+  <si>
+    <t>@article{stuhrmann2013mood,
+  title={Mood-congruent amygdala responses to subliminally presented facial expressions in major depression: Associations with anhedonia},
+  author={Stuhrmann, Anja and Dohm, Katharina and Kugel, Harald and Zwanzger, Peter and Redlich, Ronny and Grotegerd, Dominik and Rauch, Astrid Veronika and Arolt, Volker and Heindel, Walter and Suslow, Thomas and Zwitserlood, Pienie and Dannlowski, Udo},
+  journal={Journal of Psychiatry and Neuroscience},
+  year={2013},
+  volume={38},
+  number={4},
+  pages={249--258},
+  doi={10.1503/jpn.120060}
+}</t>
+  </si>
+  <si>
+    <t>Mood-congruent amygdala responses to subliminally presented facial expressions in major depression: Associations with anhedonia</t>
+  </si>
+  <si>
+    <t>Anja Stuhrmann; Katharina Dohm; Harald Kugel; Peter Zwanzger; Ronny Redlich; Dominik Grotegerd; Astrid Veronika Rauch; Volker Arolt; Walter Heindel; Thomas Suslow; Pienie Zwitserlood; Udo Dannlowski</t>
+  </si>
+  <si>
+    <t>Journal of Psychiatry &amp; Neuroscience</t>
+  </si>
+  <si>
+    <t>249–258</t>
+  </si>
+  <si>
+    <t>10.31222/osf.io/sjyp3</t>
+  </si>
+  <si>
+    <t>Kohrt, F., Smaldino, P. E., McElreath, R., &amp; Schönbrodt, F. D. (2022). Replication of the natural selection of bad science. MetaArXiv. https://doi.org/10.31222/osf.io/sjyp3</t>
+  </si>
+  <si>
+    <t>@article{kohrt2022replication,
+  title={Replication of the natural selection of bad science},
+  author={Kohrt, Florian and Smaldino, Paul E. and McElreath, Richard and Schönbrodt, Felix D.},
+  journal={MetaArXiv},
+  year={2022},
+  doi={10.31222/osf.io/sjyp3}
+}</t>
+  </si>
+  <si>
+    <t>Replication of the natural selection of bad science</t>
+  </si>
+  <si>
+    <t>Florian Kohrt; Paul E. Smaldino; Richard McElreath; Felix D. Schönbrodt</t>
+  </si>
+  <si>
+    <t>MetaArXiv</t>
+  </si>
+  <si>
+    <t>10.31234/osf.io/2h59n</t>
+  </si>
+  <si>
+    <t>Crawford, J. (2020). Close and conceptual replications of Waytz, Dungan, and Young (2013), Studies 2b and 4. PsyArXiv. https://doi.org/10.31234/osf.io/2h59n</t>
+  </si>
+  <si>
+    <t>@article{crawford2020close,
+  title={Close and Conceptual Replications of Waytz, Dungan, and Young (2013) Studies 2b and 4},
+  author={Crawford, Jarret},
+  journal={PsyArXiv},
+  year={2020},
+  doi={10.31234/osf.io/2h59n}
+}</t>
+  </si>
+  <si>
+    <t>Close and Conceptual Replications of Waytz, Dungan, &amp; Young (2013) Studies 2b and 4</t>
+  </si>
+  <si>
+    <t>Jarret Crawford</t>
+  </si>
+  <si>
+    <t>10.17705/1atrr.00046</t>
+  </si>
+  <si>
+    <t>Zeng, M., Lin, S., &amp; Armstrong, D. J. (2020). Are all Internet users’ information privacy concerns (IUIPC) created equal? AIS Transactions on Replication Research, 6, Article 3. https://doi.org/10.17705/1atrr.00046</t>
+  </si>
+  <si>
+    <t>@article{zeng2020privacy,
+  title={Are All Internet Users' Information Privacy Concerns (IUIPC) Created Equal?},
+  author={Zeng, Miaoyi and Lin, Shuaifu and Armstrong, Deborah J.},
+  journal={AIS Transactions on Replication Research},
+  year={2020},
+  volume={6},
+  number={3},
+  doi={10.17705/1atrr.00046}
+}</t>
+  </si>
+  <si>
+    <t>Are All Internet Users’ Information Privacy Concerns (IUIPC) Created Equal?</t>
+  </si>
+  <si>
+    <t>Miaoyi Zeng; Shuaifu Lin; Deborah J. Armstrong</t>
+  </si>
+  <si>
+    <t>10.17705/1atrr.00066</t>
+  </si>
+  <si>
+    <t>Carte, T. A., Wang, N., Yetgin, E., &amp; Kim, I. (2021). Conflict asymmetry in face-to-face and computer mediated teams. AIS Transactions on Replication Research, 7(1), 1–19. https://doi.org/10.17705/1atrr.00066</t>
+  </si>
+  <si>
+    <t>@article{carte2021conflict,
+  title={Conflict Asymmetry in Face-to-face and Computer Mediated Teams},
+  author={Carte, Traci A. and Wang, Nan and Yetgin, Emre and Kim, Inchan},
+  journal={AIS Transactions on Replication Research},
+  year={2021},
+  volume={7},
+  number={1},
+  pages={1--19},
+  doi={10.17705/1atrr.00066}
+}</t>
+  </si>
+  <si>
+    <t>Conflict Asymmetry in Face-to-face and Computer Mediated Teams</t>
+  </si>
+  <si>
+    <t>Traci A. Carte; Nan Wang; Emre Yetgin; Inchan Kim</t>
+  </si>
+  <si>
+    <t>1–19</t>
+  </si>
+  <si>
+    <t>10.31234/osf.io/pgqj2</t>
+  </si>
+  <si>
+    <t>Feinberg, L., Wong, A., &amp; Hartshorne, J. K. (2022). Replication of Bonatti, Peña, Nespor, &amp; Mehler (2005), Experiment 1. PsyArXiv. https://doi.org/10.31234/osf.io/pgqj2</t>
+  </si>
+  <si>
+    <t>@article{feinberg2022replication,
+  title={Replication of Bonatti, Peña, Nespor, &amp; Mehler (2005) Experiment 1},
+  author={Feinberg, Lily and Wong, Alyson and Hartshorne, Joshua K.},
+  journal={PsyArXiv},
+  year={2022},
+  doi={10.31234/osf.io/pgqj2}
+}</t>
+  </si>
+  <si>
+    <t>Replication of Bonatti, Peña, Nespor, &amp; Mehler (2005) Experiment 1</t>
+  </si>
+  <si>
+    <t>Lily Feinberg; Alyson Wong; Joshua K. Hartshorne</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5029,6 +5418,10 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5047,18 +5440,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{C2354E34-5EB8-4A2C-ADEA-D0CEFF1F7247}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5360,10 +5758,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:SF278"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:SF294"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5395,7 +5793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -5406,7 +5804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -5417,7 +5815,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5428,7 +5826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -5439,7 +5837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -5450,7 +5848,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -5461,7 +5859,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -5472,7 +5870,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -5483,7 +5881,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -5494,7 +5892,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -5505,7 +5903,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -5516,7 +5914,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -5527,7 +5925,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -5538,7 +5936,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -5549,7 +5947,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -5560,7 +5958,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -5571,7 +5969,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -5582,7 +5980,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -5593,7 +5991,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -5604,7 +6002,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -5615,7 +6013,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -5626,7 +6024,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -5637,7 +6035,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -5648,7 +6046,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -5659,7 +6057,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -5667,7 +6065,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>84</v>
       </c>
@@ -5678,7 +6076,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -5689,7 +6087,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>90</v>
       </c>
@@ -5700,7 +6098,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>93</v>
       </c>
@@ -5711,7 +6109,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -5722,7 +6120,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>99</v>
       </c>
@@ -5733,7 +6131,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -5744,7 +6142,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -5755,7 +6153,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -5766,7 +6164,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>111</v>
       </c>
@@ -5777,7 +6175,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -5788,7 +6186,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -5799,7 +6197,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>120</v>
       </c>
@@ -5810,7 +6208,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>123</v>
       </c>
@@ -5821,7 +6219,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -5832,7 +6230,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>129</v>
       </c>
@@ -5843,7 +6241,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -5854,7 +6252,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -5865,7 +6263,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>129</v>
       </c>
@@ -5876,7 +6274,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>132</v>
       </c>
@@ -5887,7 +6285,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>135</v>
       </c>
@@ -5898,7 +6296,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>135</v>
       </c>
@@ -5909,7 +6307,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>135</v>
       </c>
@@ -5920,7 +6318,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -5931,7 +6329,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -5942,7 +6340,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>138</v>
       </c>
@@ -5953,7 +6351,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>141</v>
       </c>
@@ -5964,7 +6362,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>144</v>
       </c>
@@ -5975,7 +6373,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>144</v>
       </c>
@@ -5986,7 +6384,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>144</v>
       </c>
@@ -5997,7 +6395,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>147</v>
       </c>
@@ -6008,7 +6406,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -6019,7 +6417,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>147</v>
       </c>
@@ -6030,7 +6428,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>147</v>
       </c>
@@ -6041,7 +6439,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>150</v>
       </c>
@@ -6052,7 +6450,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>153</v>
       </c>
@@ -6063,7 +6461,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>153</v>
       </c>
@@ -6074,7 +6472,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>156</v>
       </c>
@@ -6085,7 +6483,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>156</v>
       </c>
@@ -6096,7 +6494,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>156</v>
       </c>
@@ -6107,7 +6505,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>159</v>
       </c>
@@ -6118,7 +6516,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>159</v>
       </c>
@@ -6129,7 +6527,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>159</v>
       </c>
@@ -6140,7 +6538,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>162</v>
       </c>
@@ -6151,7 +6549,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>162</v>
       </c>
@@ -6162,7 +6560,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>162</v>
       </c>
@@ -6173,7 +6571,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -6184,7 +6582,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>168</v>
       </c>
@@ -6195,7 +6593,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>168</v>
       </c>
@@ -6206,7 +6604,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>171</v>
       </c>
@@ -6217,7 +6615,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>171</v>
       </c>
@@ -6228,7 +6626,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>174</v>
       </c>
@@ -6239,7 +6637,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>174</v>
       </c>
@@ -6250,7 +6648,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>174</v>
       </c>
@@ -6261,7 +6659,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>177</v>
       </c>
@@ -6272,7 +6670,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>177</v>
       </c>
@@ -6283,7 +6681,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>177</v>
       </c>
@@ -6294,7 +6692,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>180</v>
       </c>
@@ -6305,7 +6703,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>183</v>
       </c>
@@ -6316,7 +6714,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>186</v>
       </c>
@@ -6327,7 +6725,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>186</v>
       </c>
@@ -6338,7 +6736,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>189</v>
       </c>
@@ -6349,7 +6747,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>192</v>
       </c>
@@ -6360,7 +6758,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>195</v>
       </c>
@@ -6371,7 +6769,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -6382,7 +6780,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>201</v>
       </c>
@@ -6393,7 +6791,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>201</v>
       </c>
@@ -6404,7 +6802,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -6415,7 +6813,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>201</v>
       </c>
@@ -6426,7 +6824,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -6437,7 +6835,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>201</v>
       </c>
@@ -6448,7 +6846,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -6459,7 +6857,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>201</v>
       </c>
@@ -6470,7 +6868,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>204</v>
       </c>
@@ -6481,7 +6879,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -6492,7 +6890,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>207</v>
       </c>
@@ -6503,7 +6901,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -6514,7 +6912,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -6525,7 +6923,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>216</v>
       </c>
@@ -6536,7 +6934,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>219</v>
       </c>
@@ -6547,7 +6945,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -6558,7 +6956,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>219</v>
       </c>
@@ -6569,7 +6967,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>219</v>
       </c>
@@ -6580,7 +6978,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>222</v>
       </c>
@@ -6591,7 +6989,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>225</v>
       </c>
@@ -6602,7 +7000,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
         <v>228</v>
       </c>
@@ -6613,7 +7011,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -6624,7 +7022,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>234</v>
       </c>
@@ -6635,7 +7033,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3">
       <c r="A115" t="s">
         <v>237</v>
       </c>
@@ -6646,7 +7044,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:3">
       <c r="A116" t="s">
         <v>240</v>
       </c>
@@ -6657,7 +7055,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3">
       <c r="A117" t="s">
         <v>243</v>
       </c>
@@ -6668,7 +7066,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
         <v>246</v>
       </c>
@@ -6679,7 +7077,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>249</v>
       </c>
@@ -6690,7 +7088,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3">
       <c r="A120" t="s">
         <v>252</v>
       </c>
@@ -6701,7 +7099,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3">
       <c r="A121" t="s">
         <v>255</v>
       </c>
@@ -6712,7 +7110,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
         <v>258</v>
       </c>
@@ -6723,7 +7121,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3">
       <c r="A123" t="s">
         <v>261</v>
       </c>
@@ -6734,7 +7132,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:3">
       <c r="A124" t="s">
         <v>264</v>
       </c>
@@ -6745,7 +7143,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -6756,7 +7154,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>270</v>
       </c>
@@ -6767,7 +7165,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -6778,7 +7176,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>276</v>
       </c>
@@ -6789,7 +7187,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>279</v>
       </c>
@@ -6800,7 +7198,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>282</v>
       </c>
@@ -6811,7 +7209,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>285</v>
       </c>
@@ -6822,7 +7220,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>288</v>
       </c>
@@ -6833,7 +7231,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
         <v>291</v>
       </c>
@@ -6844,7 +7242,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>294</v>
       </c>
@@ -6855,7 +7253,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
         <v>297</v>
       </c>
@@ -6866,7 +7264,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>300</v>
       </c>
@@ -6877,7 +7275,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:3">
       <c r="A137" t="s">
         <v>303</v>
       </c>
@@ -6888,7 +7286,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:3">
       <c r="A138" t="s">
         <v>306</v>
       </c>
@@ -6899,7 +7297,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:3">
       <c r="A139" t="s">
         <v>309</v>
       </c>
@@ -6910,7 +7308,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
         <v>312</v>
       </c>
@@ -6921,7 +7319,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>315</v>
       </c>
@@ -6932,7 +7330,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>318</v>
       </c>
@@ -6943,7 +7341,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:3">
       <c r="A143" t="s">
         <v>321</v>
       </c>
@@ -6954,7 +7352,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
         <v>324</v>
       </c>
@@ -6965,7 +7363,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>327</v>
       </c>
@@ -6976,7 +7374,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:3">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -6987,7 +7385,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
         <v>333</v>
       </c>
@@ -6998,7 +7396,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:3">
       <c r="A148" t="s">
         <v>336</v>
       </c>
@@ -7009,7 +7407,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:3">
       <c r="A149" t="s">
         <v>339</v>
       </c>
@@ -7020,7 +7418,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:3">
       <c r="A150" t="s">
         <v>342</v>
       </c>
@@ -7031,7 +7429,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:3">
       <c r="A151" t="s">
         <v>345</v>
       </c>
@@ -7042,7 +7440,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:3">
       <c r="A152" t="s">
         <v>348</v>
       </c>
@@ -7053,7 +7451,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:3">
       <c r="A153" t="s">
         <v>351</v>
       </c>
@@ -7064,7 +7462,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:3">
       <c r="A154" t="s">
         <v>354</v>
       </c>
@@ -7075,7 +7473,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:3">
       <c r="A155" t="s">
         <v>357</v>
       </c>
@@ -7086,7 +7484,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:3">
       <c r="A156" t="s">
         <v>360</v>
       </c>
@@ -7097,7 +7495,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:3">
       <c r="A157" t="s">
         <v>363</v>
       </c>
@@ -7108,7 +7506,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:3">
       <c r="A158" t="s">
         <v>366</v>
       </c>
@@ -7119,7 +7517,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:3">
       <c r="A159" t="s">
         <v>369</v>
       </c>
@@ -7130,7 +7528,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:3">
       <c r="A160" t="s">
         <v>372</v>
       </c>
@@ -7141,7 +7539,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:10">
       <c r="A161" t="s">
         <v>375</v>
       </c>
@@ -7152,7 +7550,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:10">
       <c r="A162" t="s">
         <v>378</v>
       </c>
@@ -7163,7 +7561,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:10">
       <c r="A163" t="s">
         <v>381</v>
       </c>
@@ -7174,7 +7572,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:10">
       <c r="A164" t="s">
         <v>384</v>
       </c>
@@ -7185,7 +7583,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:10">
       <c r="A165" t="s">
         <v>387</v>
       </c>
@@ -7196,7 +7594,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:10">
       <c r="A166" t="s">
         <v>390</v>
       </c>
@@ -7207,7 +7605,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:10">
       <c r="A167" t="s">
         <v>393</v>
       </c>
@@ -7218,7 +7616,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:10">
       <c r="A168" t="s">
         <v>396</v>
       </c>
@@ -7229,7 +7627,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:10">
       <c r="A169" t="s">
         <v>399</v>
       </c>
@@ -7240,7 +7638,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:10">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -7251,7 +7649,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:10">
       <c r="A171" t="s">
         <v>405</v>
       </c>
@@ -7262,7 +7660,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:10">
       <c r="A172" t="s">
         <v>408</v>
       </c>
@@ -7273,7 +7671,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:10">
       <c r="A173" t="s">
         <v>411</v>
       </c>
@@ -7293,7 +7691,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:10">
       <c r="A174" t="s">
         <v>416</v>
       </c>
@@ -7313,7 +7711,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:10">
       <c r="A175" t="s">
         <v>420</v>
       </c>
@@ -7333,7 +7731,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:10">
       <c r="A176" t="s">
         <v>424</v>
       </c>
@@ -7362,7 +7760,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:10">
       <c r="A177" t="s">
         <v>432</v>
       </c>
@@ -7391,7 +7789,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:10">
       <c r="A178" t="s">
         <v>434</v>
       </c>
@@ -7411,7 +7809,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:10">
       <c r="A179" t="s">
         <v>439</v>
       </c>
@@ -7431,7 +7829,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:10">
       <c r="A180" t="s">
         <v>444</v>
       </c>
@@ -7451,7 +7849,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:10">
       <c r="A181" t="s">
         <v>449</v>
       </c>
@@ -7468,7 +7866,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:10">
       <c r="A182" t="s">
         <v>453</v>
       </c>
@@ -7479,7 +7877,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:10">
       <c r="A183" t="s">
         <v>456</v>
       </c>
@@ -7490,7 +7888,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:10">
       <c r="A184" t="s">
         <v>459</v>
       </c>
@@ -7510,7 +7908,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:10">
       <c r="A185" t="s">
         <v>464</v>
       </c>
@@ -7530,7 +7928,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:10">
       <c r="A186" t="s">
         <v>469</v>
       </c>
@@ -7556,7 +7954,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:10">
       <c r="A187" t="s">
         <v>476</v>
       </c>
@@ -7567,7 +7965,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:10">
       <c r="A188" t="s">
         <v>479</v>
       </c>
@@ -7578,7 +7976,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:10">
       <c r="A189" t="s">
         <v>482</v>
       </c>
@@ -7589,7 +7987,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:10">
       <c r="A190" t="s">
         <v>485</v>
       </c>
@@ -7600,7 +7998,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:10">
       <c r="A191" t="s">
         <v>488</v>
       </c>
@@ -7611,7 +8009,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:10">
       <c r="A192" t="s">
         <v>491</v>
       </c>
@@ -7622,7 +8020,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:3">
       <c r="A193" t="s">
         <v>494</v>
       </c>
@@ -7633,7 +8031,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:3">
       <c r="A194" t="s">
         <v>497</v>
       </c>
@@ -7644,7 +8042,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:3">
       <c r="A195" t="s">
         <v>500</v>
       </c>
@@ -7655,7 +8053,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:3">
       <c r="A196" t="s">
         <v>503</v>
       </c>
@@ -7666,7 +8064,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:3">
       <c r="A197" t="s">
         <v>506</v>
       </c>
@@ -7677,7 +8075,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:3">
       <c r="A198" t="s">
         <v>509</v>
       </c>
@@ -7688,7 +8086,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:3">
       <c r="A199" t="s">
         <v>512</v>
       </c>
@@ -7699,7 +8097,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:3">
       <c r="A200" t="s">
         <v>515</v>
       </c>
@@ -7710,7 +8108,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:3">
       <c r="A201" t="s">
         <v>518</v>
       </c>
@@ -7721,7 +8119,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:3">
       <c r="A202" t="s">
         <v>521</v>
       </c>
@@ -7732,7 +8130,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:3">
       <c r="A203" t="s">
         <v>524</v>
       </c>
@@ -7743,7 +8141,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:3">
       <c r="A204" t="s">
         <v>527</v>
       </c>
@@ -7754,7 +8152,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:3">
       <c r="A205" t="s">
         <v>530</v>
       </c>
@@ -7765,7 +8163,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:3">
       <c r="A206" t="s">
         <v>533</v>
       </c>
@@ -7776,7 +8174,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:3">
       <c r="A207" t="s">
         <v>536</v>
       </c>
@@ -7787,7 +8185,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:3">
       <c r="A208" t="s">
         <v>539</v>
       </c>
@@ -7798,7 +8196,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:3">
       <c r="A209" t="s">
         <v>542</v>
       </c>
@@ -7809,7 +8207,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:3">
       <c r="A210" t="s">
         <v>545</v>
       </c>
@@ -7820,7 +8218,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:3">
       <c r="A211" t="s">
         <v>548</v>
       </c>
@@ -7831,7 +8229,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:3">
       <c r="A212" t="s">
         <v>551</v>
       </c>
@@ -7842,7 +8240,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:3">
       <c r="A213" t="s">
         <v>554</v>
       </c>
@@ -7853,7 +8251,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:3">
       <c r="A214" t="s">
         <v>557</v>
       </c>
@@ -7864,7 +8262,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:3">
       <c r="A215" t="s">
         <v>560</v>
       </c>
@@ -7875,7 +8273,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:3">
       <c r="A216" t="s">
         <v>563</v>
       </c>
@@ -7886,7 +8284,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:3">
       <c r="A217" t="s">
         <v>566</v>
       </c>
@@ -7897,7 +8295,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:3">
       <c r="A218" t="s">
         <v>569</v>
       </c>
@@ -7908,7 +8306,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:3">
       <c r="A219" t="s">
         <v>572</v>
       </c>
@@ -7919,7 +8317,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:3">
       <c r="A220" t="s">
         <v>575</v>
       </c>
@@ -7930,7 +8328,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:3">
       <c r="A221" t="s">
         <v>578</v>
       </c>
@@ -7941,7 +8339,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:3">
       <c r="A222" t="s">
         <v>581</v>
       </c>
@@ -7952,7 +8350,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:3">
       <c r="A223" t="s">
         <v>584</v>
       </c>
@@ -7963,7 +8361,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:3">
       <c r="A224" t="s">
         <v>587</v>
       </c>
@@ -7974,7 +8372,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:3">
       <c r="A225" t="s">
         <v>590</v>
       </c>
@@ -7985,7 +8383,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:3">
       <c r="A226" t="s">
         <v>593</v>
       </c>
@@ -7996,7 +8394,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:3">
       <c r="A227" t="s">
         <v>596</v>
       </c>
@@ -8007,7 +8405,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:3">
       <c r="A228" t="s">
         <v>599</v>
       </c>
@@ -8018,7 +8416,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:3">
       <c r="A229" t="s">
         <v>602</v>
       </c>
@@ -8029,7 +8427,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:3">
       <c r="A230" t="s">
         <v>605</v>
       </c>
@@ -8040,7 +8438,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:3">
       <c r="A231" t="s">
         <v>608</v>
       </c>
@@ -8051,7 +8449,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:3">
       <c r="A232" t="s">
         <v>611</v>
       </c>
@@ -8062,7 +8460,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:3">
       <c r="A233" t="s">
         <v>614</v>
       </c>
@@ -8073,7 +8471,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:3">
       <c r="A234" t="s">
         <v>617</v>
       </c>
@@ -8084,7 +8482,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:3">
       <c r="A235" t="s">
         <v>620</v>
       </c>
@@ -8095,7 +8493,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:3">
       <c r="A236" t="s">
         <v>623</v>
       </c>
@@ -8106,7 +8504,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:3">
       <c r="A237" t="s">
         <v>626</v>
       </c>
@@ -8117,7 +8515,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:3">
       <c r="A238" t="s">
         <v>629</v>
       </c>
@@ -8128,7 +8526,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:3">
       <c r="A239" t="s">
         <v>632</v>
       </c>
@@ -8139,7 +8537,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:3">
       <c r="A240" t="s">
         <v>635</v>
       </c>
@@ -8150,7 +8548,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:10">
       <c r="A241" t="s">
         <v>638</v>
       </c>
@@ -8161,7 +8559,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:10">
       <c r="A242" t="s">
         <v>641</v>
       </c>
@@ -8172,7 +8570,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:10">
       <c r="A243" t="s">
         <v>644</v>
       </c>
@@ -8183,7 +8581,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:10">
       <c r="A244" t="s">
         <v>647</v>
       </c>
@@ -8194,7 +8592,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:10">
       <c r="A245" t="s">
         <v>650</v>
       </c>
@@ -8205,7 +8603,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:10">
       <c r="A246" t="s">
         <v>653</v>
       </c>
@@ -8216,7 +8614,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:10">
       <c r="A247" t="s">
         <v>656</v>
       </c>
@@ -8227,7 +8625,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:10">
       <c r="A248" t="s">
         <v>659</v>
       </c>
@@ -8238,7 +8636,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:10">
       <c r="A249" t="s">
         <v>662</v>
       </c>
@@ -8249,7 +8647,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:10">
       <c r="A250" t="s">
         <v>665</v>
       </c>
@@ -8260,7 +8658,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:10">
       <c r="A251" t="s">
         <v>668</v>
       </c>
@@ -8271,7 +8669,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:10">
       <c r="A252" t="s">
         <v>671</v>
       </c>
@@ -8282,7 +8680,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:10">
       <c r="A253" t="s">
         <v>674</v>
       </c>
@@ -8293,7 +8691,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:10">
       <c r="A254" t="s">
         <v>677</v>
       </c>
@@ -8325,7 +8723,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:10">
       <c r="A255" t="s">
         <v>686</v>
       </c>
@@ -8357,7 +8755,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:10">
       <c r="A256" t="s">
         <v>694</v>
       </c>
@@ -8383,7 +8781,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:10">
       <c r="A257" t="s">
         <v>701</v>
       </c>
@@ -8409,7 +8807,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:10">
       <c r="A258" t="s">
         <v>708</v>
       </c>
@@ -8429,7 +8827,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:10">
       <c r="A259" t="s">
         <v>713</v>
       </c>
@@ -8449,7 +8847,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:10">
       <c r="A260" t="s">
         <v>718</v>
       </c>
@@ -8481,7 +8879,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:10">
       <c r="A261" t="s">
         <v>725</v>
       </c>
@@ -8504,7 +8902,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:10">
       <c r="A262" t="s">
         <v>731</v>
       </c>
@@ -8527,7 +8925,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:10">
       <c r="A263" t="s">
         <v>736</v>
       </c>
@@ -8547,7 +8945,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:10">
       <c r="A264" t="s">
         <v>741</v>
       </c>
@@ -8579,7 +8977,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:10">
       <c r="A265" t="s">
         <v>750</v>
       </c>
@@ -8611,7 +9009,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:10">
       <c r="A266" t="s">
         <v>758</v>
       </c>
@@ -8634,7 +9032,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:10">
       <c r="A267" t="s">
         <v>763</v>
       </c>
@@ -8663,7 +9061,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:10">
       <c r="A268" t="s">
         <v>771</v>
       </c>
@@ -8680,7 +9078,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:10">
       <c r="A269" t="s">
         <v>776</v>
       </c>
@@ -8703,7 +9101,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:10">
       <c r="A270" t="s">
         <v>782</v>
       </c>
@@ -8726,7 +9124,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:10">
       <c r="A271" t="s">
         <v>787</v>
       </c>
@@ -8746,7 +9144,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:10">
       <c r="A272" t="s">
         <v>792</v>
       </c>
@@ -8772,7 +9170,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="273" spans="1:500" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:500">
       <c r="A273" t="s">
         <v>799</v>
       </c>
@@ -8804,7 +9202,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="274" spans="1:500" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:500">
       <c r="A274" t="s">
         <v>807</v>
       </c>
@@ -8836,7 +9234,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="275" spans="1:500" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:500">
       <c r="A275" t="s">
         <v>815</v>
       </c>
@@ -8868,7 +9266,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="276" spans="1:500" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:500">
       <c r="A276" t="s">
         <v>824</v>
       </c>
@@ -8900,7 +9298,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="277" spans="1:500" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:500">
       <c r="A277" t="s">
         <v>831</v>
       </c>
@@ -8932,7 +9330,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="278" spans="1:500" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:500">
       <c r="A278" s="2" t="s">
         <v>838</v>
       </c>
@@ -9454,6 +9852,452 @@
       <c r="SE278" s="2"/>
       <c r="SF278" s="2"/>
     </row>
+    <row r="279" spans="1:500" ht="16.05" customHeight="1">
+      <c r="A279" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="G279" s="3">
+        <v>2018</v>
+      </c>
+      <c r="H279" s="3">
+        <v>20</v>
+      </c>
+      <c r="I279" s="3">
+        <v>1</v>
+      </c>
+      <c r="J279" s="3" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="280" spans="1:500">
+      <c r="A280" t="s">
+        <v>848</v>
+      </c>
+      <c r="B280" t="s">
+        <v>849</v>
+      </c>
+      <c r="C280" t="s">
+        <v>850</v>
+      </c>
+      <c r="D280" t="s">
+        <v>851</v>
+      </c>
+      <c r="E280" t="s">
+        <v>852</v>
+      </c>
+      <c r="F280" t="s">
+        <v>853</v>
+      </c>
+      <c r="G280">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="281" spans="1:500">
+      <c r="A281" t="s">
+        <v>854</v>
+      </c>
+      <c r="B281" t="s">
+        <v>855</v>
+      </c>
+      <c r="C281" t="s">
+        <v>856</v>
+      </c>
+      <c r="D281" t="s">
+        <v>857</v>
+      </c>
+      <c r="E281" t="s">
+        <v>858</v>
+      </c>
+      <c r="F281" t="s">
+        <v>691</v>
+      </c>
+      <c r="G281">
+        <v>2021</v>
+      </c>
+      <c r="H281">
+        <v>7</v>
+      </c>
+      <c r="I281">
+        <v>2</v>
+      </c>
+      <c r="J281" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="282" spans="1:500">
+      <c r="A282" t="s">
+        <v>860</v>
+      </c>
+      <c r="B282" t="s">
+        <v>861</v>
+      </c>
+      <c r="C282" t="s">
+        <v>862</v>
+      </c>
+      <c r="D282" t="s">
+        <v>863</v>
+      </c>
+      <c r="E282" t="s">
+        <v>864</v>
+      </c>
+      <c r="F282" t="s">
+        <v>865</v>
+      </c>
+      <c r="G282">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="283" spans="1:500">
+      <c r="A283" t="s">
+        <v>866</v>
+      </c>
+      <c r="B283" t="s">
+        <v>867</v>
+      </c>
+      <c r="C283" t="s">
+        <v>868</v>
+      </c>
+      <c r="D283" t="s">
+        <v>869</v>
+      </c>
+      <c r="E283" t="s">
+        <v>870</v>
+      </c>
+      <c r="F283" t="s">
+        <v>871</v>
+      </c>
+      <c r="G283">
+        <v>2020</v>
+      </c>
+      <c r="H283">
+        <v>70</v>
+      </c>
+      <c r="I283">
+        <v>3</v>
+      </c>
+      <c r="J283" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="284" spans="1:500">
+      <c r="A284" t="s">
+        <v>873</v>
+      </c>
+      <c r="B284" t="s">
+        <v>874</v>
+      </c>
+      <c r="C284" t="s">
+        <v>875</v>
+      </c>
+      <c r="D284" t="s">
+        <v>876</v>
+      </c>
+      <c r="E284" t="s">
+        <v>877</v>
+      </c>
+      <c r="F284" t="s">
+        <v>853</v>
+      </c>
+      <c r="G284">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="285" spans="1:500">
+      <c r="A285" t="s">
+        <v>878</v>
+      </c>
+      <c r="B285" t="s">
+        <v>879</v>
+      </c>
+      <c r="C285" t="s">
+        <v>880</v>
+      </c>
+      <c r="D285" t="s">
+        <v>881</v>
+      </c>
+      <c r="E285" t="s">
+        <v>882</v>
+      </c>
+      <c r="F285" t="s">
+        <v>883</v>
+      </c>
+      <c r="G285">
+        <v>2021</v>
+      </c>
+      <c r="H285">
+        <v>7</v>
+      </c>
+      <c r="I285">
+        <v>3</v>
+      </c>
+      <c r="J285" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="286" spans="1:500">
+      <c r="A286" t="s">
+        <v>815</v>
+      </c>
+      <c r="B286" t="s">
+        <v>816</v>
+      </c>
+      <c r="C286" t="s">
+        <v>885</v>
+      </c>
+      <c r="D286" t="s">
+        <v>818</v>
+      </c>
+      <c r="E286" t="s">
+        <v>819</v>
+      </c>
+      <c r="F286" t="s">
+        <v>820</v>
+      </c>
+      <c r="G286">
+        <v>2023</v>
+      </c>
+      <c r="H286">
+        <v>35</v>
+      </c>
+      <c r="I286">
+        <v>2</v>
+      </c>
+      <c r="J286" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="287" spans="1:500">
+      <c r="A287" t="s">
+        <v>887</v>
+      </c>
+      <c r="B287" t="s">
+        <v>888</v>
+      </c>
+      <c r="C287" t="s">
+        <v>889</v>
+      </c>
+      <c r="D287" t="s">
+        <v>890</v>
+      </c>
+      <c r="E287" t="s">
+        <v>891</v>
+      </c>
+      <c r="F287" t="s">
+        <v>853</v>
+      </c>
+      <c r="G287">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="288" spans="1:500">
+      <c r="A288" t="s">
+        <v>892</v>
+      </c>
+      <c r="B288" t="s">
+        <v>893</v>
+      </c>
+      <c r="C288" t="s">
+        <v>894</v>
+      </c>
+      <c r="D288" t="s">
+        <v>827</v>
+      </c>
+      <c r="E288" t="s">
+        <v>828</v>
+      </c>
+      <c r="F288" t="s">
+        <v>691</v>
+      </c>
+      <c r="G288">
+        <v>2020</v>
+      </c>
+      <c r="H288">
+        <v>6</v>
+      </c>
+      <c r="I288">
+        <v>13</v>
+      </c>
+      <c r="J288" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="A289" t="s">
+        <v>896</v>
+      </c>
+      <c r="B289" t="s">
+        <v>897</v>
+      </c>
+      <c r="C289" t="s">
+        <v>898</v>
+      </c>
+      <c r="D289" t="s">
+        <v>899</v>
+      </c>
+      <c r="E289" t="s">
+        <v>900</v>
+      </c>
+      <c r="F289" t="s">
+        <v>901</v>
+      </c>
+      <c r="G289">
+        <v>2013</v>
+      </c>
+      <c r="H289">
+        <v>38</v>
+      </c>
+      <c r="I289">
+        <v>4</v>
+      </c>
+      <c r="J289" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="A290" t="s">
+        <v>903</v>
+      </c>
+      <c r="B290" t="s">
+        <v>904</v>
+      </c>
+      <c r="C290" t="s">
+        <v>905</v>
+      </c>
+      <c r="D290" t="s">
+        <v>906</v>
+      </c>
+      <c r="E290" t="s">
+        <v>907</v>
+      </c>
+      <c r="F290" t="s">
+        <v>908</v>
+      </c>
+      <c r="G290">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10">
+      <c r="A291" t="s">
+        <v>909</v>
+      </c>
+      <c r="B291" t="s">
+        <v>910</v>
+      </c>
+      <c r="C291" t="s">
+        <v>911</v>
+      </c>
+      <c r="D291" t="s">
+        <v>912</v>
+      </c>
+      <c r="E291" t="s">
+        <v>913</v>
+      </c>
+      <c r="F291" t="s">
+        <v>853</v>
+      </c>
+      <c r="G291">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10">
+      <c r="A292" t="s">
+        <v>914</v>
+      </c>
+      <c r="B292" t="s">
+        <v>915</v>
+      </c>
+      <c r="C292" t="s">
+        <v>916</v>
+      </c>
+      <c r="D292" t="s">
+        <v>917</v>
+      </c>
+      <c r="E292" t="s">
+        <v>918</v>
+      </c>
+      <c r="F292" t="s">
+        <v>691</v>
+      </c>
+      <c r="G292">
+        <v>2020</v>
+      </c>
+      <c r="H292">
+        <v>6</v>
+      </c>
+      <c r="I292">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10">
+      <c r="A293" t="s">
+        <v>919</v>
+      </c>
+      <c r="B293" t="s">
+        <v>920</v>
+      </c>
+      <c r="C293" t="s">
+        <v>921</v>
+      </c>
+      <c r="D293" t="s">
+        <v>922</v>
+      </c>
+      <c r="E293" t="s">
+        <v>923</v>
+      </c>
+      <c r="F293" t="s">
+        <v>691</v>
+      </c>
+      <c r="G293">
+        <v>2021</v>
+      </c>
+      <c r="H293">
+        <v>7</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10">
+      <c r="A294" t="s">
+        <v>925</v>
+      </c>
+      <c r="B294" t="s">
+        <v>926</v>
+      </c>
+      <c r="C294" t="s">
+        <v>927</v>
+      </c>
+      <c r="D294" t="s">
+        <v>928</v>
+      </c>
+      <c r="E294" t="s">
+        <v>929</v>
+      </c>
+      <c r="F294" t="s">
+        <v>853</v>
+      </c>
+      <c r="G294">
+        <v>2022</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
